--- a/Excel/MonsterPillConfig.xlsx
+++ b/Excel/MonsterPillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="76">
   <si>
     <t>ID</t>
   </si>
@@ -198,6 +198,66 @@
   </si>
   <si>
     <t>900000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>幻境十一层</t>
+  </si>
+  <si>
+    <t>100000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>50000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>9000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>幻境十二层</t>
+  </si>
+  <si>
+    <t>10000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>50000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>90000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>幻境十三层</t>
+  </si>
+  <si>
+    <t>1000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>50000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>900000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>幻境十四层</t>
+  </si>
+  <si>
+    <t>100000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>50000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>9000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>幻境十五层</t>
+  </si>
+  <si>
+    <t>10000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>50000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>90000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
   </si>
 </sst>
 </file>
@@ -1174,13 +1234,13 @@
   <dimension ref="A1:N36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8" style="2" customWidth="1"/>
+    <col min="1" max="1" width="4.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.875" style="2" customWidth="1"/>
     <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="35" style="3" customWidth="1"/>
-    <col min="8" max="8" width="53.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="35.125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="48.375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="63.25" style="3" customWidth="1"/>
     <col min="9" max="9" width="12.625" style="2" customWidth="1"/>
     <col min="10" max="12" width="12.5" style="2" customWidth="1"/>
     <col min="13" max="13" width="14.125" style="2" customWidth="1"/>
@@ -1392,19 +1452,19 @@
         <v>23</v>
       </c>
       <c r="I7" s="8">
-        <f t="shared" ref="I7:I15" si="0">I6+200</f>
+        <f t="shared" ref="I7:I17" si="0">I6+200</f>
         <v>700</v>
       </c>
       <c r="J7" s="8">
-        <f t="shared" ref="J7:J15" si="1">J6+200</f>
+        <f t="shared" ref="J7:J17" si="1">J6+200</f>
         <v>700</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" ref="K7:K15" si="2">K6+200</f>
+        <f t="shared" ref="K7:K20" si="2">K6+200</f>
         <v>1700</v>
       </c>
       <c r="L7" s="8">
-        <f t="shared" ref="L7:L15" si="3">L6+2</f>
+        <f t="shared" ref="L7:L20" si="3">L6+2</f>
         <v>22</v>
       </c>
       <c r="M7" s="8">
@@ -1666,7 +1726,7 @@
         <v>34</v>
       </c>
       <c r="M13" s="8">
-        <f>M12+10</f>
+        <f t="shared" ref="M13:M17" si="5">M12+10</f>
         <v>70</v>
       </c>
       <c r="N13" s="8">
@@ -1709,7 +1769,7 @@
         <v>36</v>
       </c>
       <c r="M14" s="8">
-        <f>M13+10</f>
+        <f t="shared" si="5"/>
         <v>80</v>
       </c>
       <c r="N14" s="8">
@@ -1752,21 +1812,227 @@
         <v>38</v>
       </c>
       <c r="M15" s="8">
-        <f>M14+10</f>
+        <f t="shared" si="5"/>
         <v>90</v>
       </c>
       <c r="N15" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="6:6">
-      <c r="F16" s="7"/>
-    </row>
-    <row r="18" customHeight="1" spans="6:6">
-      <c r="F18" s="7"/>
-    </row>
-    <row r="20" customHeight="1" spans="6:6">
-      <c r="F20" s="7"/>
+    <row r="16" customHeight="1" spans="3:14">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" ref="I16:I20" si="6">I15+400</f>
+        <v>2700</v>
+      </c>
+      <c r="J16" s="8">
+        <f t="shared" ref="J16:J20" si="7">J15+400</f>
+        <v>2700</v>
+      </c>
+      <c r="K16" s="8">
+        <f t="shared" si="2"/>
+        <v>3500</v>
+      </c>
+      <c r="L16" s="8">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="M16" s="8">
+        <f t="shared" ref="M16:M20" si="8">M15+15</f>
+        <v>105</v>
+      </c>
+      <c r="N16" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:14">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I17" s="8">
+        <f t="shared" si="6"/>
+        <v>3100</v>
+      </c>
+      <c r="J17" s="8">
+        <f t="shared" si="7"/>
+        <v>3100</v>
+      </c>
+      <c r="K17" s="8">
+        <f t="shared" si="2"/>
+        <v>3700</v>
+      </c>
+      <c r="L17" s="8">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="M17" s="8">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:14">
+      <c r="C18" s="1">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="6"/>
+        <v>3500</v>
+      </c>
+      <c r="J18" s="8">
+        <f t="shared" si="7"/>
+        <v>3500</v>
+      </c>
+      <c r="K18" s="8">
+        <f t="shared" si="2"/>
+        <v>3900</v>
+      </c>
+      <c r="L18" s="8">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="M18" s="8">
+        <f t="shared" si="8"/>
+        <v>135</v>
+      </c>
+      <c r="N18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:14">
+      <c r="C19" s="1">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19" s="8">
+        <f t="shared" si="6"/>
+        <v>3900</v>
+      </c>
+      <c r="J19" s="8">
+        <f t="shared" si="7"/>
+        <v>3900</v>
+      </c>
+      <c r="K19" s="8">
+        <f t="shared" si="2"/>
+        <v>4100</v>
+      </c>
+      <c r="L19" s="8">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="M19" s="8">
+        <f t="shared" si="8"/>
+        <v>150</v>
+      </c>
+      <c r="N19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:14">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" s="8">
+        <f t="shared" si="6"/>
+        <v>4300</v>
+      </c>
+      <c r="J20" s="8">
+        <f t="shared" si="7"/>
+        <v>4300</v>
+      </c>
+      <c r="K20" s="8">
+        <f t="shared" si="2"/>
+        <v>4300</v>
+      </c>
+      <c r="L20" s="8">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="M20" s="8">
+        <f t="shared" si="8"/>
+        <v>165</v>
+      </c>
+      <c r="N20" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" customHeight="1" spans="6:6">
       <c r="F21" s="7"/>
@@ -1774,16 +2040,26 @@
     <row r="23" customHeight="1" spans="6:6">
       <c r="F23" s="7"/>
     </row>
-    <row r="24" customHeight="1" spans="6:6">
+    <row r="24" customHeight="1" spans="6:7">
       <c r="F24" s="7"/>
-    </row>
-    <row r="27" customHeight="1" spans="7:7">
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" customHeight="1" spans="7:7">
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" customHeight="1" spans="6:6">
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" customHeight="1" spans="6:7">
+      <c r="F27" s="7"/>
       <c r="G27" s="7"/>
     </row>
-    <row r="28" customHeight="1" spans="7:7">
+    <row r="28" customHeight="1" spans="6:7">
+      <c r="F28" s="7"/>
       <c r="G28" s="7"/>
     </row>
-    <row r="29" customHeight="1" spans="7:7">
+    <row r="29" customHeight="1" spans="6:7">
+      <c r="F29" s="7"/>
       <c r="G29" s="7"/>
     </row>
     <row r="30" customHeight="1" spans="7:7">
@@ -1809,7 +2085,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:H3 L3:M3 C3:C5 N3:N5 D4:H5 I3:K5 L4:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:N5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterPillConfig.xlsx
+++ b/Excel/MonsterPillConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="95">
   <si>
     <t>ID</t>
   </si>
@@ -251,13 +251,70 @@
     <t>幻境十五层</t>
   </si>
   <si>
-    <t>10000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>50000000000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>90000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+    <t>1000正</t>
+  </si>
+  <si>
+    <t>500河</t>
+  </si>
+  <si>
+    <t>9000那</t>
+  </si>
+  <si>
+    <t>幻境十六层</t>
+  </si>
+  <si>
+    <t>9999载</t>
+  </si>
+  <si>
+    <t>9999沙</t>
+  </si>
+  <si>
+    <t>9999由</t>
+  </si>
+  <si>
+    <t>幻境十七层</t>
+  </si>
+  <si>
+    <t>9999极</t>
+  </si>
+  <si>
+    <t>9999阿</t>
+  </si>
+  <si>
+    <t>9999他</t>
+  </si>
+  <si>
+    <t>幻境十八层</t>
+  </si>
+  <si>
+    <t>9999恒</t>
+  </si>
+  <si>
+    <t>9999僧</t>
+  </si>
+  <si>
+    <t>9999不</t>
+  </si>
+  <si>
+    <t>幻境十九层</t>
+  </si>
+  <si>
+    <t>9999河</t>
+  </si>
+  <si>
+    <t>9999祇</t>
+  </si>
+  <si>
+    <t>9999可</t>
+  </si>
+  <si>
+    <t>幻境二十层</t>
+  </si>
+  <si>
+    <t>9999那</t>
+  </si>
+  <si>
+    <t>9999思</t>
   </si>
 </sst>
 </file>
@@ -1238,9 +1295,9 @@
     <col min="2" max="2" width="4.875" style="2" customWidth="1"/>
     <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="35.125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="48.375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="63.25" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20.125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21.625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="23.125" style="3" customWidth="1"/>
     <col min="9" max="9" width="12.625" style="2" customWidth="1"/>
     <col min="10" max="12" width="12.5" style="2" customWidth="1"/>
     <col min="13" max="13" width="14.125" style="2" customWidth="1"/>
@@ -1460,11 +1517,11 @@
         <v>700</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" ref="K7:K20" si="2">K6+200</f>
+        <f t="shared" ref="K7:K25" si="2">K6+200</f>
         <v>1700</v>
       </c>
       <c r="L7" s="8">
-        <f t="shared" ref="L7:L20" si="3">L6+2</f>
+        <f t="shared" ref="L7:L25" si="3">L6+2</f>
         <v>22</v>
       </c>
       <c r="M7" s="8">
@@ -1839,11 +1896,11 @@
         <v>59</v>
       </c>
       <c r="I16" s="8">
-        <f t="shared" ref="I16:I20" si="6">I15+400</f>
+        <f t="shared" ref="I16:I25" si="6">I15+400</f>
         <v>2700</v>
       </c>
       <c r="J16" s="8">
-        <f t="shared" ref="J16:J20" si="7">J15+400</f>
+        <f t="shared" ref="J16:J25" si="7">J15+400</f>
         <v>2700</v>
       </c>
       <c r="K16" s="8">
@@ -1855,7 +1912,7 @@
         <v>40</v>
       </c>
       <c r="M16" s="8">
-        <f t="shared" ref="M16:M20" si="8">M15+15</f>
+        <f t="shared" ref="M16:M25" si="8">M15+15</f>
         <v>105</v>
       </c>
       <c r="N16" s="8">
@@ -2001,13 +2058,13 @@
       <c r="E20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="7" t="s">
         <v>75</v>
       </c>
       <c r="I20" s="8">
@@ -2034,21 +2091,224 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="6:6">
-      <c r="F21" s="7"/>
-    </row>
-    <row r="23" customHeight="1" spans="6:6">
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" customHeight="1" spans="6:7">
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" customHeight="1" spans="7:7">
-      <c r="G25" s="7"/>
-    </row>
-    <row r="26" customHeight="1" spans="6:6">
+    <row r="21" customHeight="1" spans="3:14">
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" ref="I21:I25" si="9">I20+800</f>
+        <v>5100</v>
+      </c>
+      <c r="J21" s="8">
+        <f t="shared" ref="J21:J25" si="10">J20+800</f>
+        <v>5100</v>
+      </c>
+      <c r="K21" s="8">
+        <f t="shared" ref="K21:K26" si="11">K20+400</f>
+        <v>4700</v>
+      </c>
+      <c r="L21" s="8">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="M21" s="8">
+        <f t="shared" ref="M21:M25" si="12">M20+30</f>
+        <v>195</v>
+      </c>
+      <c r="N21" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:14">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="9"/>
+        <v>5900</v>
+      </c>
+      <c r="J22" s="8">
+        <f t="shared" si="10"/>
+        <v>5900</v>
+      </c>
+      <c r="K22" s="8">
+        <f t="shared" si="11"/>
+        <v>5100</v>
+      </c>
+      <c r="L22" s="8">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="M22" s="8">
+        <f t="shared" si="12"/>
+        <v>225</v>
+      </c>
+      <c r="N22" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:14">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="9"/>
+        <v>6700</v>
+      </c>
+      <c r="J23" s="8">
+        <f t="shared" si="10"/>
+        <v>6700</v>
+      </c>
+      <c r="K23" s="8">
+        <f t="shared" si="11"/>
+        <v>5500</v>
+      </c>
+      <c r="L23" s="8">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="M23" s="8">
+        <f t="shared" si="12"/>
+        <v>255</v>
+      </c>
+      <c r="N23" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:14">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="I24" s="8">
+        <f t="shared" si="9"/>
+        <v>7500</v>
+      </c>
+      <c r="J24" s="8">
+        <f t="shared" si="10"/>
+        <v>7500</v>
+      </c>
+      <c r="K24" s="8">
+        <f t="shared" si="11"/>
+        <v>5900</v>
+      </c>
+      <c r="L24" s="8">
+        <f t="shared" si="3"/>
+        <v>56</v>
+      </c>
+      <c r="M24" s="8">
+        <f t="shared" si="12"/>
+        <v>285</v>
+      </c>
+      <c r="N24" s="8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:14">
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="I25" s="8">
+        <f t="shared" si="9"/>
+        <v>8300</v>
+      </c>
+      <c r="J25" s="8">
+        <f t="shared" si="10"/>
+        <v>8300</v>
+      </c>
+      <c r="K25" s="8">
+        <f t="shared" si="11"/>
+        <v>6300</v>
+      </c>
+      <c r="L25" s="8">
+        <f t="shared" si="3"/>
+        <v>58</v>
+      </c>
+      <c r="M25" s="8">
+        <f t="shared" si="12"/>
+        <v>315</v>
+      </c>
+      <c r="N25" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="6:11">
       <c r="F26" s="7"/>
+      <c r="K26" s="8"/>
     </row>
     <row r="27" customHeight="1" spans="6:7">
       <c r="F27" s="7"/>
@@ -2071,11 +2331,13 @@
     <row r="32" customHeight="1" spans="7:7">
       <c r="G32" s="7"/>
     </row>
-    <row r="33" customHeight="1" spans="7:7">
+    <row r="33" customHeight="1" spans="7:8">
       <c r="G33" s="7"/>
-    </row>
-    <row r="34" customHeight="1" spans="7:7">
+      <c r="H33" s="7"/>
+    </row>
+    <row r="34" customHeight="1" spans="7:8">
       <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
     </row>
     <row r="35" customHeight="1" spans="7:7">
       <c r="G35" s="7"/>

--- a/Excel/MonsterPillConfig.xlsx
+++ b/Excel/MonsterPillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,11 +30,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="116">
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Layer</t>
+  </si>
+  <si>
     <t>MapName</t>
   </si>
   <si>
@@ -59,6 +65,9 @@
     <t>CritRateResist</t>
   </si>
   <si>
+    <t>CritDamage</t>
+  </si>
+  <si>
     <t>ResotrePercent</t>
   </si>
   <si>
@@ -68,6 +77,15 @@
     <t>Protect</t>
   </si>
   <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>Strong</t>
+  </si>
+  <si>
+    <t>DamageMul</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -77,7 +95,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>幻境一层</t>
+    <t>double</t>
+  </si>
+  <si>
+    <t>炼体秘境一层</t>
   </si>
   <si>
     <t>幻境魔物</t>
@@ -92,7 +113,7 @@
     <t>900000000000000000000000</t>
   </si>
   <si>
-    <t>幻境二层</t>
+    <t>炼体秘境二层</t>
   </si>
   <si>
     <t>100000000000000000</t>
@@ -104,7 +125,7 @@
     <t>9000000000000000000000000000</t>
   </si>
   <si>
-    <t>幻境三层</t>
+    <t>炼体秘境三层</t>
   </si>
   <si>
     <t>10000000000000000000</t>
@@ -116,7 +137,7 @@
     <t>90000000000000000000000000000000</t>
   </si>
   <si>
-    <t>幻境四层</t>
+    <t>炼体秘境四层</t>
   </si>
   <si>
     <t>1000000000000000000000</t>
@@ -128,7 +149,7 @@
     <t>900000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>幻境五层</t>
+    <t>炼体秘境五层</t>
   </si>
   <si>
     <t>100000000000000000000000</t>
@@ -140,7 +161,7 @@
     <t>9000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>幻境六层</t>
+    <t>炼体秘境六层</t>
   </si>
   <si>
     <t>10000000000000000000000000</t>
@@ -152,7 +173,7 @@
     <t>90000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>幻境七层</t>
+    <t>炼体秘境七层</t>
   </si>
   <si>
     <t>1000000000000000000000000000</t>
@@ -164,7 +185,7 @@
     <t>900000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>幻境八层</t>
+    <t>炼体秘境八层</t>
   </si>
   <si>
     <t>100000000000000000000000000000</t>
@@ -176,7 +197,7 @@
     <t>9000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>幻境九层</t>
+    <t>炼体秘境九层</t>
   </si>
   <si>
     <t>10000000000000000000000000000000</t>
@@ -188,7 +209,7 @@
     <t>90000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>幻境十层</t>
+    <t>炼体秘境十层</t>
   </si>
   <si>
     <t>1000000000000000000000000000000000</t>
@@ -200,7 +221,7 @@
     <t>900000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>幻境十一层</t>
+    <t>炼体秘境十一层</t>
   </si>
   <si>
     <t>100000000000000000000000000000000000</t>
@@ -212,7 +233,7 @@
     <t>9000000000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>幻境十二层</t>
+    <t>炼体秘境十二层</t>
   </si>
   <si>
     <t>10000000000000000000000000000000000000</t>
@@ -224,7 +245,7 @@
     <t>90000000000000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>幻境十三层</t>
+    <t>炼体秘境十三层</t>
   </si>
   <si>
     <t>1000000000000000000000000000000000000000</t>
@@ -236,7 +257,7 @@
     <t>900000000000000000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>幻境十四层</t>
+    <t>炼体秘境十四层</t>
   </si>
   <si>
     <t>100000000000000000000000000000000000000000</t>
@@ -248,7 +269,7 @@
     <t>9000000000000000000000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>幻境十五层</t>
+    <t>炼体秘境十五层</t>
   </si>
   <si>
     <t>1000正</t>
@@ -260,7 +281,7 @@
     <t>9000那</t>
   </si>
   <si>
-    <t>幻境十六层</t>
+    <t>炼体秘境十六层</t>
   </si>
   <si>
     <t>9999载</t>
@@ -272,7 +293,7 @@
     <t>9999由</t>
   </si>
   <si>
-    <t>幻境十七层</t>
+    <t>炼体秘境十七层</t>
   </si>
   <si>
     <t>9999极</t>
@@ -284,7 +305,7 @@
     <t>9999他</t>
   </si>
   <si>
-    <t>幻境十八层</t>
+    <t>炼体秘境十八层</t>
   </si>
   <si>
     <t>9999恒</t>
@@ -296,7 +317,7 @@
     <t>9999不</t>
   </si>
   <si>
-    <t>幻境十九层</t>
+    <t>炼体秘境十九层</t>
   </si>
   <si>
     <t>9999河</t>
@@ -308,13 +329,55 @@
     <t>9999可</t>
   </si>
   <si>
-    <t>幻境二十层</t>
+    <t>炼体秘境二十层</t>
   </si>
   <si>
     <t>9999那</t>
   </si>
   <si>
     <t>9999思</t>
+  </si>
+  <si>
+    <t>练气秘境一层</t>
+  </si>
+  <si>
+    <t>炼气魔物</t>
+  </si>
+  <si>
+    <t>9E+47</t>
+  </si>
+  <si>
+    <t>9E+57</t>
+  </si>
+  <si>
+    <t>9E+77</t>
+  </si>
+  <si>
+    <t>练气秘境二层</t>
+  </si>
+  <si>
+    <t>练气秘境三层</t>
+  </si>
+  <si>
+    <t>练气秘境四层</t>
+  </si>
+  <si>
+    <t>练气秘境五层</t>
+  </si>
+  <si>
+    <t>练气秘境六层</t>
+  </si>
+  <si>
+    <t>练气秘境七层</t>
+  </si>
+  <si>
+    <t>练气秘境八层</t>
+  </si>
+  <si>
+    <t>练气秘境九层</t>
+  </si>
+  <si>
+    <t>练气秘境十层</t>
   </si>
 </sst>
 </file>
@@ -328,7 +391,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,6 +409,11 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -494,7 +562,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -504,6 +572,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -818,55 +892,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -881,80 +952,86 @@
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -966,6 +1043,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1288,59 +1369,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:T45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.875" style="2" customWidth="1"/>
-    <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="21.625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="23.125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="12.625" style="2" customWidth="1"/>
-    <col min="10" max="12" width="12.5" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="9.625" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="4.12389380530973" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.87610619469027" style="2" customWidth="1"/>
+    <col min="3" max="5" width="9.87610619469027" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.4778761061947" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.2477876106195" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.1238938053097" style="3" customWidth="1"/>
+    <col min="9" max="9" width="21.6283185840708" style="3" customWidth="1"/>
+    <col min="10" max="10" width="20.3805309734513" style="3" customWidth="1"/>
+    <col min="11" max="11" width="12.6283185840708" style="2" customWidth="1"/>
+    <col min="12" max="13" width="12.5044247787611" style="2" customWidth="1"/>
+    <col min="14" max="14" width="8" style="2" customWidth="1"/>
+    <col min="15" max="15" width="12.5044247787611" style="2" customWidth="1"/>
+    <col min="16" max="16" width="14.1238938053097" style="2" customWidth="1"/>
+    <col min="17" max="19" width="9.6283185840708" style="2" customWidth="1"/>
+    <col min="20" max="20" width="13.6637168141593" style="4" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:20">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:20">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:20">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="6" t="s">
@@ -1349,38 +1442,56 @@
       <c r="G3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="O3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:20">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="6" t="s">
@@ -1389,965 +1500,1981 @@
       <c r="G4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="O4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:20">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>14</v>
+      <c r="C5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:14">
+        <v>20</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="T5" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:20">
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="8">
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="9">
         <v>500</v>
       </c>
-      <c r="J6" s="8">
+      <c r="L6" s="9">
         <v>500</v>
       </c>
-      <c r="K6" s="8">
+      <c r="M6" s="9">
         <v>1500</v>
       </c>
-      <c r="L6" s="8">
+      <c r="N6" s="9">
+        <v>0</v>
+      </c>
+      <c r="O6" s="9">
         <v>20</v>
       </c>
-      <c r="M6" s="8">
+      <c r="P6" s="9">
         <v>30</v>
       </c>
-      <c r="N6" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:14">
+      <c r="Q6" s="9">
+        <v>0</v>
+      </c>
+      <c r="R6" s="9">
+        <v>0</v>
+      </c>
+      <c r="S6" s="9">
+        <v>0</v>
+      </c>
+      <c r="T6" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:20">
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="9" t="s">
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="9">
+        <f t="shared" ref="K7:K17" si="0">K6+200</f>
+        <v>700</v>
+      </c>
+      <c r="L7" s="9">
+        <f t="shared" ref="L7:L17" si="1">L6+200</f>
+        <v>700</v>
+      </c>
+      <c r="M7" s="9">
+        <f t="shared" ref="M7:M25" si="2">M6+200</f>
+        <v>1700</v>
+      </c>
+      <c r="N7" s="9">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9">
+        <f t="shared" ref="O7:O25" si="3">O6+2</f>
         <v>22</v>
       </c>
-      <c r="H7" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="8">
-        <f t="shared" ref="I7:I17" si="0">I6+200</f>
-        <v>700</v>
-      </c>
-      <c r="J7" s="8">
-        <f t="shared" ref="J7:J17" si="1">J6+200</f>
-        <v>700</v>
-      </c>
-      <c r="K7" s="8">
-        <f t="shared" ref="K7:K25" si="2">K6+200</f>
-        <v>1700</v>
-      </c>
-      <c r="L7" s="8">
-        <f t="shared" ref="L7:L25" si="3">L6+2</f>
-        <v>22</v>
-      </c>
-      <c r="M7" s="8">
-        <f t="shared" ref="M7:M12" si="4">M6+5</f>
+      <c r="P7" s="9">
+        <f t="shared" ref="P7:P12" si="4">P6+5</f>
         <v>35</v>
       </c>
-      <c r="N7" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:14">
+      <c r="Q7" s="9">
+        <v>0</v>
+      </c>
+      <c r="R7" s="9">
+        <v>0</v>
+      </c>
+      <c r="S7" s="9">
+        <v>0</v>
+      </c>
+      <c r="T7" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:20">
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="8">
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="9">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="J8" s="8">
+      <c r="L8" s="9">
         <f t="shared" si="1"/>
         <v>900</v>
       </c>
-      <c r="K8" s="8">
+      <c r="M8" s="9">
         <f t="shared" si="2"/>
         <v>1900</v>
       </c>
-      <c r="L8" s="8">
+      <c r="N8" s="9">
+        <v>0</v>
+      </c>
+      <c r="O8" s="9">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="M8" s="8">
+      <c r="P8" s="9">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="N8" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:14">
+      <c r="Q8" s="9">
+        <v>0</v>
+      </c>
+      <c r="R8" s="9">
+        <v>0</v>
+      </c>
+      <c r="S8" s="9">
+        <v>0</v>
+      </c>
+      <c r="T8" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:20">
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="8">
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>4</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" s="9">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="J9" s="8">
+      <c r="L9" s="9">
         <f t="shared" si="1"/>
         <v>1100</v>
       </c>
-      <c r="K9" s="8">
+      <c r="M9" s="9">
         <f t="shared" si="2"/>
         <v>2100</v>
       </c>
-      <c r="L9" s="8">
+      <c r="N9" s="9">
+        <v>0</v>
+      </c>
+      <c r="O9" s="9">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="M9" s="8">
+      <c r="P9" s="9">
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="N9" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:14">
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="9">
+        <v>0</v>
+      </c>
+      <c r="S9" s="9">
+        <v>0</v>
+      </c>
+      <c r="T9" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:20">
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" s="8">
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="9">
         <f t="shared" si="0"/>
         <v>1300</v>
       </c>
-      <c r="J10" s="8">
+      <c r="L10" s="9">
         <f t="shared" si="1"/>
         <v>1300</v>
       </c>
-      <c r="K10" s="8">
+      <c r="M10" s="9">
         <f t="shared" si="2"/>
         <v>2300</v>
       </c>
-      <c r="L10" s="8">
+      <c r="N10" s="9">
+        <v>0</v>
+      </c>
+      <c r="O10" s="9">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="M10" s="8">
+      <c r="P10" s="9">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="N10" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:14">
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+      <c r="R10" s="9">
+        <v>0</v>
+      </c>
+      <c r="S10" s="9">
+        <v>0</v>
+      </c>
+      <c r="T10" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:20">
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" s="8">
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>6</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K11" s="9">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="J11" s="8">
+      <c r="L11" s="9">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="K11" s="8">
+      <c r="M11" s="9">
         <f t="shared" si="2"/>
         <v>2500</v>
       </c>
-      <c r="L11" s="8">
+      <c r="N11" s="9">
+        <v>0</v>
+      </c>
+      <c r="O11" s="9">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="M11" s="8">
+      <c r="P11" s="9">
         <f t="shared" si="4"/>
         <v>55</v>
       </c>
-      <c r="N11" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:14">
+      <c r="Q11" s="9">
+        <v>0</v>
+      </c>
+      <c r="R11" s="9">
+        <v>0</v>
+      </c>
+      <c r="S11" s="9">
+        <v>0</v>
+      </c>
+      <c r="T11" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:20">
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="8">
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>7</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" s="9">
         <f t="shared" si="0"/>
         <v>1700</v>
       </c>
-      <c r="J12" s="8">
+      <c r="L12" s="9">
         <f t="shared" si="1"/>
         <v>1700</v>
       </c>
-      <c r="K12" s="8">
+      <c r="M12" s="9">
         <f t="shared" si="2"/>
         <v>2700</v>
       </c>
-      <c r="L12" s="8">
+      <c r="N12" s="9">
+        <v>0</v>
+      </c>
+      <c r="O12" s="9">
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
-      <c r="M12" s="8">
+      <c r="P12" s="9">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="N12" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:14">
+      <c r="Q12" s="9">
+        <v>0</v>
+      </c>
+      <c r="R12" s="9">
+        <v>0</v>
+      </c>
+      <c r="S12" s="9">
+        <v>0</v>
+      </c>
+      <c r="T12" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:20">
       <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I13" s="8">
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="K13" s="9">
         <f t="shared" si="0"/>
         <v>1900</v>
       </c>
-      <c r="J13" s="8">
+      <c r="L13" s="9">
         <f t="shared" si="1"/>
         <v>1900</v>
       </c>
-      <c r="K13" s="8">
+      <c r="M13" s="9">
         <f t="shared" si="2"/>
         <v>2900</v>
       </c>
-      <c r="L13" s="8">
+      <c r="N13" s="9">
+        <v>0</v>
+      </c>
+      <c r="O13" s="9">
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="M13" s="8">
-        <f t="shared" ref="M13:M17" si="5">M12+10</f>
+      <c r="P13" s="9">
+        <f t="shared" ref="P13:P17" si="5">P12+10</f>
         <v>70</v>
       </c>
-      <c r="N13" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:14">
+      <c r="Q13" s="9">
+        <v>0</v>
+      </c>
+      <c r="R13" s="9">
+        <v>0</v>
+      </c>
+      <c r="S13" s="9">
+        <v>0</v>
+      </c>
+      <c r="T13" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:20">
       <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I14" s="8">
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>9</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="K14" s="9">
         <f t="shared" si="0"/>
         <v>2100</v>
       </c>
-      <c r="J14" s="8">
+      <c r="L14" s="9">
         <f t="shared" si="1"/>
         <v>2100</v>
       </c>
-      <c r="K14" s="8">
+      <c r="M14" s="9">
         <f t="shared" si="2"/>
         <v>3100</v>
       </c>
-      <c r="L14" s="8">
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+      <c r="O14" s="9">
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="M14" s="8">
+      <c r="P14" s="9">
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
-      <c r="N14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:14">
+      <c r="Q14" s="9">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9">
+        <v>0</v>
+      </c>
+      <c r="S14" s="9">
+        <v>0</v>
+      </c>
+      <c r="T14" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:20">
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I15" s="8">
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="K15" s="9">
         <f t="shared" si="0"/>
         <v>2300</v>
       </c>
-      <c r="J15" s="8">
+      <c r="L15" s="9">
         <f t="shared" si="1"/>
         <v>2300</v>
       </c>
-      <c r="K15" s="8">
+      <c r="M15" s="9">
         <f t="shared" si="2"/>
         <v>3300</v>
       </c>
-      <c r="L15" s="8">
+      <c r="N15" s="9">
+        <v>0</v>
+      </c>
+      <c r="O15" s="9">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="M15" s="8">
+      <c r="P15" s="9">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="N15" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:14">
+      <c r="Q15" s="9">
+        <v>0</v>
+      </c>
+      <c r="R15" s="9">
+        <v>0</v>
+      </c>
+      <c r="S15" s="9">
+        <v>0</v>
+      </c>
+      <c r="T15" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:20">
       <c r="C16" s="1">
         <v>11</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="I16" s="8">
-        <f t="shared" ref="I16:I25" si="6">I15+400</f>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>11</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K16" s="9">
+        <f t="shared" ref="K16:K25" si="6">K15+400</f>
         <v>2700</v>
       </c>
-      <c r="J16" s="8">
-        <f t="shared" ref="J16:J25" si="7">J15+400</f>
+      <c r="L16" s="9">
+        <f t="shared" ref="L16:L25" si="7">L15+400</f>
         <v>2700</v>
       </c>
-      <c r="K16" s="8">
+      <c r="M16" s="9">
         <f t="shared" si="2"/>
         <v>3500</v>
       </c>
-      <c r="L16" s="8">
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+      <c r="O16" s="9">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="M16" s="8">
-        <f t="shared" ref="M16:M25" si="8">M15+15</f>
+      <c r="P16" s="9">
+        <f t="shared" ref="P16:P25" si="8">P15+15</f>
         <v>105</v>
       </c>
-      <c r="N16" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:14">
+      <c r="Q16" s="9">
+        <v>0</v>
+      </c>
+      <c r="R16" s="9">
+        <v>0</v>
+      </c>
+      <c r="S16" s="9">
+        <v>0</v>
+      </c>
+      <c r="T16" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:20">
       <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="I17" s="8">
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>12</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="K17" s="9">
         <f t="shared" si="6"/>
         <v>3100</v>
       </c>
-      <c r="J17" s="8">
+      <c r="L17" s="9">
         <f t="shared" si="7"/>
         <v>3100</v>
       </c>
-      <c r="K17" s="8">
+      <c r="M17" s="9">
         <f t="shared" si="2"/>
         <v>3700</v>
       </c>
-      <c r="L17" s="8">
+      <c r="N17" s="9">
+        <v>0</v>
+      </c>
+      <c r="O17" s="9">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="M17" s="8">
+      <c r="P17" s="9">
         <f t="shared" si="8"/>
         <v>120</v>
       </c>
-      <c r="N17" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:14">
+      <c r="Q17" s="9">
+        <v>0</v>
+      </c>
+      <c r="R17" s="9">
+        <v>0</v>
+      </c>
+      <c r="S17" s="9">
+        <v>0</v>
+      </c>
+      <c r="T17" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:20">
       <c r="C18" s="1">
         <v>13</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I18" s="8">
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>13</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K18" s="9">
         <f t="shared" si="6"/>
         <v>3500</v>
       </c>
-      <c r="J18" s="8">
+      <c r="L18" s="9">
         <f t="shared" si="7"/>
         <v>3500</v>
       </c>
-      <c r="K18" s="8">
+      <c r="M18" s="9">
         <f t="shared" si="2"/>
         <v>3900</v>
       </c>
-      <c r="L18" s="8">
+      <c r="N18" s="9">
+        <v>0</v>
+      </c>
+      <c r="O18" s="9">
         <f t="shared" si="3"/>
         <v>44</v>
       </c>
-      <c r="M18" s="8">
+      <c r="P18" s="9">
         <f t="shared" si="8"/>
         <v>135</v>
       </c>
-      <c r="N18" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:14">
+      <c r="Q18" s="9">
+        <v>0</v>
+      </c>
+      <c r="R18" s="9">
+        <v>0</v>
+      </c>
+      <c r="S18" s="9">
+        <v>0</v>
+      </c>
+      <c r="T18" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:20">
       <c r="C19" s="1">
         <v>14</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I19" s="8">
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>14</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K19" s="9">
         <f t="shared" si="6"/>
         <v>3900</v>
       </c>
-      <c r="J19" s="8">
+      <c r="L19" s="9">
         <f t="shared" si="7"/>
         <v>3900</v>
       </c>
-      <c r="K19" s="8">
+      <c r="M19" s="9">
         <f t="shared" si="2"/>
         <v>4100</v>
       </c>
-      <c r="L19" s="8">
+      <c r="N19" s="9">
+        <v>0</v>
+      </c>
+      <c r="O19" s="9">
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
-      <c r="M19" s="8">
+      <c r="P19" s="9">
         <f t="shared" si="8"/>
         <v>150</v>
       </c>
-      <c r="N19" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:14">
+      <c r="Q19" s="9">
+        <v>0</v>
+      </c>
+      <c r="R19" s="9">
+        <v>0</v>
+      </c>
+      <c r="S19" s="9">
+        <v>0</v>
+      </c>
+      <c r="T19" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:20">
       <c r="C20" s="1">
         <v>15</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I20" s="8">
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>15</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="K20" s="9">
         <f t="shared" si="6"/>
         <v>4300</v>
       </c>
-      <c r="J20" s="8">
+      <c r="L20" s="9">
         <f t="shared" si="7"/>
         <v>4300</v>
       </c>
-      <c r="K20" s="8">
+      <c r="M20" s="9">
         <f t="shared" si="2"/>
         <v>4300</v>
       </c>
-      <c r="L20" s="8">
+      <c r="N20" s="9">
+        <v>0</v>
+      </c>
+      <c r="O20" s="9">
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="M20" s="8">
+      <c r="P20" s="9">
         <f t="shared" si="8"/>
         <v>165</v>
       </c>
-      <c r="N20" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:14">
+      <c r="Q20" s="9">
+        <v>0</v>
+      </c>
+      <c r="R20" s="9">
+        <v>0</v>
+      </c>
+      <c r="S20" s="9">
+        <v>0</v>
+      </c>
+      <c r="T20" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:20">
       <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
         <v>16</v>
       </c>
-      <c r="F21" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I21" s="8">
-        <f t="shared" ref="I21:I25" si="9">I20+800</f>
+      <c r="F21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="K21" s="9">
+        <f t="shared" ref="K21:K25" si="9">K20+800</f>
         <v>5100</v>
       </c>
-      <c r="J21" s="8">
-        <f t="shared" ref="J21:J25" si="10">J20+800</f>
+      <c r="L21" s="9">
+        <f t="shared" ref="L21:L25" si="10">L20+800</f>
         <v>5100</v>
       </c>
-      <c r="K21" s="8">
-        <f t="shared" ref="K21:K26" si="11">K20+400</f>
+      <c r="M21" s="9">
+        <f t="shared" ref="M21:M26" si="11">M20+400</f>
         <v>4700</v>
       </c>
-      <c r="L21" s="8">
+      <c r="N21" s="9">
+        <v>0</v>
+      </c>
+      <c r="O21" s="9">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="M21" s="8">
-        <f t="shared" ref="M21:M25" si="12">M20+30</f>
+      <c r="P21" s="9">
+        <f t="shared" ref="P21:P25" si="12">P20+30</f>
         <v>195</v>
       </c>
-      <c r="N21" s="8">
+      <c r="Q21" s="9">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:14">
+      <c r="R21" s="9">
+        <v>0</v>
+      </c>
+      <c r="S21" s="9">
+        <v>0</v>
+      </c>
+      <c r="T21" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:20">
       <c r="C22" s="1">
         <v>17</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I22" s="8">
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>17</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="K22" s="9">
         <f t="shared" si="9"/>
         <v>5900</v>
       </c>
-      <c r="J22" s="8">
+      <c r="L22" s="9">
         <f t="shared" si="10"/>
         <v>5900</v>
       </c>
-      <c r="K22" s="8">
+      <c r="M22" s="9">
         <f t="shared" si="11"/>
         <v>5100</v>
       </c>
-      <c r="L22" s="8">
+      <c r="N22" s="9">
+        <v>0</v>
+      </c>
+      <c r="O22" s="9">
         <f t="shared" si="3"/>
         <v>52</v>
       </c>
-      <c r="M22" s="8">
+      <c r="P22" s="9">
         <f t="shared" si="12"/>
         <v>225</v>
       </c>
-      <c r="N22" s="8">
+      <c r="Q22" s="9">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:14">
+      <c r="R22" s="9">
+        <v>0</v>
+      </c>
+      <c r="S22" s="9">
+        <v>0</v>
+      </c>
+      <c r="T22" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:20">
       <c r="C23" s="1">
         <v>18</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="I23" s="8">
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>18</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="K23" s="9">
         <f t="shared" si="9"/>
         <v>6700</v>
       </c>
-      <c r="J23" s="8">
+      <c r="L23" s="9">
         <f t="shared" si="10"/>
         <v>6700</v>
       </c>
-      <c r="K23" s="8">
+      <c r="M23" s="9">
         <f t="shared" si="11"/>
         <v>5500</v>
       </c>
-      <c r="L23" s="8">
+      <c r="N23" s="9">
+        <v>0</v>
+      </c>
+      <c r="O23" s="9">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="M23" s="8">
+      <c r="P23" s="9">
         <f t="shared" si="12"/>
         <v>255</v>
       </c>
-      <c r="N23" s="8">
+      <c r="Q23" s="9">
         <v>30</v>
       </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:14">
+      <c r="R23" s="9">
+        <v>0</v>
+      </c>
+      <c r="S23" s="9">
+        <v>0</v>
+      </c>
+      <c r="T23" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:20">
       <c r="C24" s="1">
         <v>19</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="I24" s="8">
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>19</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="K24" s="9">
         <f t="shared" si="9"/>
         <v>7500</v>
       </c>
-      <c r="J24" s="8">
+      <c r="L24" s="9">
         <f t="shared" si="10"/>
         <v>7500</v>
       </c>
-      <c r="K24" s="8">
+      <c r="M24" s="9">
         <f t="shared" si="11"/>
         <v>5900</v>
       </c>
-      <c r="L24" s="8">
+      <c r="N24" s="9">
+        <v>0</v>
+      </c>
+      <c r="O24" s="9">
         <f t="shared" si="3"/>
         <v>56</v>
       </c>
-      <c r="M24" s="8">
+      <c r="P24" s="9">
         <f t="shared" si="12"/>
         <v>285</v>
       </c>
-      <c r="N24" s="8">
+      <c r="Q24" s="9">
         <v>40</v>
       </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:14">
+      <c r="R24" s="9">
+        <v>0</v>
+      </c>
+      <c r="S24" s="9">
+        <v>0</v>
+      </c>
+      <c r="T24" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:20">
       <c r="C25" s="1">
         <v>20</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="I25" s="8">
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
+        <v>20</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="K25" s="9">
         <f t="shared" si="9"/>
         <v>8300</v>
       </c>
-      <c r="J25" s="8">
+      <c r="L25" s="9">
         <f t="shared" si="10"/>
         <v>8300</v>
       </c>
-      <c r="K25" s="8">
+      <c r="M25" s="9">
         <f t="shared" si="11"/>
         <v>6300</v>
       </c>
-      <c r="L25" s="8">
+      <c r="N25" s="9">
+        <v>0</v>
+      </c>
+      <c r="O25" s="9">
         <f t="shared" si="3"/>
         <v>58</v>
       </c>
-      <c r="M25" s="8">
+      <c r="P25" s="9">
         <f t="shared" si="12"/>
         <v>315</v>
       </c>
-      <c r="N25" s="8">
+      <c r="Q25" s="9">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" customHeight="1" spans="6:11">
-      <c r="F26" s="7"/>
-      <c r="K26" s="8"/>
-    </row>
-    <row r="27" customHeight="1" spans="6:7">
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-    </row>
-    <row r="28" customHeight="1" spans="6:7">
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" customHeight="1" spans="6:7">
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-    </row>
-    <row r="30" customHeight="1" spans="7:7">
-      <c r="G30" s="7"/>
-    </row>
-    <row r="31" customHeight="1" spans="7:7">
-      <c r="G31" s="7"/>
-    </row>
-    <row r="32" customHeight="1" spans="7:7">
-      <c r="G32" s="7"/>
-    </row>
-    <row r="33" customHeight="1" spans="7:8">
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-    </row>
-    <row r="34" customHeight="1" spans="7:8">
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-    </row>
-    <row r="35" customHeight="1" spans="7:7">
-      <c r="G35" s="7"/>
-    </row>
-    <row r="36" customHeight="1" spans="7:7">
-      <c r="G36" s="7"/>
+      <c r="R25" s="9">
+        <v>0</v>
+      </c>
+      <c r="S25" s="9">
+        <v>0</v>
+      </c>
+      <c r="T25" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="8:20">
+      <c r="H26" s="8"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="10"/>
+      <c r="T26" s="11"/>
+    </row>
+    <row r="27" customHeight="1" spans="8:20">
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="N27" s="9"/>
+      <c r="T27" s="11"/>
+    </row>
+    <row r="28" customHeight="1" spans="8:20">
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="N28" s="9"/>
+      <c r="T28" s="11"/>
+    </row>
+    <row r="29" customHeight="1" spans="8:20">
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="N29" s="9"/>
+      <c r="T29" s="11"/>
+    </row>
+    <row r="30" customHeight="1" spans="9:20">
+      <c r="I30" s="8"/>
+      <c r="N30" s="9"/>
+      <c r="T30" s="11"/>
+    </row>
+    <row r="31" customHeight="1" spans="9:20">
+      <c r="I31" s="8"/>
+      <c r="N31" s="9"/>
+      <c r="T31" s="11"/>
+    </row>
+    <row r="32" customHeight="1" spans="9:20">
+      <c r="I32" s="8"/>
+      <c r="N32" s="9"/>
+      <c r="T32" s="11"/>
+    </row>
+    <row r="33" customHeight="1" spans="3:20">
+      <c r="C33" s="1">
+        <v>101</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K33" s="10">
+        <f t="shared" ref="K33:K42" si="13">K32+1000</f>
+        <v>1000</v>
+      </c>
+      <c r="L33" s="10">
+        <f t="shared" ref="L33:L42" si="14">L32+1000</f>
+        <v>1000</v>
+      </c>
+      <c r="M33" s="10">
+        <f t="shared" ref="M33:M42" si="15">M32+500</f>
+        <v>500</v>
+      </c>
+      <c r="N33" s="9">
+        <v>10000</v>
+      </c>
+      <c r="O33" s="10">
+        <v>1</v>
+      </c>
+      <c r="P33" s="9">
+        <v>150</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>50</v>
+      </c>
+      <c r="R33" s="9">
+        <v>0</v>
+      </c>
+      <c r="S33" s="9">
+        <v>0</v>
+      </c>
+      <c r="T33" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:20">
+      <c r="C34" s="1">
+        <v>102</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" s="1">
+        <v>2</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K34" s="10">
+        <f t="shared" si="13"/>
+        <v>2000</v>
+      </c>
+      <c r="L34" s="10">
+        <f t="shared" si="14"/>
+        <v>2000</v>
+      </c>
+      <c r="M34" s="10">
+        <f t="shared" si="15"/>
+        <v>1000</v>
+      </c>
+      <c r="N34" s="9">
+        <f t="shared" ref="N34:N42" si="16">N33+2000</f>
+        <v>12000</v>
+      </c>
+      <c r="O34" s="10">
+        <v>1</v>
+      </c>
+      <c r="P34" s="9">
+        <f t="shared" ref="P34:P42" si="17">P33+20</f>
+        <v>170</v>
+      </c>
+      <c r="Q34" s="9">
+        <v>50</v>
+      </c>
+      <c r="R34" s="9">
+        <v>0</v>
+      </c>
+      <c r="S34" s="9">
+        <v>0</v>
+      </c>
+      <c r="T34" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:20">
+      <c r="C35" s="1">
+        <v>103</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" s="1">
+        <v>3</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K35" s="10">
+        <f t="shared" si="13"/>
+        <v>3000</v>
+      </c>
+      <c r="L35" s="10">
+        <f t="shared" si="14"/>
+        <v>3000</v>
+      </c>
+      <c r="M35" s="10">
+        <f t="shared" si="15"/>
+        <v>1500</v>
+      </c>
+      <c r="N35" s="9">
+        <f t="shared" si="16"/>
+        <v>14000</v>
+      </c>
+      <c r="O35" s="10">
+        <v>1</v>
+      </c>
+      <c r="P35" s="9">
+        <f t="shared" si="17"/>
+        <v>190</v>
+      </c>
+      <c r="Q35" s="9">
+        <v>50</v>
+      </c>
+      <c r="R35" s="9">
+        <v>0</v>
+      </c>
+      <c r="S35" s="9">
+        <v>0</v>
+      </c>
+      <c r="T35" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:20">
+      <c r="C36" s="1">
+        <v>104</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2</v>
+      </c>
+      <c r="E36" s="1">
+        <v>4</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K36" s="10">
+        <f t="shared" si="13"/>
+        <v>4000</v>
+      </c>
+      <c r="L36" s="10">
+        <f t="shared" si="14"/>
+        <v>4000</v>
+      </c>
+      <c r="M36" s="10">
+        <f t="shared" si="15"/>
+        <v>2000</v>
+      </c>
+      <c r="N36" s="9">
+        <f t="shared" si="16"/>
+        <v>16000</v>
+      </c>
+      <c r="O36" s="10">
+        <v>1</v>
+      </c>
+      <c r="P36" s="9">
+        <f t="shared" si="17"/>
+        <v>210</v>
+      </c>
+      <c r="Q36" s="9">
+        <v>50</v>
+      </c>
+      <c r="R36" s="9">
+        <v>0</v>
+      </c>
+      <c r="S36" s="9">
+        <v>0</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:20">
+      <c r="C37" s="1">
+        <v>105</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37" s="1">
+        <v>5</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K37" s="10">
+        <f t="shared" si="13"/>
+        <v>5000</v>
+      </c>
+      <c r="L37" s="10">
+        <f t="shared" si="14"/>
+        <v>5000</v>
+      </c>
+      <c r="M37" s="10">
+        <f t="shared" si="15"/>
+        <v>2500</v>
+      </c>
+      <c r="N37" s="9">
+        <f t="shared" si="16"/>
+        <v>18000</v>
+      </c>
+      <c r="O37" s="10">
+        <v>1</v>
+      </c>
+      <c r="P37" s="9">
+        <f t="shared" si="17"/>
+        <v>230</v>
+      </c>
+      <c r="Q37" s="9">
+        <v>50</v>
+      </c>
+      <c r="R37" s="9">
+        <v>0</v>
+      </c>
+      <c r="S37" s="9">
+        <v>0</v>
+      </c>
+      <c r="T37" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:20">
+      <c r="C38" s="1">
+        <v>106</v>
+      </c>
+      <c r="D38" s="1">
+        <v>2</v>
+      </c>
+      <c r="E38" s="1">
+        <v>6</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K38" s="10">
+        <f t="shared" si="13"/>
+        <v>6000</v>
+      </c>
+      <c r="L38" s="10">
+        <f t="shared" si="14"/>
+        <v>6000</v>
+      </c>
+      <c r="M38" s="10">
+        <f t="shared" si="15"/>
+        <v>3000</v>
+      </c>
+      <c r="N38" s="9">
+        <f t="shared" si="16"/>
+        <v>20000</v>
+      </c>
+      <c r="O38" s="10">
+        <v>1</v>
+      </c>
+      <c r="P38" s="9">
+        <f t="shared" ref="P38:P42" si="18">P37+30</f>
+        <v>260</v>
+      </c>
+      <c r="Q38" s="9">
+        <v>50</v>
+      </c>
+      <c r="R38" s="9">
+        <v>0</v>
+      </c>
+      <c r="S38" s="9">
+        <v>0</v>
+      </c>
+      <c r="T38" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:20">
+      <c r="C39" s="1">
+        <v>107</v>
+      </c>
+      <c r="D39" s="1">
+        <v>2</v>
+      </c>
+      <c r="E39" s="1">
+        <v>7</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K39" s="10">
+        <f t="shared" si="13"/>
+        <v>7000</v>
+      </c>
+      <c r="L39" s="10">
+        <f t="shared" si="14"/>
+        <v>7000</v>
+      </c>
+      <c r="M39" s="10">
+        <f t="shared" si="15"/>
+        <v>3500</v>
+      </c>
+      <c r="N39" s="9">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="O39" s="10">
+        <v>1</v>
+      </c>
+      <c r="P39" s="9">
+        <f t="shared" si="18"/>
+        <v>290</v>
+      </c>
+      <c r="Q39" s="9">
+        <v>50</v>
+      </c>
+      <c r="R39" s="9">
+        <v>0</v>
+      </c>
+      <c r="S39" s="9">
+        <v>0</v>
+      </c>
+      <c r="T39" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:20">
+      <c r="C40" s="1">
+        <v>108</v>
+      </c>
+      <c r="D40" s="1">
+        <v>2</v>
+      </c>
+      <c r="E40" s="1">
+        <v>8</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K40" s="10">
+        <f t="shared" si="13"/>
+        <v>8000</v>
+      </c>
+      <c r="L40" s="10">
+        <f t="shared" si="14"/>
+        <v>8000</v>
+      </c>
+      <c r="M40" s="10">
+        <f t="shared" si="15"/>
+        <v>4000</v>
+      </c>
+      <c r="N40" s="9">
+        <f t="shared" si="16"/>
+        <v>24000</v>
+      </c>
+      <c r="O40" s="10">
+        <v>1</v>
+      </c>
+      <c r="P40" s="9">
+        <f t="shared" si="18"/>
+        <v>320</v>
+      </c>
+      <c r="Q40" s="9">
+        <v>50</v>
+      </c>
+      <c r="R40" s="9">
+        <v>0</v>
+      </c>
+      <c r="S40" s="9">
+        <v>0</v>
+      </c>
+      <c r="T40" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:20">
+      <c r="C41" s="1">
+        <v>109</v>
+      </c>
+      <c r="D41" s="1">
+        <v>2</v>
+      </c>
+      <c r="E41" s="1">
+        <v>9</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K41" s="10">
+        <f t="shared" si="13"/>
+        <v>9000</v>
+      </c>
+      <c r="L41" s="10">
+        <f t="shared" si="14"/>
+        <v>9000</v>
+      </c>
+      <c r="M41" s="10">
+        <f t="shared" si="15"/>
+        <v>4500</v>
+      </c>
+      <c r="N41" s="9">
+        <f t="shared" si="16"/>
+        <v>26000</v>
+      </c>
+      <c r="O41" s="10">
+        <v>1</v>
+      </c>
+      <c r="P41" s="9">
+        <f t="shared" si="18"/>
+        <v>350</v>
+      </c>
+      <c r="Q41" s="9">
+        <v>50</v>
+      </c>
+      <c r="R41" s="9">
+        <v>0</v>
+      </c>
+      <c r="S41" s="9">
+        <v>0</v>
+      </c>
+      <c r="T41" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:20">
+      <c r="C42" s="1">
+        <v>110</v>
+      </c>
+      <c r="D42" s="1">
+        <v>2</v>
+      </c>
+      <c r="E42" s="1">
+        <v>10</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K42" s="10">
+        <f t="shared" si="13"/>
+        <v>10000</v>
+      </c>
+      <c r="L42" s="10">
+        <f t="shared" si="14"/>
+        <v>10000</v>
+      </c>
+      <c r="M42" s="10">
+        <f t="shared" si="15"/>
+        <v>5000</v>
+      </c>
+      <c r="N42" s="9">
+        <f t="shared" si="16"/>
+        <v>28000</v>
+      </c>
+      <c r="O42" s="10">
+        <v>1</v>
+      </c>
+      <c r="P42" s="9">
+        <f t="shared" si="18"/>
+        <v>380</v>
+      </c>
+      <c r="Q42" s="9">
+        <v>50</v>
+      </c>
+      <c r="R42" s="9">
+        <v>0</v>
+      </c>
+      <c r="S42" s="9">
+        <v>0</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="14:20">
+      <c r="N43" s="9"/>
+      <c r="T43" s="9"/>
+    </row>
+    <row r="44" customHeight="1" spans="14:20">
+      <c r="N44" s="9"/>
+      <c r="T44" s="9"/>
+    </row>
+    <row r="45" customHeight="1" spans="14:20">
+      <c r="N45" s="9"/>
+      <c r="T45" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 R3 S3 D4 E4 R4 S4 D5 E5 N5 R5 S5 C3:C5 N3:N4 T3:T5 F3:M5 O3:Q5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterPillConfig.xlsx
+++ b/Excel/MonsterPillConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="143">
   <si>
     <t>ID</t>
   </si>
@@ -56,6 +56,12 @@
     <t>HP</t>
   </si>
   <si>
+    <t>Strong</t>
+  </si>
+  <si>
+    <t>DamageMul</t>
+  </si>
+  <si>
     <t>DamageIncrea</t>
   </si>
   <si>
@@ -80,12 +86,6 @@
     <t>Speed</t>
   </si>
   <si>
-    <t>Strong</t>
-  </si>
-  <si>
-    <t>DamageMul</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -98,178 +98,178 @@
     <t>double</t>
   </si>
   <si>
-    <t>炼体秘境一层</t>
+    <t>炼体一层</t>
   </si>
   <si>
     <t>幻境魔物</t>
   </si>
   <si>
-    <t>1000000000000000</t>
-  </si>
-  <si>
-    <t>50000000000000000</t>
-  </si>
-  <si>
-    <t>900000000000000000000000</t>
-  </si>
-  <si>
-    <t>炼体秘境二层</t>
-  </si>
-  <si>
-    <t>100000000000000000</t>
-  </si>
-  <si>
-    <t>50000000000000000000</t>
-  </si>
-  <si>
-    <t>9000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>炼体秘境三层</t>
-  </si>
-  <si>
-    <t>10000000000000000000</t>
-  </si>
-  <si>
-    <t>50000000000000000000000</t>
-  </si>
-  <si>
-    <t>90000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>炼体秘境四层</t>
-  </si>
-  <si>
-    <t>1000000000000000000000</t>
-  </si>
-  <si>
-    <t>50000000000000000000000000</t>
-  </si>
-  <si>
-    <t>900000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>炼体秘境五层</t>
-  </si>
-  <si>
-    <t>100000000000000000000000</t>
-  </si>
-  <si>
-    <t>50000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>9000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>炼体秘境六层</t>
-  </si>
-  <si>
-    <t>10000000000000000000000000</t>
-  </si>
-  <si>
-    <t>50000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>90000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>炼体秘境七层</t>
-  </si>
-  <si>
-    <t>1000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>50000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>900000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>炼体秘境八层</t>
-  </si>
-  <si>
-    <t>100000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>50000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>9000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>炼体秘境九层</t>
-  </si>
-  <si>
-    <t>10000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>50000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>90000000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>炼体秘境十层</t>
-  </si>
-  <si>
-    <t>1000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>50000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>900000000000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>炼体秘境十一层</t>
-  </si>
-  <si>
-    <t>100000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>50000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>9000000000000000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>炼体秘境十二层</t>
-  </si>
-  <si>
-    <t>10000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>50000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>90000000000000000000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>炼体秘境十三层</t>
-  </si>
-  <si>
-    <t>1000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>50000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>900000000000000000000000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>炼体秘境十四层</t>
-  </si>
-  <si>
-    <t>100000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>50000000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>9000000000000000000000000000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>炼体秘境十五层</t>
+    <t>1E+15</t>
+  </si>
+  <si>
+    <t>5E+16</t>
+  </si>
+  <si>
+    <t>9E+23</t>
+  </si>
+  <si>
+    <t>炼体二层</t>
+  </si>
+  <si>
+    <t>1E+17</t>
+  </si>
+  <si>
+    <t>5E+19</t>
+  </si>
+  <si>
+    <t>9E+27</t>
+  </si>
+  <si>
+    <t>炼体三层</t>
+  </si>
+  <si>
+    <t>1E+19</t>
+  </si>
+  <si>
+    <t>5E+22</t>
+  </si>
+  <si>
+    <t>9E+31</t>
+  </si>
+  <si>
+    <t>炼体四层</t>
+  </si>
+  <si>
+    <t>1E+21</t>
+  </si>
+  <si>
+    <t>5E+25</t>
+  </si>
+  <si>
+    <t>9E+35</t>
+  </si>
+  <si>
+    <t>炼体五层</t>
+  </si>
+  <si>
+    <t>1E+23</t>
+  </si>
+  <si>
+    <t>5E+28</t>
+  </si>
+  <si>
+    <t>9E+39</t>
+  </si>
+  <si>
+    <t>炼体六层</t>
+  </si>
+  <si>
+    <t>1E+25</t>
+  </si>
+  <si>
+    <t>5E+31</t>
+  </si>
+  <si>
+    <t>9E+43</t>
+  </si>
+  <si>
+    <t>炼体七层</t>
+  </si>
+  <si>
+    <t>1E+27</t>
+  </si>
+  <si>
+    <t>5E+34</t>
+  </si>
+  <si>
+    <t>9E+47</t>
+  </si>
+  <si>
+    <t>炼体八层</t>
+  </si>
+  <si>
+    <t>1E+29</t>
+  </si>
+  <si>
+    <t>5E+37</t>
+  </si>
+  <si>
+    <t>9E+51</t>
+  </si>
+  <si>
+    <t>炼体九层</t>
+  </si>
+  <si>
+    <t>1E+31</t>
+  </si>
+  <si>
+    <t>5E+40</t>
+  </si>
+  <si>
+    <t>9E+55</t>
+  </si>
+  <si>
+    <t>炼体十层</t>
+  </si>
+  <si>
+    <t>1E+33</t>
+  </si>
+  <si>
+    <t>5E+43</t>
+  </si>
+  <si>
+    <t>9E+59</t>
+  </si>
+  <si>
+    <t>炼体十一层</t>
+  </si>
+  <si>
+    <t>1E+35</t>
+  </si>
+  <si>
+    <t>5E+46</t>
+  </si>
+  <si>
+    <t>9E+63</t>
+  </si>
+  <si>
+    <t>炼体十二层</t>
+  </si>
+  <si>
+    <t>1E+37</t>
+  </si>
+  <si>
+    <t>5E+49</t>
+  </si>
+  <si>
+    <t>9E+67</t>
+  </si>
+  <si>
+    <t>炼体十三层</t>
+  </si>
+  <si>
+    <t>1E+39</t>
+  </si>
+  <si>
+    <t>5E+52</t>
+  </si>
+  <si>
+    <t>9E+71</t>
+  </si>
+  <si>
+    <t>炼体十四层</t>
+  </si>
+  <si>
+    <t>1E+41</t>
+  </si>
+  <si>
+    <t>5E+55</t>
+  </si>
+  <si>
+    <t>9E+75</t>
+  </si>
+  <si>
+    <t>炼体十五层</t>
   </si>
   <si>
     <t>1000正</t>
@@ -281,7 +281,7 @@
     <t>9000那</t>
   </si>
   <si>
-    <t>炼体秘境十六层</t>
+    <t>炼体十六层</t>
   </si>
   <si>
     <t>9999载</t>
@@ -293,7 +293,7 @@
     <t>9999由</t>
   </si>
   <si>
-    <t>炼体秘境十七层</t>
+    <t>炼体十七层</t>
   </si>
   <si>
     <t>9999极</t>
@@ -305,7 +305,7 @@
     <t>9999他</t>
   </si>
   <si>
-    <t>炼体秘境十八层</t>
+    <t>炼体十八层</t>
   </si>
   <si>
     <t>9999恒</t>
@@ -317,7 +317,7 @@
     <t>9999不</t>
   </si>
   <si>
-    <t>炼体秘境十九层</t>
+    <t>炼体十九层</t>
   </si>
   <si>
     <t>9999河</t>
@@ -329,7 +329,7 @@
     <t>9999可</t>
   </si>
   <si>
-    <t>炼体秘境二十层</t>
+    <t>炼体二十层</t>
   </si>
   <si>
     <t>9999那</t>
@@ -338,46 +338,127 @@
     <t>9999思</t>
   </si>
   <si>
-    <t>练气秘境一层</t>
+    <t>练气一层</t>
   </si>
   <si>
     <t>炼气魔物</t>
   </si>
   <si>
-    <t>9E+47</t>
-  </si>
-  <si>
-    <t>9E+57</t>
-  </si>
-  <si>
-    <t>9E+77</t>
-  </si>
-  <si>
-    <t>练气秘境二层</t>
-  </si>
-  <si>
-    <t>练气秘境三层</t>
-  </si>
-  <si>
-    <t>练气秘境四层</t>
-  </si>
-  <si>
-    <t>练气秘境五层</t>
-  </si>
-  <si>
-    <t>练气秘境六层</t>
-  </si>
-  <si>
-    <t>练气秘境七层</t>
-  </si>
-  <si>
-    <t>练气秘境八层</t>
-  </si>
-  <si>
-    <t>练气秘境九层</t>
-  </si>
-  <si>
-    <t>练气秘境十层</t>
+    <t>9E+50</t>
+  </si>
+  <si>
+    <t>9E+40</t>
+  </si>
+  <si>
+    <t>9E+80</t>
+  </si>
+  <si>
+    <t>1E+5</t>
+  </si>
+  <si>
+    <t>1E+20</t>
+  </si>
+  <si>
+    <t>练气二层</t>
+  </si>
+  <si>
+    <t>9E+45</t>
+  </si>
+  <si>
+    <t>9E+85</t>
+  </si>
+  <si>
+    <t>1E+6</t>
+  </si>
+  <si>
+    <t>练气三层</t>
+  </si>
+  <si>
+    <t>9E+60</t>
+  </si>
+  <si>
+    <t>9E+90</t>
+  </si>
+  <si>
+    <t>1E+7</t>
+  </si>
+  <si>
+    <t>1E+30</t>
+  </si>
+  <si>
+    <t>练气四层</t>
+  </si>
+  <si>
+    <t>9E+65</t>
+  </si>
+  <si>
+    <t>9E+95</t>
+  </si>
+  <si>
+    <t>1E+9</t>
+  </si>
+  <si>
+    <t>练气五层</t>
+  </si>
+  <si>
+    <t>9E+70</t>
+  </si>
+  <si>
+    <t>9E+100</t>
+  </si>
+  <si>
+    <t>1E+11</t>
+  </si>
+  <si>
+    <t>1E+40</t>
+  </si>
+  <si>
+    <t>练气六层</t>
+  </si>
+  <si>
+    <t>9E+105</t>
+  </si>
+  <si>
+    <t>1E+13</t>
+  </si>
+  <si>
+    <t>1E+45</t>
+  </si>
+  <si>
+    <t>练气七层</t>
+  </si>
+  <si>
+    <t>9E+110</t>
+  </si>
+  <si>
+    <t>1E+50</t>
+  </si>
+  <si>
+    <t>练气八层</t>
+  </si>
+  <si>
+    <t>9E+115</t>
+  </si>
+  <si>
+    <t>1E+55</t>
+  </si>
+  <si>
+    <t>练气九层</t>
+  </si>
+  <si>
+    <t>9E+120</t>
+  </si>
+  <si>
+    <t>1E+60</t>
+  </si>
+  <si>
+    <t>练气十层</t>
+  </si>
+  <si>
+    <t>9E+125</t>
+  </si>
+  <si>
+    <t>1E+65</t>
   </si>
 </sst>
 </file>
@@ -1043,13 +1124,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1369,7 +1451,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T45"/>
+  <dimension ref="A1:T53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.12389380530973" style="2" customWidth="1"/>
@@ -1377,17 +1459,18 @@
     <col min="3" max="5" width="9.87610619469027" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.4778761061947" style="1" customWidth="1"/>
     <col min="7" max="7" width="16.2477876106195" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.1238938053097" style="3" customWidth="1"/>
-    <col min="9" max="9" width="21.6283185840708" style="3" customWidth="1"/>
-    <col min="10" max="10" width="20.3805309734513" style="3" customWidth="1"/>
-    <col min="11" max="11" width="12.6283185840708" style="2" customWidth="1"/>
-    <col min="12" max="13" width="12.5044247787611" style="2" customWidth="1"/>
-    <col min="14" max="14" width="8" style="2" customWidth="1"/>
-    <col min="15" max="15" width="12.5044247787611" style="2" customWidth="1"/>
-    <col min="16" max="16" width="14.1238938053097" style="2" customWidth="1"/>
-    <col min="17" max="19" width="9.6283185840708" style="2" customWidth="1"/>
-    <col min="20" max="20" width="13.6637168141593" style="4" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="2"/>
+    <col min="8" max="8" width="31.3362831858407" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.5486725663717" style="3" customWidth="1"/>
+    <col min="10" max="10" width="18.5221238938053" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9.6283185840708" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11.6902654867257" style="4" customWidth="1"/>
+    <col min="13" max="13" width="12.6283185840708" style="2" customWidth="1"/>
+    <col min="14" max="15" width="12.5044247787611" style="2" customWidth="1"/>
+    <col min="16" max="16" width="8" style="2" customWidth="1"/>
+    <col min="17" max="17" width="12.5044247787611" style="2" customWidth="1"/>
+    <col min="18" max="18" width="14.1238938053097" style="2" customWidth="1"/>
+    <col min="19" max="20" width="9.6283185840708" style="2" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:20">
@@ -1568,10 +1651,10 @@
         <v>20</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>19</v>
@@ -1589,13 +1672,13 @@
         <v>19</v>
       </c>
       <c r="R5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="T5" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="T5" s="6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="3:20">
@@ -1624,33 +1707,33 @@
         <v>26</v>
       </c>
       <c r="K6" s="9">
+        <v>0</v>
+      </c>
+      <c r="L6" s="10">
+        <v>0</v>
+      </c>
+      <c r="M6" s="9">
         <v>500</v>
       </c>
-      <c r="L6" s="9">
+      <c r="N6" s="9">
         <v>500</v>
       </c>
-      <c r="M6" s="9">
+      <c r="O6" s="9">
         <v>1500</v>
       </c>
-      <c r="N6" s="9">
-        <v>0</v>
-      </c>
-      <c r="O6" s="9">
+      <c r="P6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="9">
         <v>20</v>
       </c>
-      <c r="P6" s="9">
+      <c r="R6" s="9">
         <v>30</v>
       </c>
-      <c r="Q6" s="9">
-        <v>0</v>
-      </c>
-      <c r="R6" s="9">
-        <v>0</v>
-      </c>
       <c r="S6" s="9">
         <v>0</v>
       </c>
-      <c r="T6" s="11">
+      <c r="T6" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1680,38 +1763,38 @@
         <v>30</v>
       </c>
       <c r="K7" s="9">
-        <f t="shared" ref="K7:K17" si="0">K6+200</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9">
+        <f t="shared" ref="M7:M17" si="0">M6+200</f>
         <v>700</v>
       </c>
-      <c r="L7" s="9">
-        <f t="shared" ref="L7:L17" si="1">L6+200</f>
+      <c r="N7" s="9">
+        <f t="shared" ref="N7:N17" si="1">N6+200</f>
         <v>700</v>
       </c>
-      <c r="M7" s="9">
-        <f t="shared" ref="M7:M25" si="2">M6+200</f>
+      <c r="O7" s="9">
+        <f t="shared" ref="O7:O25" si="2">O6+200</f>
         <v>1700</v>
       </c>
-      <c r="N7" s="9">
-        <v>0</v>
-      </c>
-      <c r="O7" s="9">
-        <f t="shared" ref="O7:O25" si="3">O6+2</f>
+      <c r="P7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="9">
+        <f t="shared" ref="Q7:Q25" si="3">Q6+2</f>
         <v>22</v>
       </c>
-      <c r="P7" s="9">
-        <f t="shared" ref="P7:P12" si="4">P6+5</f>
+      <c r="R7" s="9">
+        <f t="shared" ref="R7:R12" si="4">R6+5</f>
         <v>35</v>
       </c>
-      <c r="Q7" s="9">
-        <v>0</v>
-      </c>
-      <c r="R7" s="9">
-        <v>0</v>
-      </c>
       <c r="S7" s="9">
         <v>0</v>
       </c>
-      <c r="T7" s="11">
+      <c r="T7" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1741,38 +1824,38 @@
         <v>34</v>
       </c>
       <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="10">
+        <v>0</v>
+      </c>
+      <c r="M8" s="9">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="L8" s="9">
+      <c r="N8" s="9">
         <f t="shared" si="1"/>
         <v>900</v>
       </c>
-      <c r="M8" s="9">
+      <c r="O8" s="9">
         <f t="shared" si="2"/>
         <v>1900</v>
       </c>
-      <c r="N8" s="9">
-        <v>0</v>
-      </c>
-      <c r="O8" s="9">
+      <c r="P8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="P8" s="9">
+      <c r="R8" s="9">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="Q8" s="9">
-        <v>0</v>
-      </c>
-      <c r="R8" s="9">
-        <v>0</v>
-      </c>
       <c r="S8" s="9">
         <v>0</v>
       </c>
-      <c r="T8" s="11">
+      <c r="T8" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1802,38 +1885,38 @@
         <v>38</v>
       </c>
       <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="L9" s="9">
+      <c r="N9" s="9">
         <f t="shared" si="1"/>
         <v>1100</v>
       </c>
-      <c r="M9" s="9">
+      <c r="O9" s="9">
         <f t="shared" si="2"/>
         <v>2100</v>
       </c>
-      <c r="N9" s="9">
-        <v>0</v>
-      </c>
-      <c r="O9" s="9">
+      <c r="P9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="9">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="P9" s="9">
+      <c r="R9" s="9">
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="Q9" s="9">
-        <v>0</v>
-      </c>
-      <c r="R9" s="9">
-        <v>0</v>
-      </c>
       <c r="S9" s="9">
         <v>0</v>
       </c>
-      <c r="T9" s="11">
+      <c r="T9" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1863,38 +1946,38 @@
         <v>42</v>
       </c>
       <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="10">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9">
         <f t="shared" si="0"/>
         <v>1300</v>
       </c>
-      <c r="L10" s="9">
+      <c r="N10" s="9">
         <f t="shared" si="1"/>
         <v>1300</v>
       </c>
-      <c r="M10" s="9">
+      <c r="O10" s="9">
         <f t="shared" si="2"/>
         <v>2300</v>
       </c>
-      <c r="N10" s="9">
-        <v>0</v>
-      </c>
-      <c r="O10" s="9">
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="P10" s="9">
+      <c r="R10" s="9">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="Q10" s="9">
-        <v>0</v>
-      </c>
-      <c r="R10" s="9">
-        <v>0</v>
-      </c>
       <c r="S10" s="9">
         <v>0</v>
       </c>
-      <c r="T10" s="11">
+      <c r="T10" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1924,38 +2007,38 @@
         <v>46</v>
       </c>
       <c r="K11" s="9">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10">
+        <v>0</v>
+      </c>
+      <c r="M11" s="9">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="L11" s="9">
+      <c r="N11" s="9">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="M11" s="9">
+      <c r="O11" s="9">
         <f t="shared" si="2"/>
         <v>2500</v>
       </c>
-      <c r="N11" s="9">
-        <v>0</v>
-      </c>
-      <c r="O11" s="9">
+      <c r="P11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="9">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="P11" s="9">
+      <c r="R11" s="9">
         <f t="shared" si="4"/>
         <v>55</v>
       </c>
-      <c r="Q11" s="9">
-        <v>0</v>
-      </c>
-      <c r="R11" s="9">
-        <v>0</v>
-      </c>
       <c r="S11" s="9">
         <v>0</v>
       </c>
-      <c r="T11" s="11">
+      <c r="T11" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1985,38 +2068,38 @@
         <v>50</v>
       </c>
       <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="10">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9">
         <f t="shared" si="0"/>
         <v>1700</v>
       </c>
-      <c r="L12" s="9">
+      <c r="N12" s="9">
         <f t="shared" si="1"/>
         <v>1700</v>
       </c>
-      <c r="M12" s="9">
+      <c r="O12" s="9">
         <f t="shared" si="2"/>
         <v>2700</v>
       </c>
-      <c r="N12" s="9">
-        <v>0</v>
-      </c>
-      <c r="O12" s="9">
+      <c r="P12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="9">
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
-      <c r="P12" s="9">
+      <c r="R12" s="9">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="Q12" s="9">
-        <v>0</v>
-      </c>
-      <c r="R12" s="9">
-        <v>0</v>
-      </c>
       <c r="S12" s="9">
         <v>0</v>
       </c>
-      <c r="T12" s="11">
+      <c r="T12" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2046,38 +2129,38 @@
         <v>54</v>
       </c>
       <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9">
         <f t="shared" si="0"/>
         <v>1900</v>
       </c>
-      <c r="L13" s="9">
+      <c r="N13" s="9">
         <f t="shared" si="1"/>
         <v>1900</v>
       </c>
-      <c r="M13" s="9">
+      <c r="O13" s="9">
         <f t="shared" si="2"/>
         <v>2900</v>
       </c>
-      <c r="N13" s="9">
-        <v>0</v>
-      </c>
-      <c r="O13" s="9">
+      <c r="P13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="9">
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="P13" s="9">
-        <f t="shared" ref="P13:P17" si="5">P12+10</f>
+      <c r="R13" s="9">
+        <f t="shared" ref="R13:R17" si="5">R12+10</f>
         <v>70</v>
       </c>
-      <c r="Q13" s="9">
-        <v>0</v>
-      </c>
-      <c r="R13" s="9">
-        <v>0</v>
-      </c>
       <c r="S13" s="9">
         <v>0</v>
       </c>
-      <c r="T13" s="11">
+      <c r="T13" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2107,38 +2190,38 @@
         <v>58</v>
       </c>
       <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
         <f t="shared" si="0"/>
         <v>2100</v>
       </c>
-      <c r="L14" s="9">
+      <c r="N14" s="9">
         <f t="shared" si="1"/>
         <v>2100</v>
       </c>
-      <c r="M14" s="9">
+      <c r="O14" s="9">
         <f t="shared" si="2"/>
         <v>3100</v>
       </c>
-      <c r="N14" s="9">
-        <v>0</v>
-      </c>
-      <c r="O14" s="9">
+      <c r="P14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="9">
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="P14" s="9">
+      <c r="R14" s="9">
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
-      <c r="Q14" s="9">
-        <v>0</v>
-      </c>
-      <c r="R14" s="9">
-        <v>0</v>
-      </c>
       <c r="S14" s="9">
         <v>0</v>
       </c>
-      <c r="T14" s="11">
+      <c r="T14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2168,38 +2251,38 @@
         <v>62</v>
       </c>
       <c r="K15" s="9">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10">
+        <v>0</v>
+      </c>
+      <c r="M15" s="9">
         <f t="shared" si="0"/>
         <v>2300</v>
       </c>
-      <c r="L15" s="9">
+      <c r="N15" s="9">
         <f t="shared" si="1"/>
         <v>2300</v>
       </c>
-      <c r="M15" s="9">
+      <c r="O15" s="9">
         <f t="shared" si="2"/>
         <v>3300</v>
       </c>
-      <c r="N15" s="9">
-        <v>0</v>
-      </c>
-      <c r="O15" s="9">
+      <c r="P15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="9">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="P15" s="9">
+      <c r="R15" s="9">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="Q15" s="9">
-        <v>0</v>
-      </c>
-      <c r="R15" s="9">
-        <v>0</v>
-      </c>
       <c r="S15" s="9">
         <v>0</v>
       </c>
-      <c r="T15" s="11">
+      <c r="T15" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2229,38 +2312,38 @@
         <v>66</v>
       </c>
       <c r="K16" s="9">
-        <f t="shared" ref="K16:K25" si="6">K15+400</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="10">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9">
+        <f t="shared" ref="M16:M25" si="6">M15+400</f>
         <v>2700</v>
       </c>
-      <c r="L16" s="9">
-        <f t="shared" ref="L16:L25" si="7">L15+400</f>
+      <c r="N16" s="9">
+        <f t="shared" ref="N16:N25" si="7">N15+400</f>
         <v>2700</v>
       </c>
-      <c r="M16" s="9">
+      <c r="O16" s="9">
         <f t="shared" si="2"/>
         <v>3500</v>
       </c>
-      <c r="N16" s="9">
-        <v>0</v>
-      </c>
-      <c r="O16" s="9">
+      <c r="P16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="9">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="P16" s="9">
-        <f t="shared" ref="P16:P25" si="8">P15+15</f>
+      <c r="R16" s="9">
+        <f t="shared" ref="R16:R25" si="8">R15+15</f>
         <v>105</v>
       </c>
-      <c r="Q16" s="9">
-        <v>0</v>
-      </c>
-      <c r="R16" s="9">
-        <v>0</v>
-      </c>
       <c r="S16" s="9">
         <v>0</v>
       </c>
-      <c r="T16" s="11">
+      <c r="T16" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2290,38 +2373,38 @@
         <v>70</v>
       </c>
       <c r="K17" s="9">
+        <v>0</v>
+      </c>
+      <c r="L17" s="10">
+        <v>0</v>
+      </c>
+      <c r="M17" s="9">
         <f t="shared" si="6"/>
         <v>3100</v>
       </c>
-      <c r="L17" s="9">
+      <c r="N17" s="9">
         <f t="shared" si="7"/>
         <v>3100</v>
       </c>
-      <c r="M17" s="9">
+      <c r="O17" s="9">
         <f t="shared" si="2"/>
         <v>3700</v>
       </c>
-      <c r="N17" s="9">
-        <v>0</v>
-      </c>
-      <c r="O17" s="9">
+      <c r="P17" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="9">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="P17" s="9">
+      <c r="R17" s="9">
         <f t="shared" si="8"/>
         <v>120</v>
       </c>
-      <c r="Q17" s="9">
-        <v>0</v>
-      </c>
-      <c r="R17" s="9">
-        <v>0</v>
-      </c>
       <c r="S17" s="9">
         <v>0</v>
       </c>
-      <c r="T17" s="11">
+      <c r="T17" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2351,38 +2434,38 @@
         <v>74</v>
       </c>
       <c r="K18" s="9">
+        <v>0</v>
+      </c>
+      <c r="L18" s="10">
+        <v>0</v>
+      </c>
+      <c r="M18" s="9">
         <f t="shared" si="6"/>
         <v>3500</v>
       </c>
-      <c r="L18" s="9">
+      <c r="N18" s="9">
         <f t="shared" si="7"/>
         <v>3500</v>
       </c>
-      <c r="M18" s="9">
+      <c r="O18" s="9">
         <f t="shared" si="2"/>
         <v>3900</v>
       </c>
-      <c r="N18" s="9">
-        <v>0</v>
-      </c>
-      <c r="O18" s="9">
+      <c r="P18" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="9">
         <f t="shared" si="3"/>
         <v>44</v>
       </c>
-      <c r="P18" s="9">
+      <c r="R18" s="9">
         <f t="shared" si="8"/>
         <v>135</v>
       </c>
-      <c r="Q18" s="9">
-        <v>0</v>
-      </c>
-      <c r="R18" s="9">
-        <v>0</v>
-      </c>
       <c r="S18" s="9">
         <v>0</v>
       </c>
-      <c r="T18" s="11">
+      <c r="T18" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2412,38 +2495,38 @@
         <v>78</v>
       </c>
       <c r="K19" s="9">
+        <v>0</v>
+      </c>
+      <c r="L19" s="10">
+        <v>0</v>
+      </c>
+      <c r="M19" s="9">
         <f t="shared" si="6"/>
         <v>3900</v>
       </c>
-      <c r="L19" s="9">
+      <c r="N19" s="9">
         <f t="shared" si="7"/>
         <v>3900</v>
       </c>
-      <c r="M19" s="9">
+      <c r="O19" s="9">
         <f t="shared" si="2"/>
         <v>4100</v>
       </c>
-      <c r="N19" s="9">
-        <v>0</v>
-      </c>
-      <c r="O19" s="9">
+      <c r="P19" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="9">
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
-      <c r="P19" s="9">
+      <c r="R19" s="9">
         <f t="shared" si="8"/>
         <v>150</v>
       </c>
-      <c r="Q19" s="9">
-        <v>0</v>
-      </c>
-      <c r="R19" s="9">
-        <v>0</v>
-      </c>
       <c r="S19" s="9">
         <v>0</v>
       </c>
-      <c r="T19" s="11">
+      <c r="T19" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2473,38 +2556,38 @@
         <v>82</v>
       </c>
       <c r="K20" s="9">
+        <v>0</v>
+      </c>
+      <c r="L20" s="10">
+        <v>0</v>
+      </c>
+      <c r="M20" s="9">
         <f t="shared" si="6"/>
         <v>4300</v>
       </c>
-      <c r="L20" s="9">
+      <c r="N20" s="9">
         <f t="shared" si="7"/>
         <v>4300</v>
       </c>
-      <c r="M20" s="9">
+      <c r="O20" s="9">
         <f t="shared" si="2"/>
         <v>4300</v>
       </c>
-      <c r="N20" s="9">
-        <v>0</v>
-      </c>
-      <c r="O20" s="9">
+      <c r="P20" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="9">
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="P20" s="9">
+      <c r="R20" s="9">
         <f t="shared" si="8"/>
         <v>165</v>
       </c>
-      <c r="Q20" s="9">
-        <v>0</v>
-      </c>
-      <c r="R20" s="9">
-        <v>0</v>
-      </c>
       <c r="S20" s="9">
         <v>0</v>
       </c>
-      <c r="T20" s="11">
+      <c r="T20" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2534,38 +2617,38 @@
         <v>86</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" ref="K21:K25" si="9">K20+800</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="10">
+        <v>0</v>
+      </c>
+      <c r="M21" s="9">
+        <f t="shared" ref="M21:M25" si="9">M20+800</f>
         <v>5100</v>
       </c>
-      <c r="L21" s="9">
-        <f t="shared" ref="L21:L25" si="10">L20+800</f>
+      <c r="N21" s="9">
+        <f t="shared" ref="N21:N25" si="10">N20+800</f>
         <v>5100</v>
       </c>
-      <c r="M21" s="9">
-        <f t="shared" ref="M21:M26" si="11">M20+400</f>
+      <c r="O21" s="9">
+        <f t="shared" ref="O21:O26" si="11">O20+400</f>
         <v>4700</v>
       </c>
-      <c r="N21" s="9">
-        <v>0</v>
-      </c>
-      <c r="O21" s="9">
+      <c r="P21" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="9">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="P21" s="9">
-        <f t="shared" ref="P21:P25" si="12">P20+30</f>
+      <c r="R21" s="9">
+        <f t="shared" ref="R21:R25" si="12">R20+30</f>
         <v>195</v>
       </c>
-      <c r="Q21" s="9">
+      <c r="S21" s="9">
         <v>10</v>
       </c>
-      <c r="R21" s="9">
-        <v>0</v>
-      </c>
-      <c r="S21" s="9">
-        <v>0</v>
-      </c>
-      <c r="T21" s="11">
+      <c r="T21" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2595,38 +2678,38 @@
         <v>90</v>
       </c>
       <c r="K22" s="9">
+        <v>0</v>
+      </c>
+      <c r="L22" s="10">
+        <v>0</v>
+      </c>
+      <c r="M22" s="9">
         <f t="shared" si="9"/>
         <v>5900</v>
       </c>
-      <c r="L22" s="9">
+      <c r="N22" s="9">
         <f t="shared" si="10"/>
         <v>5900</v>
       </c>
-      <c r="M22" s="9">
+      <c r="O22" s="9">
         <f t="shared" si="11"/>
         <v>5100</v>
       </c>
-      <c r="N22" s="9">
-        <v>0</v>
-      </c>
-      <c r="O22" s="9">
+      <c r="P22" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="9">
         <f t="shared" si="3"/>
         <v>52</v>
       </c>
-      <c r="P22" s="9">
+      <c r="R22" s="9">
         <f t="shared" si="12"/>
         <v>225</v>
       </c>
-      <c r="Q22" s="9">
+      <c r="S22" s="9">
         <v>20</v>
       </c>
-      <c r="R22" s="9">
-        <v>0</v>
-      </c>
-      <c r="S22" s="9">
-        <v>0</v>
-      </c>
-      <c r="T22" s="11">
+      <c r="T22" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2656,38 +2739,38 @@
         <v>94</v>
       </c>
       <c r="K23" s="9">
+        <v>0</v>
+      </c>
+      <c r="L23" s="10">
+        <v>0</v>
+      </c>
+      <c r="M23" s="9">
         <f t="shared" si="9"/>
         <v>6700</v>
       </c>
-      <c r="L23" s="9">
+      <c r="N23" s="9">
         <f t="shared" si="10"/>
         <v>6700</v>
       </c>
-      <c r="M23" s="9">
+      <c r="O23" s="9">
         <f t="shared" si="11"/>
         <v>5500</v>
       </c>
-      <c r="N23" s="9">
-        <v>0</v>
-      </c>
-      <c r="O23" s="9">
+      <c r="P23" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="9">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="P23" s="9">
+      <c r="R23" s="9">
         <f t="shared" si="12"/>
         <v>255</v>
       </c>
-      <c r="Q23" s="9">
+      <c r="S23" s="9">
         <v>30</v>
       </c>
-      <c r="R23" s="9">
-        <v>0</v>
-      </c>
-      <c r="S23" s="9">
-        <v>0</v>
-      </c>
-      <c r="T23" s="11">
+      <c r="T23" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2717,38 +2800,38 @@
         <v>98</v>
       </c>
       <c r="K24" s="9">
+        <v>0</v>
+      </c>
+      <c r="L24" s="10">
+        <v>0</v>
+      </c>
+      <c r="M24" s="9">
         <f t="shared" si="9"/>
         <v>7500</v>
       </c>
-      <c r="L24" s="9">
+      <c r="N24" s="9">
         <f t="shared" si="10"/>
         <v>7500</v>
       </c>
-      <c r="M24" s="9">
+      <c r="O24" s="9">
         <f t="shared" si="11"/>
         <v>5900</v>
       </c>
-      <c r="N24" s="9">
-        <v>0</v>
-      </c>
-      <c r="O24" s="9">
+      <c r="P24" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="9">
         <f t="shared" si="3"/>
         <v>56</v>
       </c>
-      <c r="P24" s="9">
+      <c r="R24" s="9">
         <f t="shared" si="12"/>
         <v>285</v>
       </c>
-      <c r="Q24" s="9">
+      <c r="S24" s="9">
         <v>40</v>
       </c>
-      <c r="R24" s="9">
-        <v>0</v>
-      </c>
-      <c r="S24" s="9">
-        <v>0</v>
-      </c>
-      <c r="T24" s="11">
+      <c r="T24" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2778,79 +2861,79 @@
         <v>101</v>
       </c>
       <c r="K25" s="9">
+        <v>0</v>
+      </c>
+      <c r="L25" s="10">
+        <v>0</v>
+      </c>
+      <c r="M25" s="9">
         <f t="shared" si="9"/>
         <v>8300</v>
       </c>
-      <c r="L25" s="9">
+      <c r="N25" s="9">
         <f t="shared" si="10"/>
         <v>8300</v>
       </c>
-      <c r="M25" s="9">
+      <c r="O25" s="9">
         <f t="shared" si="11"/>
         <v>6300</v>
       </c>
-      <c r="N25" s="9">
-        <v>0</v>
-      </c>
-      <c r="O25" s="9">
+      <c r="P25" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="9">
         <f t="shared" si="3"/>
         <v>58</v>
       </c>
-      <c r="P25" s="9">
+      <c r="R25" s="9">
         <f t="shared" si="12"/>
         <v>315</v>
       </c>
-      <c r="Q25" s="9">
+      <c r="S25" s="9">
         <v>50</v>
       </c>
-      <c r="R25" s="9">
-        <v>0</v>
-      </c>
-      <c r="S25" s="9">
-        <v>0</v>
-      </c>
-      <c r="T25" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="8:20">
+      <c r="T25" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="8:16">
       <c r="H26" s="8"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="10"/>
-      <c r="T26" s="11"/>
-    </row>
-    <row r="27" customHeight="1" spans="8:20">
+      <c r="L26" s="10"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="11"/>
+    </row>
+    <row r="27" customHeight="1" spans="8:16">
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
-      <c r="N27" s="9"/>
-      <c r="T27" s="11"/>
-    </row>
-    <row r="28" customHeight="1" spans="8:20">
+      <c r="L27" s="10"/>
+      <c r="P27" s="9"/>
+    </row>
+    <row r="28" customHeight="1" spans="8:16">
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
-      <c r="N28" s="9"/>
-      <c r="T28" s="11"/>
-    </row>
-    <row r="29" customHeight="1" spans="8:20">
+      <c r="L28" s="10"/>
+      <c r="P28" s="9"/>
+    </row>
+    <row r="29" customHeight="1" spans="8:16">
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
-      <c r="N29" s="9"/>
-      <c r="T29" s="11"/>
-    </row>
-    <row r="30" customHeight="1" spans="9:20">
+      <c r="L29" s="10"/>
+      <c r="P29" s="9"/>
+    </row>
+    <row r="30" customHeight="1" spans="9:16">
       <c r="I30" s="8"/>
-      <c r="N30" s="9"/>
-      <c r="T30" s="11"/>
-    </row>
-    <row r="31" customHeight="1" spans="9:20">
+      <c r="L30" s="10"/>
+      <c r="P30" s="9"/>
+    </row>
+    <row r="31" customHeight="1" spans="9:16">
       <c r="I31" s="8"/>
-      <c r="N31" s="9"/>
-      <c r="T31" s="11"/>
-    </row>
-    <row r="32" customHeight="1" spans="9:20">
+      <c r="L31" s="10"/>
+      <c r="P31" s="9"/>
+    </row>
+    <row r="32" customHeight="1" spans="9:16">
       <c r="I32" s="8"/>
-      <c r="N32" s="9"/>
-      <c r="T32" s="11"/>
+      <c r="L32" s="10"/>
+      <c r="P32" s="9"/>
     </row>
     <row r="33" customHeight="1" spans="3:20">
       <c r="C33" s="1">
@@ -2877,38 +2960,35 @@
       <c r="J33" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="K33" s="10">
-        <f t="shared" ref="K33:K42" si="13">K32+1000</f>
-        <v>1000</v>
-      </c>
-      <c r="L33" s="10">
-        <f t="shared" ref="L33:L42" si="14">L32+1000</f>
-        <v>1000</v>
-      </c>
-      <c r="M33" s="10">
-        <f t="shared" ref="M33:M42" si="15">M32+500</f>
-        <v>500</v>
-      </c>
-      <c r="N33" s="9">
+      <c r="K33" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L33" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="M33" s="11">
         <v>10000</v>
       </c>
-      <c r="O33" s="10">
-        <v>1</v>
-      </c>
-      <c r="P33" s="9">
+      <c r="N33" s="11">
+        <v>10000</v>
+      </c>
+      <c r="O33" s="11">
+        <v>10000</v>
+      </c>
+      <c r="P33" s="11">
+        <v>10000</v>
+      </c>
+      <c r="Q33" s="11">
+        <v>0</v>
+      </c>
+      <c r="R33" s="9">
         <v>150</v>
       </c>
-      <c r="Q33" s="9">
-        <v>50</v>
-      </c>
-      <c r="R33" s="9">
-        <v>0</v>
-      </c>
       <c r="S33" s="9">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="T33" s="9">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:20">
@@ -2922,54 +3002,54 @@
         <v>2</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="K34" s="10">
-        <f t="shared" si="13"/>
-        <v>2000</v>
-      </c>
-      <c r="L34" s="10">
-        <f t="shared" si="14"/>
-        <v>2000</v>
-      </c>
-      <c r="M34" s="10">
-        <f t="shared" si="15"/>
-        <v>1000</v>
-      </c>
-      <c r="N34" s="9">
-        <f t="shared" ref="N34:N42" si="16">N33+2000</f>
+        <v>111</v>
+      </c>
+      <c r="K34" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="L34" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="M34" s="11">
+        <f t="shared" ref="M33:M42" si="13">M33+1000</f>
+        <v>11000</v>
+      </c>
+      <c r="N34" s="11">
+        <f t="shared" ref="N33:N42" si="14">N33+1000</f>
+        <v>11000</v>
+      </c>
+      <c r="O34" s="11">
+        <f t="shared" ref="O34:O42" si="15">O33+1500</f>
+        <v>11500</v>
+      </c>
+      <c r="P34" s="9">
+        <f t="shared" ref="P34:P42" si="16">P33+2000</f>
         <v>12000</v>
       </c>
-      <c r="O34" s="10">
-        <v>1</v>
-      </c>
-      <c r="P34" s="9">
-        <f t="shared" ref="P34:P42" si="17">P33+20</f>
+      <c r="Q34" s="11">
+        <v>0</v>
+      </c>
+      <c r="R34" s="9">
+        <f t="shared" ref="R34:R42" si="17">R33+20</f>
         <v>170</v>
       </c>
-      <c r="Q34" s="9">
-        <v>50</v>
-      </c>
-      <c r="R34" s="9">
-        <v>0</v>
-      </c>
       <c r="S34" s="9">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="T34" s="9">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:20">
@@ -2983,54 +3063,54 @@
         <v>3</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H35" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="I35" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="I35" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="J35" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="K35" s="10">
+        <v>115</v>
+      </c>
+      <c r="K35" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="L35" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="M35" s="11">
         <f t="shared" si="13"/>
-        <v>3000</v>
-      </c>
-      <c r="L35" s="10">
+        <v>12000</v>
+      </c>
+      <c r="N35" s="11">
         <f t="shared" si="14"/>
-        <v>3000</v>
-      </c>
-      <c r="M35" s="10">
+        <v>12000</v>
+      </c>
+      <c r="O35" s="11">
         <f t="shared" si="15"/>
-        <v>1500</v>
-      </c>
-      <c r="N35" s="9">
+        <v>13000</v>
+      </c>
+      <c r="P35" s="9">
         <f t="shared" si="16"/>
         <v>14000</v>
       </c>
-      <c r="O35" s="10">
-        <v>1</v>
-      </c>
-      <c r="P35" s="9">
+      <c r="Q35" s="11">
+        <v>0</v>
+      </c>
+      <c r="R35" s="9">
         <f t="shared" si="17"/>
         <v>190</v>
       </c>
-      <c r="Q35" s="9">
-        <v>50</v>
-      </c>
-      <c r="R35" s="9">
-        <v>0</v>
-      </c>
       <c r="S35" s="9">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="T35" s="9">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:20">
@@ -3044,54 +3124,54 @@
         <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="K36" s="10">
+        <v>120</v>
+      </c>
+      <c r="K36" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="L36" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="M36" s="11">
         <f t="shared" si="13"/>
-        <v>4000</v>
-      </c>
-      <c r="L36" s="10">
+        <v>13000</v>
+      </c>
+      <c r="N36" s="11">
         <f t="shared" si="14"/>
-        <v>4000</v>
-      </c>
-      <c r="M36" s="10">
+        <v>13000</v>
+      </c>
+      <c r="O36" s="11">
         <f t="shared" si="15"/>
-        <v>2000</v>
-      </c>
-      <c r="N36" s="9">
+        <v>14500</v>
+      </c>
+      <c r="P36" s="9">
         <f t="shared" si="16"/>
         <v>16000</v>
       </c>
-      <c r="O36" s="10">
-        <v>1</v>
-      </c>
-      <c r="P36" s="9">
+      <c r="Q36" s="11">
+        <v>0</v>
+      </c>
+      <c r="R36" s="9">
         <f t="shared" si="17"/>
         <v>210</v>
       </c>
-      <c r="Q36" s="9">
-        <v>50</v>
-      </c>
-      <c r="R36" s="9">
-        <v>0</v>
-      </c>
       <c r="S36" s="9">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="T36" s="9">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:20">
@@ -3105,54 +3185,54 @@
         <v>5</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="K37" s="10">
+        <v>124</v>
+      </c>
+      <c r="K37" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="L37" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="M37" s="11">
         <f t="shared" si="13"/>
-        <v>5000</v>
-      </c>
-      <c r="L37" s="10">
+        <v>14000</v>
+      </c>
+      <c r="N37" s="11">
         <f t="shared" si="14"/>
-        <v>5000</v>
-      </c>
-      <c r="M37" s="10">
+        <v>14000</v>
+      </c>
+      <c r="O37" s="11">
         <f t="shared" si="15"/>
-        <v>2500</v>
-      </c>
-      <c r="N37" s="9">
+        <v>16000</v>
+      </c>
+      <c r="P37" s="9">
         <f t="shared" si="16"/>
         <v>18000</v>
       </c>
-      <c r="O37" s="10">
-        <v>1</v>
-      </c>
-      <c r="P37" s="9">
+      <c r="Q37" s="11">
+        <v>0</v>
+      </c>
+      <c r="R37" s="9">
         <f t="shared" si="17"/>
         <v>230</v>
       </c>
-      <c r="Q37" s="9">
-        <v>50</v>
-      </c>
-      <c r="R37" s="9">
-        <v>0</v>
-      </c>
       <c r="S37" s="9">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="T37" s="9">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:20">
@@ -3166,54 +3246,54 @@
         <v>6</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="K38" s="10">
+        <v>128</v>
+      </c>
+      <c r="K38" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="L38" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="M38" s="11">
         <f t="shared" si="13"/>
-        <v>6000</v>
-      </c>
-      <c r="L38" s="10">
+        <v>15000</v>
+      </c>
+      <c r="N38" s="11">
         <f t="shared" si="14"/>
-        <v>6000</v>
-      </c>
-      <c r="M38" s="10">
+        <v>15000</v>
+      </c>
+      <c r="O38" s="11">
         <f t="shared" si="15"/>
-        <v>3000</v>
-      </c>
-      <c r="N38" s="9">
+        <v>17500</v>
+      </c>
+      <c r="P38" s="9">
         <f t="shared" si="16"/>
         <v>20000</v>
       </c>
-      <c r="O38" s="10">
-        <v>1</v>
-      </c>
-      <c r="P38" s="9">
-        <f t="shared" ref="P38:P42" si="18">P37+30</f>
-        <v>260</v>
-      </c>
-      <c r="Q38" s="9">
-        <v>50</v>
+      <c r="Q38" s="11">
+        <v>0</v>
       </c>
       <c r="R38" s="9">
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>250</v>
       </c>
       <c r="S38" s="9">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="T38" s="9">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:20">
@@ -3227,54 +3307,54 @@
         <v>7</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="K39" s="10">
+        <v>132</v>
+      </c>
+      <c r="K39" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="M39" s="11">
         <f t="shared" si="13"/>
-        <v>7000</v>
-      </c>
-      <c r="L39" s="10">
+        <v>16000</v>
+      </c>
+      <c r="N39" s="11">
         <f t="shared" si="14"/>
-        <v>7000</v>
-      </c>
-      <c r="M39" s="10">
+        <v>16000</v>
+      </c>
+      <c r="O39" s="11">
         <f t="shared" si="15"/>
-        <v>3500</v>
-      </c>
-      <c r="N39" s="9">
+        <v>19000</v>
+      </c>
+      <c r="P39" s="9">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="O39" s="10">
-        <v>1</v>
-      </c>
-      <c r="P39" s="9">
-        <f t="shared" si="18"/>
-        <v>290</v>
-      </c>
-      <c r="Q39" s="9">
-        <v>50</v>
+      <c r="Q39" s="11">
+        <v>0</v>
       </c>
       <c r="R39" s="9">
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>270</v>
       </c>
       <c r="S39" s="9">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="T39" s="9">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:20">
@@ -3288,54 +3368,54 @@
         <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="K40" s="10">
+        <v>135</v>
+      </c>
+      <c r="K40" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L40" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="M40" s="11">
         <f t="shared" si="13"/>
-        <v>8000</v>
-      </c>
-      <c r="L40" s="10">
+        <v>17000</v>
+      </c>
+      <c r="N40" s="11">
         <f t="shared" si="14"/>
-        <v>8000</v>
-      </c>
-      <c r="M40" s="10">
+        <v>17000</v>
+      </c>
+      <c r="O40" s="11">
         <f t="shared" si="15"/>
-        <v>4000</v>
-      </c>
-      <c r="N40" s="9">
+        <v>20500</v>
+      </c>
+      <c r="P40" s="9">
         <f t="shared" si="16"/>
         <v>24000</v>
       </c>
-      <c r="O40" s="10">
-        <v>1</v>
-      </c>
-      <c r="P40" s="9">
-        <f t="shared" si="18"/>
-        <v>320</v>
-      </c>
-      <c r="Q40" s="9">
-        <v>50</v>
+      <c r="Q40" s="11">
+        <v>0</v>
       </c>
       <c r="R40" s="9">
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>290</v>
       </c>
       <c r="S40" s="9">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="T40" s="9">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:20">
@@ -3349,54 +3429,54 @@
         <v>9</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="K41" s="10">
+        <v>138</v>
+      </c>
+      <c r="K41" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="L41" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="M41" s="11">
         <f t="shared" si="13"/>
-        <v>9000</v>
-      </c>
-      <c r="L41" s="10">
+        <v>18000</v>
+      </c>
+      <c r="N41" s="11">
         <f t="shared" si="14"/>
-        <v>9000</v>
-      </c>
-      <c r="M41" s="10">
+        <v>18000</v>
+      </c>
+      <c r="O41" s="11">
         <f t="shared" si="15"/>
-        <v>4500</v>
-      </c>
-      <c r="N41" s="9">
+        <v>22000</v>
+      </c>
+      <c r="P41" s="9">
         <f t="shared" si="16"/>
         <v>26000</v>
       </c>
-      <c r="O41" s="10">
-        <v>1</v>
-      </c>
-      <c r="P41" s="9">
-        <f t="shared" si="18"/>
-        <v>350</v>
-      </c>
-      <c r="Q41" s="9">
-        <v>50</v>
+      <c r="Q41" s="11">
+        <v>0</v>
       </c>
       <c r="R41" s="9">
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>310</v>
       </c>
       <c r="S41" s="9">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="T41" s="9">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:20">
@@ -3410,71 +3490,76 @@
         <v>10</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="K42" s="10">
+        <v>141</v>
+      </c>
+      <c r="K42" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="L42" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="M42" s="11">
         <f t="shared" si="13"/>
-        <v>10000</v>
-      </c>
-      <c r="L42" s="10">
+        <v>19000</v>
+      </c>
+      <c r="N42" s="11">
         <f t="shared" si="14"/>
-        <v>10000</v>
-      </c>
-      <c r="M42" s="10">
+        <v>19000</v>
+      </c>
+      <c r="O42" s="11">
         <f t="shared" si="15"/>
-        <v>5000</v>
-      </c>
-      <c r="N42" s="9">
+        <v>23500</v>
+      </c>
+      <c r="P42" s="9">
         <f t="shared" si="16"/>
         <v>28000</v>
       </c>
-      <c r="O42" s="10">
-        <v>1</v>
-      </c>
-      <c r="P42" s="9">
-        <f t="shared" si="18"/>
-        <v>380</v>
-      </c>
-      <c r="Q42" s="9">
-        <v>50</v>
+      <c r="Q42" s="11">
+        <v>0</v>
       </c>
       <c r="R42" s="9">
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>330</v>
       </c>
       <c r="S42" s="9">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="T42" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="14:20">
-      <c r="N43" s="9"/>
-      <c r="T43" s="9"/>
-    </row>
-    <row r="44" customHeight="1" spans="14:20">
-      <c r="N44" s="9"/>
-      <c r="T44" s="9"/>
-    </row>
-    <row r="45" customHeight="1" spans="14:20">
-      <c r="N45" s="9"/>
-      <c r="T45" s="9"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="12:16">
+      <c r="L43" s="9"/>
+      <c r="P43" s="9"/>
+    </row>
+    <row r="44" customHeight="1" spans="12:16">
+      <c r="L44" s="9"/>
+      <c r="P44" s="9"/>
+    </row>
+    <row r="45" customHeight="1" spans="12:16">
+      <c r="L45" s="9"/>
+      <c r="P45" s="9"/>
+    </row>
+    <row r="53" customHeight="1" spans="8:8">
+      <c r="H53" s="8">
+        <v>9e+27</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 R3 S3 D4 E4 R4 S4 D5 E5 N5 R5 S5 C3:C5 N3:N4 T3:T5 F3:M5 O3:Q5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:E3 K3 T3 C3:C5 K4:K5 L3:L5 T4:T5 F3:J5 D4:E5 M3:S5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterPillConfig.xlsx
+++ b/Excel/MonsterPillConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="138">
   <si>
     <t>ID</t>
   </si>
@@ -80,6 +80,9 @@
     <t>Miss</t>
   </si>
   <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
     <t>Protect</t>
   </si>
   <si>
@@ -353,9 +356,6 @@
     <t>9E+80</t>
   </si>
   <si>
-    <t>1E+5</t>
-  </si>
-  <si>
     <t>1E+20</t>
   </si>
   <si>
@@ -368,9 +368,6 @@
     <t>9E+85</t>
   </si>
   <si>
-    <t>1E+6</t>
-  </si>
-  <si>
     <t>练气三层</t>
   </si>
   <si>
@@ -380,9 +377,6 @@
     <t>9E+90</t>
   </si>
   <si>
-    <t>1E+7</t>
-  </si>
-  <si>
     <t>1E+30</t>
   </si>
   <si>
@@ -395,9 +389,6 @@
     <t>9E+95</t>
   </si>
   <si>
-    <t>1E+9</t>
-  </si>
-  <si>
     <t>练气五层</t>
   </si>
   <si>
@@ -407,9 +398,6 @@
     <t>9E+100</t>
   </si>
   <si>
-    <t>1E+11</t>
-  </si>
-  <si>
     <t>1E+40</t>
   </si>
   <si>
@@ -417,9 +405,6 @@
   </si>
   <si>
     <t>9E+105</t>
-  </si>
-  <si>
-    <t>1E+13</t>
   </si>
   <si>
     <t>1E+45</t>
@@ -1451,7 +1436,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T53"/>
+  <dimension ref="A1:U53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.12389380530973" style="2" customWidth="1"/>
@@ -1468,12 +1453,13 @@
     <col min="14" max="15" width="12.5044247787611" style="2" customWidth="1"/>
     <col min="16" max="16" width="8" style="2" customWidth="1"/>
     <col min="17" max="17" width="12.5044247787611" style="2" customWidth="1"/>
-    <col min="18" max="18" width="14.1238938053097" style="2" customWidth="1"/>
-    <col min="19" max="20" width="9.6283185840708" style="2" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="2"/>
+    <col min="18" max="18" width="11.0176991150442" style="2" customWidth="1"/>
+    <col min="19" max="19" width="10.4247787610619" style="2" customWidth="1"/>
+    <col min="20" max="21" width="9.6283185840708" style="2" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:20">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="H1" s="5"/>
@@ -1489,8 +1475,9 @@
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:20">
+      <c r="U1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="H2" s="5"/>
@@ -1506,8 +1493,9 @@
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:20">
+      <c r="U2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="6" t="s">
@@ -1564,12 +1552,15 @@
       <c r="T3" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:20">
+      <c r="U3" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1</v>
@@ -1622,66 +1613,72 @@
       <c r="T4" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:20">
+      <c r="U4" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="O5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="P5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="Q5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="6" t="s">
+      <c r="R5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>19</v>
-      </c>
       <c r="S5" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T5" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:20">
+        <v>20</v>
+      </c>
+      <c r="U5" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:21">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1692,19 +1689,19 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K6" s="9">
         <v>0</v>
@@ -1736,8 +1733,11 @@
       <c r="T6" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:20">
+      <c r="U6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:21">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1748,19 +1748,19 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K7" s="9">
         <v>0</v>
@@ -1797,8 +1797,11 @@
       <c r="T7" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:20">
+      <c r="U7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:21">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1809,19 +1812,19 @@
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K8" s="9">
         <v>0</v>
@@ -1858,8 +1861,11 @@
       <c r="T8" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:20">
+      <c r="U8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:21">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1870,19 +1876,19 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K9" s="9">
         <v>0</v>
@@ -1919,8 +1925,11 @@
       <c r="T9" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:20">
+      <c r="U9" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:21">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1931,19 +1940,19 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K10" s="9">
         <v>0</v>
@@ -1980,8 +1989,11 @@
       <c r="T10" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:20">
+      <c r="U10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:21">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1992,19 +2004,19 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K11" s="9">
         <v>0</v>
@@ -2041,8 +2053,11 @@
       <c r="T11" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:20">
+      <c r="U11" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:21">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -2053,19 +2068,19 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K12" s="9">
         <v>0</v>
@@ -2102,8 +2117,11 @@
       <c r="T12" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:20">
+      <c r="U12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:21">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -2114,19 +2132,19 @@
         <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K13" s="9">
         <v>0</v>
@@ -2163,8 +2181,11 @@
       <c r="T13" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:20">
+      <c r="U13" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:21">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -2175,19 +2196,19 @@
         <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K14" s="9">
         <v>0</v>
@@ -2224,8 +2245,11 @@
       <c r="T14" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:20">
+      <c r="U14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:21">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -2236,19 +2260,19 @@
         <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K15" s="9">
         <v>0</v>
@@ -2285,8 +2309,11 @@
       <c r="T15" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:20">
+      <c r="U15" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:21">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -2297,19 +2324,19 @@
         <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K16" s="9">
         <v>0</v>
@@ -2346,8 +2373,11 @@
       <c r="T16" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:20">
+      <c r="U16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:21">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -2358,19 +2388,19 @@
         <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K17" s="9">
         <v>0</v>
@@ -2407,8 +2437,11 @@
       <c r="T17" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:20">
+      <c r="U17" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:21">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -2419,19 +2452,19 @@
         <v>13</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K18" s="9">
         <v>0</v>
@@ -2468,8 +2501,11 @@
       <c r="T18" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:20">
+      <c r="U18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:21">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -2480,19 +2516,19 @@
         <v>14</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K19" s="9">
         <v>0</v>
@@ -2529,8 +2565,11 @@
       <c r="T19" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:20">
+      <c r="U19" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:21">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -2541,19 +2580,19 @@
         <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K20" s="9">
         <v>0</v>
@@ -2590,8 +2629,11 @@
       <c r="T20" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:20">
+      <c r="U20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:21">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -2602,19 +2644,19 @@
         <v>16</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K21" s="9">
         <v>0</v>
@@ -2646,13 +2688,16 @@
         <v>195</v>
       </c>
       <c r="S21" s="9">
+        <v>0</v>
+      </c>
+      <c r="T21" s="9">
         <v>10</v>
       </c>
-      <c r="T21" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:20">
+      <c r="U21" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:21">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -2663,19 +2708,19 @@
         <v>17</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K22" s="9">
         <v>0</v>
@@ -2707,13 +2752,16 @@
         <v>225</v>
       </c>
       <c r="S22" s="9">
+        <v>0</v>
+      </c>
+      <c r="T22" s="9">
         <v>20</v>
       </c>
-      <c r="T22" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:20">
+      <c r="U22" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:21">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -2724,19 +2772,19 @@
         <v>18</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K23" s="9">
         <v>0</v>
@@ -2768,13 +2816,16 @@
         <v>255</v>
       </c>
       <c r="S23" s="9">
+        <v>0</v>
+      </c>
+      <c r="T23" s="9">
         <v>30</v>
       </c>
-      <c r="T23" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:20">
+      <c r="U23" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:21">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -2785,19 +2836,19 @@
         <v>19</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K24" s="9">
         <v>0</v>
@@ -2829,13 +2880,16 @@
         <v>285</v>
       </c>
       <c r="S24" s="9">
+        <v>0</v>
+      </c>
+      <c r="T24" s="9">
         <v>40</v>
       </c>
-      <c r="T24" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:20">
+      <c r="U24" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:21">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -2846,19 +2900,19 @@
         <v>20</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K25" s="9">
         <v>0</v>
@@ -2890,9 +2944,12 @@
         <v>315</v>
       </c>
       <c r="S25" s="9">
+        <v>0</v>
+      </c>
+      <c r="T25" s="9">
         <v>50</v>
       </c>
-      <c r="T25" s="9">
+      <c r="U25" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2935,7 +2992,7 @@
       <c r="L32" s="10"/>
       <c r="P32" s="9"/>
     </row>
-    <row r="33" customHeight="1" spans="3:20">
+    <row r="33" customHeight="1" spans="3:21">
       <c r="C33" s="1">
         <v>101</v>
       </c>
@@ -2946,22 +3003,22 @@
         <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>108</v>
@@ -2979,19 +3036,20 @@
         <v>10000</v>
       </c>
       <c r="Q33" s="11">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="R33" s="9">
         <v>150</v>
       </c>
-      <c r="S33" s="9">
+      <c r="S33" s="9"/>
+      <c r="T33" s="9">
         <v>99</v>
       </c>
-      <c r="T33" s="9">
+      <c r="U33" s="9">
         <v>200</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="3:20">
+    <row r="34" customHeight="1" spans="3:21">
       <c r="C34" s="1">
         <v>102</v>
       </c>
@@ -3005,10 +3063,10 @@
         <v>109</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I34" s="12" t="s">
         <v>110</v>
@@ -3017,10 +3075,10 @@
         <v>111</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="L34" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M34" s="11">
         <f t="shared" ref="M33:M42" si="13">M33+1000</f>
@@ -3038,21 +3096,23 @@
         <f t="shared" ref="P34:P42" si="16">P33+2000</f>
         <v>12000</v>
       </c>
-      <c r="Q34" s="11">
-        <v>0</v>
+      <c r="Q34" s="9">
+        <f t="shared" ref="Q34:Q42" si="17">Q33+20</f>
+        <v>170</v>
       </c>
       <c r="R34" s="9">
-        <f t="shared" ref="R34:R42" si="17">R33+20</f>
+        <f t="shared" ref="R34:R42" si="18">R33+20</f>
         <v>170</v>
       </c>
-      <c r="S34" s="9">
+      <c r="S34" s="9"/>
+      <c r="T34" s="9">
         <v>99</v>
       </c>
-      <c r="T34" s="9">
+      <c r="U34" s="9">
         <v>200</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="3:20">
+    <row r="35" customHeight="1" spans="3:21">
       <c r="C35" s="1">
         <v>103</v>
       </c>
@@ -3063,25 +3123,25 @@
         <v>3</v>
       </c>
       <c r="F35" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H35" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H35" s="12" t="s">
+      <c r="I35" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J35" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="I35" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="J35" s="12" t="s">
+      <c r="K35" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="K35" s="13" t="s">
-        <v>116</v>
-      </c>
       <c r="L35" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M35" s="11">
         <f t="shared" si="13"/>
@@ -3099,21 +3159,23 @@
         <f t="shared" si="16"/>
         <v>14000</v>
       </c>
-      <c r="Q35" s="11">
-        <v>0</v>
-      </c>
-      <c r="R35" s="9">
+      <c r="Q35" s="9">
         <f t="shared" si="17"/>
         <v>190</v>
       </c>
-      <c r="S35" s="9">
+      <c r="R35" s="9">
+        <f t="shared" si="18"/>
+        <v>190</v>
+      </c>
+      <c r="S35" s="9"/>
+      <c r="T35" s="9">
         <v>99</v>
       </c>
-      <c r="T35" s="9">
+      <c r="U35" s="9">
         <v>200</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="3:20">
+    <row r="36" customHeight="1" spans="3:21">
       <c r="C36" s="1">
         <v>104</v>
       </c>
@@ -3124,25 +3186,25 @@
         <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="J36" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H36" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="I36" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>120</v>
-      </c>
       <c r="K36" s="13" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="L36" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M36" s="11">
         <f t="shared" si="13"/>
@@ -3160,21 +3222,23 @@
         <f t="shared" si="16"/>
         <v>16000</v>
       </c>
-      <c r="Q36" s="11">
-        <v>0</v>
-      </c>
-      <c r="R36" s="9">
+      <c r="Q36" s="9">
         <f t="shared" si="17"/>
         <v>210</v>
       </c>
-      <c r="S36" s="9">
+      <c r="R36" s="9">
+        <f t="shared" si="18"/>
+        <v>210</v>
+      </c>
+      <c r="S36" s="9"/>
+      <c r="T36" s="9">
         <v>99</v>
       </c>
-      <c r="T36" s="9">
+      <c r="U36" s="9">
         <v>200</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="3:20">
+    <row r="37" customHeight="1" spans="3:21">
       <c r="C37" s="1">
         <v>105</v>
       </c>
@@ -3185,25 +3249,25 @@
         <v>5</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="K37" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="K37" s="13" t="s">
-        <v>125</v>
-      </c>
       <c r="L37" s="13" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M37" s="11">
         <f t="shared" si="13"/>
@@ -3221,21 +3285,23 @@
         <f t="shared" si="16"/>
         <v>18000</v>
       </c>
-      <c r="Q37" s="11">
-        <v>0</v>
-      </c>
-      <c r="R37" s="9">
+      <c r="Q37" s="9">
         <f t="shared" si="17"/>
         <v>230</v>
       </c>
-      <c r="S37" s="9">
+      <c r="R37" s="9">
+        <f t="shared" si="18"/>
+        <v>230</v>
+      </c>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9">
         <v>99</v>
       </c>
-      <c r="T37" s="9">
+      <c r="U37" s="9">
         <v>200</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="3:20">
+    <row r="38" customHeight="1" spans="3:21">
       <c r="C38" s="1">
         <v>106</v>
       </c>
@@ -3246,25 +3312,25 @@
         <v>6</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="L38" s="13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="M38" s="11">
         <f t="shared" si="13"/>
@@ -3282,21 +3348,23 @@
         <f t="shared" si="16"/>
         <v>20000</v>
       </c>
-      <c r="Q38" s="11">
-        <v>0</v>
-      </c>
-      <c r="R38" s="9">
+      <c r="Q38" s="9">
         <f t="shared" si="17"/>
         <v>250</v>
       </c>
-      <c r="S38" s="9">
+      <c r="R38" s="9">
+        <f t="shared" si="18"/>
+        <v>250</v>
+      </c>
+      <c r="S38" s="9"/>
+      <c r="T38" s="9">
         <v>99</v>
       </c>
-      <c r="T38" s="9">
+      <c r="U38" s="9">
         <v>200</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="3:20">
+    <row r="39" customHeight="1" spans="3:21">
       <c r="C39" s="1">
         <v>107</v>
       </c>
@@ -3307,25 +3375,25 @@
         <v>7</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="K39" s="13" t="s">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="L39" s="13" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="M39" s="11">
         <f t="shared" si="13"/>
@@ -3343,21 +3411,23 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="Q39" s="11">
-        <v>0</v>
-      </c>
-      <c r="R39" s="9">
+      <c r="Q39" s="9">
         <f t="shared" si="17"/>
         <v>270</v>
       </c>
-      <c r="S39" s="9">
+      <c r="R39" s="9">
+        <f t="shared" si="18"/>
+        <v>270</v>
+      </c>
+      <c r="S39" s="9"/>
+      <c r="T39" s="9">
         <v>99</v>
       </c>
-      <c r="T39" s="9">
+      <c r="U39" s="9">
         <v>200</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="3:20">
+    <row r="40" customHeight="1" spans="3:21">
       <c r="C40" s="1">
         <v>108</v>
       </c>
@@ -3368,25 +3438,25 @@
         <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>111</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K40" s="13" t="s">
-        <v>28</v>
+        <v>131</v>
       </c>
       <c r="L40" s="13" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="M40" s="11">
         <f t="shared" si="13"/>
@@ -3404,21 +3474,23 @@
         <f t="shared" si="16"/>
         <v>24000</v>
       </c>
-      <c r="Q40" s="11">
-        <v>0</v>
-      </c>
-      <c r="R40" s="9">
+      <c r="Q40" s="9">
         <f t="shared" si="17"/>
         <v>290</v>
       </c>
-      <c r="S40" s="9">
+      <c r="R40" s="9">
+        <f t="shared" si="18"/>
+        <v>290</v>
+      </c>
+      <c r="S40" s="9"/>
+      <c r="T40" s="9">
         <v>99</v>
       </c>
-      <c r="T40" s="9">
+      <c r="U40" s="9">
         <v>200</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="3:20">
+    <row r="41" customHeight="1" spans="3:21">
       <c r="C41" s="1">
         <v>109</v>
       </c>
@@ -3429,25 +3501,25 @@
         <v>9</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="K41" s="13" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="L41" s="13" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="M41" s="11">
         <f t="shared" si="13"/>
@@ -3465,21 +3537,23 @@
         <f t="shared" si="16"/>
         <v>26000</v>
       </c>
-      <c r="Q41" s="11">
-        <v>0</v>
-      </c>
-      <c r="R41" s="9">
+      <c r="Q41" s="9">
         <f t="shared" si="17"/>
         <v>310</v>
       </c>
-      <c r="S41" s="9">
+      <c r="R41" s="9">
+        <f t="shared" si="18"/>
+        <v>310</v>
+      </c>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9">
         <v>99</v>
       </c>
-      <c r="T41" s="9">
+      <c r="U41" s="9">
         <v>200</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="3:20">
+    <row r="42" customHeight="1" spans="3:21">
       <c r="C42" s="1">
         <v>110</v>
       </c>
@@ -3490,25 +3564,25 @@
         <v>10</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I42" s="12" t="s">
         <v>111</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="K42" s="13" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="L42" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M42" s="11">
         <f t="shared" si="13"/>
@@ -3526,17 +3600,19 @@
         <f t="shared" si="16"/>
         <v>28000</v>
       </c>
-      <c r="Q42" s="11">
-        <v>0</v>
-      </c>
-      <c r="R42" s="9">
+      <c r="Q42" s="9">
         <f t="shared" si="17"/>
         <v>330</v>
       </c>
-      <c r="S42" s="9">
+      <c r="R42" s="9">
+        <f t="shared" si="18"/>
+        <v>330</v>
+      </c>
+      <c r="S42" s="9"/>
+      <c r="T42" s="9">
         <v>99</v>
       </c>
-      <c r="T42" s="9">
+      <c r="U42" s="9">
         <v>200</v>
       </c>
     </row>
@@ -3559,7 +3635,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:E3 K3 T3 C3:C5 K4:K5 L3:L5 T4:T5 F3:J5 D4:E5 M3:S5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:U5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterPillConfig.xlsx
+++ b/Excel/MonsterPillConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="151">
   <si>
     <t>ID</t>
   </si>
@@ -89,6 +89,9 @@
     <t>Speed</t>
   </si>
   <si>
+    <t>SkillIdList</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -101,6 +104,9 @@
     <t>double</t>
   </si>
   <si>
+    <t>int[]</t>
+  </si>
+  <si>
     <t>炼体一层</t>
   </si>
   <si>
@@ -116,6 +122,9 @@
     <t>9E+23</t>
   </si>
   <si>
+    <t>1002,3001,1008</t>
+  </si>
+  <si>
     <t>炼体二层</t>
   </si>
   <si>
@@ -128,6 +137,9 @@
     <t>9E+27</t>
   </si>
   <si>
+    <t>1001,1004,1007</t>
+  </si>
+  <si>
     <t>炼体三层</t>
   </si>
   <si>
@@ -140,6 +152,9 @@
     <t>9E+31</t>
   </si>
   <si>
+    <t>2002,2007,2008,2009</t>
+  </si>
+  <si>
     <t>炼体四层</t>
   </si>
   <si>
@@ -152,6 +167,9 @@
     <t>9E+35</t>
   </si>
   <si>
+    <t>1002,2009,2007,1009</t>
+  </si>
+  <si>
     <t>炼体五层</t>
   </si>
   <si>
@@ -164,6 +182,9 @@
     <t>9E+39</t>
   </si>
   <si>
+    <t>1004,2009,2007,2002,1001</t>
+  </si>
+  <si>
     <t>炼体六层</t>
   </si>
   <si>
@@ -359,6 +380,9 @@
     <t>1E+20</t>
   </si>
   <si>
+    <t>1004,2002,2003,2007,2009</t>
+  </si>
+  <si>
     <t>练气二层</t>
   </si>
   <si>
@@ -380,6 +404,9 @@
     <t>1E+30</t>
   </si>
   <si>
+    <t>1E+26</t>
+  </si>
+  <si>
     <t>练气四层</t>
   </si>
   <si>
@@ -401,6 +428,9 @@
     <t>1E+40</t>
   </si>
   <si>
+    <t>1E+32</t>
+  </si>
+  <si>
     <t>练气六层</t>
   </si>
   <si>
@@ -419,6 +449,9 @@
     <t>1E+50</t>
   </si>
   <si>
+    <t>1E+38</t>
+  </si>
+  <si>
     <t>练气八层</t>
   </si>
   <si>
@@ -437,6 +470,9 @@
     <t>1E+60</t>
   </si>
   <si>
+    <t>1E+44</t>
+  </si>
+  <si>
     <t>练气十层</t>
   </si>
   <si>
@@ -444,6 +480,9 @@
   </si>
   <si>
     <t>1E+65</t>
+  </si>
+  <si>
+    <t>1E+47</t>
   </si>
 </sst>
 </file>
@@ -1088,7 +1127,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1113,10 +1152,16 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1436,7 +1481,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U53"/>
+  <dimension ref="A1:V53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.12389380530973" style="2" customWidth="1"/>
@@ -1456,10 +1501,11 @@
     <col min="18" max="18" width="11.0176991150442" style="2" customWidth="1"/>
     <col min="19" max="19" width="10.4247787610619" style="2" customWidth="1"/>
     <col min="20" max="21" width="9.6283185840708" style="2" customWidth="1"/>
+    <col min="22" max="22" width="28.4867256637168" style="2" customWidth="1"/>
     <col min="24" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:21">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="H1" s="5"/>
@@ -1476,8 +1522,9 @@
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:21">
+      <c r="V1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="H2" s="5"/>
@@ -1494,8 +1541,9 @@
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:21">
+      <c r="V2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="6" t="s">
@@ -1555,12 +1603,15 @@
       <c r="U3" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:21">
+      <c r="V3" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1</v>
@@ -1616,69 +1667,75 @@
       <c r="U4" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:21">
+      <c r="V4" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="O5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="P5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="Q5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="R5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="S5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>20</v>
-      </c>
       <c r="T5" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U5" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:21">
+        <v>23</v>
+      </c>
+      <c r="V5" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:22">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1689,19 +1746,19 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="H6" s="15" t="s">
         <v>27</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>29</v>
       </c>
       <c r="K6" s="9">
         <v>0</v>
@@ -1736,8 +1793,11 @@
       <c r="U6" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:21">
+      <c r="V6" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:22">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1748,19 +1808,19 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>31</v>
+        <v>26</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>34</v>
       </c>
       <c r="K7" s="9">
         <v>0</v>
@@ -1800,8 +1860,11 @@
       <c r="U7" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:21">
+      <c r="V7" s="16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:22">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1812,19 +1875,19 @@
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>35</v>
+        <v>26</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>39</v>
       </c>
       <c r="K8" s="9">
         <v>0</v>
@@ -1864,8 +1927,11 @@
       <c r="U8" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:21">
+      <c r="V8" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:22">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1876,19 +1942,19 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>39</v>
+        <v>26</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>44</v>
       </c>
       <c r="K9" s="9">
         <v>0</v>
@@ -1928,8 +1994,11 @@
       <c r="U9" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:21">
+      <c r="V9" s="16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:22">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1940,19 +2009,19 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>43</v>
+        <v>26</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>49</v>
       </c>
       <c r="K10" s="9">
         <v>0</v>
@@ -1992,8 +2061,11 @@
       <c r="U10" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:21">
+      <c r="V10" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:22">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -2004,19 +2076,19 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>47</v>
+        <v>26</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>54</v>
       </c>
       <c r="K11" s="9">
         <v>0</v>
@@ -2056,8 +2128,9 @@
       <c r="U11" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:21">
+      <c r="V11" s="13"/>
+    </row>
+    <row r="12" customHeight="1" spans="3:22">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -2068,19 +2141,19 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>51</v>
+        <v>26</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="K12" s="9">
         <v>0</v>
@@ -2120,8 +2193,11 @@
       <c r="U12" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:21">
+      <c r="V12" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:22">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -2132,19 +2208,19 @@
         <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>55</v>
+        <v>26</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>62</v>
       </c>
       <c r="K13" s="9">
         <v>0</v>
@@ -2184,8 +2260,11 @@
       <c r="U13" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:21">
+      <c r="V13" s="16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:22">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -2196,19 +2275,19 @@
         <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>59</v>
+        <v>26</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="K14" s="9">
         <v>0</v>
@@ -2248,6 +2327,9 @@
       <c r="U14" s="9">
         <v>0</v>
       </c>
+      <c r="V14" s="16" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="15" customHeight="1" spans="3:21">
       <c r="C15" s="1">
@@ -2260,19 +2342,19 @@
         <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>63</v>
+        <v>26</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>70</v>
       </c>
       <c r="K15" s="9">
         <v>0</v>
@@ -2324,19 +2406,19 @@
         <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>67</v>
+        <v>26</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>74</v>
       </c>
       <c r="K16" s="9">
         <v>0</v>
@@ -2388,19 +2470,19 @@
         <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>71</v>
+        <v>26</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="K17" s="9">
         <v>0</v>
@@ -2452,19 +2534,19 @@
         <v>13</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>75</v>
+        <v>26</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>82</v>
       </c>
       <c r="K18" s="9">
         <v>0</v>
@@ -2516,19 +2598,19 @@
         <v>14</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>79</v>
+        <v>26</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>86</v>
       </c>
       <c r="K19" s="9">
         <v>0</v>
@@ -2580,19 +2662,19 @@
         <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="K20" s="9">
         <v>0</v>
@@ -2644,19 +2726,19 @@
         <v>16</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="K21" s="9">
         <v>0</v>
@@ -2684,8 +2766,8 @@
         <v>50</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" ref="R21:R25" si="12">R20+30</f>
-        <v>195</v>
+        <f t="shared" ref="R21:R25" si="12">R20+25</f>
+        <v>190</v>
       </c>
       <c r="S21" s="9">
         <v>0</v>
@@ -2708,19 +2790,19 @@
         <v>17</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K22" s="9">
         <v>0</v>
@@ -2749,7 +2831,7 @@
       </c>
       <c r="R22" s="9">
         <f t="shared" si="12"/>
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="S22" s="9">
         <v>0</v>
@@ -2772,19 +2854,19 @@
         <v>18</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="K23" s="9">
         <v>0</v>
@@ -2813,7 +2895,7 @@
       </c>
       <c r="R23" s="9">
         <f t="shared" si="12"/>
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="S23" s="9">
         <v>0</v>
@@ -2836,19 +2918,19 @@
         <v>19</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K24" s="9">
         <v>0</v>
@@ -2877,7 +2959,7 @@
       </c>
       <c r="R24" s="9">
         <f t="shared" si="12"/>
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="S24" s="9">
         <v>0</v>
@@ -2900,19 +2982,19 @@
         <v>20</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K25" s="9">
         <v>0</v>
@@ -2941,7 +3023,7 @@
       </c>
       <c r="R25" s="9">
         <f t="shared" si="12"/>
-        <v>315</v>
+        <v>290</v>
       </c>
       <c r="S25" s="9">
         <v>0</v>
@@ -2992,7 +3074,7 @@
       <c r="L32" s="10"/>
       <c r="P32" s="9"/>
     </row>
-    <row r="33" customHeight="1" spans="3:21">
+    <row r="33" customHeight="1" spans="3:22">
       <c r="C33" s="1">
         <v>101</v>
       </c>
@@ -3003,25 +3085,25 @@
         <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H33" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="I33" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="J33" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L33" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>115</v>
       </c>
       <c r="M33" s="11">
         <v>10000</v>
@@ -3046,10 +3128,13 @@
         <v>99</v>
       </c>
       <c r="U33" s="9">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:21">
+        <v>100</v>
+      </c>
+      <c r="V33" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:22">
       <c r="C34" s="1">
         <v>102</v>
       </c>
@@ -3060,25 +3145,25 @@
         <v>2</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H34" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="I34" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="J34" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="K34" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="L34" s="13" t="s">
-        <v>45</v>
+      <c r="H34" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="I34" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>47</v>
       </c>
       <c r="M34" s="11">
         <f t="shared" ref="M33:M42" si="13">M33+1000</f>
@@ -3089,8 +3174,8 @@
         <v>11000</v>
       </c>
       <c r="O34" s="11">
-        <f t="shared" ref="O34:O42" si="15">O33+1500</f>
-        <v>11500</v>
+        <f t="shared" ref="O34:O42" si="15">O33+2000</f>
+        <v>12000</v>
       </c>
       <c r="P34" s="9">
         <f t="shared" ref="P34:P42" si="16">P33+2000</f>
@@ -3101,18 +3186,21 @@
         <v>170</v>
       </c>
       <c r="R34" s="9">
-        <f t="shared" ref="R34:R42" si="18">R33+20</f>
-        <v>170</v>
+        <f t="shared" ref="R34:R42" si="18">R33+30</f>
+        <v>180</v>
       </c>
       <c r="S34" s="9"/>
       <c r="T34" s="9">
         <v>99</v>
       </c>
       <c r="U34" s="9">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:21">
+        <v>100</v>
+      </c>
+      <c r="V34" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:22">
       <c r="C35" s="1">
         <v>103</v>
       </c>
@@ -3123,25 +3211,25 @@
         <v>3</v>
       </c>
       <c r="F35" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="I35" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H35" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="I35" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="J35" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="K35" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="L35" s="13" t="s">
-        <v>115</v>
+      <c r="J35" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>124</v>
       </c>
       <c r="M35" s="11">
         <f t="shared" si="13"/>
@@ -3153,7 +3241,7 @@
       </c>
       <c r="O35" s="11">
         <f t="shared" si="15"/>
-        <v>13000</v>
+        <v>14000</v>
       </c>
       <c r="P35" s="9">
         <f t="shared" si="16"/>
@@ -3165,17 +3253,20 @@
       </c>
       <c r="R35" s="9">
         <f t="shared" si="18"/>
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="S35" s="9"/>
       <c r="T35" s="9">
         <v>99</v>
       </c>
       <c r="U35" s="9">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:21">
+        <v>100</v>
+      </c>
+      <c r="V35" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:22">
       <c r="C36" s="1">
         <v>104</v>
       </c>
@@ -3186,25 +3277,25 @@
         <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H36" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="I36" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="K36" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="L36" s="13" t="s">
-        <v>65</v>
+        <v>111</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J36" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="M36" s="11">
         <f t="shared" si="13"/>
@@ -3216,7 +3307,7 @@
       </c>
       <c r="O36" s="11">
         <f t="shared" si="15"/>
-        <v>14500</v>
+        <v>16000</v>
       </c>
       <c r="P36" s="9">
         <f t="shared" si="16"/>
@@ -3228,17 +3319,20 @@
       </c>
       <c r="R36" s="9">
         <f t="shared" si="18"/>
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="S36" s="9"/>
       <c r="T36" s="9">
         <v>99</v>
       </c>
       <c r="U36" s="9">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:21">
+        <v>100</v>
+      </c>
+      <c r="V36" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:22">
       <c r="C37" s="1">
         <v>105</v>
       </c>
@@ -3249,25 +3343,25 @@
         <v>5</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="J37" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="I37" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="K37" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="L37" s="13" t="s">
-        <v>122</v>
+      <c r="J37" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>132</v>
       </c>
       <c r="M37" s="11">
         <f t="shared" si="13"/>
@@ -3279,7 +3373,7 @@
       </c>
       <c r="O37" s="11">
         <f t="shared" si="15"/>
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="P37" s="9">
         <f t="shared" si="16"/>
@@ -3291,17 +3385,20 @@
       </c>
       <c r="R37" s="9">
         <f t="shared" si="18"/>
-        <v>230</v>
+        <v>270</v>
       </c>
       <c r="S37" s="9"/>
       <c r="T37" s="9">
         <v>99</v>
       </c>
       <c r="U37" s="9">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:21">
+        <v>100</v>
+      </c>
+      <c r="V37" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:22">
       <c r="C38" s="1">
         <v>106</v>
       </c>
@@ -3312,25 +3409,25 @@
         <v>6</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H38" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="I38" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="K38" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="L38" s="13" t="s">
-        <v>125</v>
+        <v>111</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="J38" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="M38" s="11">
         <f t="shared" si="13"/>
@@ -3342,7 +3439,7 @@
       </c>
       <c r="O38" s="11">
         <f t="shared" si="15"/>
-        <v>17500</v>
+        <v>20000</v>
       </c>
       <c r="P38" s="9">
         <f t="shared" si="16"/>
@@ -3354,17 +3451,20 @@
       </c>
       <c r="R38" s="9">
         <f t="shared" si="18"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="S38" s="9"/>
       <c r="T38" s="9">
         <v>99</v>
       </c>
       <c r="U38" s="9">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:21">
+        <v>100</v>
+      </c>
+      <c r="V38" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:22">
       <c r="C39" s="1">
         <v>107</v>
       </c>
@@ -3375,25 +3475,25 @@
         <v>7</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H39" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="I39" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="J39" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="K39" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="L39" s="13" t="s">
-        <v>128</v>
+        <v>111</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="I39" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="J39" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>139</v>
       </c>
       <c r="M39" s="11">
         <f t="shared" si="13"/>
@@ -3405,7 +3505,7 @@
       </c>
       <c r="O39" s="11">
         <f t="shared" si="15"/>
-        <v>19000</v>
+        <v>22000</v>
       </c>
       <c r="P39" s="9">
         <f t="shared" si="16"/>
@@ -3417,17 +3517,20 @@
       </c>
       <c r="R39" s="9">
         <f t="shared" si="18"/>
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="S39" s="9"/>
       <c r="T39" s="9">
         <v>99</v>
       </c>
       <c r="U39" s="9">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:21">
+        <v>100</v>
+      </c>
+      <c r="V39" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:22">
       <c r="C40" s="1">
         <v>108</v>
       </c>
@@ -3438,25 +3541,25 @@
         <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H40" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="I40" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="J40" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="K40" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="L40" s="13" t="s">
-        <v>131</v>
+      <c r="H40" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="I40" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="J40" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>84</v>
       </c>
       <c r="M40" s="11">
         <f t="shared" si="13"/>
@@ -3468,7 +3571,7 @@
       </c>
       <c r="O40" s="11">
         <f t="shared" si="15"/>
-        <v>20500</v>
+        <v>24000</v>
       </c>
       <c r="P40" s="9">
         <f t="shared" si="16"/>
@@ -3480,17 +3583,20 @@
       </c>
       <c r="R40" s="9">
         <f t="shared" si="18"/>
-        <v>290</v>
+        <v>360</v>
       </c>
       <c r="S40" s="9"/>
       <c r="T40" s="9">
         <v>99</v>
       </c>
       <c r="U40" s="9">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:21">
+        <v>100</v>
+      </c>
+      <c r="V40" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:22">
       <c r="C41" s="1">
         <v>109</v>
       </c>
@@ -3501,25 +3607,25 @@
         <v>9</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H41" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I41" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="I41" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="J41" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="K41" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="L41" s="13" t="s">
-        <v>134</v>
+      <c r="J41" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>146</v>
       </c>
       <c r="M41" s="11">
         <f t="shared" si="13"/>
@@ -3531,7 +3637,7 @@
       </c>
       <c r="O41" s="11">
         <f t="shared" si="15"/>
-        <v>22000</v>
+        <v>26000</v>
       </c>
       <c r="P41" s="9">
         <f t="shared" si="16"/>
@@ -3543,17 +3649,20 @@
       </c>
       <c r="R41" s="9">
         <f t="shared" si="18"/>
-        <v>310</v>
+        <v>390</v>
       </c>
       <c r="S41" s="9"/>
       <c r="T41" s="9">
         <v>99</v>
       </c>
       <c r="U41" s="9">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:21">
+        <v>100</v>
+      </c>
+      <c r="V41" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:22">
       <c r="C42" s="1">
         <v>110</v>
       </c>
@@ -3564,25 +3673,25 @@
         <v>10</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="I42" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="J42" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="K42" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="L42" s="13" t="s">
-        <v>137</v>
+      <c r="H42" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="J42" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>150</v>
       </c>
       <c r="M42" s="11">
         <f t="shared" si="13"/>
@@ -3594,7 +3703,7 @@
       </c>
       <c r="O42" s="11">
         <f t="shared" si="15"/>
-        <v>23500</v>
+        <v>28000</v>
       </c>
       <c r="P42" s="9">
         <f t="shared" si="16"/>
@@ -3606,14 +3715,17 @@
       </c>
       <c r="R42" s="9">
         <f t="shared" si="18"/>
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="S42" s="9"/>
       <c r="T42" s="9">
         <v>99</v>
       </c>
       <c r="U42" s="9">
-        <v>200</v>
+        <v>100</v>
+      </c>
+      <c r="V42" s="17" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="12:16">
@@ -3629,13 +3741,11 @@
       <c r="P45" s="9"/>
     </row>
     <row r="53" customHeight="1" spans="8:8">
-      <c r="H53" s="8">
-        <v>9e+27</v>
-      </c>
+      <c r="H53" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:U5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:V5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterPillConfig.xlsx
+++ b/Excel/MonsterPillConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="158">
   <si>
     <t>ID</t>
   </si>
@@ -377,7 +377,10 @@
     <t>9E+80</t>
   </si>
   <si>
-    <t>1E+20</t>
+    <t>1E+8</t>
+  </si>
+  <si>
+    <t>1E+18</t>
   </si>
   <si>
     <t>1004,2002,2003,2007,2009</t>
@@ -386,103 +389,121 @@
     <t>练气二层</t>
   </si>
   <si>
+    <t>9E+54</t>
+  </si>
+  <si>
     <t>9E+45</t>
   </si>
   <si>
     <t>9E+85</t>
   </si>
   <si>
+    <t>1E+12</t>
+  </si>
+  <si>
+    <t>1E+22</t>
+  </si>
+  <si>
     <t>练气三层</t>
   </si>
   <si>
+    <t>9E+58</t>
+  </si>
+  <si>
+    <t>9E+90</t>
+  </si>
+  <si>
+    <t>1E+26</t>
+  </si>
+  <si>
+    <t>练气四层</t>
+  </si>
+  <si>
+    <t>9E+62</t>
+  </si>
+  <si>
+    <t>9E+95</t>
+  </si>
+  <si>
+    <t>练气五层</t>
+  </si>
+  <si>
+    <t>9E+66</t>
+  </si>
+  <si>
     <t>9E+60</t>
   </si>
   <si>
-    <t>9E+90</t>
-  </si>
-  <si>
-    <t>1E+30</t>
-  </si>
-  <si>
-    <t>1E+26</t>
-  </si>
-  <si>
-    <t>练气四层</t>
+    <t>9E+100</t>
+  </si>
+  <si>
+    <t>1E+36</t>
+  </si>
+  <si>
+    <t>练气六层</t>
+  </si>
+  <si>
+    <t>9E+70</t>
   </si>
   <si>
     <t>9E+65</t>
   </si>
   <si>
-    <t>9E+95</t>
-  </si>
-  <si>
-    <t>练气五层</t>
-  </si>
-  <si>
-    <t>9E+70</t>
-  </si>
-  <si>
-    <t>9E+100</t>
-  </si>
-  <si>
-    <t>1E+40</t>
-  </si>
-  <si>
-    <t>1E+32</t>
-  </si>
-  <si>
-    <t>练气六层</t>
-  </si>
-  <si>
     <t>9E+105</t>
   </si>
   <si>
-    <t>1E+45</t>
+    <t>1E+42</t>
   </si>
   <si>
     <t>练气七层</t>
   </si>
   <si>
+    <t>9E+74</t>
+  </si>
+  <si>
     <t>9E+110</t>
   </si>
   <si>
-    <t>1E+50</t>
-  </si>
-  <si>
-    <t>1E+38</t>
+    <t>1E+48</t>
   </si>
   <si>
     <t>练气八层</t>
   </si>
   <si>
+    <t>9E+78</t>
+  </si>
+  <si>
     <t>9E+115</t>
   </si>
   <si>
-    <t>1E+55</t>
+    <t>1E+46</t>
+  </si>
+  <si>
+    <t>1E+53</t>
   </si>
   <si>
     <t>练气九层</t>
   </si>
   <si>
+    <t>9E+82</t>
+  </si>
+  <si>
     <t>9E+120</t>
   </si>
   <si>
     <t>1E+60</t>
   </si>
   <si>
-    <t>1E+44</t>
-  </si>
-  <si>
     <t>练气十层</t>
   </si>
   <si>
+    <t>9E+86</t>
+  </si>
+  <si>
     <t>9E+125</t>
   </si>
   <si>
-    <t>1E+65</t>
-  </si>
-  <si>
-    <t>1E+47</t>
+    <t>1E+68</t>
   </si>
 </sst>
 </file>
@@ -667,12 +688,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1003,7 +1030,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1027,16 +1054,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1045,91 +1072,92 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1138,30 +1166,42 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1481,257 +1521,257 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.12389380530973" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.87610619469027" style="2" customWidth="1"/>
+    <col min="1" max="1" width="4.12389380530973" style="3" customWidth="1"/>
+    <col min="2" max="2" width="4.87610619469027" style="3" customWidth="1"/>
     <col min="3" max="5" width="9.87610619469027" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.4778761061947" style="1" customWidth="1"/>
     <col min="7" max="7" width="16.2477876106195" style="1" customWidth="1"/>
-    <col min="8" max="8" width="31.3362831858407" style="3" customWidth="1"/>
-    <col min="9" max="9" width="12.5486725663717" style="3" customWidth="1"/>
-    <col min="10" max="10" width="18.5221238938053" style="3" customWidth="1"/>
-    <col min="11" max="11" width="9.6283185840708" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.6902654867257" style="4" customWidth="1"/>
-    <col min="13" max="13" width="12.6283185840708" style="2" customWidth="1"/>
-    <col min="14" max="15" width="12.5044247787611" style="2" customWidth="1"/>
-    <col min="16" max="16" width="8" style="2" customWidth="1"/>
-    <col min="17" max="17" width="12.5044247787611" style="2" customWidth="1"/>
-    <col min="18" max="18" width="11.0176991150442" style="2" customWidth="1"/>
-    <col min="19" max="19" width="10.4247787610619" style="2" customWidth="1"/>
-    <col min="20" max="21" width="9.6283185840708" style="2" customWidth="1"/>
-    <col min="22" max="22" width="28.4867256637168" style="2" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="2"/>
+    <col min="8" max="8" width="31.3362831858407" style="4" customWidth="1"/>
+    <col min="9" max="9" width="12.5486725663717" style="4" customWidth="1"/>
+    <col min="10" max="10" width="18.5221238938053" style="4" customWidth="1"/>
+    <col min="11" max="11" width="9.6283185840708" style="3" customWidth="1"/>
+    <col min="12" max="12" width="11.6902654867257" style="5" customWidth="1"/>
+    <col min="13" max="13" width="12.6283185840708" style="3" customWidth="1"/>
+    <col min="14" max="15" width="12.5044247787611" style="3" customWidth="1"/>
+    <col min="16" max="16" width="8" style="3" customWidth="1"/>
+    <col min="17" max="17" width="12.5044247787611" style="3" customWidth="1"/>
+    <col min="18" max="18" width="11.0176991150442" style="3" customWidth="1"/>
+    <col min="19" max="19" width="10.4247787610619" style="3" customWidth="1"/>
+    <col min="20" max="21" width="9.6283185840708" style="3" customWidth="1"/>
+    <col min="22" max="22" width="28.4867256637168" style="3" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="12" t="s">
+      <c r="V3" s="16" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="6" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="R4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="S4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="T4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="U4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="V4" s="12" t="s">
+      <c r="V4" s="16" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="6" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="Q5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="R5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="S5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="T5" s="6" t="s">
+      <c r="T5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="U5" s="6" t="s">
+      <c r="U5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="V5" s="12" t="s">
+      <c r="V5" s="16" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1751,49 +1791,49 @@
       <c r="G6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="9">
-        <v>0</v>
-      </c>
-      <c r="L6" s="10">
-        <v>0</v>
-      </c>
-      <c r="M6" s="9">
+      <c r="K6" s="12">
+        <v>0</v>
+      </c>
+      <c r="L6" s="13">
+        <v>0</v>
+      </c>
+      <c r="M6" s="12">
         <v>500</v>
       </c>
-      <c r="N6" s="9">
+      <c r="N6" s="12">
         <v>500</v>
       </c>
-      <c r="O6" s="9">
+      <c r="O6" s="12">
         <v>1500</v>
       </c>
-      <c r="P6" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="9">
+      <c r="P6" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="12">
         <v>20</v>
       </c>
-      <c r="R6" s="9">
+      <c r="R6" s="12">
         <v>30</v>
       </c>
-      <c r="S6" s="9">
-        <v>0</v>
-      </c>
-      <c r="T6" s="9">
-        <v>0</v>
-      </c>
-      <c r="U6" s="9">
-        <v>0</v>
-      </c>
-      <c r="V6" s="16" t="s">
+      <c r="S6" s="12">
+        <v>0</v>
+      </c>
+      <c r="T6" s="12">
+        <v>0</v>
+      </c>
+      <c r="U6" s="12">
+        <v>0</v>
+      </c>
+      <c r="V6" s="22" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1813,54 +1853,54 @@
       <c r="G7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K7" s="9">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10">
-        <v>0</v>
-      </c>
-      <c r="M7" s="9">
+      <c r="K7" s="12">
+        <v>0</v>
+      </c>
+      <c r="L7" s="13">
+        <v>0</v>
+      </c>
+      <c r="M7" s="12">
         <f t="shared" ref="M7:M17" si="0">M6+200</f>
         <v>700</v>
       </c>
-      <c r="N7" s="9">
+      <c r="N7" s="12">
         <f t="shared" ref="N7:N17" si="1">N6+200</f>
         <v>700</v>
       </c>
-      <c r="O7" s="9">
+      <c r="O7" s="12">
         <f t="shared" ref="O7:O25" si="2">O6+200</f>
         <v>1700</v>
       </c>
-      <c r="P7" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="9">
+      <c r="P7" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="12">
         <f t="shared" ref="Q7:Q25" si="3">Q6+2</f>
         <v>22</v>
       </c>
-      <c r="R7" s="9">
+      <c r="R7" s="12">
         <f t="shared" ref="R7:R12" si="4">R6+5</f>
         <v>35</v>
       </c>
-      <c r="S7" s="9">
-        <v>0</v>
-      </c>
-      <c r="T7" s="9">
-        <v>0</v>
-      </c>
-      <c r="U7" s="9">
-        <v>0</v>
-      </c>
-      <c r="V7" s="16" t="s">
+      <c r="S7" s="12">
+        <v>0</v>
+      </c>
+      <c r="T7" s="12">
+        <v>0</v>
+      </c>
+      <c r="U7" s="12">
+        <v>0</v>
+      </c>
+      <c r="V7" s="22" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1880,54 +1920,54 @@
       <c r="G8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="K8" s="9">
-        <v>0</v>
-      </c>
-      <c r="L8" s="10">
-        <v>0</v>
-      </c>
-      <c r="M8" s="9">
+      <c r="K8" s="12">
+        <v>0</v>
+      </c>
+      <c r="L8" s="13">
+        <v>0</v>
+      </c>
+      <c r="M8" s="12">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="N8" s="9">
+      <c r="N8" s="12">
         <f t="shared" si="1"/>
         <v>900</v>
       </c>
-      <c r="O8" s="9">
+      <c r="O8" s="12">
         <f t="shared" si="2"/>
         <v>1900</v>
       </c>
-      <c r="P8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="9">
+      <c r="P8" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="12">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="R8" s="9">
+      <c r="R8" s="12">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="S8" s="9">
-        <v>0</v>
-      </c>
-      <c r="T8" s="9">
-        <v>0</v>
-      </c>
-      <c r="U8" s="9">
-        <v>0</v>
-      </c>
-      <c r="V8" s="16" t="s">
+      <c r="S8" s="12">
+        <v>0</v>
+      </c>
+      <c r="T8" s="12">
+        <v>0</v>
+      </c>
+      <c r="U8" s="12">
+        <v>0</v>
+      </c>
+      <c r="V8" s="22" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1947,54 +1987,54 @@
       <c r="G9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="K9" s="9">
-        <v>0</v>
-      </c>
-      <c r="L9" s="10">
-        <v>0</v>
-      </c>
-      <c r="M9" s="9">
+      <c r="K9" s="12">
+        <v>0</v>
+      </c>
+      <c r="L9" s="13">
+        <v>0</v>
+      </c>
+      <c r="M9" s="12">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="N9" s="9">
+      <c r="N9" s="12">
         <f t="shared" si="1"/>
         <v>1100</v>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="12">
         <f t="shared" si="2"/>
         <v>2100</v>
       </c>
-      <c r="P9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="9">
+      <c r="P9" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="12">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="R9" s="9">
+      <c r="R9" s="12">
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="S9" s="9">
-        <v>0</v>
-      </c>
-      <c r="T9" s="9">
-        <v>0</v>
-      </c>
-      <c r="U9" s="9">
-        <v>0</v>
-      </c>
-      <c r="V9" s="16" t="s">
+      <c r="S9" s="12">
+        <v>0</v>
+      </c>
+      <c r="T9" s="12">
+        <v>0</v>
+      </c>
+      <c r="U9" s="12">
+        <v>0</v>
+      </c>
+      <c r="V9" s="22" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2014,54 +2054,54 @@
       <c r="G10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="9">
-        <v>0</v>
-      </c>
-      <c r="L10" s="10">
-        <v>0</v>
-      </c>
-      <c r="M10" s="9">
+      <c r="K10" s="12">
+        <v>0</v>
+      </c>
+      <c r="L10" s="13">
+        <v>0</v>
+      </c>
+      <c r="M10" s="12">
         <f t="shared" si="0"/>
         <v>1300</v>
       </c>
-      <c r="N10" s="9">
+      <c r="N10" s="12">
         <f t="shared" si="1"/>
         <v>1300</v>
       </c>
-      <c r="O10" s="9">
+      <c r="O10" s="12">
         <f t="shared" si="2"/>
         <v>2300</v>
       </c>
-      <c r="P10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="9">
+      <c r="P10" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="12">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="R10" s="9">
+      <c r="R10" s="12">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="S10" s="9">
-        <v>0</v>
-      </c>
-      <c r="T10" s="9">
-        <v>0</v>
-      </c>
-      <c r="U10" s="9">
-        <v>0</v>
-      </c>
-      <c r="V10" s="16" t="s">
+      <c r="S10" s="12">
+        <v>0</v>
+      </c>
+      <c r="T10" s="12">
+        <v>0</v>
+      </c>
+      <c r="U10" s="12">
+        <v>0</v>
+      </c>
+      <c r="V10" s="22" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2081,54 +2121,54 @@
       <c r="G11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="K11" s="9">
-        <v>0</v>
-      </c>
-      <c r="L11" s="10">
-        <v>0</v>
-      </c>
-      <c r="M11" s="9">
+      <c r="K11" s="12">
+        <v>0</v>
+      </c>
+      <c r="L11" s="13">
+        <v>0</v>
+      </c>
+      <c r="M11" s="12">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="N11" s="9">
+      <c r="N11" s="12">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="12">
         <f t="shared" si="2"/>
         <v>2500</v>
       </c>
-      <c r="P11" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="9">
+      <c r="P11" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="12">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="R11" s="9">
+      <c r="R11" s="12">
         <f t="shared" si="4"/>
         <v>55</v>
       </c>
-      <c r="S11" s="9">
-        <v>0</v>
-      </c>
-      <c r="T11" s="9">
-        <v>0</v>
-      </c>
-      <c r="U11" s="9">
-        <v>0</v>
-      </c>
-      <c r="V11" s="13"/>
+      <c r="S11" s="12">
+        <v>0</v>
+      </c>
+      <c r="T11" s="12">
+        <v>0</v>
+      </c>
+      <c r="U11" s="12">
+        <v>0</v>
+      </c>
+      <c r="V11" s="17"/>
     </row>
     <row r="12" customHeight="1" spans="3:22">
       <c r="C12" s="1">
@@ -2146,54 +2186,54 @@
       <c r="G12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="K12" s="9">
-        <v>0</v>
-      </c>
-      <c r="L12" s="10">
-        <v>0</v>
-      </c>
-      <c r="M12" s="9">
+      <c r="K12" s="12">
+        <v>0</v>
+      </c>
+      <c r="L12" s="13">
+        <v>0</v>
+      </c>
+      <c r="M12" s="12">
         <f t="shared" si="0"/>
         <v>1700</v>
       </c>
-      <c r="N12" s="9">
+      <c r="N12" s="12">
         <f t="shared" si="1"/>
         <v>1700</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="12">
         <f t="shared" si="2"/>
         <v>2700</v>
       </c>
-      <c r="P12" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="9">
+      <c r="P12" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="12">
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
-      <c r="R12" s="9">
+      <c r="R12" s="12">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="S12" s="9">
-        <v>0</v>
-      </c>
-      <c r="T12" s="9">
-        <v>0</v>
-      </c>
-      <c r="U12" s="9">
-        <v>0</v>
-      </c>
-      <c r="V12" s="16" t="s">
+      <c r="S12" s="12">
+        <v>0</v>
+      </c>
+      <c r="T12" s="12">
+        <v>0</v>
+      </c>
+      <c r="U12" s="12">
+        <v>0</v>
+      </c>
+      <c r="V12" s="22" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2213,54 +2253,54 @@
       <c r="G13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="J13" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="K13" s="9">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10">
-        <v>0</v>
-      </c>
-      <c r="M13" s="9">
+      <c r="K13" s="12">
+        <v>0</v>
+      </c>
+      <c r="L13" s="13">
+        <v>0</v>
+      </c>
+      <c r="M13" s="12">
         <f t="shared" si="0"/>
         <v>1900</v>
       </c>
-      <c r="N13" s="9">
+      <c r="N13" s="12">
         <f t="shared" si="1"/>
         <v>1900</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="12">
         <f t="shared" si="2"/>
         <v>2900</v>
       </c>
-      <c r="P13" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="9">
+      <c r="P13" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="12">
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="R13" s="9">
+      <c r="R13" s="12">
         <f t="shared" ref="R13:R17" si="5">R12+10</f>
         <v>70</v>
       </c>
-      <c r="S13" s="9">
-        <v>0</v>
-      </c>
-      <c r="T13" s="9">
-        <v>0</v>
-      </c>
-      <c r="U13" s="9">
-        <v>0</v>
-      </c>
-      <c r="V13" s="16" t="s">
+      <c r="S13" s="12">
+        <v>0</v>
+      </c>
+      <c r="T13" s="12">
+        <v>0</v>
+      </c>
+      <c r="U13" s="12">
+        <v>0</v>
+      </c>
+      <c r="V13" s="22" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2280,54 +2320,54 @@
       <c r="G14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="J14" s="15" t="s">
+      <c r="J14" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="K14" s="9">
-        <v>0</v>
-      </c>
-      <c r="L14" s="10">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9">
+      <c r="K14" s="12">
+        <v>0</v>
+      </c>
+      <c r="L14" s="13">
+        <v>0</v>
+      </c>
+      <c r="M14" s="12">
         <f t="shared" si="0"/>
         <v>2100</v>
       </c>
-      <c r="N14" s="9">
+      <c r="N14" s="12">
         <f t="shared" si="1"/>
         <v>2100</v>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="12">
         <f t="shared" si="2"/>
         <v>3100</v>
       </c>
-      <c r="P14" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="9">
+      <c r="P14" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="12">
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="R14" s="9">
+      <c r="R14" s="12">
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
-      <c r="S14" s="9">
-        <v>0</v>
-      </c>
-      <c r="T14" s="9">
-        <v>0</v>
-      </c>
-      <c r="U14" s="9">
-        <v>0</v>
-      </c>
-      <c r="V14" s="16" t="s">
+      <c r="S14" s="12">
+        <v>0</v>
+      </c>
+      <c r="T14" s="12">
+        <v>0</v>
+      </c>
+      <c r="U14" s="12">
+        <v>0</v>
+      </c>
+      <c r="V14" s="22" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2347,51 +2387,51 @@
       <c r="G15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="K15" s="9">
-        <v>0</v>
-      </c>
-      <c r="L15" s="10">
-        <v>0</v>
-      </c>
-      <c r="M15" s="9">
+      <c r="K15" s="12">
+        <v>0</v>
+      </c>
+      <c r="L15" s="13">
+        <v>0</v>
+      </c>
+      <c r="M15" s="12">
         <f t="shared" si="0"/>
         <v>2300</v>
       </c>
-      <c r="N15" s="9">
+      <c r="N15" s="12">
         <f t="shared" si="1"/>
         <v>2300</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="12">
         <f t="shared" si="2"/>
         <v>3300</v>
       </c>
-      <c r="P15" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="9">
+      <c r="P15" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="12">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="R15" s="9">
+      <c r="R15" s="12">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="S15" s="9">
-        <v>0</v>
-      </c>
-      <c r="T15" s="9">
-        <v>0</v>
-      </c>
-      <c r="U15" s="9">
+      <c r="S15" s="12">
+        <v>0</v>
+      </c>
+      <c r="T15" s="12">
+        <v>0</v>
+      </c>
+      <c r="U15" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2411,51 +2451,51 @@
       <c r="G16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="H16" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="J16" s="15" t="s">
+      <c r="J16" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="K16" s="9">
-        <v>0</v>
-      </c>
-      <c r="L16" s="10">
-        <v>0</v>
-      </c>
-      <c r="M16" s="9">
+      <c r="K16" s="12">
+        <v>0</v>
+      </c>
+      <c r="L16" s="13">
+        <v>0</v>
+      </c>
+      <c r="M16" s="12">
         <f t="shared" ref="M16:M25" si="6">M15+400</f>
         <v>2700</v>
       </c>
-      <c r="N16" s="9">
+      <c r="N16" s="12">
         <f t="shared" ref="N16:N25" si="7">N15+400</f>
         <v>2700</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="12">
         <f t="shared" si="2"/>
         <v>3500</v>
       </c>
-      <c r="P16" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="9">
+      <c r="P16" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="12">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="R16" s="9">
+      <c r="R16" s="12">
         <f t="shared" ref="R16:R25" si="8">R15+15</f>
         <v>105</v>
       </c>
-      <c r="S16" s="9">
-        <v>0</v>
-      </c>
-      <c r="T16" s="9">
-        <v>0</v>
-      </c>
-      <c r="U16" s="9">
+      <c r="S16" s="12">
+        <v>0</v>
+      </c>
+      <c r="T16" s="12">
+        <v>0</v>
+      </c>
+      <c r="U16" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2475,51 +2515,51 @@
       <c r="G17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="J17" s="15" t="s">
+      <c r="J17" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="9">
-        <v>0</v>
-      </c>
-      <c r="L17" s="10">
-        <v>0</v>
-      </c>
-      <c r="M17" s="9">
+      <c r="K17" s="12">
+        <v>0</v>
+      </c>
+      <c r="L17" s="13">
+        <v>0</v>
+      </c>
+      <c r="M17" s="12">
         <f t="shared" si="6"/>
         <v>3100</v>
       </c>
-      <c r="N17" s="9">
+      <c r="N17" s="12">
         <f t="shared" si="7"/>
         <v>3100</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="12">
         <f t="shared" si="2"/>
         <v>3700</v>
       </c>
-      <c r="P17" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="9">
+      <c r="P17" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="12">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="R17" s="9">
+      <c r="R17" s="12">
         <f t="shared" si="8"/>
         <v>120</v>
       </c>
-      <c r="S17" s="9">
-        <v>0</v>
-      </c>
-      <c r="T17" s="9">
-        <v>0</v>
-      </c>
-      <c r="U17" s="9">
+      <c r="S17" s="12">
+        <v>0</v>
+      </c>
+      <c r="T17" s="12">
+        <v>0</v>
+      </c>
+      <c r="U17" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2539,51 +2579,51 @@
       <c r="G18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="I18" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="J18" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="K18" s="9">
-        <v>0</v>
-      </c>
-      <c r="L18" s="10">
-        <v>0</v>
-      </c>
-      <c r="M18" s="9">
+      <c r="K18" s="12">
+        <v>0</v>
+      </c>
+      <c r="L18" s="13">
+        <v>0</v>
+      </c>
+      <c r="M18" s="12">
         <f t="shared" si="6"/>
         <v>3500</v>
       </c>
-      <c r="N18" s="9">
+      <c r="N18" s="12">
         <f t="shared" si="7"/>
         <v>3500</v>
       </c>
-      <c r="O18" s="9">
+      <c r="O18" s="12">
         <f t="shared" si="2"/>
         <v>3900</v>
       </c>
-      <c r="P18" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="9">
+      <c r="P18" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="12">
         <f t="shared" si="3"/>
         <v>44</v>
       </c>
-      <c r="R18" s="9">
+      <c r="R18" s="12">
         <f t="shared" si="8"/>
         <v>135</v>
       </c>
-      <c r="S18" s="9">
-        <v>0</v>
-      </c>
-      <c r="T18" s="9">
-        <v>0</v>
-      </c>
-      <c r="U18" s="9">
+      <c r="S18" s="12">
+        <v>0</v>
+      </c>
+      <c r="T18" s="12">
+        <v>0</v>
+      </c>
+      <c r="U18" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2603,51 +2643,51 @@
       <c r="G19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="H19" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="I19" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="J19" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="K19" s="9">
-        <v>0</v>
-      </c>
-      <c r="L19" s="10">
-        <v>0</v>
-      </c>
-      <c r="M19" s="9">
+      <c r="K19" s="12">
+        <v>0</v>
+      </c>
+      <c r="L19" s="13">
+        <v>0</v>
+      </c>
+      <c r="M19" s="12">
         <f t="shared" si="6"/>
         <v>3900</v>
       </c>
-      <c r="N19" s="9">
+      <c r="N19" s="12">
         <f t="shared" si="7"/>
         <v>3900</v>
       </c>
-      <c r="O19" s="9">
+      <c r="O19" s="12">
         <f t="shared" si="2"/>
         <v>4100</v>
       </c>
-      <c r="P19" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="9">
+      <c r="P19" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="12">
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
-      <c r="R19" s="9">
+      <c r="R19" s="12">
         <f t="shared" si="8"/>
         <v>150</v>
       </c>
-      <c r="S19" s="9">
-        <v>0</v>
-      </c>
-      <c r="T19" s="9">
-        <v>0</v>
-      </c>
-      <c r="U19" s="9">
+      <c r="S19" s="12">
+        <v>0</v>
+      </c>
+      <c r="T19" s="12">
+        <v>0</v>
+      </c>
+      <c r="U19" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2667,51 +2707,51 @@
       <c r="G20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="I20" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="J20" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="K20" s="9">
-        <v>0</v>
-      </c>
-      <c r="L20" s="10">
-        <v>0</v>
-      </c>
-      <c r="M20" s="9">
+      <c r="K20" s="12">
+        <v>0</v>
+      </c>
+      <c r="L20" s="13">
+        <v>0</v>
+      </c>
+      <c r="M20" s="12">
         <f t="shared" si="6"/>
         <v>4300</v>
       </c>
-      <c r="N20" s="9">
+      <c r="N20" s="12">
         <f t="shared" si="7"/>
         <v>4300</v>
       </c>
-      <c r="O20" s="9">
+      <c r="O20" s="12">
         <f t="shared" si="2"/>
         <v>4300</v>
       </c>
-      <c r="P20" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="9">
+      <c r="P20" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="12">
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="R20" s="9">
+      <c r="R20" s="12">
         <f t="shared" si="8"/>
         <v>165</v>
       </c>
-      <c r="S20" s="9">
-        <v>0</v>
-      </c>
-      <c r="T20" s="9">
-        <v>0</v>
-      </c>
-      <c r="U20" s="9">
+      <c r="S20" s="12">
+        <v>0</v>
+      </c>
+      <c r="T20" s="12">
+        <v>0</v>
+      </c>
+      <c r="U20" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2731,51 +2771,51 @@
       <c r="G21" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="J21" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="K21" s="9">
-        <v>0</v>
-      </c>
-      <c r="L21" s="10">
-        <v>0</v>
-      </c>
-      <c r="M21" s="9">
+      <c r="K21" s="12">
+        <v>0</v>
+      </c>
+      <c r="L21" s="13">
+        <v>0</v>
+      </c>
+      <c r="M21" s="12">
         <f t="shared" ref="M21:M25" si="9">M20+800</f>
         <v>5100</v>
       </c>
-      <c r="N21" s="9">
+      <c r="N21" s="12">
         <f t="shared" ref="N21:N25" si="10">N20+800</f>
         <v>5100</v>
       </c>
-      <c r="O21" s="9">
+      <c r="O21" s="12">
         <f t="shared" ref="O21:O26" si="11">O20+400</f>
         <v>4700</v>
       </c>
-      <c r="P21" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="9">
+      <c r="P21" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="12">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="R21" s="9">
+      <c r="R21" s="12">
         <f t="shared" ref="R21:R25" si="12">R20+25</f>
         <v>190</v>
       </c>
-      <c r="S21" s="9">
-        <v>0</v>
-      </c>
-      <c r="T21" s="9">
+      <c r="S21" s="12">
+        <v>0</v>
+      </c>
+      <c r="T21" s="12">
         <v>10</v>
       </c>
-      <c r="U21" s="9">
+      <c r="U21" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2795,51 +2835,51 @@
       <c r="G22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I22" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="J22" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="K22" s="9">
-        <v>0</v>
-      </c>
-      <c r="L22" s="10">
-        <v>0</v>
-      </c>
-      <c r="M22" s="9">
+      <c r="K22" s="12">
+        <v>0</v>
+      </c>
+      <c r="L22" s="13">
+        <v>0</v>
+      </c>
+      <c r="M22" s="12">
         <f t="shared" si="9"/>
         <v>5900</v>
       </c>
-      <c r="N22" s="9">
+      <c r="N22" s="12">
         <f t="shared" si="10"/>
         <v>5900</v>
       </c>
-      <c r="O22" s="9">
+      <c r="O22" s="12">
         <f t="shared" si="11"/>
         <v>5100</v>
       </c>
-      <c r="P22" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="9">
+      <c r="P22" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="12">
         <f t="shared" si="3"/>
         <v>52</v>
       </c>
-      <c r="R22" s="9">
+      <c r="R22" s="12">
         <f t="shared" si="12"/>
         <v>215</v>
       </c>
-      <c r="S22" s="9">
-        <v>0</v>
-      </c>
-      <c r="T22" s="9">
+      <c r="S22" s="12">
+        <v>0</v>
+      </c>
+      <c r="T22" s="12">
         <v>20</v>
       </c>
-      <c r="U22" s="9">
+      <c r="U22" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2859,51 +2899,51 @@
       <c r="G23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I23" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="J23" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="K23" s="9">
-        <v>0</v>
-      </c>
-      <c r="L23" s="10">
-        <v>0</v>
-      </c>
-      <c r="M23" s="9">
+      <c r="K23" s="12">
+        <v>0</v>
+      </c>
+      <c r="L23" s="13">
+        <v>0</v>
+      </c>
+      <c r="M23" s="12">
         <f t="shared" si="9"/>
         <v>6700</v>
       </c>
-      <c r="N23" s="9">
+      <c r="N23" s="12">
         <f t="shared" si="10"/>
         <v>6700</v>
       </c>
-      <c r="O23" s="9">
+      <c r="O23" s="12">
         <f t="shared" si="11"/>
         <v>5500</v>
       </c>
-      <c r="P23" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="9">
+      <c r="P23" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="12">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="R23" s="9">
+      <c r="R23" s="12">
         <f t="shared" si="12"/>
         <v>240</v>
       </c>
-      <c r="S23" s="9">
-        <v>0</v>
-      </c>
-      <c r="T23" s="9">
+      <c r="S23" s="12">
+        <v>0</v>
+      </c>
+      <c r="T23" s="12">
         <v>30</v>
       </c>
-      <c r="U23" s="9">
+      <c r="U23" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2923,51 +2963,51 @@
       <c r="G24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="J24" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="K24" s="9">
-        <v>0</v>
-      </c>
-      <c r="L24" s="10">
-        <v>0</v>
-      </c>
-      <c r="M24" s="9">
+      <c r="K24" s="12">
+        <v>0</v>
+      </c>
+      <c r="L24" s="13">
+        <v>0</v>
+      </c>
+      <c r="M24" s="12">
         <f t="shared" si="9"/>
         <v>7500</v>
       </c>
-      <c r="N24" s="9">
+      <c r="N24" s="12">
         <f t="shared" si="10"/>
         <v>7500</v>
       </c>
-      <c r="O24" s="9">
+      <c r="O24" s="12">
         <f t="shared" si="11"/>
         <v>5900</v>
       </c>
-      <c r="P24" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="9">
+      <c r="P24" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="12">
         <f t="shared" si="3"/>
         <v>56</v>
       </c>
-      <c r="R24" s="9">
+      <c r="R24" s="12">
         <f t="shared" si="12"/>
         <v>265</v>
       </c>
-      <c r="S24" s="9">
-        <v>0</v>
-      </c>
-      <c r="T24" s="9">
+      <c r="S24" s="12">
+        <v>0</v>
+      </c>
+      <c r="T24" s="12">
         <v>40</v>
       </c>
-      <c r="U24" s="9">
+      <c r="U24" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2987,92 +3027,92 @@
       <c r="G25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="I25" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="J25" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="K25" s="9">
-        <v>0</v>
-      </c>
-      <c r="L25" s="10">
-        <v>0</v>
-      </c>
-      <c r="M25" s="9">
+      <c r="K25" s="12">
+        <v>0</v>
+      </c>
+      <c r="L25" s="13">
+        <v>0</v>
+      </c>
+      <c r="M25" s="12">
         <f t="shared" si="9"/>
         <v>8300</v>
       </c>
-      <c r="N25" s="9">
+      <c r="N25" s="12">
         <f t="shared" si="10"/>
         <v>8300</v>
       </c>
-      <c r="O25" s="9">
+      <c r="O25" s="12">
         <f t="shared" si="11"/>
         <v>6300</v>
       </c>
-      <c r="P25" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="9">
+      <c r="P25" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="12">
         <f t="shared" si="3"/>
         <v>58</v>
       </c>
-      <c r="R25" s="9">
+      <c r="R25" s="12">
         <f t="shared" si="12"/>
         <v>290</v>
       </c>
-      <c r="S25" s="9">
-        <v>0</v>
-      </c>
-      <c r="T25" s="9">
+      <c r="S25" s="12">
+        <v>0</v>
+      </c>
+      <c r="T25" s="12">
         <v>50</v>
       </c>
-      <c r="U25" s="9">
+      <c r="U25" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="8:16">
-      <c r="H26" s="8"/>
-      <c r="L26" s="10"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="11"/>
+      <c r="H26" s="9"/>
+      <c r="L26" s="13"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="14"/>
     </row>
     <row r="27" customHeight="1" spans="8:16">
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="L27" s="10"/>
-      <c r="P27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="L27" s="13"/>
+      <c r="P27" s="12"/>
     </row>
     <row r="28" customHeight="1" spans="8:16">
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="L28" s="10"/>
-      <c r="P28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="L28" s="13"/>
+      <c r="P28" s="12"/>
     </row>
     <row r="29" customHeight="1" spans="8:16">
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="L29" s="10"/>
-      <c r="P29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="L29" s="13"/>
+      <c r="P29" s="12"/>
     </row>
     <row r="30" customHeight="1" spans="9:16">
-      <c r="I30" s="8"/>
-      <c r="L30" s="10"/>
-      <c r="P30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="L30" s="13"/>
+      <c r="P30" s="12"/>
     </row>
     <row r="31" customHeight="1" spans="9:16">
-      <c r="I31" s="8"/>
-      <c r="L31" s="10"/>
-      <c r="P31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="L31" s="13"/>
+      <c r="P31" s="12"/>
     </row>
     <row r="32" customHeight="1" spans="9:16">
-      <c r="I32" s="8"/>
-      <c r="L32" s="10"/>
-      <c r="P32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="L32" s="13"/>
+      <c r="P32" s="12"/>
     </row>
     <row r="33" customHeight="1" spans="3:22">
       <c r="C33" s="1">
@@ -3090,48 +3130,50 @@
       <c r="G33" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H33" s="15" t="s">
+      <c r="H33" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="I33" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="J33" s="15" t="s">
+      <c r="J33" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="K33" s="16" t="s">
+      <c r="K33" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="L33" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="M33" s="11">
+      <c r="L33" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="M33" s="14">
         <v>10000</v>
       </c>
-      <c r="N33" s="11">
+      <c r="N33" s="14">
         <v>10000</v>
       </c>
-      <c r="O33" s="11">
+      <c r="O33" s="14">
         <v>10000</v>
       </c>
-      <c r="P33" s="11">
+      <c r="P33" s="14">
         <v>10000</v>
       </c>
-      <c r="Q33" s="11">
+      <c r="Q33" s="12">
+        <v>0</v>
+      </c>
+      <c r="R33" s="14">
         <v>150</v>
       </c>
-      <c r="R33" s="9">
+      <c r="S33" s="12">
         <v>150</v>
       </c>
-      <c r="S33" s="9"/>
-      <c r="T33" s="9">
+      <c r="T33" s="12">
         <v>99</v>
       </c>
-      <c r="U33" s="9">
+      <c r="U33" s="12">
         <v>100</v>
       </c>
-      <c r="V33" s="17" t="s">
-        <v>116</v>
+      <c r="V33" s="23" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:22">
@@ -3145,59 +3187,61 @@
         <v>2</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H34" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="I34" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="J34" s="15" t="s">
+      <c r="H34" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="K34" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="L34" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="M34" s="11">
+      <c r="I34" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="J34" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="K34" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="L34" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="M34" s="14">
         <f t="shared" ref="M33:M42" si="13">M33+1000</f>
         <v>11000</v>
       </c>
-      <c r="N34" s="11">
+      <c r="N34" s="14">
         <f t="shared" ref="N33:N42" si="14">N33+1000</f>
         <v>11000</v>
       </c>
-      <c r="O34" s="11">
+      <c r="O34" s="14">
         <f t="shared" ref="O34:O42" si="15">O33+2000</f>
         <v>12000</v>
       </c>
-      <c r="P34" s="9">
+      <c r="P34" s="12">
         <f t="shared" ref="P34:P42" si="16">P33+2000</f>
         <v>12000</v>
       </c>
-      <c r="Q34" s="9">
-        <f t="shared" ref="Q34:Q42" si="17">Q33+20</f>
+      <c r="Q34" s="12">
+        <v>0</v>
+      </c>
+      <c r="R34" s="12">
+        <f t="shared" ref="R34:R42" si="17">R33+20</f>
         <v>170</v>
       </c>
-      <c r="R34" s="9">
-        <f t="shared" ref="R34:R42" si="18">R33+30</f>
+      <c r="S34" s="12">
+        <f t="shared" ref="S34:S42" si="18">S33+30</f>
         <v>180</v>
       </c>
-      <c r="S34" s="9"/>
-      <c r="T34" s="9">
+      <c r="T34" s="12">
         <v>99</v>
       </c>
-      <c r="U34" s="9">
+      <c r="U34" s="12">
         <v>100</v>
       </c>
-      <c r="V34" s="17" t="s">
-        <v>116</v>
+      <c r="V34" s="23" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:22">
@@ -3211,59 +3255,61 @@
         <v>3</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H35" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="I35" s="15" t="s">
+      <c r="H35" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="I35" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="J35" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="K35" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="L35" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="M35" s="11">
+      <c r="J35" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="K35" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="M35" s="14">
         <f t="shared" si="13"/>
         <v>12000</v>
       </c>
-      <c r="N35" s="11">
+      <c r="N35" s="14">
         <f t="shared" si="14"/>
         <v>12000</v>
       </c>
-      <c r="O35" s="11">
+      <c r="O35" s="14">
         <f t="shared" si="15"/>
         <v>14000</v>
       </c>
-      <c r="P35" s="9">
+      <c r="P35" s="12">
         <f t="shared" si="16"/>
         <v>14000</v>
       </c>
-      <c r="Q35" s="9">
+      <c r="Q35" s="12">
+        <v>0</v>
+      </c>
+      <c r="R35" s="12">
         <f t="shared" si="17"/>
         <v>190</v>
       </c>
-      <c r="R35" s="9">
+      <c r="S35" s="12">
         <f t="shared" si="18"/>
         <v>210</v>
       </c>
-      <c r="S35" s="9"/>
-      <c r="T35" s="9">
+      <c r="T35" s="12">
         <v>99</v>
       </c>
-      <c r="U35" s="9">
+      <c r="U35" s="12">
         <v>100</v>
       </c>
-      <c r="V35" s="17" t="s">
-        <v>116</v>
+      <c r="V35" s="23" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:22">
@@ -3277,59 +3323,61 @@
         <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H36" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="I36" s="15" t="s">
+      <c r="H36" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="I36" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="J36" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="K36" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="L36" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="M36" s="11">
+      <c r="J36" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="K36" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="L36" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="M36" s="14">
         <f t="shared" si="13"/>
         <v>13000</v>
       </c>
-      <c r="N36" s="11">
+      <c r="N36" s="14">
         <f t="shared" si="14"/>
         <v>13000</v>
       </c>
-      <c r="O36" s="11">
+      <c r="O36" s="14">
         <f t="shared" si="15"/>
         <v>16000</v>
       </c>
-      <c r="P36" s="9">
+      <c r="P36" s="12">
         <f t="shared" si="16"/>
         <v>16000</v>
       </c>
-      <c r="Q36" s="9">
+      <c r="Q36" s="12">
+        <v>0</v>
+      </c>
+      <c r="R36" s="12">
         <f t="shared" si="17"/>
         <v>210</v>
       </c>
-      <c r="R36" s="9">
+      <c r="S36" s="12">
         <f t="shared" si="18"/>
         <v>240</v>
       </c>
-      <c r="S36" s="9"/>
-      <c r="T36" s="9">
+      <c r="T36" s="12">
         <v>99</v>
       </c>
-      <c r="U36" s="9">
+      <c r="U36" s="12">
         <v>100</v>
       </c>
-      <c r="V36" s="17" t="s">
-        <v>116</v>
+      <c r="V36" s="23" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:22">
@@ -3343,59 +3391,61 @@
         <v>5</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H37" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="I37" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="J37" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="K37" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="L37" s="16" t="s">
+      <c r="H37" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="M37" s="11">
+      <c r="I37" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="J37" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="K37" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="L37" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="M37" s="14">
         <f t="shared" si="13"/>
         <v>14000</v>
       </c>
-      <c r="N37" s="11">
+      <c r="N37" s="14">
         <f t="shared" si="14"/>
         <v>14000</v>
       </c>
-      <c r="O37" s="11">
+      <c r="O37" s="14">
         <f t="shared" si="15"/>
         <v>18000</v>
       </c>
-      <c r="P37" s="9">
+      <c r="P37" s="12">
         <f t="shared" si="16"/>
         <v>18000</v>
       </c>
-      <c r="Q37" s="9">
+      <c r="Q37" s="12">
+        <v>0</v>
+      </c>
+      <c r="R37" s="12">
         <f t="shared" si="17"/>
         <v>230</v>
       </c>
-      <c r="R37" s="9">
+      <c r="S37" s="12">
         <f t="shared" si="18"/>
         <v>270</v>
       </c>
-      <c r="S37" s="9"/>
-      <c r="T37" s="9">
+      <c r="T37" s="12">
         <v>99</v>
       </c>
-      <c r="U37" s="9">
+      <c r="U37" s="12">
         <v>100</v>
       </c>
-      <c r="V37" s="17" t="s">
-        <v>116</v>
+      <c r="V37" s="23" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:22">
@@ -3409,126 +3459,131 @@
         <v>6</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H38" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="I38" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="J38" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="K38" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="L38" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="M38" s="11">
+      <c r="H38" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="I38" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="J38" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="K38" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="L38" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="M38" s="14">
         <f t="shared" si="13"/>
         <v>15000</v>
       </c>
-      <c r="N38" s="11">
+      <c r="N38" s="14">
         <f t="shared" si="14"/>
         <v>15000</v>
       </c>
-      <c r="O38" s="11">
+      <c r="O38" s="14">
         <f t="shared" si="15"/>
         <v>20000</v>
       </c>
-      <c r="P38" s="9">
+      <c r="P38" s="12">
         <f t="shared" si="16"/>
         <v>20000</v>
       </c>
-      <c r="Q38" s="9">
+      <c r="Q38" s="12">
+        <v>0</v>
+      </c>
+      <c r="R38" s="12">
         <f t="shared" si="17"/>
         <v>250</v>
       </c>
-      <c r="R38" s="9">
+      <c r="S38" s="12">
         <f t="shared" si="18"/>
         <v>300</v>
       </c>
-      <c r="S38" s="9"/>
-      <c r="T38" s="9">
+      <c r="T38" s="12">
         <v>99</v>
       </c>
-      <c r="U38" s="9">
+      <c r="U38" s="12">
         <v>100</v>
       </c>
-      <c r="V38" s="17" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:22">
-      <c r="C39" s="1">
+      <c r="V38" s="23" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C39" s="10">
         <v>107</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39" s="10">
         <v>2</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="10">
         <v>7</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G39" s="1" t="s">
+      <c r="F39" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="H39" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="I39" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="J39" s="15" t="s">
+      <c r="H39" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="I39" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="K39" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="L39" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="M39" s="11">
+      <c r="J39" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="K39" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="L39" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="M39" s="15">
         <f t="shared" si="13"/>
         <v>16000</v>
       </c>
-      <c r="N39" s="11">
+      <c r="N39" s="15">
         <f t="shared" si="14"/>
         <v>16000</v>
       </c>
-      <c r="O39" s="11">
+      <c r="O39" s="15">
         <f t="shared" si="15"/>
         <v>22000</v>
       </c>
-      <c r="P39" s="9">
+      <c r="P39" s="2">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="Q39" s="9">
+      <c r="Q39" s="2">
+        <v>0</v>
+      </c>
+      <c r="R39" s="2">
         <f t="shared" si="17"/>
         <v>270</v>
       </c>
-      <c r="R39" s="9">
+      <c r="S39" s="2">
         <f t="shared" si="18"/>
         <v>330</v>
       </c>
-      <c r="S39" s="9"/>
-      <c r="T39" s="9">
+      <c r="T39" s="2">
         <v>99</v>
       </c>
-      <c r="U39" s="9">
+      <c r="U39" s="2">
         <v>100</v>
       </c>
-      <c r="V39" s="17" t="s">
-        <v>116</v>
-      </c>
+      <c r="V39" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="W39" s="20"/>
     </row>
     <row r="40" customHeight="1" spans="3:22">
       <c r="C40" s="1">
@@ -3541,59 +3596,61 @@
         <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H40" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="I40" s="15" t="s">
+      <c r="H40" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="I40" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="J40" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="K40" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="L40" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="M40" s="11">
+      <c r="J40" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="K40" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="L40" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="M40" s="14">
         <f t="shared" si="13"/>
         <v>17000</v>
       </c>
-      <c r="N40" s="11">
+      <c r="N40" s="14">
         <f t="shared" si="14"/>
         <v>17000</v>
       </c>
-      <c r="O40" s="11">
+      <c r="O40" s="14">
         <f t="shared" si="15"/>
         <v>24000</v>
       </c>
-      <c r="P40" s="9">
+      <c r="P40" s="12">
         <f t="shared" si="16"/>
         <v>24000</v>
       </c>
-      <c r="Q40" s="9">
+      <c r="Q40" s="12">
+        <v>0</v>
+      </c>
+      <c r="R40" s="12">
         <f t="shared" si="17"/>
         <v>290</v>
       </c>
-      <c r="R40" s="9">
+      <c r="S40" s="12">
         <f t="shared" si="18"/>
         <v>360</v>
       </c>
-      <c r="S40" s="9"/>
-      <c r="T40" s="9">
+      <c r="T40" s="12">
         <v>99</v>
       </c>
-      <c r="U40" s="9">
+      <c r="U40" s="12">
         <v>100</v>
       </c>
-      <c r="V40" s="17" t="s">
-        <v>116</v>
+      <c r="V40" s="23" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:22">
@@ -3607,59 +3664,61 @@
         <v>9</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H41" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="I41" s="15" t="s">
+      <c r="H41" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="I41" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="J41" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="K41" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="L41" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="M41" s="11">
+      <c r="J41" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="K41" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="L41" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="M41" s="14">
         <f t="shared" si="13"/>
         <v>18000</v>
       </c>
-      <c r="N41" s="11">
+      <c r="N41" s="14">
         <f t="shared" si="14"/>
         <v>18000</v>
       </c>
-      <c r="O41" s="11">
+      <c r="O41" s="14">
         <f t="shared" si="15"/>
         <v>26000</v>
       </c>
-      <c r="P41" s="9">
+      <c r="P41" s="12">
         <f t="shared" si="16"/>
         <v>26000</v>
       </c>
-      <c r="Q41" s="9">
+      <c r="Q41" s="12">
+        <v>0</v>
+      </c>
+      <c r="R41" s="12">
         <f t="shared" si="17"/>
         <v>310</v>
       </c>
-      <c r="R41" s="9">
+      <c r="S41" s="12">
         <f t="shared" si="18"/>
         <v>390</v>
       </c>
-      <c r="S41" s="9"/>
-      <c r="T41" s="9">
+      <c r="T41" s="12">
         <v>99</v>
       </c>
-      <c r="U41" s="9">
+      <c r="U41" s="12">
         <v>100</v>
       </c>
-      <c r="V41" s="17" t="s">
-        <v>116</v>
+      <c r="V41" s="23" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:22">
@@ -3673,75 +3732,77 @@
         <v>10</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H42" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="J42" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="K42" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="L42" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="M42" s="11">
+      <c r="H42" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="I42" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="J42" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="K42" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="L42" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="M42" s="14">
         <f t="shared" si="13"/>
         <v>19000</v>
       </c>
-      <c r="N42" s="11">
+      <c r="N42" s="14">
         <f t="shared" si="14"/>
         <v>19000</v>
       </c>
-      <c r="O42" s="11">
+      <c r="O42" s="14">
         <f t="shared" si="15"/>
         <v>28000</v>
       </c>
-      <c r="P42" s="9">
+      <c r="P42" s="12">
         <f t="shared" si="16"/>
         <v>28000</v>
       </c>
-      <c r="Q42" s="9">
+      <c r="Q42" s="12">
+        <v>0</v>
+      </c>
+      <c r="R42" s="12">
         <f t="shared" si="17"/>
         <v>330</v>
       </c>
-      <c r="R42" s="9">
+      <c r="S42" s="12">
         <f t="shared" si="18"/>
         <v>420</v>
       </c>
-      <c r="S42" s="9"/>
-      <c r="T42" s="9">
+      <c r="T42" s="12">
         <v>99</v>
       </c>
-      <c r="U42" s="9">
+      <c r="U42" s="12">
         <v>100</v>
       </c>
-      <c r="V42" s="17" t="s">
-        <v>116</v>
+      <c r="V42" s="23" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="12:16">
-      <c r="L43" s="9"/>
-      <c r="P43" s="9"/>
+      <c r="L43" s="12"/>
+      <c r="P43" s="12"/>
     </row>
     <row r="44" customHeight="1" spans="12:16">
-      <c r="L44" s="9"/>
-      <c r="P44" s="9"/>
+      <c r="L44" s="12"/>
+      <c r="P44" s="12"/>
     </row>
     <row r="45" customHeight="1" spans="12:16">
-      <c r="L45" s="9"/>
-      <c r="P45" s="9"/>
+      <c r="L45" s="12"/>
+      <c r="P45" s="12"/>
     </row>
     <row r="53" customHeight="1" spans="8:8">
-      <c r="H53" s="8"/>
+      <c r="H53" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/MonsterPillConfig.xlsx
+++ b/Excel/MonsterPillConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="248">
   <si>
     <t>ID</t>
   </si>
@@ -59,6 +59,9 @@
     <t>Strong</t>
   </si>
   <si>
+    <t>Parray</t>
+  </si>
+  <si>
     <t>DamageMul</t>
   </si>
   <si>
@@ -504,6 +507,273 @@
   </si>
   <si>
     <t>1E+68</t>
+  </si>
+  <si>
+    <t>练气十一层</t>
+  </si>
+  <si>
+    <t>9E+135</t>
+  </si>
+  <si>
+    <t>1E+10</t>
+  </si>
+  <si>
+    <t>1E+78</t>
+  </si>
+  <si>
+    <t>练气十二层</t>
+  </si>
+  <si>
+    <t>9E+96</t>
+  </si>
+  <si>
+    <t>9E+145</t>
+  </si>
+  <si>
+    <t>1E+61</t>
+  </si>
+  <si>
+    <t>1E+20</t>
+  </si>
+  <si>
+    <t>1E+88</t>
+  </si>
+  <si>
+    <t>练气十三层</t>
+  </si>
+  <si>
+    <t>9E+106</t>
+  </si>
+  <si>
+    <t>9E+91</t>
+  </si>
+  <si>
+    <t>9E+155</t>
+  </si>
+  <si>
+    <t>1E+62</t>
+  </si>
+  <si>
+    <t>1E+30</t>
+  </si>
+  <si>
+    <t>1E+98</t>
+  </si>
+  <si>
+    <t>练气十四层</t>
+  </si>
+  <si>
+    <t>9E+116</t>
+  </si>
+  <si>
+    <t>9E+92</t>
+  </si>
+  <si>
+    <t>9E+165</t>
+  </si>
+  <si>
+    <t>1E+63</t>
+  </si>
+  <si>
+    <t>1E+40</t>
+  </si>
+  <si>
+    <t>1E+108</t>
+  </si>
+  <si>
+    <t>练气十五层</t>
+  </si>
+  <si>
+    <t>9E+126</t>
+  </si>
+  <si>
+    <t>9E+93</t>
+  </si>
+  <si>
+    <t>9E+175</t>
+  </si>
+  <si>
+    <t>1E+64</t>
+  </si>
+  <si>
+    <t>1E+50</t>
+  </si>
+  <si>
+    <t>1E+118</t>
+  </si>
+  <si>
+    <t>练气十六层</t>
+  </si>
+  <si>
+    <t>9E+136</t>
+  </si>
+  <si>
+    <t>9E+94</t>
+  </si>
+  <si>
+    <t>9E+185</t>
+  </si>
+  <si>
+    <t>1E+65</t>
+  </si>
+  <si>
+    <t>1E+128</t>
+  </si>
+  <si>
+    <t>练气十七层</t>
+  </si>
+  <si>
+    <t>9E+146</t>
+  </si>
+  <si>
+    <t>9E+195</t>
+  </si>
+  <si>
+    <t>1E+66</t>
+  </si>
+  <si>
+    <t>1E+70</t>
+  </si>
+  <si>
+    <t>1E+138</t>
+  </si>
+  <si>
+    <t>练气十八层</t>
+  </si>
+  <si>
+    <t>9E+156</t>
+  </si>
+  <si>
+    <t>9E+205</t>
+  </si>
+  <si>
+    <t>1E+67</t>
+  </si>
+  <si>
+    <t>1E+80</t>
+  </si>
+  <si>
+    <t>1E+148</t>
+  </si>
+  <si>
+    <t>练气十九层</t>
+  </si>
+  <si>
+    <t>9E+166</t>
+  </si>
+  <si>
+    <t>9E+97</t>
+  </si>
+  <si>
+    <t>9E+215</t>
+  </si>
+  <si>
+    <t>1E+90</t>
+  </si>
+  <si>
+    <t>1E+158</t>
+  </si>
+  <si>
+    <t>练气二十层</t>
+  </si>
+  <si>
+    <t>9E+176</t>
+  </si>
+  <si>
+    <t>9E+98</t>
+  </si>
+  <si>
+    <t>9E+225</t>
+  </si>
+  <si>
+    <t>1E+69</t>
+  </si>
+  <si>
+    <t>1E+100</t>
+  </si>
+  <si>
+    <t>1E+168</t>
+  </si>
+  <si>
+    <t>炼神一层</t>
+  </si>
+  <si>
+    <t>炼神魔物</t>
+  </si>
+  <si>
+    <t>9E+150</t>
+  </si>
+  <si>
+    <t>1004,2002,2003,2007,2009,2012,1012</t>
+  </si>
+  <si>
+    <t>炼神二层</t>
+  </si>
+  <si>
+    <t>9E+160</t>
+  </si>
+  <si>
+    <t>炼神三层</t>
+  </si>
+  <si>
+    <t>9E+170</t>
+  </si>
+  <si>
+    <t>炼神四层</t>
+  </si>
+  <si>
+    <t>9E+130</t>
+  </si>
+  <si>
+    <t>9E+180</t>
+  </si>
+  <si>
+    <t>1E+75</t>
+  </si>
+  <si>
+    <t>炼神五层</t>
+  </si>
+  <si>
+    <t>9E+140</t>
+  </si>
+  <si>
+    <t>9E+190</t>
+  </si>
+  <si>
+    <t>炼神六层</t>
+  </si>
+  <si>
+    <t>9E+200</t>
+  </si>
+  <si>
+    <t>1E+85</t>
+  </si>
+  <si>
+    <t>炼神七层</t>
+  </si>
+  <si>
+    <t>9E+210</t>
+  </si>
+  <si>
+    <t>炼神八层</t>
+  </si>
+  <si>
+    <t>9E+220</t>
+  </si>
+  <si>
+    <t>1E+95</t>
+  </si>
+  <si>
+    <t>炼神九层</t>
+  </si>
+  <si>
+    <t>9E+230</t>
+  </si>
+  <si>
+    <t>炼神十层</t>
+  </si>
+  <si>
+    <t>9E+240</t>
   </si>
 </sst>
 </file>
@@ -1154,9 +1424,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1175,6 +1446,10 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1183,15 +1458,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1521,261 +1805,272 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W53"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.12389380530973" style="3" customWidth="1"/>
-    <col min="2" max="2" width="4.87610619469027" style="3" customWidth="1"/>
-    <col min="3" max="5" width="9.87610619469027" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.4778761061947" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.2477876106195" style="1" customWidth="1"/>
-    <col min="8" max="8" width="31.3362831858407" style="4" customWidth="1"/>
-    <col min="9" max="9" width="12.5486725663717" style="4" customWidth="1"/>
-    <col min="10" max="10" width="18.5221238938053" style="4" customWidth="1"/>
-    <col min="11" max="11" width="9.6283185840708" style="3" customWidth="1"/>
-    <col min="12" max="12" width="11.6902654867257" style="5" customWidth="1"/>
-    <col min="13" max="13" width="12.6283185840708" style="3" customWidth="1"/>
-    <col min="14" max="15" width="12.5044247787611" style="3" customWidth="1"/>
-    <col min="16" max="16" width="8" style="3" customWidth="1"/>
-    <col min="17" max="17" width="12.5044247787611" style="3" customWidth="1"/>
-    <col min="18" max="18" width="11.0176991150442" style="3" customWidth="1"/>
-    <col min="19" max="19" width="10.4247787610619" style="3" customWidth="1"/>
-    <col min="20" max="21" width="9.6283185840708" style="3" customWidth="1"/>
-    <col min="22" max="22" width="28.4867256637168" style="3" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="4.125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="4.875" style="4" customWidth="1"/>
+    <col min="3" max="5" width="9.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.475" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="31.3333333333333" style="5" customWidth="1"/>
+    <col min="9" max="9" width="12.55" style="5" customWidth="1"/>
+    <col min="10" max="10" width="18.525" style="5" customWidth="1"/>
+    <col min="11" max="12" width="9.625" style="4" customWidth="1"/>
+    <col min="13" max="13" width="11.6916666666667" style="6" customWidth="1"/>
+    <col min="14" max="14" width="12.625" style="4" customWidth="1"/>
+    <col min="15" max="16" width="12.5083333333333" style="4" customWidth="1"/>
+    <col min="17" max="17" width="8" style="4" customWidth="1"/>
+    <col min="18" max="18" width="12.5083333333333" style="4" customWidth="1"/>
+    <col min="19" max="19" width="11.0166666666667" style="4" customWidth="1"/>
+    <col min="20" max="20" width="10.425" style="4" customWidth="1"/>
+    <col min="21" max="22" width="9.625" style="4" customWidth="1"/>
+    <col min="23" max="23" width="28.4833333333333" style="4" customWidth="1"/>
+    <col min="25" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="Q3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="R3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="S3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="T3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="U3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="16" t="s">
+      <c r="V3" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="7" t="s">
+      <c r="W3" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="7" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="Q4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="R4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="S4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="7" t="s">
+      <c r="T4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="7" t="s">
+      <c r="U4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="V4" s="16" t="s">
+      <c r="V4" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="W4" s="20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="F5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="O5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="P5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="Q5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="U5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V5" s="16" t="s">
+      <c r="R5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="S5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="T5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="V5" s="8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:22">
+      <c r="W5" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:23">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1786,58 +2081,59 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="H6" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="I6" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="12">
-        <v>0</v>
-      </c>
-      <c r="L6" s="13">
-        <v>0</v>
-      </c>
-      <c r="M6" s="12">
+      <c r="J6" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="15">
+        <v>0</v>
+      </c>
+      <c r="L6" s="15"/>
+      <c r="M6" s="16">
+        <v>0</v>
+      </c>
+      <c r="N6" s="15">
         <v>500</v>
       </c>
-      <c r="N6" s="12">
+      <c r="O6" s="15">
         <v>500</v>
       </c>
-      <c r="O6" s="12">
+      <c r="P6" s="15">
         <v>1500</v>
       </c>
-      <c r="P6" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="12">
+      <c r="Q6" s="15">
+        <v>0</v>
+      </c>
+      <c r="R6" s="15">
         <v>20</v>
       </c>
-      <c r="R6" s="12">
+      <c r="S6" s="15">
         <v>30</v>
       </c>
-      <c r="S6" s="12">
-        <v>0</v>
-      </c>
-      <c r="T6" s="12">
-        <v>0</v>
-      </c>
-      <c r="U6" s="12">
-        <v>0</v>
-      </c>
-      <c r="V6" s="22" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:22">
+      <c r="T6" s="15">
+        <v>0</v>
+      </c>
+      <c r="U6" s="15">
+        <v>0</v>
+      </c>
+      <c r="V6" s="15">
+        <v>0</v>
+      </c>
+      <c r="W6" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:23">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1848,63 +2144,64 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="I7" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="K7" s="12">
-        <v>0</v>
-      </c>
-      <c r="L7" s="13">
-        <v>0</v>
-      </c>
-      <c r="M7" s="12">
-        <f t="shared" ref="M7:M17" si="0">M6+200</f>
+      <c r="J7" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="15">
+        <v>0</v>
+      </c>
+      <c r="L7" s="15"/>
+      <c r="M7" s="16">
+        <v>0</v>
+      </c>
+      <c r="N7" s="15">
+        <f t="shared" ref="N7:N17" si="0">N6+200</f>
         <v>700</v>
       </c>
-      <c r="N7" s="12">
-        <f t="shared" ref="N7:N17" si="1">N6+200</f>
+      <c r="O7" s="15">
+        <f t="shared" ref="O7:O17" si="1">O6+200</f>
         <v>700</v>
       </c>
-      <c r="O7" s="12">
-        <f t="shared" ref="O7:O25" si="2">O6+200</f>
+      <c r="P7" s="15">
+        <f t="shared" ref="P7:P25" si="2">P6+200</f>
         <v>1700</v>
       </c>
-      <c r="P7" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="12">
-        <f t="shared" ref="Q7:Q25" si="3">Q6+2</f>
+      <c r="Q7" s="15">
+        <v>0</v>
+      </c>
+      <c r="R7" s="15">
+        <f t="shared" ref="R7:R25" si="3">R6+2</f>
         <v>22</v>
       </c>
-      <c r="R7" s="12">
-        <f t="shared" ref="R7:R12" si="4">R6+5</f>
+      <c r="S7" s="15">
+        <f t="shared" ref="S7:S12" si="4">S6+5</f>
         <v>35</v>
       </c>
-      <c r="S7" s="12">
-        <v>0</v>
-      </c>
-      <c r="T7" s="12">
-        <v>0</v>
-      </c>
-      <c r="U7" s="12">
-        <v>0</v>
-      </c>
-      <c r="V7" s="22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:22">
+      <c r="T7" s="15">
+        <v>0</v>
+      </c>
+      <c r="U7" s="15">
+        <v>0</v>
+      </c>
+      <c r="V7" s="15">
+        <v>0</v>
+      </c>
+      <c r="W7" s="29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:23">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1915,63 +2212,64 @@
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="I8" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="K8" s="12">
-        <v>0</v>
-      </c>
-      <c r="L8" s="13">
-        <v>0</v>
-      </c>
-      <c r="M8" s="12">
+      <c r="J8" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" s="15">
+        <v>0</v>
+      </c>
+      <c r="L8" s="15"/>
+      <c r="M8" s="16">
+        <v>0</v>
+      </c>
+      <c r="N8" s="15">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="N8" s="12">
+      <c r="O8" s="15">
         <f t="shared" si="1"/>
         <v>900</v>
       </c>
-      <c r="O8" s="12">
+      <c r="P8" s="15">
         <f t="shared" si="2"/>
         <v>1900</v>
       </c>
-      <c r="P8" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="12">
+      <c r="Q8" s="15">
+        <v>0</v>
+      </c>
+      <c r="R8" s="15">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="R8" s="12">
+      <c r="S8" s="15">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="S8" s="12">
-        <v>0</v>
-      </c>
-      <c r="T8" s="12">
-        <v>0</v>
-      </c>
-      <c r="U8" s="12">
-        <v>0</v>
-      </c>
-      <c r="V8" s="22" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:22">
+      <c r="T8" s="15">
+        <v>0</v>
+      </c>
+      <c r="U8" s="15">
+        <v>0</v>
+      </c>
+      <c r="V8" s="15">
+        <v>0</v>
+      </c>
+      <c r="W8" s="29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:23">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1982,63 +2280,64 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="I9" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="K9" s="12">
-        <v>0</v>
-      </c>
-      <c r="L9" s="13">
-        <v>0</v>
-      </c>
-      <c r="M9" s="12">
+      <c r="J9" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="15">
+        <v>0</v>
+      </c>
+      <c r="L9" s="15"/>
+      <c r="M9" s="16">
+        <v>0</v>
+      </c>
+      <c r="N9" s="15">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="N9" s="12">
+      <c r="O9" s="15">
         <f t="shared" si="1"/>
         <v>1100</v>
       </c>
-      <c r="O9" s="12">
+      <c r="P9" s="15">
         <f t="shared" si="2"/>
         <v>2100</v>
       </c>
-      <c r="P9" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="12">
+      <c r="Q9" s="15">
+        <v>0</v>
+      </c>
+      <c r="R9" s="15">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="R9" s="12">
+      <c r="S9" s="15">
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="S9" s="12">
-        <v>0</v>
-      </c>
-      <c r="T9" s="12">
-        <v>0</v>
-      </c>
-      <c r="U9" s="12">
-        <v>0</v>
-      </c>
-      <c r="V9" s="22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:22">
+      <c r="T9" s="15">
+        <v>0</v>
+      </c>
+      <c r="U9" s="15">
+        <v>0</v>
+      </c>
+      <c r="V9" s="15">
+        <v>0</v>
+      </c>
+      <c r="W9" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:23">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -2049,63 +2348,64 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="I10" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="12">
-        <v>0</v>
-      </c>
-      <c r="L10" s="13">
-        <v>0</v>
-      </c>
-      <c r="M10" s="12">
+      <c r="J10" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" s="15">
+        <v>0</v>
+      </c>
+      <c r="L10" s="15"/>
+      <c r="M10" s="16">
+        <v>0</v>
+      </c>
+      <c r="N10" s="15">
         <f t="shared" si="0"/>
         <v>1300</v>
       </c>
-      <c r="N10" s="12">
+      <c r="O10" s="15">
         <f t="shared" si="1"/>
         <v>1300</v>
       </c>
-      <c r="O10" s="12">
+      <c r="P10" s="15">
         <f t="shared" si="2"/>
         <v>2300</v>
       </c>
-      <c r="P10" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="12">
+      <c r="Q10" s="15">
+        <v>0</v>
+      </c>
+      <c r="R10" s="15">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="R10" s="12">
+      <c r="S10" s="15">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="S10" s="12">
-        <v>0</v>
-      </c>
-      <c r="T10" s="12">
-        <v>0</v>
-      </c>
-      <c r="U10" s="12">
-        <v>0</v>
-      </c>
-      <c r="V10" s="22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:22">
+      <c r="T10" s="15">
+        <v>0</v>
+      </c>
+      <c r="U10" s="15">
+        <v>0</v>
+      </c>
+      <c r="V10" s="15">
+        <v>0</v>
+      </c>
+      <c r="W10" s="29" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:23">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -2116,61 +2416,62 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="I11" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="I11" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="K11" s="12">
-        <v>0</v>
-      </c>
-      <c r="L11" s="13">
-        <v>0</v>
-      </c>
-      <c r="M11" s="12">
+      <c r="J11" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="K11" s="15">
+        <v>0</v>
+      </c>
+      <c r="L11" s="15"/>
+      <c r="M11" s="16">
+        <v>0</v>
+      </c>
+      <c r="N11" s="15">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="N11" s="12">
+      <c r="O11" s="15">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="O11" s="12">
+      <c r="P11" s="15">
         <f t="shared" si="2"/>
         <v>2500</v>
       </c>
-      <c r="P11" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="12">
+      <c r="Q11" s="15">
+        <v>0</v>
+      </c>
+      <c r="R11" s="15">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="R11" s="12">
+      <c r="S11" s="15">
         <f t="shared" si="4"/>
         <v>55</v>
       </c>
-      <c r="S11" s="12">
-        <v>0</v>
-      </c>
-      <c r="T11" s="12">
-        <v>0</v>
-      </c>
-      <c r="U11" s="12">
-        <v>0</v>
-      </c>
-      <c r="V11" s="17"/>
-    </row>
-    <row r="12" customHeight="1" spans="3:22">
+      <c r="T11" s="15">
+        <v>0</v>
+      </c>
+      <c r="U11" s="15">
+        <v>0</v>
+      </c>
+      <c r="V11" s="15">
+        <v>0</v>
+      </c>
+      <c r="W11" s="21"/>
+    </row>
+    <row r="12" customHeight="1" spans="3:23">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -2181,63 +2482,64 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="I12" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="21" t="s">
+      <c r="I12" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="K12" s="12">
-        <v>0</v>
-      </c>
-      <c r="L12" s="13">
-        <v>0</v>
-      </c>
-      <c r="M12" s="12">
+      <c r="J12" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="K12" s="15">
+        <v>0</v>
+      </c>
+      <c r="L12" s="15"/>
+      <c r="M12" s="16">
+        <v>0</v>
+      </c>
+      <c r="N12" s="15">
         <f t="shared" si="0"/>
         <v>1700</v>
       </c>
-      <c r="N12" s="12">
+      <c r="O12" s="15">
         <f t="shared" si="1"/>
         <v>1700</v>
       </c>
-      <c r="O12" s="12">
+      <c r="P12" s="15">
         <f t="shared" si="2"/>
         <v>2700</v>
       </c>
-      <c r="P12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="12">
+      <c r="Q12" s="15">
+        <v>0</v>
+      </c>
+      <c r="R12" s="15">
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
-      <c r="R12" s="12">
+      <c r="S12" s="15">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="S12" s="12">
-        <v>0</v>
-      </c>
-      <c r="T12" s="12">
-        <v>0</v>
-      </c>
-      <c r="U12" s="12">
-        <v>0</v>
-      </c>
-      <c r="V12" s="22" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:22">
+      <c r="T12" s="15">
+        <v>0</v>
+      </c>
+      <c r="U12" s="15">
+        <v>0</v>
+      </c>
+      <c r="V12" s="15">
+        <v>0</v>
+      </c>
+      <c r="W12" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:23">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -2248,63 +2550,64 @@
         <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="I13" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="J13" s="21" t="s">
+      <c r="I13" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="K13" s="12">
-        <v>0</v>
-      </c>
-      <c r="L13" s="13">
-        <v>0</v>
-      </c>
-      <c r="M13" s="12">
+      <c r="J13" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="K13" s="15">
+        <v>0</v>
+      </c>
+      <c r="L13" s="15"/>
+      <c r="M13" s="16">
+        <v>0</v>
+      </c>
+      <c r="N13" s="15">
         <f t="shared" si="0"/>
         <v>1900</v>
       </c>
-      <c r="N13" s="12">
+      <c r="O13" s="15">
         <f t="shared" si="1"/>
         <v>1900</v>
       </c>
-      <c r="O13" s="12">
+      <c r="P13" s="15">
         <f t="shared" si="2"/>
         <v>2900</v>
       </c>
-      <c r="P13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="12">
+      <c r="Q13" s="15">
+        <v>0</v>
+      </c>
+      <c r="R13" s="15">
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="R13" s="12">
-        <f t="shared" ref="R13:R17" si="5">R12+10</f>
+      <c r="S13" s="15">
+        <f t="shared" ref="S13:S17" si="5">S12+10</f>
         <v>70</v>
       </c>
-      <c r="S13" s="12">
-        <v>0</v>
-      </c>
-      <c r="T13" s="12">
-        <v>0</v>
-      </c>
-      <c r="U13" s="12">
-        <v>0</v>
-      </c>
-      <c r="V13" s="22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:22">
+      <c r="T13" s="15">
+        <v>0</v>
+      </c>
+      <c r="U13" s="15">
+        <v>0</v>
+      </c>
+      <c r="V13" s="15">
+        <v>0</v>
+      </c>
+      <c r="W13" s="29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:23">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -2315,63 +2618,64 @@
         <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="I14" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="K14" s="12">
-        <v>0</v>
-      </c>
-      <c r="L14" s="13">
-        <v>0</v>
-      </c>
-      <c r="M14" s="12">
+      <c r="J14" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" s="15">
+        <v>0</v>
+      </c>
+      <c r="L14" s="15"/>
+      <c r="M14" s="16">
+        <v>0</v>
+      </c>
+      <c r="N14" s="15">
         <f t="shared" si="0"/>
         <v>2100</v>
       </c>
-      <c r="N14" s="12">
+      <c r="O14" s="15">
         <f t="shared" si="1"/>
         <v>2100</v>
       </c>
-      <c r="O14" s="12">
+      <c r="P14" s="15">
         <f t="shared" si="2"/>
         <v>3100</v>
       </c>
-      <c r="P14" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="12">
+      <c r="Q14" s="15">
+        <v>0</v>
+      </c>
+      <c r="R14" s="15">
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="R14" s="12">
+      <c r="S14" s="15">
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
-      <c r="S14" s="12">
-        <v>0</v>
-      </c>
-      <c r="T14" s="12">
-        <v>0</v>
-      </c>
-      <c r="U14" s="12">
-        <v>0</v>
-      </c>
-      <c r="V14" s="22" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:21">
+      <c r="T14" s="15">
+        <v>0</v>
+      </c>
+      <c r="U14" s="15">
+        <v>0</v>
+      </c>
+      <c r="V14" s="15">
+        <v>0</v>
+      </c>
+      <c r="W14" s="29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:22">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -2382,60 +2686,61 @@
         <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="I15" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="J15" s="21" t="s">
+      <c r="I15" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="K15" s="12">
-        <v>0</v>
-      </c>
-      <c r="L15" s="13">
-        <v>0</v>
-      </c>
-      <c r="M15" s="12">
+      <c r="J15" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="K15" s="15">
+        <v>0</v>
+      </c>
+      <c r="L15" s="15"/>
+      <c r="M15" s="16">
+        <v>0</v>
+      </c>
+      <c r="N15" s="15">
         <f t="shared" si="0"/>
         <v>2300</v>
       </c>
-      <c r="N15" s="12">
+      <c r="O15" s="15">
         <f t="shared" si="1"/>
         <v>2300</v>
       </c>
-      <c r="O15" s="12">
+      <c r="P15" s="15">
         <f t="shared" si="2"/>
         <v>3300</v>
       </c>
-      <c r="P15" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="12">
+      <c r="Q15" s="15">
+        <v>0</v>
+      </c>
+      <c r="R15" s="15">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="R15" s="12">
+      <c r="S15" s="15">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="S15" s="12">
-        <v>0</v>
-      </c>
-      <c r="T15" s="12">
-        <v>0</v>
-      </c>
-      <c r="U15" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:21">
+      <c r="T15" s="15">
+        <v>0</v>
+      </c>
+      <c r="U15" s="15">
+        <v>0</v>
+      </c>
+      <c r="V15" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:22">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -2446,60 +2751,61 @@
         <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="I16" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="J16" s="21" t="s">
+      <c r="I16" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="K16" s="12">
-        <v>0</v>
-      </c>
-      <c r="L16" s="13">
-        <v>0</v>
-      </c>
-      <c r="M16" s="12">
-        <f t="shared" ref="M16:M25" si="6">M15+400</f>
+      <c r="J16" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="K16" s="15">
+        <v>0</v>
+      </c>
+      <c r="L16" s="15"/>
+      <c r="M16" s="16">
+        <v>0</v>
+      </c>
+      <c r="N16" s="15">
+        <f t="shared" ref="N16:N25" si="6">N15+400</f>
         <v>2700</v>
       </c>
-      <c r="N16" s="12">
-        <f t="shared" ref="N16:N25" si="7">N15+400</f>
+      <c r="O16" s="15">
+        <f t="shared" ref="O16:O25" si="7">O15+400</f>
         <v>2700</v>
       </c>
-      <c r="O16" s="12">
+      <c r="P16" s="15">
         <f t="shared" si="2"/>
         <v>3500</v>
       </c>
-      <c r="P16" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="12">
+      <c r="Q16" s="15">
+        <v>0</v>
+      </c>
+      <c r="R16" s="15">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="R16" s="12">
-        <f t="shared" ref="R16:R25" si="8">R15+15</f>
+      <c r="S16" s="15">
+        <f t="shared" ref="S16:S25" si="8">S15+15</f>
         <v>105</v>
       </c>
-      <c r="S16" s="12">
-        <v>0</v>
-      </c>
-      <c r="T16" s="12">
-        <v>0</v>
-      </c>
-      <c r="U16" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:21">
+      <c r="T16" s="15">
+        <v>0</v>
+      </c>
+      <c r="U16" s="15">
+        <v>0</v>
+      </c>
+      <c r="V16" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:22">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -2510,60 +2816,61 @@
         <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="I17" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="J17" s="21" t="s">
+      <c r="I17" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="12">
-        <v>0</v>
-      </c>
-      <c r="L17" s="13">
-        <v>0</v>
-      </c>
-      <c r="M17" s="12">
+      <c r="J17" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="K17" s="15">
+        <v>0</v>
+      </c>
+      <c r="L17" s="15"/>
+      <c r="M17" s="16">
+        <v>0</v>
+      </c>
+      <c r="N17" s="15">
         <f t="shared" si="6"/>
         <v>3100</v>
       </c>
-      <c r="N17" s="12">
+      <c r="O17" s="15">
         <f t="shared" si="7"/>
         <v>3100</v>
       </c>
-      <c r="O17" s="12">
+      <c r="P17" s="15">
         <f t="shared" si="2"/>
         <v>3700</v>
       </c>
-      <c r="P17" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="12">
+      <c r="Q17" s="15">
+        <v>0</v>
+      </c>
+      <c r="R17" s="15">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="R17" s="12">
+      <c r="S17" s="15">
         <f t="shared" si="8"/>
         <v>120</v>
       </c>
-      <c r="S17" s="12">
-        <v>0</v>
-      </c>
-      <c r="T17" s="12">
-        <v>0</v>
-      </c>
-      <c r="U17" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:21">
+      <c r="T17" s="15">
+        <v>0</v>
+      </c>
+      <c r="U17" s="15">
+        <v>0</v>
+      </c>
+      <c r="V17" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:22">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -2574,60 +2881,61 @@
         <v>13</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="I18" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="J18" s="21" t="s">
+      <c r="I18" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="K18" s="12">
-        <v>0</v>
-      </c>
-      <c r="L18" s="13">
-        <v>0</v>
-      </c>
-      <c r="M18" s="12">
+      <c r="J18" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" s="15">
+        <v>0</v>
+      </c>
+      <c r="L18" s="15"/>
+      <c r="M18" s="16">
+        <v>0</v>
+      </c>
+      <c r="N18" s="15">
         <f t="shared" si="6"/>
         <v>3500</v>
       </c>
-      <c r="N18" s="12">
+      <c r="O18" s="15">
         <f t="shared" si="7"/>
         <v>3500</v>
       </c>
-      <c r="O18" s="12">
+      <c r="P18" s="15">
         <f t="shared" si="2"/>
         <v>3900</v>
       </c>
-      <c r="P18" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="12">
+      <c r="Q18" s="15">
+        <v>0</v>
+      </c>
+      <c r="R18" s="15">
         <f t="shared" si="3"/>
         <v>44</v>
       </c>
-      <c r="R18" s="12">
+      <c r="S18" s="15">
         <f t="shared" si="8"/>
         <v>135</v>
       </c>
-      <c r="S18" s="12">
-        <v>0</v>
-      </c>
-      <c r="T18" s="12">
-        <v>0</v>
-      </c>
-      <c r="U18" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:21">
+      <c r="T18" s="15">
+        <v>0</v>
+      </c>
+      <c r="U18" s="15">
+        <v>0</v>
+      </c>
+      <c r="V18" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:22">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -2638,60 +2946,61 @@
         <v>14</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="I19" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="J19" s="21" t="s">
+      <c r="I19" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="K19" s="12">
-        <v>0</v>
-      </c>
-      <c r="L19" s="13">
-        <v>0</v>
-      </c>
-      <c r="M19" s="12">
+      <c r="J19" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="K19" s="15">
+        <v>0</v>
+      </c>
+      <c r="L19" s="15"/>
+      <c r="M19" s="16">
+        <v>0</v>
+      </c>
+      <c r="N19" s="15">
         <f t="shared" si="6"/>
         <v>3900</v>
       </c>
-      <c r="N19" s="12">
+      <c r="O19" s="15">
         <f t="shared" si="7"/>
         <v>3900</v>
       </c>
-      <c r="O19" s="12">
+      <c r="P19" s="15">
         <f t="shared" si="2"/>
         <v>4100</v>
       </c>
-      <c r="P19" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="12">
+      <c r="Q19" s="15">
+        <v>0</v>
+      </c>
+      <c r="R19" s="15">
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
-      <c r="R19" s="12">
+      <c r="S19" s="15">
         <f t="shared" si="8"/>
         <v>150</v>
       </c>
-      <c r="S19" s="12">
-        <v>0</v>
-      </c>
-      <c r="T19" s="12">
-        <v>0</v>
-      </c>
-      <c r="U19" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:21">
+      <c r="T19" s="15">
+        <v>0</v>
+      </c>
+      <c r="U19" s="15">
+        <v>0</v>
+      </c>
+      <c r="V19" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:22">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -2702,60 +3011,61 @@
         <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="I20" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="I20" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="K20" s="12">
-        <v>0</v>
-      </c>
-      <c r="L20" s="13">
-        <v>0</v>
-      </c>
-      <c r="M20" s="12">
+      <c r="J20" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" s="15">
+        <v>0</v>
+      </c>
+      <c r="L20" s="15"/>
+      <c r="M20" s="16">
+        <v>0</v>
+      </c>
+      <c r="N20" s="15">
         <f t="shared" si="6"/>
         <v>4300</v>
       </c>
-      <c r="N20" s="12">
+      <c r="O20" s="15">
         <f t="shared" si="7"/>
         <v>4300</v>
       </c>
-      <c r="O20" s="12">
+      <c r="P20" s="15">
         <f t="shared" si="2"/>
         <v>4300</v>
       </c>
-      <c r="P20" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="12">
+      <c r="Q20" s="15">
+        <v>0</v>
+      </c>
+      <c r="R20" s="15">
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="R20" s="12">
+      <c r="S20" s="15">
         <f t="shared" si="8"/>
         <v>165</v>
       </c>
-      <c r="S20" s="12">
-        <v>0</v>
-      </c>
-      <c r="T20" s="12">
-        <v>0</v>
-      </c>
-      <c r="U20" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:21">
+      <c r="T20" s="15">
+        <v>0</v>
+      </c>
+      <c r="U20" s="15">
+        <v>0</v>
+      </c>
+      <c r="V20" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:22">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -2766,60 +3076,61 @@
         <v>16</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="I21" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="I21" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="K21" s="12">
-        <v>0</v>
-      </c>
-      <c r="L21" s="13">
-        <v>0</v>
-      </c>
-      <c r="M21" s="12">
-        <f t="shared" ref="M21:M25" si="9">M20+800</f>
+      <c r="J21" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="K21" s="15">
+        <v>0</v>
+      </c>
+      <c r="L21" s="15"/>
+      <c r="M21" s="16">
+        <v>0</v>
+      </c>
+      <c r="N21" s="15">
+        <f t="shared" ref="N21:N25" si="9">N20+800</f>
         <v>5100</v>
       </c>
-      <c r="N21" s="12">
-        <f t="shared" ref="N21:N25" si="10">N20+800</f>
+      <c r="O21" s="15">
+        <f t="shared" ref="O21:O25" si="10">O20+800</f>
         <v>5100</v>
       </c>
-      <c r="O21" s="12">
-        <f t="shared" ref="O21:O26" si="11">O20+400</f>
+      <c r="P21" s="15">
+        <f t="shared" ref="P21:P26" si="11">P20+400</f>
         <v>4700</v>
       </c>
-      <c r="P21" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="12">
+      <c r="Q21" s="15">
+        <v>0</v>
+      </c>
+      <c r="R21" s="15">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="R21" s="12">
-        <f t="shared" ref="R21:R25" si="12">R20+25</f>
+      <c r="S21" s="15">
+        <f t="shared" ref="S21:S25" si="12">S20+25</f>
         <v>190</v>
       </c>
-      <c r="S21" s="12">
-        <v>0</v>
-      </c>
-      <c r="T21" s="12">
+      <c r="T21" s="15">
+        <v>0</v>
+      </c>
+      <c r="U21" s="15">
         <v>10</v>
       </c>
-      <c r="U21" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:21">
+      <c r="V21" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:22">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -2830,60 +3141,61 @@
         <v>17</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="I22" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="I22" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="K22" s="12">
-        <v>0</v>
-      </c>
-      <c r="L22" s="13">
-        <v>0</v>
-      </c>
-      <c r="M22" s="12">
+      <c r="J22" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="K22" s="15">
+        <v>0</v>
+      </c>
+      <c r="L22" s="15"/>
+      <c r="M22" s="16">
+        <v>0</v>
+      </c>
+      <c r="N22" s="15">
         <f t="shared" si="9"/>
         <v>5900</v>
       </c>
-      <c r="N22" s="12">
+      <c r="O22" s="15">
         <f t="shared" si="10"/>
         <v>5900</v>
       </c>
-      <c r="O22" s="12">
+      <c r="P22" s="15">
         <f t="shared" si="11"/>
         <v>5100</v>
       </c>
-      <c r="P22" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="12">
+      <c r="Q22" s="15">
+        <v>0</v>
+      </c>
+      <c r="R22" s="15">
         <f t="shared" si="3"/>
         <v>52</v>
       </c>
-      <c r="R22" s="12">
+      <c r="S22" s="15">
         <f t="shared" si="12"/>
         <v>215</v>
       </c>
-      <c r="S22" s="12">
-        <v>0</v>
-      </c>
-      <c r="T22" s="12">
+      <c r="T22" s="15">
+        <v>0</v>
+      </c>
+      <c r="U22" s="15">
         <v>20</v>
       </c>
-      <c r="U22" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:21">
+      <c r="V22" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:22">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -2894,60 +3206,61 @@
         <v>18</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="I23" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="I23" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="K23" s="12">
-        <v>0</v>
-      </c>
-      <c r="L23" s="13">
-        <v>0</v>
-      </c>
-      <c r="M23" s="12">
+      <c r="J23" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="K23" s="15">
+        <v>0</v>
+      </c>
+      <c r="L23" s="15"/>
+      <c r="M23" s="16">
+        <v>0</v>
+      </c>
+      <c r="N23" s="15">
         <f t="shared" si="9"/>
         <v>6700</v>
       </c>
-      <c r="N23" s="12">
+      <c r="O23" s="15">
         <f t="shared" si="10"/>
         <v>6700</v>
       </c>
-      <c r="O23" s="12">
+      <c r="P23" s="15">
         <f t="shared" si="11"/>
         <v>5500</v>
       </c>
-      <c r="P23" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="12">
+      <c r="Q23" s="15">
+        <v>0</v>
+      </c>
+      <c r="R23" s="15">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="R23" s="12">
+      <c r="S23" s="15">
         <f t="shared" si="12"/>
         <v>240</v>
       </c>
-      <c r="S23" s="12">
-        <v>0</v>
-      </c>
-      <c r="T23" s="12">
+      <c r="T23" s="15">
+        <v>0</v>
+      </c>
+      <c r="U23" s="15">
         <v>30</v>
       </c>
-      <c r="U23" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:21">
+      <c r="V23" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:22">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -2958,60 +3271,61 @@
         <v>19</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="I24" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="J24" s="9" t="s">
+      <c r="I24" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="K24" s="12">
-        <v>0</v>
-      </c>
-      <c r="L24" s="13">
-        <v>0</v>
-      </c>
-      <c r="M24" s="12">
+      <c r="J24" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="K24" s="15">
+        <v>0</v>
+      </c>
+      <c r="L24" s="15"/>
+      <c r="M24" s="16">
+        <v>0</v>
+      </c>
+      <c r="N24" s="15">
         <f t="shared" si="9"/>
         <v>7500</v>
       </c>
-      <c r="N24" s="12">
+      <c r="O24" s="15">
         <f t="shared" si="10"/>
         <v>7500</v>
       </c>
-      <c r="O24" s="12">
+      <c r="P24" s="15">
         <f t="shared" si="11"/>
         <v>5900</v>
       </c>
-      <c r="P24" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="12">
+      <c r="Q24" s="15">
+        <v>0</v>
+      </c>
+      <c r="R24" s="15">
         <f t="shared" si="3"/>
         <v>56</v>
       </c>
-      <c r="R24" s="12">
+      <c r="S24" s="15">
         <f t="shared" si="12"/>
         <v>265</v>
       </c>
-      <c r="S24" s="12">
-        <v>0</v>
-      </c>
-      <c r="T24" s="12">
+      <c r="T24" s="15">
+        <v>0</v>
+      </c>
+      <c r="U24" s="15">
         <v>40</v>
       </c>
-      <c r="U24" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:21">
+      <c r="V24" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:22">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -3022,99 +3336,100 @@
         <v>20</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="J25" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I25" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="K25" s="12">
-        <v>0</v>
-      </c>
-      <c r="L25" s="13">
-        <v>0</v>
-      </c>
-      <c r="M25" s="12">
+      <c r="J25" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="K25" s="15">
+        <v>0</v>
+      </c>
+      <c r="L25" s="15"/>
+      <c r="M25" s="16">
+        <v>0</v>
+      </c>
+      <c r="N25" s="15">
         <f t="shared" si="9"/>
         <v>8300</v>
       </c>
-      <c r="N25" s="12">
+      <c r="O25" s="15">
         <f t="shared" si="10"/>
         <v>8300</v>
       </c>
-      <c r="O25" s="12">
+      <c r="P25" s="15">
         <f t="shared" si="11"/>
         <v>6300</v>
       </c>
-      <c r="P25" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="12">
+      <c r="Q25" s="15">
+        <v>0</v>
+      </c>
+      <c r="R25" s="15">
         <f t="shared" si="3"/>
         <v>58</v>
       </c>
-      <c r="R25" s="12">
+      <c r="S25" s="15">
         <f t="shared" si="12"/>
         <v>290</v>
       </c>
-      <c r="S25" s="12">
-        <v>0</v>
-      </c>
-      <c r="T25" s="12">
+      <c r="T25" s="15">
+        <v>0</v>
+      </c>
+      <c r="U25" s="15">
         <v>50</v>
       </c>
-      <c r="U25" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="8:16">
-      <c r="H26" s="9"/>
-      <c r="L26" s="13"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="14"/>
-    </row>
-    <row r="27" customHeight="1" spans="8:16">
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="L27" s="13"/>
-      <c r="P27" s="12"/>
-    </row>
-    <row r="28" customHeight="1" spans="8:16">
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="L28" s="13"/>
-      <c r="P28" s="12"/>
-    </row>
-    <row r="29" customHeight="1" spans="8:16">
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="L29" s="13"/>
-      <c r="P29" s="12"/>
-    </row>
-    <row r="30" customHeight="1" spans="9:16">
-      <c r="I30" s="9"/>
-      <c r="L30" s="13"/>
-      <c r="P30" s="12"/>
-    </row>
-    <row r="31" customHeight="1" spans="9:16">
-      <c r="I31" s="9"/>
-      <c r="L31" s="13"/>
-      <c r="P31" s="12"/>
-    </row>
-    <row r="32" customHeight="1" spans="9:16">
-      <c r="I32" s="9"/>
-      <c r="L32" s="13"/>
-      <c r="P32" s="12"/>
-    </row>
-    <row r="33" customHeight="1" spans="3:22">
+      <c r="V25" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="8:17">
+      <c r="H26" s="10"/>
+      <c r="M26" s="16"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="17"/>
+    </row>
+    <row r="27" customHeight="1" spans="8:17">
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="M27" s="16"/>
+      <c r="Q27" s="15"/>
+    </row>
+    <row r="28" customHeight="1" spans="8:17">
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="M28" s="16"/>
+      <c r="Q28" s="15"/>
+    </row>
+    <row r="29" customHeight="1" spans="8:17">
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="M29" s="16"/>
+      <c r="Q29" s="15"/>
+    </row>
+    <row r="30" customHeight="1" spans="9:17">
+      <c r="I30" s="10"/>
+      <c r="M30" s="16"/>
+      <c r="Q30" s="15"/>
+    </row>
+    <row r="31" customHeight="1" spans="9:17">
+      <c r="I31" s="10"/>
+      <c r="M31" s="16"/>
+      <c r="Q31" s="15"/>
+    </row>
+    <row r="32" customHeight="1" spans="9:17">
+      <c r="I32" s="10"/>
+      <c r="M32" s="16"/>
+      <c r="Q32" s="15"/>
+    </row>
+    <row r="33" customHeight="1" spans="3:23">
       <c r="C33" s="1">
         <v>101</v>
       </c>
@@ -3125,58 +3440,59 @@
         <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H33" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="I33" s="21" t="s">
+      <c r="H33" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="J33" s="21" t="s">
+      <c r="I33" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="K33" s="22" t="s">
+      <c r="J33" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="L33" s="22" t="s">
+      <c r="K33" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="M33" s="14">
+      <c r="L33" s="15"/>
+      <c r="M33" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="N33" s="17">
         <v>10000</v>
       </c>
-      <c r="N33" s="14">
+      <c r="O33" s="17">
         <v>10000</v>
       </c>
-      <c r="O33" s="14">
+      <c r="P33" s="17">
         <v>10000</v>
       </c>
-      <c r="P33" s="14">
+      <c r="Q33" s="17">
         <v>10000</v>
       </c>
-      <c r="Q33" s="12">
-        <v>0</v>
-      </c>
-      <c r="R33" s="14">
+      <c r="R33" s="15">
+        <v>0</v>
+      </c>
+      <c r="S33" s="22">
         <v>150</v>
       </c>
-      <c r="S33" s="12">
+      <c r="T33" s="15">
         <v>150</v>
       </c>
-      <c r="T33" s="12">
+      <c r="U33" s="15">
         <v>99</v>
       </c>
-      <c r="U33" s="12">
+      <c r="V33" s="15">
         <v>100</v>
       </c>
-      <c r="V33" s="23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:22">
+      <c r="W33" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:23">
       <c r="C34" s="1">
         <v>102</v>
       </c>
@@ -3187,64 +3503,65 @@
         <v>2</v>
       </c>
       <c r="F34" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H34" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="I34" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="J34" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="K34" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="L34" s="15"/>
+      <c r="M34" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="N34" s="17">
+        <f t="shared" ref="N33:N52" si="13">N33+1000</f>
+        <v>11000</v>
+      </c>
+      <c r="O34" s="17">
+        <f t="shared" ref="O33:O52" si="14">O33+1000</f>
+        <v>11000</v>
+      </c>
+      <c r="P34" s="17">
+        <f t="shared" ref="P34:P52" si="15">P33+2000</f>
+        <v>12000</v>
+      </c>
+      <c r="Q34" s="19">
+        <f t="shared" ref="Q34:Q52" si="16">Q33+2000</f>
+        <v>12000</v>
+      </c>
+      <c r="R34" s="15">
+        <v>0</v>
+      </c>
+      <c r="S34" s="15">
+        <f t="shared" ref="S34:S52" si="17">S33+20</f>
+        <v>170</v>
+      </c>
+      <c r="T34" s="15">
+        <f t="shared" ref="T34:T52" si="18">T33+30</f>
+        <v>180</v>
+      </c>
+      <c r="U34" s="15">
+        <v>99</v>
+      </c>
+      <c r="V34" s="15">
+        <v>100</v>
+      </c>
+      <c r="W34" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H34" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="I34" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="J34" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="K34" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="L34" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="M34" s="14">
-        <f t="shared" ref="M33:M42" si="13">M33+1000</f>
-        <v>11000</v>
-      </c>
-      <c r="N34" s="14">
-        <f t="shared" ref="N33:N42" si="14">N33+1000</f>
-        <v>11000</v>
-      </c>
-      <c r="O34" s="14">
-        <f t="shared" ref="O34:O42" si="15">O33+2000</f>
-        <v>12000</v>
-      </c>
-      <c r="P34" s="12">
-        <f t="shared" ref="P34:P42" si="16">P33+2000</f>
-        <v>12000</v>
-      </c>
-      <c r="Q34" s="12">
-        <v>0</v>
-      </c>
-      <c r="R34" s="12">
-        <f t="shared" ref="R34:R42" si="17">R33+20</f>
-        <v>170</v>
-      </c>
-      <c r="S34" s="12">
-        <f t="shared" ref="S34:S42" si="18">S33+30</f>
-        <v>180</v>
-      </c>
-      <c r="T34" s="12">
-        <v>99</v>
-      </c>
-      <c r="U34" s="12">
-        <v>100</v>
-      </c>
-      <c r="V34" s="23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:22">
+    </row>
+    <row r="35" customHeight="1" spans="3:23">
       <c r="C35" s="1">
         <v>103</v>
       </c>
@@ -3255,64 +3572,65 @@
         <v>3</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H35" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="I35" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="J35" s="21" t="s">
+      <c r="H35" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="K35" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="L35" s="22" t="s">
+      <c r="I35" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="J35" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="M35" s="14">
+      <c r="K35" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="L35" s="15"/>
+      <c r="M35" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="N35" s="17">
         <f t="shared" si="13"/>
         <v>12000</v>
       </c>
-      <c r="N35" s="14">
+      <c r="O35" s="17">
         <f t="shared" si="14"/>
         <v>12000</v>
       </c>
-      <c r="O35" s="14">
+      <c r="P35" s="17">
         <f t="shared" si="15"/>
         <v>14000</v>
       </c>
-      <c r="P35" s="12">
+      <c r="Q35" s="19">
         <f t="shared" si="16"/>
         <v>14000</v>
       </c>
-      <c r="Q35" s="12">
-        <v>0</v>
-      </c>
-      <c r="R35" s="12">
+      <c r="R35" s="15">
+        <v>0</v>
+      </c>
+      <c r="S35" s="15">
         <f t="shared" si="17"/>
         <v>190</v>
       </c>
-      <c r="S35" s="12">
+      <c r="T35" s="15">
         <f t="shared" si="18"/>
         <v>210</v>
       </c>
-      <c r="T35" s="12">
+      <c r="U35" s="15">
         <v>99</v>
       </c>
-      <c r="U35" s="12">
+      <c r="V35" s="15">
         <v>100</v>
       </c>
-      <c r="V35" s="23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:22">
+      <c r="W35" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:23">
       <c r="C36" s="1">
         <v>104</v>
       </c>
@@ -3323,64 +3641,65 @@
         <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H36" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="I36" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="J36" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="H36" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="K36" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="L36" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="M36" s="14">
+      <c r="I36" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="J36" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="K36" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="L36" s="15"/>
+      <c r="M36" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="N36" s="17">
         <f t="shared" si="13"/>
         <v>13000</v>
       </c>
-      <c r="N36" s="14">
+      <c r="O36" s="17">
         <f t="shared" si="14"/>
         <v>13000</v>
       </c>
-      <c r="O36" s="14">
+      <c r="P36" s="17">
         <f t="shared" si="15"/>
         <v>16000</v>
       </c>
-      <c r="P36" s="12">
+      <c r="Q36" s="19">
         <f t="shared" si="16"/>
         <v>16000</v>
       </c>
-      <c r="Q36" s="12">
-        <v>0</v>
-      </c>
-      <c r="R36" s="12">
+      <c r="R36" s="15">
+        <v>0</v>
+      </c>
+      <c r="S36" s="15">
         <f t="shared" si="17"/>
         <v>210</v>
       </c>
-      <c r="S36" s="12">
+      <c r="T36" s="15">
         <f t="shared" si="18"/>
         <v>240</v>
       </c>
-      <c r="T36" s="12">
+      <c r="U36" s="15">
         <v>99</v>
       </c>
-      <c r="U36" s="12">
+      <c r="V36" s="15">
         <v>100</v>
       </c>
-      <c r="V36" s="23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:22">
+      <c r="W36" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:23">
       <c r="C37" s="1">
         <v>105</v>
       </c>
@@ -3391,64 +3710,65 @@
         <v>5</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H37" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="I37" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="H37" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="J37" s="21" t="s">
+      <c r="I37" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="K37" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="L37" s="22" t="s">
+      <c r="J37" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="M37" s="14">
+      <c r="K37" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="L37" s="15"/>
+      <c r="M37" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="N37" s="17">
         <f t="shared" si="13"/>
         <v>14000</v>
       </c>
-      <c r="N37" s="14">
+      <c r="O37" s="17">
         <f t="shared" si="14"/>
         <v>14000</v>
       </c>
-      <c r="O37" s="14">
+      <c r="P37" s="17">
         <f t="shared" si="15"/>
         <v>18000</v>
       </c>
-      <c r="P37" s="12">
+      <c r="Q37" s="19">
         <f t="shared" si="16"/>
         <v>18000</v>
       </c>
-      <c r="Q37" s="12">
-        <v>0</v>
-      </c>
-      <c r="R37" s="12">
+      <c r="R37" s="15">
+        <v>0</v>
+      </c>
+      <c r="S37" s="15">
         <f t="shared" si="17"/>
         <v>230</v>
       </c>
-      <c r="S37" s="12">
+      <c r="T37" s="15">
         <f t="shared" si="18"/>
         <v>270</v>
       </c>
-      <c r="T37" s="12">
+      <c r="U37" s="15">
         <v>99</v>
       </c>
-      <c r="U37" s="12">
+      <c r="V37" s="15">
         <v>100</v>
       </c>
-      <c r="V37" s="23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:22">
+      <c r="W37" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:23">
       <c r="C38" s="1">
         <v>106</v>
       </c>
@@ -3459,133 +3779,134 @@
         <v>6</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H38" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="I38" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="H38" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="J38" s="21" t="s">
+      <c r="I38" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="K38" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="L38" s="22" t="s">
+      <c r="J38" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="M38" s="14">
+      <c r="K38" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="L38" s="15"/>
+      <c r="M38" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="N38" s="17">
         <f t="shared" si="13"/>
         <v>15000</v>
       </c>
-      <c r="N38" s="14">
+      <c r="O38" s="17">
         <f t="shared" si="14"/>
         <v>15000</v>
       </c>
-      <c r="O38" s="14">
+      <c r="P38" s="17">
         <f t="shared" si="15"/>
         <v>20000</v>
       </c>
-      <c r="P38" s="12">
+      <c r="Q38" s="19">
         <f t="shared" si="16"/>
         <v>20000</v>
       </c>
-      <c r="Q38" s="12">
-        <v>0</v>
-      </c>
-      <c r="R38" s="12">
+      <c r="R38" s="15">
+        <v>0</v>
+      </c>
+      <c r="S38" s="15">
         <f t="shared" si="17"/>
         <v>250</v>
       </c>
-      <c r="S38" s="12">
+      <c r="T38" s="15">
         <f t="shared" si="18"/>
         <v>300</v>
       </c>
-      <c r="T38" s="12">
+      <c r="U38" s="15">
         <v>99</v>
       </c>
-      <c r="U38" s="12">
+      <c r="V38" s="15">
         <v>100</v>
       </c>
-      <c r="V38" s="23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C39" s="10">
+      <c r="W38" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C39" s="11">
         <v>107</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D39" s="11">
         <v>2</v>
       </c>
-      <c r="E39" s="10">
+      <c r="E39" s="11">
         <v>7</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="H39" s="24" t="s">
+      <c r="F39" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="I39" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="J39" s="24" t="s">
+      <c r="G39" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="H39" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="K39" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="L39" s="25" t="s">
+      <c r="I39" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="J39" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="M39" s="15">
+      <c r="K39" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="M39" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="N39" s="17">
         <f t="shared" si="13"/>
         <v>16000</v>
       </c>
-      <c r="N39" s="15">
+      <c r="O39" s="17">
         <f t="shared" si="14"/>
         <v>16000</v>
       </c>
-      <c r="O39" s="15">
+      <c r="P39" s="17">
         <f t="shared" si="15"/>
         <v>22000</v>
       </c>
-      <c r="P39" s="2">
+      <c r="Q39" s="2">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="Q39" s="2">
-        <v>0</v>
-      </c>
       <c r="R39" s="2">
+        <v>0</v>
+      </c>
+      <c r="S39" s="2">
         <f t="shared" si="17"/>
         <v>270</v>
       </c>
-      <c r="S39" s="2">
+      <c r="T39" s="2">
         <f t="shared" si="18"/>
         <v>330</v>
       </c>
-      <c r="T39" s="2">
+      <c r="U39" s="2">
         <v>99</v>
       </c>
-      <c r="U39" s="2">
+      <c r="V39" s="2">
         <v>100</v>
       </c>
-      <c r="V39" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="W39" s="20"/>
-    </row>
-    <row r="40" customHeight="1" spans="3:22">
+      <c r="W39" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="X39" s="25"/>
+    </row>
+    <row r="40" customHeight="1" spans="3:23">
       <c r="C40" s="1">
         <v>108</v>
       </c>
@@ -3596,64 +3917,65 @@
         <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H40" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="I40" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="J40" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="H40" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="K40" s="22" t="s">
+      <c r="I40" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="J40" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="L40" s="22" t="s">
+      <c r="K40" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="M40" s="14">
+      <c r="L40" s="15"/>
+      <c r="M40" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="N40" s="17">
         <f t="shared" si="13"/>
         <v>17000</v>
       </c>
-      <c r="N40" s="14">
+      <c r="O40" s="17">
         <f t="shared" si="14"/>
         <v>17000</v>
       </c>
-      <c r="O40" s="14">
+      <c r="P40" s="17">
         <f t="shared" si="15"/>
         <v>24000</v>
       </c>
-      <c r="P40" s="12">
+      <c r="Q40" s="19">
         <f t="shared" si="16"/>
         <v>24000</v>
       </c>
-      <c r="Q40" s="12">
-        <v>0</v>
-      </c>
-      <c r="R40" s="12">
+      <c r="R40" s="15">
+        <v>0</v>
+      </c>
+      <c r="S40" s="15">
         <f t="shared" si="17"/>
         <v>290</v>
       </c>
-      <c r="S40" s="12">
+      <c r="T40" s="15">
         <f t="shared" si="18"/>
         <v>360</v>
       </c>
-      <c r="T40" s="12">
+      <c r="U40" s="15">
         <v>99</v>
       </c>
-      <c r="U40" s="12">
+      <c r="V40" s="15">
         <v>100</v>
       </c>
-      <c r="V40" s="23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:22">
+      <c r="W40" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:23">
       <c r="C41" s="1">
         <v>109</v>
       </c>
@@ -3664,64 +3986,65 @@
         <v>9</v>
       </c>
       <c r="F41" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H41" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="I41" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="J41" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="K41" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H41" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="I41" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="J41" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="K41" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="L41" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="M41" s="14">
+      <c r="L41" s="15"/>
+      <c r="M41" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="N41" s="17">
         <f t="shared" si="13"/>
         <v>18000</v>
       </c>
-      <c r="N41" s="14">
+      <c r="O41" s="17">
         <f t="shared" si="14"/>
         <v>18000</v>
       </c>
-      <c r="O41" s="14">
+      <c r="P41" s="17">
         <f t="shared" si="15"/>
         <v>26000</v>
       </c>
-      <c r="P41" s="12">
+      <c r="Q41" s="19">
         <f t="shared" si="16"/>
         <v>26000</v>
       </c>
-      <c r="Q41" s="12">
-        <v>0</v>
-      </c>
-      <c r="R41" s="12">
+      <c r="R41" s="15">
+        <v>0</v>
+      </c>
+      <c r="S41" s="15">
         <f t="shared" si="17"/>
         <v>310</v>
       </c>
-      <c r="S41" s="12">
+      <c r="T41" s="15">
         <f t="shared" si="18"/>
         <v>390</v>
       </c>
-      <c r="T41" s="12">
+      <c r="U41" s="15">
         <v>99</v>
       </c>
-      <c r="U41" s="12">
+      <c r="V41" s="15">
         <v>100</v>
       </c>
-      <c r="V41" s="23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:22">
+      <c r="W41" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:23">
       <c r="C42" s="1">
         <v>110</v>
       </c>
@@ -3732,81 +4055,1521 @@
         <v>10</v>
       </c>
       <c r="F42" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H42" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="I42" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="J42" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="K42" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H42" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="I42" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="J42" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="K42" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="L42" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="M42" s="14">
+      <c r="L42" s="15"/>
+      <c r="M42" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="N42" s="17">
         <f t="shared" si="13"/>
         <v>19000</v>
       </c>
-      <c r="N42" s="14">
+      <c r="O42" s="17">
         <f t="shared" si="14"/>
         <v>19000</v>
       </c>
-      <c r="O42" s="14">
+      <c r="P42" s="17">
         <f t="shared" si="15"/>
         <v>28000</v>
       </c>
-      <c r="P42" s="12">
+      <c r="Q42" s="19">
         <f t="shared" si="16"/>
         <v>28000</v>
       </c>
-      <c r="Q42" s="12">
-        <v>0</v>
-      </c>
-      <c r="R42" s="12">
+      <c r="R42" s="15">
+        <v>0</v>
+      </c>
+      <c r="S42" s="15">
         <f t="shared" si="17"/>
         <v>330</v>
       </c>
-      <c r="S42" s="12">
+      <c r="T42" s="15">
         <f t="shared" si="18"/>
         <v>420</v>
       </c>
-      <c r="T42" s="12">
+      <c r="U42" s="15">
         <v>99</v>
       </c>
-      <c r="U42" s="12">
+      <c r="V42" s="15">
         <v>100</v>
       </c>
-      <c r="V42" s="23" t="s">
+      <c r="W42" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" s="3" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C43" s="13">
+        <v>111</v>
+      </c>
+      <c r="D43" s="13">
+        <v>2</v>
+      </c>
+      <c r="E43" s="13">
+        <v>11</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="H43" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="I43" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="J43" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="K43" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="L43" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="M43" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="N43" s="18">
+        <f t="shared" si="13"/>
+        <v>20000</v>
+      </c>
+      <c r="O43" s="18">
+        <f t="shared" si="14"/>
+        <v>20000</v>
+      </c>
+      <c r="P43" s="18">
+        <f t="shared" si="15"/>
+        <v>30000</v>
+      </c>
+      <c r="Q43" s="3">
+        <f t="shared" si="16"/>
+        <v>30000</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <f t="shared" ref="S43:S52" si="19">S42+30</f>
+        <v>360</v>
+      </c>
+      <c r="T43" s="3">
+        <f t="shared" ref="T43:T52" si="20">T42+40</f>
+        <v>460</v>
+      </c>
+      <c r="U43" s="3">
+        <v>99</v>
+      </c>
+      <c r="V43" s="3">
+        <v>120</v>
+      </c>
+      <c r="W43" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" customHeight="1" spans="3:23">
+      <c r="C44" s="1">
+        <v>112</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1">
+        <v>12</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H44" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="I44" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="J44" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="K44" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="L44" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="M44" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="N44" s="17">
+        <f t="shared" ref="N44:N52" si="21">N43+5000</f>
+        <v>25000</v>
+      </c>
+      <c r="O44" s="17">
+        <f t="shared" ref="O44:O52" si="22">O43+5000</f>
+        <v>25000</v>
+      </c>
+      <c r="P44" s="17">
+        <f t="shared" ref="P44:P52" si="23">P43+4000</f>
+        <v>34000</v>
+      </c>
+      <c r="Q44" s="17">
+        <f t="shared" ref="Q44:Q52" si="24">Q43+4000</f>
+        <v>34000</v>
+      </c>
+      <c r="R44" s="15">
+        <v>0</v>
+      </c>
+      <c r="S44" s="15">
+        <f t="shared" si="19"/>
+        <v>390</v>
+      </c>
+      <c r="T44" s="15">
+        <f t="shared" si="20"/>
+        <v>500</v>
+      </c>
+      <c r="U44" s="15">
+        <v>99</v>
+      </c>
+      <c r="V44" s="15">
+        <v>140</v>
+      </c>
+      <c r="W44" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:23">
+      <c r="C45" s="1">
+        <v>113</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2</v>
+      </c>
+      <c r="E45" s="1">
+        <v>13</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H45" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="I45" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="J45" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="K45" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="L45" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="M45" s="29" t="s">
+        <v>175</v>
+      </c>
+      <c r="N45" s="17">
+        <f t="shared" si="21"/>
+        <v>30000</v>
+      </c>
+      <c r="O45" s="17">
+        <f t="shared" si="22"/>
+        <v>30000</v>
+      </c>
+      <c r="P45" s="17">
+        <f t="shared" si="23"/>
+        <v>38000</v>
+      </c>
+      <c r="Q45" s="17">
+        <f t="shared" si="24"/>
+        <v>38000</v>
+      </c>
+      <c r="R45" s="15">
+        <v>0</v>
+      </c>
+      <c r="S45" s="15">
+        <f t="shared" si="19"/>
+        <v>420</v>
+      </c>
+      <c r="T45" s="15">
+        <f t="shared" si="20"/>
+        <v>540</v>
+      </c>
+      <c r="U45" s="15">
+        <v>99</v>
+      </c>
+      <c r="V45" s="15">
+        <f t="shared" ref="V45:V52" si="25">V44+20</f>
+        <v>160</v>
+      </c>
+      <c r="W45" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:23">
+      <c r="C46" s="1">
+        <v>114</v>
+      </c>
+      <c r="D46" s="1">
+        <v>2</v>
+      </c>
+      <c r="E46" s="1">
+        <v>14</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H46" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="I46" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="J46" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="K46" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="L46" s="35" t="s">
+        <v>181</v>
+      </c>
+      <c r="M46" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="N46" s="17">
+        <f t="shared" si="21"/>
+        <v>35000</v>
+      </c>
+      <c r="O46" s="17">
+        <f t="shared" si="22"/>
+        <v>35000</v>
+      </c>
+      <c r="P46" s="17">
+        <f t="shared" si="23"/>
+        <v>42000</v>
+      </c>
+      <c r="Q46" s="17">
+        <f t="shared" si="24"/>
+        <v>42000</v>
+      </c>
+      <c r="R46" s="15">
+        <v>0</v>
+      </c>
+      <c r="S46" s="15">
+        <f t="shared" si="19"/>
+        <v>450</v>
+      </c>
+      <c r="T46" s="15">
+        <f t="shared" si="20"/>
+        <v>580</v>
+      </c>
+      <c r="U46" s="15">
+        <v>99</v>
+      </c>
+      <c r="V46" s="15">
+        <f t="shared" si="25"/>
+        <v>180</v>
+      </c>
+      <c r="W46" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:23">
+      <c r="C47" s="1">
+        <v>115</v>
+      </c>
+      <c r="D47" s="1">
+        <v>2</v>
+      </c>
+      <c r="E47" s="1">
+        <v>15</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H47" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="I47" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="J47" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="K47" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="L47" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="M47" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="N47" s="17">
+        <f t="shared" si="21"/>
+        <v>40000</v>
+      </c>
+      <c r="O47" s="17">
+        <f t="shared" si="22"/>
+        <v>40000</v>
+      </c>
+      <c r="P47" s="17">
+        <f t="shared" si="23"/>
+        <v>46000</v>
+      </c>
+      <c r="Q47" s="17">
+        <f t="shared" si="24"/>
+        <v>46000</v>
+      </c>
+      <c r="R47" s="15">
+        <v>0</v>
+      </c>
+      <c r="S47" s="15">
+        <f t="shared" si="19"/>
+        <v>480</v>
+      </c>
+      <c r="T47" s="15">
+        <f t="shared" si="20"/>
+        <v>620</v>
+      </c>
+      <c r="U47" s="15">
+        <v>99</v>
+      </c>
+      <c r="V47" s="15">
+        <f t="shared" si="25"/>
+        <v>200</v>
+      </c>
+      <c r="W47" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:23">
+      <c r="C48" s="1">
+        <v>116</v>
+      </c>
+      <c r="D48" s="1">
+        <v>2</v>
+      </c>
+      <c r="E48" s="1">
+        <v>16</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H48" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="I48" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="J48" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="K48" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="L48" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="M48" s="29" t="s">
+        <v>195</v>
+      </c>
+      <c r="N48" s="17">
+        <f t="shared" si="21"/>
+        <v>45000</v>
+      </c>
+      <c r="O48" s="17">
+        <f t="shared" si="22"/>
+        <v>45000</v>
+      </c>
+      <c r="P48" s="17">
+        <f t="shared" si="23"/>
+        <v>50000</v>
+      </c>
+      <c r="Q48" s="17">
+        <f t="shared" si="24"/>
+        <v>50000</v>
+      </c>
+      <c r="R48" s="15">
+        <v>0</v>
+      </c>
+      <c r="S48" s="15">
+        <f t="shared" si="19"/>
+        <v>510</v>
+      </c>
+      <c r="T48" s="15">
+        <f t="shared" si="20"/>
+        <v>660</v>
+      </c>
+      <c r="U48" s="15">
+        <v>99</v>
+      </c>
+      <c r="V48" s="15">
+        <f t="shared" si="25"/>
+        <v>220</v>
+      </c>
+      <c r="W48" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:23">
+      <c r="C49" s="1">
         <v>117</v>
       </c>
-    </row>
-    <row r="43" customHeight="1" spans="12:16">
-      <c r="L43" s="12"/>
-      <c r="P43" s="12"/>
-    </row>
-    <row r="44" customHeight="1" spans="12:16">
-      <c r="L44" s="12"/>
-      <c r="P44" s="12"/>
-    </row>
-    <row r="45" customHeight="1" spans="12:16">
-      <c r="L45" s="12"/>
-      <c r="P45" s="12"/>
-    </row>
-    <row r="53" customHeight="1" spans="8:8">
-      <c r="H53" s="9"/>
+      <c r="D49" s="1">
+        <v>2</v>
+      </c>
+      <c r="E49" s="1">
+        <v>17</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H49" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="I49" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="J49" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="K49" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="L49" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="M49" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="N49" s="17">
+        <f t="shared" si="21"/>
+        <v>50000</v>
+      </c>
+      <c r="O49" s="17">
+        <f t="shared" si="22"/>
+        <v>50000</v>
+      </c>
+      <c r="P49" s="17">
+        <f t="shared" si="23"/>
+        <v>54000</v>
+      </c>
+      <c r="Q49" s="17">
+        <f t="shared" si="24"/>
+        <v>54000</v>
+      </c>
+      <c r="R49" s="15">
+        <v>0</v>
+      </c>
+      <c r="S49" s="15">
+        <f t="shared" si="19"/>
+        <v>540</v>
+      </c>
+      <c r="T49" s="15">
+        <f t="shared" si="20"/>
+        <v>700</v>
+      </c>
+      <c r="U49" s="15">
+        <v>99</v>
+      </c>
+      <c r="V49" s="15">
+        <f t="shared" si="25"/>
+        <v>240</v>
+      </c>
+      <c r="W49" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:23">
+      <c r="C50" s="1">
+        <v>118</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2</v>
+      </c>
+      <c r="E50" s="1">
+        <v>18</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H50" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="I50" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="J50" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="K50" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="L50" s="35" t="s">
+        <v>206</v>
+      </c>
+      <c r="M50" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="N50" s="17">
+        <f t="shared" si="21"/>
+        <v>55000</v>
+      </c>
+      <c r="O50" s="17">
+        <f t="shared" si="22"/>
+        <v>55000</v>
+      </c>
+      <c r="P50" s="17">
+        <f t="shared" si="23"/>
+        <v>58000</v>
+      </c>
+      <c r="Q50" s="17">
+        <f t="shared" si="24"/>
+        <v>58000</v>
+      </c>
+      <c r="R50" s="15">
+        <v>0</v>
+      </c>
+      <c r="S50" s="15">
+        <f t="shared" si="19"/>
+        <v>570</v>
+      </c>
+      <c r="T50" s="15">
+        <f t="shared" si="20"/>
+        <v>740</v>
+      </c>
+      <c r="U50" s="15">
+        <v>99</v>
+      </c>
+      <c r="V50" s="15">
+        <f t="shared" si="25"/>
+        <v>260</v>
+      </c>
+      <c r="W50" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:23">
+      <c r="C51" s="1">
+        <v>119</v>
+      </c>
+      <c r="D51" s="1">
+        <v>2</v>
+      </c>
+      <c r="E51" s="1">
+        <v>19</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H51" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="I51" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="J51" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="K51" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="L51" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="M51" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="N51" s="17">
+        <f t="shared" si="21"/>
+        <v>60000</v>
+      </c>
+      <c r="O51" s="17">
+        <f t="shared" si="22"/>
+        <v>60000</v>
+      </c>
+      <c r="P51" s="17">
+        <f t="shared" si="23"/>
+        <v>62000</v>
+      </c>
+      <c r="Q51" s="17">
+        <f t="shared" si="24"/>
+        <v>62000</v>
+      </c>
+      <c r="R51" s="15">
+        <v>0</v>
+      </c>
+      <c r="S51" s="15">
+        <f t="shared" si="19"/>
+        <v>600</v>
+      </c>
+      <c r="T51" s="15">
+        <f t="shared" si="20"/>
+        <v>780</v>
+      </c>
+      <c r="U51" s="15">
+        <v>99</v>
+      </c>
+      <c r="V51" s="15">
+        <f t="shared" si="25"/>
+        <v>280</v>
+      </c>
+      <c r="W51" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:23">
+      <c r="C52" s="1">
+        <v>120</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2</v>
+      </c>
+      <c r="E52" s="1">
+        <v>20</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H52" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="I52" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="J52" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="K52" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="L52" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="M52" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="N52" s="17">
+        <f t="shared" si="21"/>
+        <v>65000</v>
+      </c>
+      <c r="O52" s="17">
+        <f t="shared" si="22"/>
+        <v>65000</v>
+      </c>
+      <c r="P52" s="17">
+        <f t="shared" si="23"/>
+        <v>66000</v>
+      </c>
+      <c r="Q52" s="17">
+        <f t="shared" si="24"/>
+        <v>66000</v>
+      </c>
+      <c r="R52" s="15">
+        <v>0</v>
+      </c>
+      <c r="S52" s="15">
+        <f t="shared" si="19"/>
+        <v>630</v>
+      </c>
+      <c r="T52" s="15">
+        <f t="shared" si="20"/>
+        <v>820</v>
+      </c>
+      <c r="U52" s="15">
+        <v>99</v>
+      </c>
+      <c r="V52" s="15">
+        <f t="shared" si="25"/>
+        <v>300</v>
+      </c>
+      <c r="W52" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="13:17">
+      <c r="M53" s="15"/>
+      <c r="N53" s="19"/>
+      <c r="O53" s="19"/>
+      <c r="P53" s="19"/>
+      <c r="Q53" s="19"/>
+    </row>
+    <row r="54" customHeight="1" spans="13:17">
+      <c r="M54" s="15"/>
+      <c r="N54" s="19"/>
+      <c r="O54" s="19"/>
+      <c r="P54" s="19"/>
+      <c r="Q54" s="19"/>
+    </row>
+    <row r="55" customHeight="1" spans="13:17">
+      <c r="M55" s="15"/>
+      <c r="N55" s="19"/>
+      <c r="O55" s="19"/>
+      <c r="P55" s="19"/>
+      <c r="Q55" s="19"/>
+    </row>
+    <row r="56" customHeight="1" spans="3:23">
+      <c r="C56" s="1">
+        <v>201</v>
+      </c>
+      <c r="D56" s="1">
+        <v>3</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H56" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="I56" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="J56" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="K56" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="L56" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="M56" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="N56" s="17">
+        <v>100000</v>
+      </c>
+      <c r="O56" s="17">
+        <v>100000</v>
+      </c>
+      <c r="P56" s="17">
+        <v>100000</v>
+      </c>
+      <c r="Q56" s="17">
+        <v>100000</v>
+      </c>
+      <c r="R56" s="15">
+        <v>0</v>
+      </c>
+      <c r="S56" s="22">
+        <v>400</v>
+      </c>
+      <c r="T56" s="15">
+        <v>600</v>
+      </c>
+      <c r="U56" s="15">
+        <v>99</v>
+      </c>
+      <c r="V56" s="15">
+        <v>200</v>
+      </c>
+      <c r="W56" s="30" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:23">
+      <c r="C57" s="1">
+        <v>202</v>
+      </c>
+      <c r="D57" s="1">
+        <v>3</v>
+      </c>
+      <c r="E57" s="1">
+        <v>2</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H57" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="I57" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="J57" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="K57" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="L57" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="M57" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="N57" s="17">
+        <f t="shared" ref="N57:Q57" si="26">N56+20000</f>
+        <v>120000</v>
+      </c>
+      <c r="O57" s="17">
+        <f t="shared" si="26"/>
+        <v>120000</v>
+      </c>
+      <c r="P57" s="17">
+        <f t="shared" si="26"/>
+        <v>120000</v>
+      </c>
+      <c r="Q57" s="17">
+        <f t="shared" si="26"/>
+        <v>120000</v>
+      </c>
+      <c r="R57" s="15">
+        <v>0</v>
+      </c>
+      <c r="S57" s="15">
+        <f t="shared" ref="S57:S65" si="27">S56+30</f>
+        <v>430</v>
+      </c>
+      <c r="T57" s="15">
+        <f t="shared" ref="T57:T65" si="28">T56+30</f>
+        <v>630</v>
+      </c>
+      <c r="U57" s="15">
+        <v>99</v>
+      </c>
+      <c r="V57" s="15">
+        <f t="shared" ref="V57:V65" si="29">V56+20</f>
+        <v>220</v>
+      </c>
+      <c r="W57" s="30" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:23">
+      <c r="C58" s="1">
+        <v>203</v>
+      </c>
+      <c r="D58" s="1">
+        <v>3</v>
+      </c>
+      <c r="E58" s="1">
+        <v>3</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H58" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="I58" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="J58" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="K58" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="L58" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="M58" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="N58" s="17">
+        <f t="shared" ref="N58:Q58" si="30">N57+20000</f>
+        <v>140000</v>
+      </c>
+      <c r="O58" s="17">
+        <f t="shared" si="30"/>
+        <v>140000</v>
+      </c>
+      <c r="P58" s="17">
+        <f t="shared" si="30"/>
+        <v>140000</v>
+      </c>
+      <c r="Q58" s="17">
+        <f t="shared" si="30"/>
+        <v>140000</v>
+      </c>
+      <c r="R58" s="15">
+        <v>0</v>
+      </c>
+      <c r="S58" s="15">
+        <f t="shared" si="27"/>
+        <v>460</v>
+      </c>
+      <c r="T58" s="15">
+        <f t="shared" si="28"/>
+        <v>660</v>
+      </c>
+      <c r="U58" s="15">
+        <v>99</v>
+      </c>
+      <c r="V58" s="15">
+        <f t="shared" si="29"/>
+        <v>240</v>
+      </c>
+      <c r="W58" s="30" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:23">
+      <c r="C59" s="1">
+        <v>204</v>
+      </c>
+      <c r="D59" s="1">
+        <v>3</v>
+      </c>
+      <c r="E59" s="1">
+        <v>4</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H59" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="I59" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="J59" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="K59" s="29" t="s">
+        <v>232</v>
+      </c>
+      <c r="L59" s="29" t="s">
+        <v>232</v>
+      </c>
+      <c r="M59" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="N59" s="17">
+        <f t="shared" ref="N59:Q59" si="31">N58+20000</f>
+        <v>160000</v>
+      </c>
+      <c r="O59" s="17">
+        <f t="shared" si="31"/>
+        <v>160000</v>
+      </c>
+      <c r="P59" s="17">
+        <f t="shared" si="31"/>
+        <v>160000</v>
+      </c>
+      <c r="Q59" s="17">
+        <f t="shared" si="31"/>
+        <v>160000</v>
+      </c>
+      <c r="R59" s="15">
+        <v>0</v>
+      </c>
+      <c r="S59" s="15">
+        <f t="shared" si="27"/>
+        <v>490</v>
+      </c>
+      <c r="T59" s="15">
+        <f t="shared" si="28"/>
+        <v>690</v>
+      </c>
+      <c r="U59" s="15">
+        <v>99</v>
+      </c>
+      <c r="V59" s="15">
+        <f t="shared" si="29"/>
+        <v>260</v>
+      </c>
+      <c r="W59" s="30" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:23">
+      <c r="C60" s="1">
+        <v>205</v>
+      </c>
+      <c r="D60" s="1">
+        <v>3</v>
+      </c>
+      <c r="E60" s="1">
+        <v>5</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H60" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="I60" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="J60" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="K60" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="L60" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="M60" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="N60" s="17">
+        <f t="shared" ref="N60:Q60" si="32">N59+20000</f>
+        <v>180000</v>
+      </c>
+      <c r="O60" s="17">
+        <f t="shared" si="32"/>
+        <v>180000</v>
+      </c>
+      <c r="P60" s="17">
+        <f t="shared" si="32"/>
+        <v>180000</v>
+      </c>
+      <c r="Q60" s="17">
+        <f t="shared" si="32"/>
+        <v>180000</v>
+      </c>
+      <c r="R60" s="15">
+        <v>0</v>
+      </c>
+      <c r="S60" s="15">
+        <f t="shared" si="27"/>
+        <v>520</v>
+      </c>
+      <c r="T60" s="15">
+        <f t="shared" si="28"/>
+        <v>720</v>
+      </c>
+      <c r="U60" s="15">
+        <v>99</v>
+      </c>
+      <c r="V60" s="15">
+        <f t="shared" si="29"/>
+        <v>280</v>
+      </c>
+      <c r="W60" s="30" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:23">
+      <c r="C61" s="1">
+        <v>206</v>
+      </c>
+      <c r="D61" s="1">
+        <v>3</v>
+      </c>
+      <c r="E61" s="1">
+        <v>6</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H61" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="I61" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="J61" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="K61" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="L61" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="M61" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="N61" s="17">
+        <f t="shared" ref="N61:Q61" si="33">N60+20000</f>
+        <v>200000</v>
+      </c>
+      <c r="O61" s="17">
+        <f t="shared" si="33"/>
+        <v>200000</v>
+      </c>
+      <c r="P61" s="17">
+        <f t="shared" si="33"/>
+        <v>200000</v>
+      </c>
+      <c r="Q61" s="17">
+        <f t="shared" si="33"/>
+        <v>200000</v>
+      </c>
+      <c r="R61" s="15">
+        <v>0</v>
+      </c>
+      <c r="S61" s="15">
+        <f t="shared" si="27"/>
+        <v>550</v>
+      </c>
+      <c r="T61" s="15">
+        <f t="shared" si="28"/>
+        <v>750</v>
+      </c>
+      <c r="U61" s="15">
+        <v>99</v>
+      </c>
+      <c r="V61" s="15">
+        <f t="shared" si="29"/>
+        <v>300</v>
+      </c>
+      <c r="W61" s="30" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="62" s="3" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C62" s="1">
+        <v>207</v>
+      </c>
+      <c r="D62" s="1">
+        <v>3</v>
+      </c>
+      <c r="E62" s="13">
+        <v>7</v>
+      </c>
+      <c r="F62" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H62" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="I62" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="J62" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="K62" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="L62" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="M62" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="N62" s="17">
+        <f t="shared" ref="N62:Q62" si="34">N61+20000</f>
+        <v>220000</v>
+      </c>
+      <c r="O62" s="17">
+        <f t="shared" si="34"/>
+        <v>220000</v>
+      </c>
+      <c r="P62" s="17">
+        <f t="shared" si="34"/>
+        <v>220000</v>
+      </c>
+      <c r="Q62" s="17">
+        <f t="shared" si="34"/>
+        <v>220000</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="15">
+        <f t="shared" si="27"/>
+        <v>580</v>
+      </c>
+      <c r="T62" s="15">
+        <f t="shared" si="28"/>
+        <v>780</v>
+      </c>
+      <c r="U62" s="3">
+        <v>99</v>
+      </c>
+      <c r="V62" s="15">
+        <f t="shared" si="29"/>
+        <v>320</v>
+      </c>
+      <c r="W62" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="X62" s="27"/>
+    </row>
+    <row r="63" customHeight="1" spans="3:23">
+      <c r="C63" s="1">
+        <v>208</v>
+      </c>
+      <c r="D63" s="1">
+        <v>3</v>
+      </c>
+      <c r="E63" s="1">
+        <v>8</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H63" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="I63" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="J63" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="K63" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="L63" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="M63" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="N63" s="17">
+        <f t="shared" ref="N63:Q63" si="35">N62+20000</f>
+        <v>240000</v>
+      </c>
+      <c r="O63" s="17">
+        <f t="shared" si="35"/>
+        <v>240000</v>
+      </c>
+      <c r="P63" s="17">
+        <f t="shared" si="35"/>
+        <v>240000</v>
+      </c>
+      <c r="Q63" s="17">
+        <f t="shared" si="35"/>
+        <v>240000</v>
+      </c>
+      <c r="R63" s="15">
+        <v>0</v>
+      </c>
+      <c r="S63" s="15">
+        <f t="shared" si="27"/>
+        <v>610</v>
+      </c>
+      <c r="T63" s="15">
+        <f t="shared" si="28"/>
+        <v>810</v>
+      </c>
+      <c r="U63" s="15">
+        <v>99</v>
+      </c>
+      <c r="V63" s="15">
+        <f t="shared" si="29"/>
+        <v>340</v>
+      </c>
+      <c r="W63" s="30" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:23">
+      <c r="C64" s="1">
+        <v>209</v>
+      </c>
+      <c r="D64" s="1">
+        <v>3</v>
+      </c>
+      <c r="E64" s="1">
+        <v>9</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H64" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="I64" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="J64" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="K64" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="L64" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="M64" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="N64" s="17">
+        <f t="shared" ref="N64:Q64" si="36">N63+20000</f>
+        <v>260000</v>
+      </c>
+      <c r="O64" s="17">
+        <f t="shared" si="36"/>
+        <v>260000</v>
+      </c>
+      <c r="P64" s="17">
+        <f t="shared" si="36"/>
+        <v>260000</v>
+      </c>
+      <c r="Q64" s="17">
+        <f t="shared" si="36"/>
+        <v>260000</v>
+      </c>
+      <c r="R64" s="15">
+        <v>0</v>
+      </c>
+      <c r="S64" s="15">
+        <f t="shared" si="27"/>
+        <v>640</v>
+      </c>
+      <c r="T64" s="15">
+        <f t="shared" si="28"/>
+        <v>840</v>
+      </c>
+      <c r="U64" s="15">
+        <v>99</v>
+      </c>
+      <c r="V64" s="15">
+        <f t="shared" si="29"/>
+        <v>360</v>
+      </c>
+      <c r="W64" s="30" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:23">
+      <c r="C65" s="1">
+        <v>210</v>
+      </c>
+      <c r="D65" s="1">
+        <v>3</v>
+      </c>
+      <c r="E65" s="1">
+        <v>10</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H65" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="I65" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="J65" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="K65" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="L65" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="M65" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="N65" s="17">
+        <f t="shared" ref="N65:Q65" si="37">N64+20000</f>
+        <v>280000</v>
+      </c>
+      <c r="O65" s="17">
+        <f t="shared" si="37"/>
+        <v>280000</v>
+      </c>
+      <c r="P65" s="17">
+        <f t="shared" si="37"/>
+        <v>280000</v>
+      </c>
+      <c r="Q65" s="17">
+        <f t="shared" si="37"/>
+        <v>280000</v>
+      </c>
+      <c r="R65" s="15">
+        <v>0</v>
+      </c>
+      <c r="S65" s="15">
+        <f t="shared" si="27"/>
+        <v>670</v>
+      </c>
+      <c r="T65" s="15">
+        <f t="shared" si="28"/>
+        <v>870</v>
+      </c>
+      <c r="U65" s="15">
+        <v>99</v>
+      </c>
+      <c r="V65" s="15">
+        <f t="shared" si="29"/>
+        <v>380</v>
+      </c>
+      <c r="W65" s="30" t="s">
+        <v>224</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:V5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3 L4 L5 C3:K5 M3:W5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterPillConfig.xlsx
+++ b/Excel/MonsterPillConfig.xlsx
@@ -1424,7 +1424,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1447,35 +1447,24 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1932,7 +1921,7 @@
       <c r="V3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="20" t="s">
+      <c r="W3" s="17" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1999,7 +1988,7 @@
       <c r="V4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="W4" s="20" t="s">
+      <c r="W4" s="17" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2066,7 +2055,7 @@
       <c r="V5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="W5" s="20" t="s">
+      <c r="W5" s="17" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2086,50 +2075,50 @@
       <c r="G6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="28" t="s">
+      <c r="I6" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="28" t="s">
+      <c r="J6" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="K6" s="15">
-        <v>0</v>
-      </c>
-      <c r="L6" s="15"/>
-      <c r="M6" s="16">
-        <v>0</v>
-      </c>
-      <c r="N6" s="15">
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="14">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
         <v>500</v>
       </c>
-      <c r="O6" s="15">
+      <c r="O6" s="2">
         <v>500</v>
       </c>
-      <c r="P6" s="15">
+      <c r="P6" s="2">
         <v>1500</v>
       </c>
-      <c r="Q6" s="15">
-        <v>0</v>
-      </c>
-      <c r="R6" s="15">
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2">
         <v>20</v>
       </c>
-      <c r="S6" s="15">
+      <c r="S6" s="2">
         <v>30</v>
       </c>
-      <c r="T6" s="15">
-        <v>0</v>
-      </c>
-      <c r="U6" s="15">
-        <v>0</v>
-      </c>
-      <c r="V6" s="15">
-        <v>0</v>
-      </c>
-      <c r="W6" s="29" t="s">
+      <c r="T6" s="2">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0</v>
+      </c>
+      <c r="W6" s="25" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2149,55 +2138,55 @@
       <c r="G7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="28" t="s">
+      <c r="I7" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="28" t="s">
+      <c r="J7" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="15">
-        <v>0</v>
-      </c>
-      <c r="L7" s="15"/>
-      <c r="M7" s="16">
-        <v>0</v>
-      </c>
-      <c r="N7" s="15">
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="14">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
         <f t="shared" ref="N7:N17" si="0">N6+200</f>
         <v>700</v>
       </c>
-      <c r="O7" s="15">
+      <c r="O7" s="2">
         <f t="shared" ref="O7:O17" si="1">O6+200</f>
         <v>700</v>
       </c>
-      <c r="P7" s="15">
+      <c r="P7" s="2">
         <f t="shared" ref="P7:P25" si="2">P6+200</f>
         <v>1700</v>
       </c>
-      <c r="Q7" s="15">
-        <v>0</v>
-      </c>
-      <c r="R7" s="15">
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
         <f t="shared" ref="R7:R25" si="3">R6+2</f>
         <v>22</v>
       </c>
-      <c r="S7" s="15">
+      <c r="S7" s="2">
         <f t="shared" ref="S7:S12" si="4">S6+5</f>
         <v>35</v>
       </c>
-      <c r="T7" s="15">
-        <v>0</v>
-      </c>
-      <c r="U7" s="15">
-        <v>0</v>
-      </c>
-      <c r="V7" s="15">
-        <v>0</v>
-      </c>
-      <c r="W7" s="29" t="s">
+      <c r="T7" s="2">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="25" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2217,55 +2206,55 @@
       <c r="G8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="28" t="s">
+      <c r="H8" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="28" t="s">
+      <c r="I8" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="28" t="s">
+      <c r="J8" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="K8" s="15">
-        <v>0</v>
-      </c>
-      <c r="L8" s="15"/>
-      <c r="M8" s="16">
-        <v>0</v>
-      </c>
-      <c r="N8" s="15">
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="14">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="O8" s="15">
+      <c r="O8" s="2">
         <f t="shared" si="1"/>
         <v>900</v>
       </c>
-      <c r="P8" s="15">
+      <c r="P8" s="2">
         <f t="shared" si="2"/>
         <v>1900</v>
       </c>
-      <c r="Q8" s="15">
-        <v>0</v>
-      </c>
-      <c r="R8" s="15">
+      <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="S8" s="15">
+      <c r="S8" s="2">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="T8" s="15">
-        <v>0</v>
-      </c>
-      <c r="U8" s="15">
-        <v>0</v>
-      </c>
-      <c r="V8" s="15">
-        <v>0</v>
-      </c>
-      <c r="W8" s="29" t="s">
+      <c r="T8" s="2">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0</v>
+      </c>
+      <c r="W8" s="25" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2285,55 +2274,55 @@
       <c r="G9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="H9" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="I9" s="28" t="s">
+      <c r="I9" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="J9" s="28" t="s">
+      <c r="J9" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="K9" s="15">
-        <v>0</v>
-      </c>
-      <c r="L9" s="15"/>
-      <c r="M9" s="16">
-        <v>0</v>
-      </c>
-      <c r="N9" s="15">
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2"/>
+      <c r="M9" s="14">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="O9" s="15">
+      <c r="O9" s="2">
         <f t="shared" si="1"/>
         <v>1100</v>
       </c>
-      <c r="P9" s="15">
+      <c r="P9" s="2">
         <f t="shared" si="2"/>
         <v>2100</v>
       </c>
-      <c r="Q9" s="15">
-        <v>0</v>
-      </c>
-      <c r="R9" s="15">
+      <c r="Q9" s="2">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="S9" s="15">
+      <c r="S9" s="2">
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="T9" s="15">
-        <v>0</v>
-      </c>
-      <c r="U9" s="15">
-        <v>0</v>
-      </c>
-      <c r="V9" s="15">
-        <v>0</v>
-      </c>
-      <c r="W9" s="29" t="s">
+      <c r="T9" s="2">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2">
+        <v>0</v>
+      </c>
+      <c r="W9" s="25" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2353,55 +2342,55 @@
       <c r="G10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="28" t="s">
+      <c r="H10" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="I10" s="28" t="s">
+      <c r="I10" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="J10" s="28" t="s">
+      <c r="J10" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="K10" s="15">
-        <v>0</v>
-      </c>
-      <c r="L10" s="15"/>
-      <c r="M10" s="16">
-        <v>0</v>
-      </c>
-      <c r="N10" s="15">
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2"/>
+      <c r="M10" s="14">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2">
         <f t="shared" si="0"/>
         <v>1300</v>
       </c>
-      <c r="O10" s="15">
+      <c r="O10" s="2">
         <f t="shared" si="1"/>
         <v>1300</v>
       </c>
-      <c r="P10" s="15">
+      <c r="P10" s="2">
         <f t="shared" si="2"/>
         <v>2300</v>
       </c>
-      <c r="Q10" s="15">
-        <v>0</v>
-      </c>
-      <c r="R10" s="15">
+      <c r="Q10" s="2">
+        <v>0</v>
+      </c>
+      <c r="R10" s="2">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="S10" s="15">
+      <c r="S10" s="2">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="T10" s="15">
-        <v>0</v>
-      </c>
-      <c r="U10" s="15">
-        <v>0</v>
-      </c>
-      <c r="V10" s="15">
-        <v>0</v>
-      </c>
-      <c r="W10" s="29" t="s">
+      <c r="T10" s="2">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2">
+        <v>0</v>
+      </c>
+      <c r="W10" s="25" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2421,55 +2410,55 @@
       <c r="G11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="28" t="s">
+      <c r="H11" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="I11" s="28" t="s">
+      <c r="I11" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="28" t="s">
+      <c r="J11" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="K11" s="15">
-        <v>0</v>
-      </c>
-      <c r="L11" s="15"/>
-      <c r="M11" s="16">
-        <v>0</v>
-      </c>
-      <c r="N11" s="15">
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2"/>
+      <c r="M11" s="14">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="O11" s="15">
+      <c r="O11" s="2">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="P11" s="15">
+      <c r="P11" s="2">
         <f t="shared" si="2"/>
         <v>2500</v>
       </c>
-      <c r="Q11" s="15">
-        <v>0</v>
-      </c>
-      <c r="R11" s="15">
+      <c r="Q11" s="2">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="S11" s="15">
+      <c r="S11" s="2">
         <f t="shared" si="4"/>
         <v>55</v>
       </c>
-      <c r="T11" s="15">
-        <v>0</v>
-      </c>
-      <c r="U11" s="15">
-        <v>0</v>
-      </c>
-      <c r="V11" s="15">
-        <v>0</v>
-      </c>
-      <c r="W11" s="21"/>
+      <c r="T11" s="2">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2">
+        <v>0</v>
+      </c>
+      <c r="W11" s="18"/>
     </row>
     <row r="12" customHeight="1" spans="3:23">
       <c r="C12" s="1">
@@ -2487,55 +2476,55 @@
       <c r="G12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="28" t="s">
+      <c r="H12" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="I12" s="28" t="s">
+      <c r="I12" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="28" t="s">
+      <c r="J12" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="K12" s="15">
-        <v>0</v>
-      </c>
-      <c r="L12" s="15"/>
-      <c r="M12" s="16">
-        <v>0</v>
-      </c>
-      <c r="N12" s="15">
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2"/>
+      <c r="M12" s="14">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2">
         <f t="shared" si="0"/>
         <v>1700</v>
       </c>
-      <c r="O12" s="15">
+      <c r="O12" s="2">
         <f t="shared" si="1"/>
         <v>1700</v>
       </c>
-      <c r="P12" s="15">
+      <c r="P12" s="2">
         <f t="shared" si="2"/>
         <v>2700</v>
       </c>
-      <c r="Q12" s="15">
-        <v>0</v>
-      </c>
-      <c r="R12" s="15">
+      <c r="Q12" s="2">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2">
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
-      <c r="S12" s="15">
+      <c r="S12" s="2">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="T12" s="15">
-        <v>0</v>
-      </c>
-      <c r="U12" s="15">
-        <v>0</v>
-      </c>
-      <c r="V12" s="15">
-        <v>0</v>
-      </c>
-      <c r="W12" s="29" t="s">
+      <c r="T12" s="2">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2">
+        <v>0</v>
+      </c>
+      <c r="W12" s="25" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2555,55 +2544,55 @@
       <c r="G13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="28" t="s">
+      <c r="H13" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="28" t="s">
+      <c r="I13" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="J13" s="28" t="s">
+      <c r="J13" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="K13" s="15">
-        <v>0</v>
-      </c>
-      <c r="L13" s="15"/>
-      <c r="M13" s="16">
-        <v>0</v>
-      </c>
-      <c r="N13" s="15">
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2"/>
+      <c r="M13" s="14">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2">
         <f t="shared" si="0"/>
         <v>1900</v>
       </c>
-      <c r="O13" s="15">
+      <c r="O13" s="2">
         <f t="shared" si="1"/>
         <v>1900</v>
       </c>
-      <c r="P13" s="15">
+      <c r="P13" s="2">
         <f t="shared" si="2"/>
         <v>2900</v>
       </c>
-      <c r="Q13" s="15">
-        <v>0</v>
-      </c>
-      <c r="R13" s="15">
+      <c r="Q13" s="2">
+        <v>0</v>
+      </c>
+      <c r="R13" s="2">
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="S13" s="15">
+      <c r="S13" s="2">
         <f t="shared" ref="S13:S17" si="5">S12+10</f>
         <v>70</v>
       </c>
-      <c r="T13" s="15">
-        <v>0</v>
-      </c>
-      <c r="U13" s="15">
-        <v>0</v>
-      </c>
-      <c r="V13" s="15">
-        <v>0</v>
-      </c>
-      <c r="W13" s="29" t="s">
+      <c r="T13" s="2">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2">
+        <v>0</v>
+      </c>
+      <c r="W13" s="25" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2623,55 +2612,55 @@
       <c r="G14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H14" s="28" t="s">
+      <c r="H14" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="28" t="s">
+      <c r="I14" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="28" t="s">
+      <c r="J14" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="K14" s="15">
-        <v>0</v>
-      </c>
-      <c r="L14" s="15"/>
-      <c r="M14" s="16">
-        <v>0</v>
-      </c>
-      <c r="N14" s="15">
+      <c r="K14" s="2">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="14">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2">
         <f t="shared" si="0"/>
         <v>2100</v>
       </c>
-      <c r="O14" s="15">
+      <c r="O14" s="2">
         <f t="shared" si="1"/>
         <v>2100</v>
       </c>
-      <c r="P14" s="15">
+      <c r="P14" s="2">
         <f t="shared" si="2"/>
         <v>3100</v>
       </c>
-      <c r="Q14" s="15">
-        <v>0</v>
-      </c>
-      <c r="R14" s="15">
+      <c r="Q14" s="2">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2">
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="S14" s="15">
+      <c r="S14" s="2">
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
-      <c r="T14" s="15">
-        <v>0</v>
-      </c>
-      <c r="U14" s="15">
-        <v>0</v>
-      </c>
-      <c r="V14" s="15">
-        <v>0</v>
-      </c>
-      <c r="W14" s="29" t="s">
+      <c r="T14" s="2">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2">
+        <v>0</v>
+      </c>
+      <c r="W14" s="25" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2691,52 +2680,52 @@
       <c r="G15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="28" t="s">
+      <c r="H15" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="I15" s="28" t="s">
+      <c r="I15" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="J15" s="28" t="s">
+      <c r="J15" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="K15" s="15">
-        <v>0</v>
-      </c>
-      <c r="L15" s="15"/>
-      <c r="M15" s="16">
-        <v>0</v>
-      </c>
-      <c r="N15" s="15">
+      <c r="K15" s="2">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2"/>
+      <c r="M15" s="14">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2">
         <f t="shared" si="0"/>
         <v>2300</v>
       </c>
-      <c r="O15" s="15">
+      <c r="O15" s="2">
         <f t="shared" si="1"/>
         <v>2300</v>
       </c>
-      <c r="P15" s="15">
+      <c r="P15" s="2">
         <f t="shared" si="2"/>
         <v>3300</v>
       </c>
-      <c r="Q15" s="15">
-        <v>0</v>
-      </c>
-      <c r="R15" s="15">
+      <c r="Q15" s="2">
+        <v>0</v>
+      </c>
+      <c r="R15" s="2">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="S15" s="15">
+      <c r="S15" s="2">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="T15" s="15">
-        <v>0</v>
-      </c>
-      <c r="U15" s="15">
-        <v>0</v>
-      </c>
-      <c r="V15" s="15">
+      <c r="T15" s="2">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2756,52 +2745,52 @@
       <c r="G16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H16" s="28" t="s">
+      <c r="H16" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="I16" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="J16" s="28" t="s">
+      <c r="J16" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="K16" s="15">
-        <v>0</v>
-      </c>
-      <c r="L16" s="15"/>
-      <c r="M16" s="16">
-        <v>0</v>
-      </c>
-      <c r="N16" s="15">
+      <c r="K16" s="2">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2"/>
+      <c r="M16" s="14">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2">
         <f t="shared" ref="N16:N25" si="6">N15+400</f>
         <v>2700</v>
       </c>
-      <c r="O16" s="15">
+      <c r="O16" s="2">
         <f t="shared" ref="O16:O25" si="7">O15+400</f>
         <v>2700</v>
       </c>
-      <c r="P16" s="15">
+      <c r="P16" s="2">
         <f t="shared" si="2"/>
         <v>3500</v>
       </c>
-      <c r="Q16" s="15">
-        <v>0</v>
-      </c>
-      <c r="R16" s="15">
+      <c r="Q16" s="2">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="S16" s="15">
+      <c r="S16" s="2">
         <f t="shared" ref="S16:S25" si="8">S15+15</f>
         <v>105</v>
       </c>
-      <c r="T16" s="15">
-        <v>0</v>
-      </c>
-      <c r="U16" s="15">
-        <v>0</v>
-      </c>
-      <c r="V16" s="15">
+      <c r="T16" s="2">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2821,52 +2810,52 @@
       <c r="G17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H17" s="28" t="s">
+      <c r="H17" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="I17" s="28" t="s">
+      <c r="I17" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="J17" s="28" t="s">
+      <c r="J17" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="K17" s="15">
-        <v>0</v>
-      </c>
-      <c r="L17" s="15"/>
-      <c r="M17" s="16">
-        <v>0</v>
-      </c>
-      <c r="N17" s="15">
+      <c r="K17" s="2">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="M17" s="14">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2">
         <f t="shared" si="6"/>
         <v>3100</v>
       </c>
-      <c r="O17" s="15">
+      <c r="O17" s="2">
         <f t="shared" si="7"/>
         <v>3100</v>
       </c>
-      <c r="P17" s="15">
+      <c r="P17" s="2">
         <f t="shared" si="2"/>
         <v>3700</v>
       </c>
-      <c r="Q17" s="15">
-        <v>0</v>
-      </c>
-      <c r="R17" s="15">
+      <c r="Q17" s="2">
+        <v>0</v>
+      </c>
+      <c r="R17" s="2">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="S17" s="15">
+      <c r="S17" s="2">
         <f t="shared" si="8"/>
         <v>120</v>
       </c>
-      <c r="T17" s="15">
-        <v>0</v>
-      </c>
-      <c r="U17" s="15">
-        <v>0</v>
-      </c>
-      <c r="V17" s="15">
+      <c r="T17" s="2">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2886,52 +2875,52 @@
       <c r="G18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H18" s="28" t="s">
+      <c r="H18" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="I18" s="28" t="s">
+      <c r="I18" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="J18" s="28" t="s">
+      <c r="J18" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="K18" s="15">
-        <v>0</v>
-      </c>
-      <c r="L18" s="15"/>
-      <c r="M18" s="16">
-        <v>0</v>
-      </c>
-      <c r="N18" s="15">
+      <c r="K18" s="2">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="14">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2">
         <f t="shared" si="6"/>
         <v>3500</v>
       </c>
-      <c r="O18" s="15">
+      <c r="O18" s="2">
         <f t="shared" si="7"/>
         <v>3500</v>
       </c>
-      <c r="P18" s="15">
+      <c r="P18" s="2">
         <f t="shared" si="2"/>
         <v>3900</v>
       </c>
-      <c r="Q18" s="15">
-        <v>0</v>
-      </c>
-      <c r="R18" s="15">
+      <c r="Q18" s="2">
+        <v>0</v>
+      </c>
+      <c r="R18" s="2">
         <f t="shared" si="3"/>
         <v>44</v>
       </c>
-      <c r="S18" s="15">
+      <c r="S18" s="2">
         <f t="shared" si="8"/>
         <v>135</v>
       </c>
-      <c r="T18" s="15">
-        <v>0</v>
-      </c>
-      <c r="U18" s="15">
-        <v>0</v>
-      </c>
-      <c r="V18" s="15">
+      <c r="T18" s="2">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2951,52 +2940,52 @@
       <c r="G19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="28" t="s">
+      <c r="H19" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="I19" s="28" t="s">
+      <c r="I19" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="J19" s="28" t="s">
+      <c r="J19" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="K19" s="15">
-        <v>0</v>
-      </c>
-      <c r="L19" s="15"/>
-      <c r="M19" s="16">
-        <v>0</v>
-      </c>
-      <c r="N19" s="15">
+      <c r="K19" s="2">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" s="14">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2">
         <f t="shared" si="6"/>
         <v>3900</v>
       </c>
-      <c r="O19" s="15">
+      <c r="O19" s="2">
         <f t="shared" si="7"/>
         <v>3900</v>
       </c>
-      <c r="P19" s="15">
+      <c r="P19" s="2">
         <f t="shared" si="2"/>
         <v>4100</v>
       </c>
-      <c r="Q19" s="15">
-        <v>0</v>
-      </c>
-      <c r="R19" s="15">
+      <c r="Q19" s="2">
+        <v>0</v>
+      </c>
+      <c r="R19" s="2">
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
-      <c r="S19" s="15">
+      <c r="S19" s="2">
         <f t="shared" si="8"/>
         <v>150</v>
       </c>
-      <c r="T19" s="15">
-        <v>0</v>
-      </c>
-      <c r="U19" s="15">
-        <v>0</v>
-      </c>
-      <c r="V19" s="15">
+      <c r="T19" s="2">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3025,43 +3014,43 @@
       <c r="J20" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="K20" s="15">
-        <v>0</v>
-      </c>
-      <c r="L20" s="15"/>
-      <c r="M20" s="16">
-        <v>0</v>
-      </c>
-      <c r="N20" s="15">
+      <c r="K20" s="2">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" s="14">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2">
         <f t="shared" si="6"/>
         <v>4300</v>
       </c>
-      <c r="O20" s="15">
+      <c r="O20" s="2">
         <f t="shared" si="7"/>
         <v>4300</v>
       </c>
-      <c r="P20" s="15">
+      <c r="P20" s="2">
         <f t="shared" si="2"/>
         <v>4300</v>
       </c>
-      <c r="Q20" s="15">
-        <v>0</v>
-      </c>
-      <c r="R20" s="15">
+      <c r="Q20" s="2">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2">
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="S20" s="15">
+      <c r="S20" s="2">
         <f t="shared" si="8"/>
         <v>165</v>
       </c>
-      <c r="T20" s="15">
-        <v>0</v>
-      </c>
-      <c r="U20" s="15">
-        <v>0</v>
-      </c>
-      <c r="V20" s="15">
+      <c r="T20" s="2">
+        <v>0</v>
+      </c>
+      <c r="U20" s="2">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3090,43 +3079,43 @@
       <c r="J21" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="K21" s="15">
-        <v>0</v>
-      </c>
-      <c r="L21" s="15"/>
-      <c r="M21" s="16">
-        <v>0</v>
-      </c>
-      <c r="N21" s="15">
+      <c r="K21" s="2">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2"/>
+      <c r="M21" s="14">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2">
         <f t="shared" ref="N21:N25" si="9">N20+800</f>
         <v>5100</v>
       </c>
-      <c r="O21" s="15">
+      <c r="O21" s="2">
         <f t="shared" ref="O21:O25" si="10">O20+800</f>
         <v>5100</v>
       </c>
-      <c r="P21" s="15">
+      <c r="P21" s="2">
         <f t="shared" ref="P21:P26" si="11">P20+400</f>
         <v>4700</v>
       </c>
-      <c r="Q21" s="15">
-        <v>0</v>
-      </c>
-      <c r="R21" s="15">
+      <c r="Q21" s="2">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="S21" s="15">
+      <c r="S21" s="2">
         <f t="shared" ref="S21:S25" si="12">S20+25</f>
         <v>190</v>
       </c>
-      <c r="T21" s="15">
-        <v>0</v>
-      </c>
-      <c r="U21" s="15">
+      <c r="T21" s="2">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2">
         <v>10</v>
       </c>
-      <c r="V21" s="15">
+      <c r="V21" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3155,43 +3144,43 @@
       <c r="J22" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="K22" s="15">
-        <v>0</v>
-      </c>
-      <c r="L22" s="15"/>
-      <c r="M22" s="16">
-        <v>0</v>
-      </c>
-      <c r="N22" s="15">
+      <c r="K22" s="2">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" s="14">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2">
         <f t="shared" si="9"/>
         <v>5900</v>
       </c>
-      <c r="O22" s="15">
+      <c r="O22" s="2">
         <f t="shared" si="10"/>
         <v>5900</v>
       </c>
-      <c r="P22" s="15">
+      <c r="P22" s="2">
         <f t="shared" si="11"/>
         <v>5100</v>
       </c>
-      <c r="Q22" s="15">
-        <v>0</v>
-      </c>
-      <c r="R22" s="15">
+      <c r="Q22" s="2">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2">
         <f t="shared" si="3"/>
         <v>52</v>
       </c>
-      <c r="S22" s="15">
+      <c r="S22" s="2">
         <f t="shared" si="12"/>
         <v>215</v>
       </c>
-      <c r="T22" s="15">
-        <v>0</v>
-      </c>
-      <c r="U22" s="15">
+      <c r="T22" s="2">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2">
         <v>20</v>
       </c>
-      <c r="V22" s="15">
+      <c r="V22" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3220,43 +3209,43 @@
       <c r="J23" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="K23" s="15">
-        <v>0</v>
-      </c>
-      <c r="L23" s="15"/>
-      <c r="M23" s="16">
-        <v>0</v>
-      </c>
-      <c r="N23" s="15">
+      <c r="K23" s="2">
+        <v>0</v>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" s="14">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2">
         <f t="shared" si="9"/>
         <v>6700</v>
       </c>
-      <c r="O23" s="15">
+      <c r="O23" s="2">
         <f t="shared" si="10"/>
         <v>6700</v>
       </c>
-      <c r="P23" s="15">
+      <c r="P23" s="2">
         <f t="shared" si="11"/>
         <v>5500</v>
       </c>
-      <c r="Q23" s="15">
-        <v>0</v>
-      </c>
-      <c r="R23" s="15">
+      <c r="Q23" s="2">
+        <v>0</v>
+      </c>
+      <c r="R23" s="2">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="S23" s="15">
+      <c r="S23" s="2">
         <f t="shared" si="12"/>
         <v>240</v>
       </c>
-      <c r="T23" s="15">
-        <v>0</v>
-      </c>
-      <c r="U23" s="15">
+      <c r="T23" s="2">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2">
         <v>30</v>
       </c>
-      <c r="V23" s="15">
+      <c r="V23" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3285,43 +3274,43 @@
       <c r="J24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="K24" s="15">
-        <v>0</v>
-      </c>
-      <c r="L24" s="15"/>
-      <c r="M24" s="16">
-        <v>0</v>
-      </c>
-      <c r="N24" s="15">
+      <c r="K24" s="2">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" s="14">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2">
         <f t="shared" si="9"/>
         <v>7500</v>
       </c>
-      <c r="O24" s="15">
+      <c r="O24" s="2">
         <f t="shared" si="10"/>
         <v>7500</v>
       </c>
-      <c r="P24" s="15">
+      <c r="P24" s="2">
         <f t="shared" si="11"/>
         <v>5900</v>
       </c>
-      <c r="Q24" s="15">
-        <v>0</v>
-      </c>
-      <c r="R24" s="15">
+      <c r="Q24" s="2">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2">
         <f t="shared" si="3"/>
         <v>56</v>
       </c>
-      <c r="S24" s="15">
+      <c r="S24" s="2">
         <f t="shared" si="12"/>
         <v>265</v>
       </c>
-      <c r="T24" s="15">
-        <v>0</v>
-      </c>
-      <c r="U24" s="15">
+      <c r="T24" s="2">
+        <v>0</v>
+      </c>
+      <c r="U24" s="2">
         <v>40</v>
       </c>
-      <c r="V24" s="15">
+      <c r="V24" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3350,84 +3339,84 @@
       <c r="J25" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="K25" s="15">
-        <v>0</v>
-      </c>
-      <c r="L25" s="15"/>
-      <c r="M25" s="16">
-        <v>0</v>
-      </c>
-      <c r="N25" s="15">
+      <c r="K25" s="2">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2"/>
+      <c r="M25" s="14">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2">
         <f t="shared" si="9"/>
         <v>8300</v>
       </c>
-      <c r="O25" s="15">
+      <c r="O25" s="2">
         <f t="shared" si="10"/>
         <v>8300</v>
       </c>
-      <c r="P25" s="15">
+      <c r="P25" s="2">
         <f t="shared" si="11"/>
         <v>6300</v>
       </c>
-      <c r="Q25" s="15">
-        <v>0</v>
-      </c>
-      <c r="R25" s="15">
+      <c r="Q25" s="2">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2">
         <f t="shared" si="3"/>
         <v>58</v>
       </c>
-      <c r="S25" s="15">
+      <c r="S25" s="2">
         <f t="shared" si="12"/>
         <v>290</v>
       </c>
-      <c r="T25" s="15">
-        <v>0</v>
-      </c>
-      <c r="U25" s="15">
+      <c r="T25" s="2">
+        <v>0</v>
+      </c>
+      <c r="U25" s="2">
         <v>50</v>
       </c>
-      <c r="V25" s="15">
+      <c r="V25" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="8:17">
       <c r="H26" s="10"/>
-      <c r="M26" s="16"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="17"/>
+      <c r="M26" s="14"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="15"/>
     </row>
     <row r="27" customHeight="1" spans="8:17">
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
-      <c r="M27" s="16"/>
-      <c r="Q27" s="15"/>
+      <c r="M27" s="14"/>
+      <c r="Q27" s="2"/>
     </row>
     <row r="28" customHeight="1" spans="8:17">
       <c r="H28" s="10"/>
       <c r="I28" s="10"/>
-      <c r="M28" s="16"/>
-      <c r="Q28" s="15"/>
+      <c r="M28" s="14"/>
+      <c r="Q28" s="2"/>
     </row>
     <row r="29" customHeight="1" spans="8:17">
       <c r="H29" s="10"/>
       <c r="I29" s="10"/>
-      <c r="M29" s="16"/>
-      <c r="Q29" s="15"/>
+      <c r="M29" s="14"/>
+      <c r="Q29" s="2"/>
     </row>
     <row r="30" customHeight="1" spans="9:17">
       <c r="I30" s="10"/>
-      <c r="M30" s="16"/>
-      <c r="Q30" s="15"/>
+      <c r="M30" s="14"/>
+      <c r="Q30" s="2"/>
     </row>
     <row r="31" customHeight="1" spans="9:17">
       <c r="I31" s="10"/>
-      <c r="M31" s="16"/>
-      <c r="Q31" s="15"/>
+      <c r="M31" s="14"/>
+      <c r="Q31" s="2"/>
     </row>
     <row r="32" customHeight="1" spans="9:17">
       <c r="I32" s="10"/>
-      <c r="M32" s="16"/>
-      <c r="Q32" s="15"/>
+      <c r="M32" s="14"/>
+      <c r="Q32" s="2"/>
     </row>
     <row r="33" customHeight="1" spans="3:23">
       <c r="C33" s="1">
@@ -3437,7 +3426,7 @@
         <v>2</v>
       </c>
       <c r="E33" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>111</v>
@@ -3445,50 +3434,50 @@
       <c r="G33" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H33" s="28" t="s">
+      <c r="H33" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="I33" s="28" t="s">
+      <c r="I33" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="J33" s="28" t="s">
+      <c r="J33" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="K33" s="29" t="s">
+      <c r="K33" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="L33" s="15"/>
-      <c r="M33" s="29" t="s">
+      <c r="L33" s="2"/>
+      <c r="M33" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="N33" s="17">
+      <c r="N33" s="15">
         <v>10000</v>
       </c>
-      <c r="O33" s="17">
+      <c r="O33" s="15">
         <v>10000</v>
       </c>
-      <c r="P33" s="17">
+      <c r="P33" s="15">
         <v>10000</v>
       </c>
-      <c r="Q33" s="17">
+      <c r="Q33" s="15">
         <v>10000</v>
       </c>
-      <c r="R33" s="15">
-        <v>0</v>
-      </c>
-      <c r="S33" s="22">
+      <c r="R33" s="2">
+        <v>0</v>
+      </c>
+      <c r="S33" s="19">
         <v>150</v>
       </c>
-      <c r="T33" s="15">
+      <c r="T33" s="2">
         <v>150</v>
       </c>
-      <c r="U33" s="15">
+      <c r="U33" s="2">
         <v>99</v>
       </c>
-      <c r="V33" s="15">
+      <c r="V33" s="2">
         <v>100</v>
       </c>
-      <c r="W33" s="30" t="s">
+      <c r="W33" s="26" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3500,7 +3489,7 @@
         <v>2</v>
       </c>
       <c r="E34" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>119</v>
@@ -3508,56 +3497,56 @@
       <c r="G34" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H34" s="28" t="s">
+      <c r="H34" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="I34" s="28" t="s">
+      <c r="I34" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="J34" s="28" t="s">
+      <c r="J34" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="K34" s="29" t="s">
+      <c r="K34" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="L34" s="15"/>
-      <c r="M34" s="29" t="s">
+      <c r="L34" s="2"/>
+      <c r="M34" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="N34" s="17">
+      <c r="N34" s="15">
         <f t="shared" ref="N33:N52" si="13">N33+1000</f>
         <v>11000</v>
       </c>
-      <c r="O34" s="17">
+      <c r="O34" s="15">
         <f t="shared" ref="O33:O52" si="14">O33+1000</f>
         <v>11000</v>
       </c>
-      <c r="P34" s="17">
+      <c r="P34" s="15">
         <f t="shared" ref="P34:P52" si="15">P33+2000</f>
         <v>12000</v>
       </c>
-      <c r="Q34" s="19">
+      <c r="Q34" s="2">
         <f t="shared" ref="Q34:Q52" si="16">Q33+2000</f>
         <v>12000</v>
       </c>
-      <c r="R34" s="15">
-        <v>0</v>
-      </c>
-      <c r="S34" s="15">
+      <c r="R34" s="2">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2">
         <f t="shared" ref="S34:S52" si="17">S33+20</f>
         <v>170</v>
       </c>
-      <c r="T34" s="15">
+      <c r="T34" s="2">
         <f t="shared" ref="T34:T52" si="18">T33+30</f>
         <v>180</v>
       </c>
-      <c r="U34" s="15">
+      <c r="U34" s="2">
         <v>99</v>
       </c>
-      <c r="V34" s="15">
+      <c r="V34" s="2">
         <v>100</v>
       </c>
-      <c r="W34" s="30" t="s">
+      <c r="W34" s="26" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3569,7 +3558,7 @@
         <v>2</v>
       </c>
       <c r="E35" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>125</v>
@@ -3577,56 +3566,56 @@
       <c r="G35" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H35" s="28" t="s">
+      <c r="H35" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="I35" s="28" t="s">
+      <c r="I35" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="J35" s="28" t="s">
+      <c r="J35" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="K35" s="29" t="s">
+      <c r="K35" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="L35" s="15"/>
-      <c r="M35" s="29" t="s">
+      <c r="L35" s="2"/>
+      <c r="M35" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="N35" s="17">
+      <c r="N35" s="15">
         <f t="shared" si="13"/>
         <v>12000</v>
       </c>
-      <c r="O35" s="17">
+      <c r="O35" s="15">
         <f t="shared" si="14"/>
         <v>12000</v>
       </c>
-      <c r="P35" s="17">
+      <c r="P35" s="15">
         <f t="shared" si="15"/>
         <v>14000</v>
       </c>
-      <c r="Q35" s="19">
+      <c r="Q35" s="2">
         <f t="shared" si="16"/>
         <v>14000</v>
       </c>
-      <c r="R35" s="15">
-        <v>0</v>
-      </c>
-      <c r="S35" s="15">
+      <c r="R35" s="2">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2">
         <f t="shared" si="17"/>
         <v>190</v>
       </c>
-      <c r="T35" s="15">
+      <c r="T35" s="2">
         <f t="shared" si="18"/>
         <v>210</v>
       </c>
-      <c r="U35" s="15">
+      <c r="U35" s="2">
         <v>99</v>
       </c>
-      <c r="V35" s="15">
+      <c r="V35" s="2">
         <v>100</v>
       </c>
-      <c r="W35" s="30" t="s">
+      <c r="W35" s="26" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3638,7 +3627,7 @@
         <v>2</v>
       </c>
       <c r="E36" s="1">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>129</v>
@@ -3646,56 +3635,56 @@
       <c r="G36" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H36" s="28" t="s">
+      <c r="H36" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="I36" s="28" t="s">
+      <c r="I36" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="J36" s="28" t="s">
+      <c r="J36" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="K36" s="29" t="s">
+      <c r="K36" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="L36" s="15"/>
-      <c r="M36" s="29" t="s">
+      <c r="L36" s="2"/>
+      <c r="M36" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="N36" s="17">
+      <c r="N36" s="15">
         <f t="shared" si="13"/>
         <v>13000</v>
       </c>
-      <c r="O36" s="17">
+      <c r="O36" s="15">
         <f t="shared" si="14"/>
         <v>13000</v>
       </c>
-      <c r="P36" s="17">
+      <c r="P36" s="15">
         <f t="shared" si="15"/>
         <v>16000</v>
       </c>
-      <c r="Q36" s="19">
+      <c r="Q36" s="2">
         <f t="shared" si="16"/>
         <v>16000</v>
       </c>
-      <c r="R36" s="15">
-        <v>0</v>
-      </c>
-      <c r="S36" s="15">
+      <c r="R36" s="2">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2">
         <f t="shared" si="17"/>
         <v>210</v>
       </c>
-      <c r="T36" s="15">
+      <c r="T36" s="2">
         <f t="shared" si="18"/>
         <v>240</v>
       </c>
-      <c r="U36" s="15">
+      <c r="U36" s="2">
         <v>99</v>
       </c>
-      <c r="V36" s="15">
+      <c r="V36" s="2">
         <v>100</v>
       </c>
-      <c r="W36" s="30" t="s">
+      <c r="W36" s="26" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3707,7 +3696,7 @@
         <v>2</v>
       </c>
       <c r="E37" s="1">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>132</v>
@@ -3715,56 +3704,56 @@
       <c r="G37" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H37" s="28" t="s">
+      <c r="H37" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="I37" s="28" t="s">
+      <c r="I37" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="J37" s="28" t="s">
+      <c r="J37" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="K37" s="29" t="s">
+      <c r="K37" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="L37" s="15"/>
-      <c r="M37" s="29" t="s">
+      <c r="L37" s="2"/>
+      <c r="M37" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="N37" s="17">
+      <c r="N37" s="15">
         <f t="shared" si="13"/>
         <v>14000</v>
       </c>
-      <c r="O37" s="17">
+      <c r="O37" s="15">
         <f t="shared" si="14"/>
         <v>14000</v>
       </c>
-      <c r="P37" s="17">
+      <c r="P37" s="15">
         <f t="shared" si="15"/>
         <v>18000</v>
       </c>
-      <c r="Q37" s="19">
+      <c r="Q37" s="2">
         <f t="shared" si="16"/>
         <v>18000</v>
       </c>
-      <c r="R37" s="15">
-        <v>0</v>
-      </c>
-      <c r="S37" s="15">
+      <c r="R37" s="2">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2">
         <f t="shared" si="17"/>
         <v>230</v>
       </c>
-      <c r="T37" s="15">
+      <c r="T37" s="2">
         <f t="shared" si="18"/>
         <v>270</v>
       </c>
-      <c r="U37" s="15">
+      <c r="U37" s="2">
         <v>99</v>
       </c>
-      <c r="V37" s="15">
+      <c r="V37" s="2">
         <v>100</v>
       </c>
-      <c r="W37" s="30" t="s">
+      <c r="W37" s="26" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3776,7 +3765,7 @@
         <v>2</v>
       </c>
       <c r="E38" s="1">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>137</v>
@@ -3784,56 +3773,56 @@
       <c r="G38" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H38" s="28" t="s">
+      <c r="H38" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="I38" s="28" t="s">
+      <c r="I38" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="J38" s="28" t="s">
+      <c r="J38" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="K38" s="29" t="s">
+      <c r="K38" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="L38" s="15"/>
-      <c r="M38" s="29" t="s">
+      <c r="L38" s="2"/>
+      <c r="M38" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="N38" s="17">
+      <c r="N38" s="15">
         <f t="shared" si="13"/>
         <v>15000</v>
       </c>
-      <c r="O38" s="17">
+      <c r="O38" s="15">
         <f t="shared" si="14"/>
         <v>15000</v>
       </c>
-      <c r="P38" s="17">
+      <c r="P38" s="15">
         <f t="shared" si="15"/>
         <v>20000</v>
       </c>
-      <c r="Q38" s="19">
+      <c r="Q38" s="2">
         <f t="shared" si="16"/>
         <v>20000</v>
       </c>
-      <c r="R38" s="15">
-        <v>0</v>
-      </c>
-      <c r="S38" s="15">
+      <c r="R38" s="2">
+        <v>0</v>
+      </c>
+      <c r="S38" s="2">
         <f t="shared" si="17"/>
         <v>250</v>
       </c>
-      <c r="T38" s="15">
+      <c r="T38" s="2">
         <f t="shared" si="18"/>
         <v>300</v>
       </c>
-      <c r="U38" s="15">
+      <c r="U38" s="2">
         <v>99</v>
       </c>
-      <c r="V38" s="15">
+      <c r="V38" s="2">
         <v>100</v>
       </c>
-      <c r="W38" s="30" t="s">
+      <c r="W38" s="26" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3844,8 +3833,8 @@
       <c r="D39" s="11">
         <v>2</v>
       </c>
-      <c r="E39" s="11">
-        <v>7</v>
+      <c r="E39" s="1">
+        <v>16</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>142</v>
@@ -3853,30 +3842,30 @@
       <c r="G39" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="H39" s="31" t="s">
+      <c r="H39" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="I39" s="31" t="s">
+      <c r="I39" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="J39" s="31" t="s">
+      <c r="J39" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="K39" s="32" t="s">
+      <c r="K39" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="M39" s="32" t="s">
+      <c r="M39" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="N39" s="17">
+      <c r="N39" s="15">
         <f t="shared" si="13"/>
         <v>16000</v>
       </c>
-      <c r="O39" s="17">
+      <c r="O39" s="15">
         <f t="shared" si="14"/>
         <v>16000</v>
       </c>
-      <c r="P39" s="17">
+      <c r="P39" s="15">
         <f t="shared" si="15"/>
         <v>22000</v>
       </c>
@@ -3901,10 +3890,10 @@
       <c r="V39" s="2">
         <v>100</v>
       </c>
-      <c r="W39" s="33" t="s">
+      <c r="W39" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="X39" s="25"/>
+      <c r="X39" s="21"/>
     </row>
     <row r="40" customHeight="1" spans="3:23">
       <c r="C40" s="1">
@@ -3914,7 +3903,7 @@
         <v>2</v>
       </c>
       <c r="E40" s="1">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>146</v>
@@ -3922,56 +3911,56 @@
       <c r="G40" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H40" s="28" t="s">
+      <c r="H40" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="I40" s="28" t="s">
+      <c r="I40" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="J40" s="28" t="s">
+      <c r="J40" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="K40" s="29" t="s">
+      <c r="K40" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="L40" s="15"/>
-      <c r="M40" s="29" t="s">
+      <c r="L40" s="2"/>
+      <c r="M40" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="N40" s="17">
+      <c r="N40" s="15">
         <f t="shared" si="13"/>
         <v>17000</v>
       </c>
-      <c r="O40" s="17">
+      <c r="O40" s="15">
         <f t="shared" si="14"/>
         <v>17000</v>
       </c>
-      <c r="P40" s="17">
+      <c r="P40" s="15">
         <f t="shared" si="15"/>
         <v>24000</v>
       </c>
-      <c r="Q40" s="19">
+      <c r="Q40" s="2">
         <f t="shared" si="16"/>
         <v>24000</v>
       </c>
-      <c r="R40" s="15">
-        <v>0</v>
-      </c>
-      <c r="S40" s="15">
+      <c r="R40" s="2">
+        <v>0</v>
+      </c>
+      <c r="S40" s="2">
         <f t="shared" si="17"/>
         <v>290</v>
       </c>
-      <c r="T40" s="15">
+      <c r="T40" s="2">
         <f t="shared" si="18"/>
         <v>360</v>
       </c>
-      <c r="U40" s="15">
+      <c r="U40" s="2">
         <v>99</v>
       </c>
-      <c r="V40" s="15">
+      <c r="V40" s="2">
         <v>100</v>
       </c>
-      <c r="W40" s="30" t="s">
+      <c r="W40" s="26" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3983,7 +3972,7 @@
         <v>2</v>
       </c>
       <c r="E41" s="1">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>151</v>
@@ -3991,56 +3980,56 @@
       <c r="G41" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H41" s="28" t="s">
+      <c r="H41" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="I41" s="28" t="s">
+      <c r="I41" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="J41" s="28" t="s">
+      <c r="J41" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="K41" s="29" t="s">
+      <c r="K41" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="L41" s="15"/>
-      <c r="M41" s="29" t="s">
+      <c r="L41" s="2"/>
+      <c r="M41" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="N41" s="17">
+      <c r="N41" s="15">
         <f t="shared" si="13"/>
         <v>18000</v>
       </c>
-      <c r="O41" s="17">
+      <c r="O41" s="15">
         <f t="shared" si="14"/>
         <v>18000</v>
       </c>
-      <c r="P41" s="17">
+      <c r="P41" s="15">
         <f t="shared" si="15"/>
         <v>26000</v>
       </c>
-      <c r="Q41" s="19">
+      <c r="Q41" s="2">
         <f t="shared" si="16"/>
         <v>26000</v>
       </c>
-      <c r="R41" s="15">
-        <v>0</v>
-      </c>
-      <c r="S41" s="15">
+      <c r="R41" s="2">
+        <v>0</v>
+      </c>
+      <c r="S41" s="2">
         <f t="shared" si="17"/>
         <v>310</v>
       </c>
-      <c r="T41" s="15">
+      <c r="T41" s="2">
         <f t="shared" si="18"/>
         <v>390</v>
       </c>
-      <c r="U41" s="15">
+      <c r="U41" s="2">
         <v>99</v>
       </c>
-      <c r="V41" s="15">
+      <c r="V41" s="2">
         <v>100</v>
       </c>
-      <c r="W41" s="30" t="s">
+      <c r="W41" s="26" t="s">
         <v>118</v>
       </c>
     </row>
@@ -4052,7 +4041,7 @@
         <v>2</v>
       </c>
       <c r="E42" s="1">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>155</v>
@@ -4060,102 +4049,102 @@
       <c r="G42" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H42" s="28" t="s">
+      <c r="H42" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="I42" s="28" t="s">
+      <c r="I42" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="J42" s="28" t="s">
+      <c r="J42" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="K42" s="29" t="s">
+      <c r="K42" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="L42" s="15"/>
-      <c r="M42" s="29" t="s">
+      <c r="L42" s="2"/>
+      <c r="M42" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="N42" s="17">
+      <c r="N42" s="15">
         <f t="shared" si="13"/>
         <v>19000</v>
       </c>
-      <c r="O42" s="17">
+      <c r="O42" s="15">
         <f t="shared" si="14"/>
         <v>19000</v>
       </c>
-      <c r="P42" s="17">
+      <c r="P42" s="15">
         <f t="shared" si="15"/>
         <v>28000</v>
       </c>
-      <c r="Q42" s="19">
+      <c r="Q42" s="2">
         <f t="shared" si="16"/>
         <v>28000</v>
       </c>
-      <c r="R42" s="15">
-        <v>0</v>
-      </c>
-      <c r="S42" s="15">
+      <c r="R42" s="2">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2">
         <f t="shared" si="17"/>
         <v>330</v>
       </c>
-      <c r="T42" s="15">
+      <c r="T42" s="2">
         <f t="shared" si="18"/>
         <v>420</v>
       </c>
-      <c r="U42" s="15">
+      <c r="U42" s="2">
         <v>99</v>
       </c>
-      <c r="V42" s="15">
+      <c r="V42" s="2">
         <v>100</v>
       </c>
-      <c r="W42" s="30" t="s">
+      <c r="W42" s="26" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" customHeight="1" spans="3:24">
-      <c r="C43" s="13">
+      <c r="C43" s="12">
         <v>111</v>
       </c>
-      <c r="D43" s="13">
+      <c r="D43" s="12">
         <v>2</v>
       </c>
-      <c r="E43" s="13">
-        <v>11</v>
-      </c>
-      <c r="F43" s="13" t="s">
+      <c r="E43" s="1">
+        <v>20</v>
+      </c>
+      <c r="F43" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="G43" s="13" t="s">
+      <c r="G43" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="H43" s="34" t="s">
+      <c r="H43" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="I43" s="34" t="s">
+      <c r="I43" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="J43" s="34" t="s">
+      <c r="J43" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="K43" s="35" t="s">
+      <c r="K43" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="L43" s="35" t="s">
+      <c r="L43" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="M43" s="35" t="s">
+      <c r="M43" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="N43" s="18">
+      <c r="N43" s="16">
         <f t="shared" si="13"/>
         <v>20000</v>
       </c>
-      <c r="O43" s="18">
+      <c r="O43" s="16">
         <f t="shared" si="14"/>
         <v>20000</v>
       </c>
-      <c r="P43" s="18">
+      <c r="P43" s="16">
         <f t="shared" si="15"/>
         <v>30000</v>
       </c>
@@ -4180,10 +4169,10 @@
       <c r="V43" s="3">
         <v>120</v>
       </c>
-      <c r="W43" s="36" t="s">
+      <c r="W43" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="X43" s="27"/>
+      <c r="X43" s="23"/>
     </row>
     <row r="44" customHeight="1" spans="3:23">
       <c r="C44" s="1">
@@ -4193,7 +4182,7 @@
         <v>2</v>
       </c>
       <c r="E44" s="1">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>163</v>
@@ -4201,58 +4190,58 @@
       <c r="G44" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H44" s="28" t="s">
+      <c r="H44" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="I44" s="28" t="s">
+      <c r="I44" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="J44" s="28" t="s">
+      <c r="J44" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="K44" s="29" t="s">
+      <c r="K44" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="L44" s="35" t="s">
+      <c r="L44" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="M44" s="29" t="s">
+      <c r="M44" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="N44" s="17">
+      <c r="N44" s="15">
         <f t="shared" ref="N44:N52" si="21">N43+5000</f>
         <v>25000</v>
       </c>
-      <c r="O44" s="17">
+      <c r="O44" s="15">
         <f t="shared" ref="O44:O52" si="22">O43+5000</f>
         <v>25000</v>
       </c>
-      <c r="P44" s="17">
+      <c r="P44" s="15">
         <f t="shared" ref="P44:P52" si="23">P43+4000</f>
         <v>34000</v>
       </c>
-      <c r="Q44" s="17">
+      <c r="Q44" s="15">
         <f t="shared" ref="Q44:Q52" si="24">Q43+4000</f>
         <v>34000</v>
       </c>
-      <c r="R44" s="15">
-        <v>0</v>
-      </c>
-      <c r="S44" s="15">
+      <c r="R44" s="2">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2">
         <f t="shared" si="19"/>
         <v>390</v>
       </c>
-      <c r="T44" s="15">
+      <c r="T44" s="2">
         <f t="shared" si="20"/>
         <v>500</v>
       </c>
-      <c r="U44" s="15">
+      <c r="U44" s="2">
         <v>99</v>
       </c>
-      <c r="V44" s="15">
+      <c r="V44" s="2">
         <v>140</v>
       </c>
-      <c r="W44" s="30" t="s">
+      <c r="W44" s="26" t="s">
         <v>118</v>
       </c>
     </row>
@@ -4264,7 +4253,7 @@
         <v>2</v>
       </c>
       <c r="E45" s="1">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>169</v>
@@ -4272,59 +4261,59 @@
       <c r="G45" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H45" s="28" t="s">
+      <c r="H45" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="I45" s="28" t="s">
+      <c r="I45" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="J45" s="28" t="s">
+      <c r="J45" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="K45" s="29" t="s">
+      <c r="K45" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="L45" s="35" t="s">
+      <c r="L45" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="M45" s="29" t="s">
+      <c r="M45" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="N45" s="17">
+      <c r="N45" s="15">
         <f t="shared" si="21"/>
         <v>30000</v>
       </c>
-      <c r="O45" s="17">
+      <c r="O45" s="15">
         <f t="shared" si="22"/>
         <v>30000</v>
       </c>
-      <c r="P45" s="17">
+      <c r="P45" s="15">
         <f t="shared" si="23"/>
         <v>38000</v>
       </c>
-      <c r="Q45" s="17">
+      <c r="Q45" s="15">
         <f t="shared" si="24"/>
         <v>38000</v>
       </c>
-      <c r="R45" s="15">
-        <v>0</v>
-      </c>
-      <c r="S45" s="15">
+      <c r="R45" s="2">
+        <v>0</v>
+      </c>
+      <c r="S45" s="2">
         <f t="shared" si="19"/>
         <v>420</v>
       </c>
-      <c r="T45" s="15">
+      <c r="T45" s="2">
         <f t="shared" si="20"/>
         <v>540</v>
       </c>
-      <c r="U45" s="15">
+      <c r="U45" s="2">
         <v>99</v>
       </c>
-      <c r="V45" s="15">
+      <c r="V45" s="2">
         <f t="shared" ref="V45:V52" si="25">V44+20</f>
         <v>160</v>
       </c>
-      <c r="W45" s="30" t="s">
+      <c r="W45" s="26" t="s">
         <v>118</v>
       </c>
     </row>
@@ -4336,7 +4325,7 @@
         <v>2</v>
       </c>
       <c r="E46" s="1">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>176</v>
@@ -4344,59 +4333,59 @@
       <c r="G46" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H46" s="28" t="s">
+      <c r="H46" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="I46" s="28" t="s">
+      <c r="I46" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="J46" s="28" t="s">
+      <c r="J46" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="K46" s="29" t="s">
+      <c r="K46" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="L46" s="35" t="s">
+      <c r="L46" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="M46" s="29" t="s">
+      <c r="M46" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="N46" s="17">
+      <c r="N46" s="15">
         <f t="shared" si="21"/>
         <v>35000</v>
       </c>
-      <c r="O46" s="17">
+      <c r="O46" s="15">
         <f t="shared" si="22"/>
         <v>35000</v>
       </c>
-      <c r="P46" s="17">
+      <c r="P46" s="15">
         <f t="shared" si="23"/>
         <v>42000</v>
       </c>
-      <c r="Q46" s="17">
+      <c r="Q46" s="15">
         <f t="shared" si="24"/>
         <v>42000</v>
       </c>
-      <c r="R46" s="15">
-        <v>0</v>
-      </c>
-      <c r="S46" s="15">
+      <c r="R46" s="2">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2">
         <f t="shared" si="19"/>
         <v>450</v>
       </c>
-      <c r="T46" s="15">
+      <c r="T46" s="2">
         <f t="shared" si="20"/>
         <v>580</v>
       </c>
-      <c r="U46" s="15">
+      <c r="U46" s="2">
         <v>99</v>
       </c>
-      <c r="V46" s="15">
+      <c r="V46" s="2">
         <f t="shared" si="25"/>
         <v>180</v>
       </c>
-      <c r="W46" s="30" t="s">
+      <c r="W46" s="26" t="s">
         <v>118</v>
       </c>
     </row>
@@ -4408,7 +4397,7 @@
         <v>2</v>
       </c>
       <c r="E47" s="1">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>183</v>
@@ -4416,59 +4405,59 @@
       <c r="G47" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H47" s="28" t="s">
+      <c r="H47" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="I47" s="28" t="s">
+      <c r="I47" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="J47" s="28" t="s">
+      <c r="J47" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="K47" s="29" t="s">
+      <c r="K47" s="25" t="s">
         <v>187</v>
       </c>
-      <c r="L47" s="35" t="s">
+      <c r="L47" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="M47" s="29" t="s">
+      <c r="M47" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="N47" s="17">
+      <c r="N47" s="15">
         <f t="shared" si="21"/>
         <v>40000</v>
       </c>
-      <c r="O47" s="17">
+      <c r="O47" s="15">
         <f t="shared" si="22"/>
         <v>40000</v>
       </c>
-      <c r="P47" s="17">
+      <c r="P47" s="15">
         <f t="shared" si="23"/>
         <v>46000</v>
       </c>
-      <c r="Q47" s="17">
+      <c r="Q47" s="15">
         <f t="shared" si="24"/>
         <v>46000</v>
       </c>
-      <c r="R47" s="15">
-        <v>0</v>
-      </c>
-      <c r="S47" s="15">
+      <c r="R47" s="2">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2">
         <f t="shared" si="19"/>
         <v>480</v>
       </c>
-      <c r="T47" s="15">
+      <c r="T47" s="2">
         <f t="shared" si="20"/>
         <v>620</v>
       </c>
-      <c r="U47" s="15">
+      <c r="U47" s="2">
         <v>99</v>
       </c>
-      <c r="V47" s="15">
+      <c r="V47" s="2">
         <f t="shared" si="25"/>
         <v>200</v>
       </c>
-      <c r="W47" s="30" t="s">
+      <c r="W47" s="26" t="s">
         <v>118</v>
       </c>
     </row>
@@ -4480,7 +4469,7 @@
         <v>2</v>
       </c>
       <c r="E48" s="1">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>190</v>
@@ -4488,59 +4477,59 @@
       <c r="G48" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H48" s="28" t="s">
+      <c r="H48" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="I48" s="28" t="s">
+      <c r="I48" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="J48" s="28" t="s">
+      <c r="J48" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="K48" s="29" t="s">
+      <c r="K48" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="L48" s="35" t="s">
+      <c r="L48" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="M48" s="29" t="s">
+      <c r="M48" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="N48" s="17">
+      <c r="N48" s="15">
         <f t="shared" si="21"/>
         <v>45000</v>
       </c>
-      <c r="O48" s="17">
+      <c r="O48" s="15">
         <f t="shared" si="22"/>
         <v>45000</v>
       </c>
-      <c r="P48" s="17">
+      <c r="P48" s="15">
         <f t="shared" si="23"/>
         <v>50000</v>
       </c>
-      <c r="Q48" s="17">
+      <c r="Q48" s="15">
         <f t="shared" si="24"/>
         <v>50000</v>
       </c>
-      <c r="R48" s="15">
-        <v>0</v>
-      </c>
-      <c r="S48" s="15">
+      <c r="R48" s="2">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2">
         <f t="shared" si="19"/>
         <v>510</v>
       </c>
-      <c r="T48" s="15">
+      <c r="T48" s="2">
         <f t="shared" si="20"/>
         <v>660</v>
       </c>
-      <c r="U48" s="15">
+      <c r="U48" s="2">
         <v>99</v>
       </c>
-      <c r="V48" s="15">
+      <c r="V48" s="2">
         <f t="shared" si="25"/>
         <v>220</v>
       </c>
-      <c r="W48" s="30" t="s">
+      <c r="W48" s="26" t="s">
         <v>118</v>
       </c>
     </row>
@@ -4552,7 +4541,7 @@
         <v>2</v>
       </c>
       <c r="E49" s="1">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>196</v>
@@ -4560,59 +4549,59 @@
       <c r="G49" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H49" s="28" t="s">
+      <c r="H49" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="I49" s="28" t="s">
+      <c r="I49" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="J49" s="28" t="s">
+      <c r="J49" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="K49" s="29" t="s">
+      <c r="K49" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="L49" s="35" t="s">
+      <c r="L49" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="M49" s="29" t="s">
+      <c r="M49" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="N49" s="17">
+      <c r="N49" s="15">
         <f t="shared" si="21"/>
         <v>50000</v>
       </c>
-      <c r="O49" s="17">
+      <c r="O49" s="15">
         <f t="shared" si="22"/>
         <v>50000</v>
       </c>
-      <c r="P49" s="17">
+      <c r="P49" s="15">
         <f t="shared" si="23"/>
         <v>54000</v>
       </c>
-      <c r="Q49" s="17">
+      <c r="Q49" s="15">
         <f t="shared" si="24"/>
         <v>54000</v>
       </c>
-      <c r="R49" s="15">
-        <v>0</v>
-      </c>
-      <c r="S49" s="15">
+      <c r="R49" s="2">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2">
         <f t="shared" si="19"/>
         <v>540</v>
       </c>
-      <c r="T49" s="15">
+      <c r="T49" s="2">
         <f t="shared" si="20"/>
         <v>700</v>
       </c>
-      <c r="U49" s="15">
+      <c r="U49" s="2">
         <v>99</v>
       </c>
-      <c r="V49" s="15">
+      <c r="V49" s="2">
         <f t="shared" si="25"/>
         <v>240</v>
       </c>
-      <c r="W49" s="30" t="s">
+      <c r="W49" s="26" t="s">
         <v>118</v>
       </c>
     </row>
@@ -4624,7 +4613,7 @@
         <v>2</v>
       </c>
       <c r="E50" s="1">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>202</v>
@@ -4632,59 +4621,59 @@
       <c r="G50" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H50" s="28" t="s">
+      <c r="H50" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="I50" s="28" t="s">
+      <c r="I50" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="J50" s="28" t="s">
+      <c r="J50" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="K50" s="29" t="s">
+      <c r="K50" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="L50" s="35" t="s">
+      <c r="L50" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="M50" s="29" t="s">
+      <c r="M50" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="N50" s="17">
+      <c r="N50" s="15">
         <f t="shared" si="21"/>
         <v>55000</v>
       </c>
-      <c r="O50" s="17">
+      <c r="O50" s="15">
         <f t="shared" si="22"/>
         <v>55000</v>
       </c>
-      <c r="P50" s="17">
+      <c r="P50" s="15">
         <f t="shared" si="23"/>
         <v>58000</v>
       </c>
-      <c r="Q50" s="17">
+      <c r="Q50" s="15">
         <f t="shared" si="24"/>
         <v>58000</v>
       </c>
-      <c r="R50" s="15">
-        <v>0</v>
-      </c>
-      <c r="S50" s="15">
+      <c r="R50" s="2">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2">
         <f t="shared" si="19"/>
         <v>570</v>
       </c>
-      <c r="T50" s="15">
+      <c r="T50" s="2">
         <f t="shared" si="20"/>
         <v>740</v>
       </c>
-      <c r="U50" s="15">
+      <c r="U50" s="2">
         <v>99</v>
       </c>
-      <c r="V50" s="15">
+      <c r="V50" s="2">
         <f t="shared" si="25"/>
         <v>260</v>
       </c>
-      <c r="W50" s="30" t="s">
+      <c r="W50" s="26" t="s">
         <v>118</v>
       </c>
     </row>
@@ -4696,7 +4685,7 @@
         <v>2</v>
       </c>
       <c r="E51" s="1">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>208</v>
@@ -4704,59 +4693,59 @@
       <c r="G51" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H51" s="28" t="s">
+      <c r="H51" s="24" t="s">
         <v>209</v>
       </c>
-      <c r="I51" s="28" t="s">
+      <c r="I51" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="J51" s="28" t="s">
+      <c r="J51" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="K51" s="29" t="s">
+      <c r="K51" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="L51" s="35" t="s">
+      <c r="L51" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="M51" s="29" t="s">
+      <c r="M51" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="N51" s="17">
+      <c r="N51" s="15">
         <f t="shared" si="21"/>
         <v>60000</v>
       </c>
-      <c r="O51" s="17">
+      <c r="O51" s="15">
         <f t="shared" si="22"/>
         <v>60000</v>
       </c>
-      <c r="P51" s="17">
+      <c r="P51" s="15">
         <f t="shared" si="23"/>
         <v>62000</v>
       </c>
-      <c r="Q51" s="17">
+      <c r="Q51" s="15">
         <f t="shared" si="24"/>
         <v>62000</v>
       </c>
-      <c r="R51" s="15">
-        <v>0</v>
-      </c>
-      <c r="S51" s="15">
+      <c r="R51" s="2">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2">
         <f t="shared" si="19"/>
         <v>600</v>
       </c>
-      <c r="T51" s="15">
+      <c r="T51" s="2">
         <f t="shared" si="20"/>
         <v>780</v>
       </c>
-      <c r="U51" s="15">
+      <c r="U51" s="2">
         <v>99</v>
       </c>
-      <c r="V51" s="15">
+      <c r="V51" s="2">
         <f t="shared" si="25"/>
         <v>280</v>
       </c>
-      <c r="W51" s="30" t="s">
+      <c r="W51" s="26" t="s">
         <v>118</v>
       </c>
     </row>
@@ -4768,7 +4757,7 @@
         <v>2</v>
       </c>
       <c r="E52" s="1">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>214</v>
@@ -4776,82 +4765,82 @@
       <c r="G52" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H52" s="28" t="s">
+      <c r="H52" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="I52" s="28" t="s">
+      <c r="I52" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="J52" s="28" t="s">
+      <c r="J52" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="K52" s="29" t="s">
+      <c r="K52" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="L52" s="35" t="s">
+      <c r="L52" s="28" t="s">
         <v>219</v>
       </c>
-      <c r="M52" s="29" t="s">
+      <c r="M52" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="N52" s="17">
+      <c r="N52" s="15">
         <f t="shared" si="21"/>
         <v>65000</v>
       </c>
-      <c r="O52" s="17">
+      <c r="O52" s="15">
         <f t="shared" si="22"/>
         <v>65000</v>
       </c>
-      <c r="P52" s="17">
+      <c r="P52" s="15">
         <f t="shared" si="23"/>
         <v>66000</v>
       </c>
-      <c r="Q52" s="17">
+      <c r="Q52" s="15">
         <f t="shared" si="24"/>
         <v>66000</v>
       </c>
-      <c r="R52" s="15">
-        <v>0</v>
-      </c>
-      <c r="S52" s="15">
+      <c r="R52" s="2">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2">
         <f t="shared" si="19"/>
         <v>630</v>
       </c>
-      <c r="T52" s="15">
+      <c r="T52" s="2">
         <f t="shared" si="20"/>
         <v>820</v>
       </c>
-      <c r="U52" s="15">
+      <c r="U52" s="2">
         <v>99</v>
       </c>
-      <c r="V52" s="15">
+      <c r="V52" s="2">
         <f t="shared" si="25"/>
         <v>300</v>
       </c>
-      <c r="W52" s="30" t="s">
+      <c r="W52" s="26" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="13:17">
-      <c r="M53" s="15"/>
-      <c r="N53" s="19"/>
-      <c r="O53" s="19"/>
-      <c r="P53" s="19"/>
-      <c r="Q53" s="19"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
     </row>
     <row r="54" customHeight="1" spans="13:17">
-      <c r="M54" s="15"/>
-      <c r="N54" s="19"/>
-      <c r="O54" s="19"/>
-      <c r="P54" s="19"/>
-      <c r="Q54" s="19"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
     </row>
     <row r="55" customHeight="1" spans="13:17">
-      <c r="M55" s="15"/>
-      <c r="N55" s="19"/>
-      <c r="O55" s="19"/>
-      <c r="P55" s="19"/>
-      <c r="Q55" s="19"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
     </row>
     <row r="56" customHeight="1" spans="3:23">
       <c r="C56" s="1">
@@ -4861,7 +4850,7 @@
         <v>3</v>
       </c>
       <c r="E56" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>221</v>
@@ -4869,52 +4858,52 @@
       <c r="G56" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H56" s="28" t="s">
+      <c r="H56" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="I56" s="28" t="s">
+      <c r="I56" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="J56" s="28" t="s">
+      <c r="J56" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="K56" s="29" t="s">
+      <c r="K56" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="L56" s="29" t="s">
+      <c r="L56" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="M56" s="28" t="s">
+      <c r="M56" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="N56" s="17">
+      <c r="N56" s="15">
         <v>100000</v>
       </c>
-      <c r="O56" s="17">
+      <c r="O56" s="15">
         <v>100000</v>
       </c>
-      <c r="P56" s="17">
+      <c r="P56" s="15">
         <v>100000</v>
       </c>
-      <c r="Q56" s="17">
+      <c r="Q56" s="15">
         <v>100000</v>
       </c>
-      <c r="R56" s="15">
-        <v>0</v>
-      </c>
-      <c r="S56" s="22">
+      <c r="R56" s="2">
+        <v>0</v>
+      </c>
+      <c r="S56" s="19">
         <v>400</v>
       </c>
-      <c r="T56" s="15">
+      <c r="T56" s="2">
         <v>600</v>
       </c>
-      <c r="U56" s="15">
+      <c r="U56" s="2">
         <v>99</v>
       </c>
-      <c r="V56" s="15">
+      <c r="V56" s="2">
         <v>200</v>
       </c>
-      <c r="W56" s="30" t="s">
+      <c r="W56" s="26" t="s">
         <v>224</v>
       </c>
     </row>
@@ -4926,7 +4915,7 @@
         <v>3</v>
       </c>
       <c r="E57" s="1">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>225</v>
@@ -4934,59 +4923,59 @@
       <c r="G57" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H57" s="28" t="s">
+      <c r="H57" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="I57" s="28" t="s">
+      <c r="I57" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="J57" s="28" t="s">
+      <c r="J57" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="K57" s="29" t="s">
+      <c r="K57" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="L57" s="29" t="s">
+      <c r="L57" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="M57" s="28" t="s">
+      <c r="M57" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="N57" s="17">
+      <c r="N57" s="15">
         <f t="shared" ref="N57:Q57" si="26">N56+20000</f>
         <v>120000</v>
       </c>
-      <c r="O57" s="17">
+      <c r="O57" s="15">
         <f t="shared" si="26"/>
         <v>120000</v>
       </c>
-      <c r="P57" s="17">
+      <c r="P57" s="15">
         <f t="shared" si="26"/>
         <v>120000</v>
       </c>
-      <c r="Q57" s="17">
+      <c r="Q57" s="15">
         <f t="shared" si="26"/>
         <v>120000</v>
       </c>
-      <c r="R57" s="15">
-        <v>0</v>
-      </c>
-      <c r="S57" s="15">
+      <c r="R57" s="2">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2">
         <f t="shared" ref="S57:S65" si="27">S56+30</f>
         <v>430</v>
       </c>
-      <c r="T57" s="15">
+      <c r="T57" s="2">
         <f t="shared" ref="T57:T65" si="28">T56+30</f>
         <v>630</v>
       </c>
-      <c r="U57" s="15">
+      <c r="U57" s="2">
         <v>99</v>
       </c>
-      <c r="V57" s="15">
+      <c r="V57" s="2">
         <f t="shared" ref="V57:V65" si="29">V56+20</f>
         <v>220</v>
       </c>
-      <c r="W57" s="30" t="s">
+      <c r="W57" s="26" t="s">
         <v>224</v>
       </c>
     </row>
@@ -4998,7 +4987,7 @@
         <v>3</v>
       </c>
       <c r="E58" s="1">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>227</v>
@@ -5006,59 +4995,59 @@
       <c r="G58" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H58" s="28" t="s">
+      <c r="H58" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="I58" s="28" t="s">
+      <c r="I58" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="J58" s="28" t="s">
+      <c r="J58" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="K58" s="29" t="s">
+      <c r="K58" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="L58" s="29" t="s">
+      <c r="L58" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="M58" s="28" t="s">
+      <c r="M58" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="N58" s="17">
+      <c r="N58" s="15">
         <f t="shared" ref="N58:Q58" si="30">N57+20000</f>
         <v>140000</v>
       </c>
-      <c r="O58" s="17">
+      <c r="O58" s="15">
         <f t="shared" si="30"/>
         <v>140000</v>
       </c>
-      <c r="P58" s="17">
+      <c r="P58" s="15">
         <f t="shared" si="30"/>
         <v>140000</v>
       </c>
-      <c r="Q58" s="17">
+      <c r="Q58" s="15">
         <f t="shared" si="30"/>
         <v>140000</v>
       </c>
-      <c r="R58" s="15">
-        <v>0</v>
-      </c>
-      <c r="S58" s="15">
+      <c r="R58" s="2">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2">
         <f t="shared" si="27"/>
         <v>460</v>
       </c>
-      <c r="T58" s="15">
+      <c r="T58" s="2">
         <f t="shared" si="28"/>
         <v>660</v>
       </c>
-      <c r="U58" s="15">
+      <c r="U58" s="2">
         <v>99</v>
       </c>
-      <c r="V58" s="15">
+      <c r="V58" s="2">
         <f t="shared" si="29"/>
         <v>240</v>
       </c>
-      <c r="W58" s="30" t="s">
+      <c r="W58" s="26" t="s">
         <v>224</v>
       </c>
     </row>
@@ -5070,7 +5059,7 @@
         <v>3</v>
       </c>
       <c r="E59" s="1">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>229</v>
@@ -5078,59 +5067,59 @@
       <c r="G59" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H59" s="28" t="s">
+      <c r="H59" s="24" t="s">
         <v>230</v>
       </c>
-      <c r="I59" s="28" t="s">
+      <c r="I59" s="24" t="s">
         <v>230</v>
       </c>
-      <c r="J59" s="28" t="s">
+      <c r="J59" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="K59" s="29" t="s">
+      <c r="K59" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="L59" s="29" t="s">
+      <c r="L59" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="M59" s="28" t="s">
+      <c r="M59" s="24" t="s">
         <v>230</v>
       </c>
-      <c r="N59" s="17">
+      <c r="N59" s="15">
         <f t="shared" ref="N59:Q59" si="31">N58+20000</f>
         <v>160000</v>
       </c>
-      <c r="O59" s="17">
+      <c r="O59" s="15">
         <f t="shared" si="31"/>
         <v>160000</v>
       </c>
-      <c r="P59" s="17">
+      <c r="P59" s="15">
         <f t="shared" si="31"/>
         <v>160000</v>
       </c>
-      <c r="Q59" s="17">
+      <c r="Q59" s="15">
         <f t="shared" si="31"/>
         <v>160000</v>
       </c>
-      <c r="R59" s="15">
-        <v>0</v>
-      </c>
-      <c r="S59" s="15">
+      <c r="R59" s="2">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2">
         <f t="shared" si="27"/>
         <v>490</v>
       </c>
-      <c r="T59" s="15">
+      <c r="T59" s="2">
         <f t="shared" si="28"/>
         <v>690</v>
       </c>
-      <c r="U59" s="15">
+      <c r="U59" s="2">
         <v>99</v>
       </c>
-      <c r="V59" s="15">
+      <c r="V59" s="2">
         <f t="shared" si="29"/>
         <v>260</v>
       </c>
-      <c r="W59" s="30" t="s">
+      <c r="W59" s="26" t="s">
         <v>224</v>
       </c>
     </row>
@@ -5142,7 +5131,7 @@
         <v>3</v>
       </c>
       <c r="E60" s="1">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>233</v>
@@ -5150,59 +5139,59 @@
       <c r="G60" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H60" s="28" t="s">
+      <c r="H60" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="I60" s="28" t="s">
+      <c r="I60" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="J60" s="28" t="s">
+      <c r="J60" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="K60" s="29" t="s">
+      <c r="K60" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="L60" s="29" t="s">
+      <c r="L60" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="M60" s="28" t="s">
+      <c r="M60" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="N60" s="17">
+      <c r="N60" s="15">
         <f t="shared" ref="N60:Q60" si="32">N59+20000</f>
         <v>180000</v>
       </c>
-      <c r="O60" s="17">
+      <c r="O60" s="15">
         <f t="shared" si="32"/>
         <v>180000</v>
       </c>
-      <c r="P60" s="17">
+      <c r="P60" s="15">
         <f t="shared" si="32"/>
         <v>180000</v>
       </c>
-      <c r="Q60" s="17">
+      <c r="Q60" s="15">
         <f t="shared" si="32"/>
         <v>180000</v>
       </c>
-      <c r="R60" s="15">
-        <v>0</v>
-      </c>
-      <c r="S60" s="15">
+      <c r="R60" s="2">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2">
         <f t="shared" si="27"/>
         <v>520</v>
       </c>
-      <c r="T60" s="15">
+      <c r="T60" s="2">
         <f t="shared" si="28"/>
         <v>720</v>
       </c>
-      <c r="U60" s="15">
+      <c r="U60" s="2">
         <v>99</v>
       </c>
-      <c r="V60" s="15">
+      <c r="V60" s="2">
         <f t="shared" si="29"/>
         <v>280</v>
       </c>
-      <c r="W60" s="30" t="s">
+      <c r="W60" s="26" t="s">
         <v>224</v>
       </c>
     </row>
@@ -5214,7 +5203,7 @@
         <v>3</v>
       </c>
       <c r="E61" s="1">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>236</v>
@@ -5222,59 +5211,59 @@
       <c r="G61" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H61" s="28" t="s">
+      <c r="H61" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="I61" s="28" t="s">
+      <c r="I61" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="J61" s="28" t="s">
+      <c r="J61" s="24" t="s">
         <v>237</v>
       </c>
-      <c r="K61" s="29" t="s">
+      <c r="K61" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="L61" s="29" t="s">
+      <c r="L61" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="M61" s="28" t="s">
+      <c r="M61" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="N61" s="17">
+      <c r="N61" s="15">
         <f t="shared" ref="N61:Q61" si="33">N60+20000</f>
         <v>200000</v>
       </c>
-      <c r="O61" s="17">
+      <c r="O61" s="15">
         <f t="shared" si="33"/>
         <v>200000</v>
       </c>
-      <c r="P61" s="17">
+      <c r="P61" s="15">
         <f t="shared" si="33"/>
         <v>200000</v>
       </c>
-      <c r="Q61" s="17">
+      <c r="Q61" s="15">
         <f t="shared" si="33"/>
         <v>200000</v>
       </c>
-      <c r="R61" s="15">
-        <v>0</v>
-      </c>
-      <c r="S61" s="15">
+      <c r="R61" s="2">
+        <v>0</v>
+      </c>
+      <c r="S61" s="2">
         <f t="shared" si="27"/>
         <v>550</v>
       </c>
-      <c r="T61" s="15">
+      <c r="T61" s="2">
         <f t="shared" si="28"/>
         <v>750</v>
       </c>
-      <c r="U61" s="15">
+      <c r="U61" s="2">
         <v>99</v>
       </c>
-      <c r="V61" s="15">
+      <c r="V61" s="2">
         <f t="shared" si="29"/>
         <v>300</v>
       </c>
-      <c r="W61" s="30" t="s">
+      <c r="W61" s="26" t="s">
         <v>224</v>
       </c>
     </row>
@@ -5285,71 +5274,71 @@
       <c r="D62" s="1">
         <v>3</v>
       </c>
-      <c r="E62" s="13">
-        <v>7</v>
-      </c>
-      <c r="F62" s="13" t="s">
+      <c r="E62" s="1">
+        <v>26</v>
+      </c>
+      <c r="F62" s="12" t="s">
         <v>239</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H62" s="34" t="s">
+      <c r="H62" s="27" t="s">
         <v>226</v>
       </c>
-      <c r="I62" s="34" t="s">
+      <c r="I62" s="27" t="s">
         <v>226</v>
       </c>
-      <c r="J62" s="34" t="s">
+      <c r="J62" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="K62" s="35" t="s">
+      <c r="K62" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="L62" s="35" t="s">
+      <c r="L62" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="M62" s="34" t="s">
+      <c r="M62" s="27" t="s">
         <v>226</v>
       </c>
-      <c r="N62" s="17">
+      <c r="N62" s="15">
         <f t="shared" ref="N62:Q62" si="34">N61+20000</f>
         <v>220000</v>
       </c>
-      <c r="O62" s="17">
+      <c r="O62" s="15">
         <f t="shared" si="34"/>
         <v>220000</v>
       </c>
-      <c r="P62" s="17">
+      <c r="P62" s="15">
         <f t="shared" si="34"/>
         <v>220000</v>
       </c>
-      <c r="Q62" s="17">
+      <c r="Q62" s="15">
         <f t="shared" si="34"/>
         <v>220000</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
-      <c r="S62" s="15">
+      <c r="S62" s="2">
         <f t="shared" si="27"/>
         <v>580</v>
       </c>
-      <c r="T62" s="15">
+      <c r="T62" s="2">
         <f t="shared" si="28"/>
         <v>780</v>
       </c>
       <c r="U62" s="3">
         <v>99</v>
       </c>
-      <c r="V62" s="15">
+      <c r="V62" s="2">
         <f t="shared" si="29"/>
         <v>320</v>
       </c>
-      <c r="W62" s="30" t="s">
+      <c r="W62" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="X62" s="27"/>
+      <c r="X62" s="23"/>
     </row>
     <row r="63" customHeight="1" spans="3:23">
       <c r="C63" s="1">
@@ -5359,7 +5348,7 @@
         <v>3</v>
       </c>
       <c r="E63" s="1">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>241</v>
@@ -5367,59 +5356,59 @@
       <c r="G63" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H63" s="28" t="s">
+      <c r="H63" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="I63" s="28" t="s">
+      <c r="I63" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="J63" s="28" t="s">
+      <c r="J63" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="K63" s="29" t="s">
+      <c r="K63" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="L63" s="29" t="s">
+      <c r="L63" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="M63" s="28" t="s">
+      <c r="M63" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="N63" s="17">
+      <c r="N63" s="15">
         <f t="shared" ref="N63:Q63" si="35">N62+20000</f>
         <v>240000</v>
       </c>
-      <c r="O63" s="17">
+      <c r="O63" s="15">
         <f t="shared" si="35"/>
         <v>240000</v>
       </c>
-      <c r="P63" s="17">
+      <c r="P63" s="15">
         <f t="shared" si="35"/>
         <v>240000</v>
       </c>
-      <c r="Q63" s="17">
+      <c r="Q63" s="15">
         <f t="shared" si="35"/>
         <v>240000</v>
       </c>
-      <c r="R63" s="15">
-        <v>0</v>
-      </c>
-      <c r="S63" s="15">
+      <c r="R63" s="2">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2">
         <f t="shared" si="27"/>
         <v>610</v>
       </c>
-      <c r="T63" s="15">
+      <c r="T63" s="2">
         <f t="shared" si="28"/>
         <v>810</v>
       </c>
-      <c r="U63" s="15">
+      <c r="U63" s="2">
         <v>99</v>
       </c>
-      <c r="V63" s="15">
+      <c r="V63" s="2">
         <f t="shared" si="29"/>
         <v>340</v>
       </c>
-      <c r="W63" s="30" t="s">
+      <c r="W63" s="26" t="s">
         <v>224</v>
       </c>
     </row>
@@ -5431,7 +5420,7 @@
         <v>3</v>
       </c>
       <c r="E64" s="1">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>244</v>
@@ -5439,59 +5428,59 @@
       <c r="G64" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H64" s="28" t="s">
+      <c r="H64" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="I64" s="28" t="s">
+      <c r="I64" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="J64" s="28" t="s">
+      <c r="J64" s="24" t="s">
         <v>245</v>
       </c>
-      <c r="K64" s="29" t="s">
+      <c r="K64" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="L64" s="29" t="s">
+      <c r="L64" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="M64" s="28" t="s">
+      <c r="M64" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="N64" s="17">
+      <c r="N64" s="15">
         <f t="shared" ref="N64:Q64" si="36">N63+20000</f>
         <v>260000</v>
       </c>
-      <c r="O64" s="17">
+      <c r="O64" s="15">
         <f t="shared" si="36"/>
         <v>260000</v>
       </c>
-      <c r="P64" s="17">
+      <c r="P64" s="15">
         <f t="shared" si="36"/>
         <v>260000</v>
       </c>
-      <c r="Q64" s="17">
+      <c r="Q64" s="15">
         <f t="shared" si="36"/>
         <v>260000</v>
       </c>
-      <c r="R64" s="15">
-        <v>0</v>
-      </c>
-      <c r="S64" s="15">
+      <c r="R64" s="2">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2">
         <f t="shared" si="27"/>
         <v>640</v>
       </c>
-      <c r="T64" s="15">
+      <c r="T64" s="2">
         <f t="shared" si="28"/>
         <v>840</v>
       </c>
-      <c r="U64" s="15">
+      <c r="U64" s="2">
         <v>99</v>
       </c>
-      <c r="V64" s="15">
+      <c r="V64" s="2">
         <f t="shared" si="29"/>
         <v>360</v>
       </c>
-      <c r="W64" s="30" t="s">
+      <c r="W64" s="26" t="s">
         <v>224</v>
       </c>
     </row>
@@ -5503,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="E65" s="1">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>246</v>
@@ -5511,65 +5500,65 @@
       <c r="G65" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H65" s="28" t="s">
+      <c r="H65" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="I65" s="28" t="s">
+      <c r="I65" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="J65" s="28" t="s">
+      <c r="J65" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="K65" s="29" t="s">
+      <c r="K65" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="L65" s="29" t="s">
+      <c r="L65" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="M65" s="28" t="s">
+      <c r="M65" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="N65" s="17">
+      <c r="N65" s="15">
         <f t="shared" ref="N65:Q65" si="37">N64+20000</f>
         <v>280000</v>
       </c>
-      <c r="O65" s="17">
+      <c r="O65" s="15">
         <f t="shared" si="37"/>
         <v>280000</v>
       </c>
-      <c r="P65" s="17">
+      <c r="P65" s="15">
         <f t="shared" si="37"/>
         <v>280000</v>
       </c>
-      <c r="Q65" s="17">
+      <c r="Q65" s="15">
         <f t="shared" si="37"/>
         <v>280000</v>
       </c>
-      <c r="R65" s="15">
-        <v>0</v>
-      </c>
-      <c r="S65" s="15">
+      <c r="R65" s="2">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2">
         <f t="shared" si="27"/>
         <v>670</v>
       </c>
-      <c r="T65" s="15">
+      <c r="T65" s="2">
         <f t="shared" si="28"/>
         <v>870</v>
       </c>
-      <c r="U65" s="15">
+      <c r="U65" s="2">
         <v>99</v>
       </c>
-      <c r="V65" s="15">
+      <c r="V65" s="2">
         <f t="shared" si="29"/>
         <v>380</v>
       </c>
-      <c r="W65" s="30" t="s">
+      <c r="W65" s="26" t="s">
         <v>224</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3 L4 L5 C3:K5 M3:W5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:W5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterPillConfig.xlsx
+++ b/Excel/MonsterPillConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="247">
   <si>
     <t>ID</t>
   </si>
@@ -41,6 +41,9 @@
     <t>Layer</t>
   </si>
   <si>
+    <t>RequireCycle</t>
+  </si>
+  <si>
     <t>MapName</t>
   </si>
   <si>
@@ -515,7 +518,10 @@
     <t>9E+135</t>
   </si>
   <si>
-    <t>1E+10</t>
+    <t>1E+50</t>
+  </si>
+  <si>
+    <t>1E+20</t>
   </si>
   <si>
     <t>1E+78</t>
@@ -530,10 +536,7 @@
     <t>9E+145</t>
   </si>
   <si>
-    <t>1E+61</t>
-  </si>
-  <si>
-    <t>1E+20</t>
+    <t>1E+52</t>
   </si>
   <si>
     <t>1E+88</t>
@@ -551,229 +554,223 @@
     <t>9E+155</t>
   </si>
   <si>
+    <t>1E+54</t>
+  </si>
+  <si>
+    <t>1E+30</t>
+  </si>
+  <si>
+    <t>1E+98</t>
+  </si>
+  <si>
+    <t>练气十四层</t>
+  </si>
+  <si>
+    <t>9E+116</t>
+  </si>
+  <si>
+    <t>9E+92</t>
+  </si>
+  <si>
+    <t>9E+165</t>
+  </si>
+  <si>
+    <t>1E+56</t>
+  </si>
+  <si>
+    <t>1E+108</t>
+  </si>
+  <si>
+    <t>练气十五层</t>
+  </si>
+  <si>
+    <t>9E+126</t>
+  </si>
+  <si>
+    <t>9E+93</t>
+  </si>
+  <si>
+    <t>9E+175</t>
+  </si>
+  <si>
+    <t>1E+58</t>
+  </si>
+  <si>
+    <t>1E+40</t>
+  </si>
+  <si>
+    <t>1E+118</t>
+  </si>
+  <si>
+    <t>练气十六层</t>
+  </si>
+  <si>
+    <t>9E+136</t>
+  </si>
+  <si>
+    <t>9E+94</t>
+  </si>
+  <si>
+    <t>9E+185</t>
+  </si>
+  <si>
+    <t>1E+45</t>
+  </si>
+  <si>
+    <t>1E+128</t>
+  </si>
+  <si>
+    <t>练气十七层</t>
+  </si>
+  <si>
+    <t>9E+146</t>
+  </si>
+  <si>
+    <t>9E+195</t>
+  </si>
+  <si>
     <t>1E+62</t>
   </si>
   <si>
-    <t>1E+30</t>
-  </si>
-  <si>
-    <t>1E+98</t>
-  </si>
-  <si>
-    <t>练气十四层</t>
-  </si>
-  <si>
-    <t>9E+116</t>
-  </si>
-  <si>
-    <t>9E+92</t>
-  </si>
-  <si>
-    <t>9E+165</t>
-  </si>
-  <si>
-    <t>1E+63</t>
-  </si>
-  <si>
-    <t>1E+40</t>
-  </si>
-  <si>
-    <t>1E+108</t>
-  </si>
-  <si>
-    <t>练气十五层</t>
-  </si>
-  <si>
-    <t>9E+126</t>
-  </si>
-  <si>
-    <t>9E+93</t>
-  </si>
-  <si>
-    <t>9E+175</t>
+    <t>1E+138</t>
+  </si>
+  <si>
+    <t>练气十八层</t>
+  </si>
+  <si>
+    <t>9E+156</t>
+  </si>
+  <si>
+    <t>9E+205</t>
   </si>
   <si>
     <t>1E+64</t>
   </si>
   <si>
-    <t>1E+50</t>
-  </si>
-  <si>
-    <t>1E+118</t>
-  </si>
-  <si>
-    <t>练气十六层</t>
-  </si>
-  <si>
-    <t>9E+136</t>
-  </si>
-  <si>
-    <t>9E+94</t>
-  </si>
-  <si>
-    <t>9E+185</t>
+    <t>1E+55</t>
+  </si>
+  <si>
+    <t>1E+148</t>
+  </si>
+  <si>
+    <t>练气十九层</t>
+  </si>
+  <si>
+    <t>9E+166</t>
+  </si>
+  <si>
+    <t>9E+97</t>
+  </si>
+  <si>
+    <t>9E+215</t>
+  </si>
+  <si>
+    <t>1E+66</t>
+  </si>
+  <si>
+    <t>1E+158</t>
+  </si>
+  <si>
+    <t>练气二十层</t>
+  </si>
+  <si>
+    <t>9E+176</t>
+  </si>
+  <si>
+    <t>9E+98</t>
+  </si>
+  <si>
+    <t>9E+225</t>
   </si>
   <si>
     <t>1E+65</t>
   </si>
   <si>
-    <t>1E+128</t>
-  </si>
-  <si>
-    <t>练气十七层</t>
-  </si>
-  <si>
-    <t>9E+146</t>
-  </si>
-  <si>
-    <t>9E+195</t>
-  </si>
-  <si>
-    <t>1E+66</t>
+    <t>1E+168</t>
+  </si>
+  <si>
+    <t>炼神一层</t>
+  </si>
+  <si>
+    <t>炼神魔物</t>
+  </si>
+  <si>
+    <t>9E+150</t>
+  </si>
+  <si>
+    <t>1004,2002,2003,2007,2009,2012,1012</t>
+  </si>
+  <si>
+    <t>炼神二层</t>
+  </si>
+  <si>
+    <t>9E+160</t>
+  </si>
+  <si>
+    <t>炼神三层</t>
+  </si>
+  <si>
+    <t>9E+170</t>
+  </si>
+  <si>
+    <t>炼神四层</t>
+  </si>
+  <si>
+    <t>9E+130</t>
+  </si>
+  <si>
+    <t>9E+180</t>
+  </si>
+  <si>
+    <t>炼神五层</t>
+  </si>
+  <si>
+    <t>9E+140</t>
+  </si>
+  <si>
+    <t>9E+190</t>
+  </si>
+  <si>
+    <t>炼神六层</t>
+  </si>
+  <si>
+    <t>9E+200</t>
+  </si>
+  <si>
+    <t>炼神七层</t>
+  </si>
+  <si>
+    <t>9E+210</t>
   </si>
   <si>
     <t>1E+70</t>
   </si>
   <si>
-    <t>1E+138</t>
-  </si>
-  <si>
-    <t>练气十八层</t>
-  </si>
-  <si>
-    <t>9E+156</t>
-  </si>
-  <si>
-    <t>9E+205</t>
-  </si>
-  <si>
-    <t>1E+67</t>
+    <t>炼神八层</t>
+  </si>
+  <si>
+    <t>9E+220</t>
+  </si>
+  <si>
+    <t>1E+75</t>
+  </si>
+  <si>
+    <t>炼神九层</t>
+  </si>
+  <si>
+    <t>9E+230</t>
   </si>
   <si>
     <t>1E+80</t>
   </si>
   <si>
-    <t>1E+148</t>
-  </si>
-  <si>
-    <t>练气十九层</t>
-  </si>
-  <si>
-    <t>9E+166</t>
-  </si>
-  <si>
-    <t>9E+97</t>
-  </si>
-  <si>
-    <t>9E+215</t>
-  </si>
-  <si>
-    <t>1E+90</t>
-  </si>
-  <si>
-    <t>1E+158</t>
-  </si>
-  <si>
-    <t>练气二十层</t>
-  </si>
-  <si>
-    <t>9E+176</t>
-  </si>
-  <si>
-    <t>9E+98</t>
-  </si>
-  <si>
-    <t>9E+225</t>
-  </si>
-  <si>
-    <t>1E+69</t>
-  </si>
-  <si>
-    <t>1E+100</t>
-  </si>
-  <si>
-    <t>1E+168</t>
-  </si>
-  <si>
-    <t>炼神一层</t>
-  </si>
-  <si>
-    <t>炼神魔物</t>
-  </si>
-  <si>
-    <t>9E+150</t>
-  </si>
-  <si>
-    <t>1004,2002,2003,2007,2009,2012,1012</t>
-  </si>
-  <si>
-    <t>炼神二层</t>
-  </si>
-  <si>
-    <t>9E+160</t>
-  </si>
-  <si>
-    <t>炼神三层</t>
-  </si>
-  <si>
-    <t>9E+170</t>
-  </si>
-  <si>
-    <t>炼神四层</t>
-  </si>
-  <si>
-    <t>9E+130</t>
-  </si>
-  <si>
-    <t>9E+180</t>
-  </si>
-  <si>
-    <t>1E+75</t>
-  </si>
-  <si>
-    <t>炼神五层</t>
-  </si>
-  <si>
-    <t>9E+140</t>
-  </si>
-  <si>
-    <t>9E+190</t>
-  </si>
-  <si>
-    <t>炼神六层</t>
-  </si>
-  <si>
-    <t>9E+200</t>
+    <t>炼神十层</t>
+  </si>
+  <si>
+    <t>9E+240</t>
   </si>
   <si>
     <t>1E+85</t>
-  </si>
-  <si>
-    <t>炼神七层</t>
-  </si>
-  <si>
-    <t>9E+210</t>
-  </si>
-  <si>
-    <t>炼神八层</t>
-  </si>
-  <si>
-    <t>9E+220</t>
-  </si>
-  <si>
-    <t>1E+95</t>
-  </si>
-  <si>
-    <t>炼神九层</t>
-  </si>
-  <si>
-    <t>9E+230</t>
-  </si>
-  <si>
-    <t>炼神十层</t>
-  </si>
-  <si>
-    <t>9E+240</t>
   </si>
 </sst>
 </file>
@@ -958,7 +955,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -967,19 +964,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1300,7 +1285,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1324,16 +1309,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1342,93 +1327,92 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1436,45 +1420,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1794,89 +1765,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:Y68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="4.875" style="4" customWidth="1"/>
-    <col min="3" max="5" width="9.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.475" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="31.3333333333333" style="5" customWidth="1"/>
-    <col min="9" max="9" width="12.55" style="5" customWidth="1"/>
-    <col min="10" max="10" width="18.525" style="5" customWidth="1"/>
-    <col min="11" max="12" width="9.625" style="4" customWidth="1"/>
-    <col min="13" max="13" width="11.6916666666667" style="6" customWidth="1"/>
-    <col min="14" max="14" width="12.625" style="4" customWidth="1"/>
-    <col min="15" max="16" width="12.5083333333333" style="4" customWidth="1"/>
-    <col min="17" max="17" width="8" style="4" customWidth="1"/>
-    <col min="18" max="18" width="12.5083333333333" style="4" customWidth="1"/>
-    <col min="19" max="19" width="11.0166666666667" style="4" customWidth="1"/>
-    <col min="20" max="20" width="10.425" style="4" customWidth="1"/>
-    <col min="21" max="22" width="9.625" style="4" customWidth="1"/>
-    <col min="23" max="23" width="28.4833333333333" style="4" customWidth="1"/>
-    <col min="25" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="4.125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="4.875" style="3" customWidth="1"/>
+    <col min="3" max="6" width="9.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.475" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.9166666666667" style="4" customWidth="1"/>
+    <col min="10" max="10" width="12.55" style="4" customWidth="1"/>
+    <col min="11" max="11" width="18.525" style="4" customWidth="1"/>
+    <col min="12" max="13" width="9.625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="11.6916666666667" style="5" customWidth="1"/>
+    <col min="15" max="15" width="12.625" style="3" customWidth="1"/>
+    <col min="16" max="17" width="12.5083333333333" style="3" customWidth="1"/>
+    <col min="18" max="18" width="8" style="3" customWidth="1"/>
+    <col min="19" max="19" width="12.5083333333333" style="3" customWidth="1"/>
+    <col min="20" max="20" width="11.0166666666667" style="3" customWidth="1"/>
+    <col min="21" max="21" width="10.425" style="3" customWidth="1"/>
+    <col min="22" max="23" width="9.625" style="3" customWidth="1"/>
+    <col min="24" max="24" width="28.4833333333333" style="3" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="8" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:24">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:24">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:24">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="6" t="s">
         <v>5</v>
       </c>
       <c r="I3" s="9" t="s">
@@ -1885,65 +1856,68 @@
       <c r="J3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="P3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="R3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="S3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="8" t="s">
+      <c r="T3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="U3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="8" t="s">
+      <c r="V3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="17" t="s">
+      <c r="W3" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="8" t="s">
+      <c r="X3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="8" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:24">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="6" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="9" t="s">
@@ -1952,114 +1926,120 @@
       <c r="J4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="O4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="P4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="Q4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="8" t="s">
+      <c r="R4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="8" t="s">
+      <c r="S4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="8" t="s">
+      <c r="T4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="8" t="s">
+      <c r="U4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="V4" s="8" t="s">
+      <c r="V4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="W4" s="17" t="s">
+      <c r="W4" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="8" t="s">
+      <c r="X4" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:24">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="E5" s="6" t="s">
         <v>23</v>
       </c>
+      <c r="F5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>24</v>
+      </c>
       <c r="I5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="P5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="Q5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="R5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="S5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="N5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="T5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="U5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="V5" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="W5" s="17" t="s">
+      <c r="T5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="U5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="V5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="W5" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:23">
+      <c r="X5" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:24">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -2069,60 +2049,63 @@
       <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>26</v>
+      <c r="F6" s="1">
+        <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="I6" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="24" t="s">
+      <c r="J6" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="K6" s="2">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="14">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2">
-        <v>500</v>
+      <c r="K6" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2"/>
+      <c r="N6" s="11">
+        <v>0</v>
       </c>
       <c r="O6" s="2">
         <v>500</v>
       </c>
       <c r="P6" s="2">
+        <v>500</v>
+      </c>
+      <c r="Q6" s="2">
         <v>1500</v>
       </c>
-      <c r="Q6" s="2">
-        <v>0</v>
-      </c>
       <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2">
         <v>20</v>
       </c>
-      <c r="S6" s="2">
+      <c r="T6" s="2">
         <v>30</v>
       </c>
-      <c r="T6" s="2">
-        <v>0</v>
-      </c>
       <c r="U6" s="2">
         <v>0</v>
       </c>
       <c r="V6" s="2">
         <v>0</v>
       </c>
-      <c r="W6" s="25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:23">
+      <c r="W6" s="2">
+        <v>0</v>
+      </c>
+      <c r="X6" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:24">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -2132,65 +2115,68 @@
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>32</v>
+      <c r="F7" s="1">
+        <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="24" t="s">
+      <c r="H7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="24" t="s">
+      <c r="J7" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="2">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="14">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2">
-        <f t="shared" ref="N7:N17" si="0">N6+200</f>
+      <c r="K7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="11">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
+        <f t="shared" ref="O7:O17" si="0">O6+200</f>
         <v>700</v>
       </c>
-      <c r="O7" s="2">
-        <f t="shared" ref="O7:O17" si="1">O6+200</f>
+      <c r="P7" s="2">
+        <f t="shared" ref="P7:P17" si="1">P6+200</f>
         <v>700</v>
       </c>
-      <c r="P7" s="2">
-        <f t="shared" ref="P7:P25" si="2">P6+200</f>
+      <c r="Q7" s="2">
+        <f t="shared" ref="Q7:Q25" si="2">Q6+200</f>
         <v>1700</v>
       </c>
-      <c r="Q7" s="2">
-        <v>0</v>
-      </c>
       <c r="R7" s="2">
-        <f t="shared" ref="R7:R25" si="3">R6+2</f>
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <f t="shared" ref="S7:S25" si="3">S6+2</f>
         <v>22</v>
       </c>
-      <c r="S7" s="2">
-        <f t="shared" ref="S7:S12" si="4">S6+5</f>
+      <c r="T7" s="2">
+        <f t="shared" ref="T7:T12" si="4">T6+5</f>
         <v>35</v>
       </c>
-      <c r="T7" s="2">
-        <v>0</v>
-      </c>
       <c r="U7" s="2">
         <v>0</v>
       </c>
       <c r="V7" s="2">
         <v>0</v>
       </c>
-      <c r="W7" s="25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:23">
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:24">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -2200,65 +2186,68 @@
       <c r="E8" s="1">
         <v>3</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>37</v>
+      <c r="F8" s="1">
+        <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="H8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="24" t="s">
+      <c r="J8" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="14">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2">
+      <c r="K8" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="N8" s="11">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="O8" s="2">
+      <c r="P8" s="2">
         <f t="shared" si="1"/>
         <v>900</v>
       </c>
-      <c r="P8" s="2">
+      <c r="Q8" s="2">
         <f t="shared" si="2"/>
         <v>1900</v>
       </c>
-      <c r="Q8" s="2">
-        <v>0</v>
-      </c>
       <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="S8" s="2">
+      <c r="T8" s="2">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="T8" s="2">
-        <v>0</v>
-      </c>
       <c r="U8" s="2">
         <v>0</v>
       </c>
       <c r="V8" s="2">
         <v>0</v>
       </c>
-      <c r="W8" s="25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:23">
+      <c r="W8" s="2">
+        <v>0</v>
+      </c>
+      <c r="X8" s="18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:24">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -2268,65 +2257,68 @@
       <c r="E9" s="1">
         <v>4</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>42</v>
+      <c r="F9" s="1">
+        <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="I9" s="24" t="s">
+      <c r="H9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J9" s="24" t="s">
+      <c r="J9" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="K9" s="2">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="14">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2">
+      <c r="K9" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2"/>
+      <c r="N9" s="11">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="O9" s="2">
+      <c r="P9" s="2">
         <f t="shared" si="1"/>
         <v>1100</v>
       </c>
-      <c r="P9" s="2">
+      <c r="Q9" s="2">
         <f t="shared" si="2"/>
         <v>2100</v>
       </c>
-      <c r="Q9" s="2">
-        <v>0</v>
-      </c>
       <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="S9" s="2">
+      <c r="T9" s="2">
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="T9" s="2">
-        <v>0</v>
-      </c>
       <c r="U9" s="2">
         <v>0</v>
       </c>
       <c r="V9" s="2">
         <v>0</v>
       </c>
-      <c r="W9" s="25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:23">
+      <c r="W9" s="2">
+        <v>0</v>
+      </c>
+      <c r="X9" s="18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:24">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -2336,65 +2328,68 @@
       <c r="E10" s="1">
         <v>5</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>47</v>
+      <c r="F10" s="1">
+        <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="H10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="J10" s="24" t="s">
+      <c r="J10" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="K10" s="2">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="14">
-        <v>0</v>
-      </c>
-      <c r="N10" s="2">
+      <c r="K10" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2"/>
+      <c r="N10" s="11">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2">
         <f t="shared" si="0"/>
         <v>1300</v>
       </c>
-      <c r="O10" s="2">
+      <c r="P10" s="2">
         <f t="shared" si="1"/>
         <v>1300</v>
       </c>
-      <c r="P10" s="2">
+      <c r="Q10" s="2">
         <f t="shared" si="2"/>
         <v>2300</v>
       </c>
-      <c r="Q10" s="2">
-        <v>0</v>
-      </c>
       <c r="R10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="S10" s="2">
+      <c r="T10" s="2">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="T10" s="2">
-        <v>0</v>
-      </c>
       <c r="U10" s="2">
         <v>0</v>
       </c>
       <c r="V10" s="2">
         <v>0</v>
       </c>
-      <c r="W10" s="25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:23">
+      <c r="W10" s="2">
+        <v>0</v>
+      </c>
+      <c r="X10" s="18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:24">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -2404,63 +2399,66 @@
       <c r="E11" s="1">
         <v>6</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>52</v>
+      <c r="F11" s="1">
+        <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="I11" s="24" t="s">
+      <c r="H11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="K11" s="2">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="14">
-        <v>0</v>
-      </c>
-      <c r="N11" s="2">
+      <c r="K11" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2"/>
+      <c r="N11" s="11">
+        <v>0</v>
+      </c>
+      <c r="O11" s="2">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="O11" s="2">
+      <c r="P11" s="2">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="P11" s="2">
+      <c r="Q11" s="2">
         <f t="shared" si="2"/>
         <v>2500</v>
       </c>
-      <c r="Q11" s="2">
-        <v>0</v>
-      </c>
       <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="S11" s="2">
+      <c r="T11" s="2">
         <f t="shared" si="4"/>
         <v>55</v>
       </c>
-      <c r="T11" s="2">
-        <v>0</v>
-      </c>
       <c r="U11" s="2">
         <v>0</v>
       </c>
       <c r="V11" s="2">
         <v>0</v>
       </c>
-      <c r="W11" s="18"/>
-    </row>
-    <row r="12" customHeight="1" spans="3:23">
+      <c r="W11" s="2">
+        <v>0</v>
+      </c>
+      <c r="X11" s="14"/>
+    </row>
+    <row r="12" customHeight="1" spans="3:24">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -2470,65 +2468,68 @@
       <c r="E12" s="1">
         <v>7</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>56</v>
+      <c r="F12" s="1">
+        <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="I12" s="24" t="s">
+      <c r="H12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J12" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="K12" s="2">
-        <v>0</v>
-      </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="14">
-        <v>0</v>
-      </c>
-      <c r="N12" s="2">
+      <c r="K12" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="11">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2">
         <f t="shared" si="0"/>
         <v>1700</v>
       </c>
-      <c r="O12" s="2">
+      <c r="P12" s="2">
         <f t="shared" si="1"/>
         <v>1700</v>
       </c>
-      <c r="P12" s="2">
+      <c r="Q12" s="2">
         <f t="shared" si="2"/>
         <v>2700</v>
       </c>
-      <c r="Q12" s="2">
-        <v>0</v>
-      </c>
       <c r="R12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2">
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
-      <c r="S12" s="2">
+      <c r="T12" s="2">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="T12" s="2">
-        <v>0</v>
-      </c>
       <c r="U12" s="2">
         <v>0</v>
       </c>
       <c r="V12" s="2">
         <v>0</v>
       </c>
-      <c r="W12" s="25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:23">
+      <c r="W12" s="2">
+        <v>0</v>
+      </c>
+      <c r="X12" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:24">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -2538,65 +2539,68 @@
       <c r="E13" s="1">
         <v>8</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>60</v>
+      <c r="F13" s="1">
+        <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="24" t="s">
+      <c r="H13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="J13" s="24" t="s">
+      <c r="J13" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="K13" s="2">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="14">
-        <v>0</v>
-      </c>
-      <c r="N13" s="2">
+      <c r="K13" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2"/>
+      <c r="N13" s="11">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2">
         <f t="shared" si="0"/>
         <v>1900</v>
       </c>
-      <c r="O13" s="2">
+      <c r="P13" s="2">
         <f t="shared" si="1"/>
         <v>1900</v>
       </c>
-      <c r="P13" s="2">
+      <c r="Q13" s="2">
         <f t="shared" si="2"/>
         <v>2900</v>
       </c>
-      <c r="Q13" s="2">
-        <v>0</v>
-      </c>
       <c r="R13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2">
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="S13" s="2">
-        <f t="shared" ref="S13:S17" si="5">S12+10</f>
+      <c r="T13" s="2">
+        <f t="shared" ref="T13:T17" si="5">T12+10</f>
         <v>70</v>
       </c>
-      <c r="T13" s="2">
-        <v>0</v>
-      </c>
       <c r="U13" s="2">
         <v>0</v>
       </c>
       <c r="V13" s="2">
         <v>0</v>
       </c>
-      <c r="W13" s="25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:23">
+      <c r="W13" s="2">
+        <v>0</v>
+      </c>
+      <c r="X13" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:24">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -2606,65 +2610,68 @@
       <c r="E14" s="1">
         <v>9</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>64</v>
+      <c r="F14" s="1">
+        <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="24" t="s">
+      <c r="H14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="24" t="s">
+      <c r="J14" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="K14" s="2">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="14">
-        <v>0</v>
-      </c>
-      <c r="N14" s="2">
+      <c r="K14" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2"/>
+      <c r="N14" s="11">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2">
         <f t="shared" si="0"/>
         <v>2100</v>
       </c>
-      <c r="O14" s="2">
+      <c r="P14" s="2">
         <f t="shared" si="1"/>
         <v>2100</v>
       </c>
-      <c r="P14" s="2">
+      <c r="Q14" s="2">
         <f t="shared" si="2"/>
         <v>3100</v>
       </c>
-      <c r="Q14" s="2">
-        <v>0</v>
-      </c>
       <c r="R14" s="2">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2">
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="S14" s="2">
+      <c r="T14" s="2">
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
-      <c r="T14" s="2">
-        <v>0</v>
-      </c>
       <c r="U14" s="2">
         <v>0</v>
       </c>
       <c r="V14" s="2">
         <v>0</v>
       </c>
-      <c r="W14" s="25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:22">
+      <c r="W14" s="2">
+        <v>0</v>
+      </c>
+      <c r="X14" s="18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:23">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -2674,62 +2681,65 @@
       <c r="E15" s="1">
         <v>10</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>68</v>
+      <c r="F15" s="1">
+        <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="I15" s="24" t="s">
+      <c r="H15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J15" s="24" t="s">
+      <c r="J15" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="K15" s="2">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="14">
-        <v>0</v>
-      </c>
-      <c r="N15" s="2">
+      <c r="K15" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="L15" s="2">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2"/>
+      <c r="N15" s="11">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2">
         <f t="shared" si="0"/>
         <v>2300</v>
       </c>
-      <c r="O15" s="2">
+      <c r="P15" s="2">
         <f t="shared" si="1"/>
         <v>2300</v>
       </c>
-      <c r="P15" s="2">
+      <c r="Q15" s="2">
         <f t="shared" si="2"/>
         <v>3300</v>
       </c>
-      <c r="Q15" s="2">
-        <v>0</v>
-      </c>
       <c r="R15" s="2">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="S15" s="2">
+      <c r="T15" s="2">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="T15" s="2">
-        <v>0</v>
-      </c>
       <c r="U15" s="2">
         <v>0</v>
       </c>
       <c r="V15" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:22">
+      <c r="W15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:23">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -2739,62 +2749,65 @@
       <c r="E16" s="1">
         <v>11</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>72</v>
+      <c r="F16" s="1">
+        <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H16" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="I16" s="24" t="s">
+      <c r="H16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="J16" s="24" t="s">
+      <c r="J16" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="K16" s="2">
-        <v>0</v>
-      </c>
-      <c r="L16" s="2"/>
-      <c r="M16" s="14">
-        <v>0</v>
-      </c>
-      <c r="N16" s="2">
-        <f t="shared" ref="N16:N25" si="6">N15+400</f>
+      <c r="K16" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2"/>
+      <c r="N16" s="11">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2">
+        <f t="shared" ref="O16:O25" si="6">O15+400</f>
         <v>2700</v>
       </c>
-      <c r="O16" s="2">
-        <f t="shared" ref="O16:O25" si="7">O15+400</f>
+      <c r="P16" s="2">
+        <f t="shared" ref="P16:P25" si="7">P15+400</f>
         <v>2700</v>
       </c>
-      <c r="P16" s="2">
+      <c r="Q16" s="2">
         <f t="shared" si="2"/>
         <v>3500</v>
       </c>
-      <c r="Q16" s="2">
-        <v>0</v>
-      </c>
       <c r="R16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="S16" s="2">
-        <f t="shared" ref="S16:S25" si="8">S15+15</f>
+      <c r="T16" s="2">
+        <f t="shared" ref="T16:T25" si="8">T15+15</f>
         <v>105</v>
       </c>
-      <c r="T16" s="2">
-        <v>0</v>
-      </c>
       <c r="U16" s="2">
         <v>0</v>
       </c>
       <c r="V16" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:22">
+      <c r="W16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:23">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -2804,62 +2817,65 @@
       <c r="E17" s="1">
         <v>12</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>76</v>
+      <c r="F17" s="1">
+        <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="I17" s="24" t="s">
+      <c r="H17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="J17" s="24" t="s">
+      <c r="J17" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="K17" s="2">
-        <v>0</v>
-      </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="14">
-        <v>0</v>
-      </c>
-      <c r="N17" s="2">
+      <c r="K17" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L17" s="2">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2"/>
+      <c r="N17" s="11">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2">
         <f t="shared" si="6"/>
         <v>3100</v>
       </c>
-      <c r="O17" s="2">
+      <c r="P17" s="2">
         <f t="shared" si="7"/>
         <v>3100</v>
       </c>
-      <c r="P17" s="2">
+      <c r="Q17" s="2">
         <f t="shared" si="2"/>
         <v>3700</v>
       </c>
-      <c r="Q17" s="2">
-        <v>0</v>
-      </c>
       <c r="R17" s="2">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="S17" s="2">
+      <c r="T17" s="2">
         <f t="shared" si="8"/>
         <v>120</v>
       </c>
-      <c r="T17" s="2">
-        <v>0</v>
-      </c>
       <c r="U17" s="2">
         <v>0</v>
       </c>
       <c r="V17" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:22">
+      <c r="W17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:23">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -2869,62 +2885,65 @@
       <c r="E18" s="1">
         <v>13</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>80</v>
+      <c r="F18" s="1">
+        <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H18" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="I18" s="24" t="s">
+      <c r="H18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="J18" s="24" t="s">
+      <c r="J18" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="K18" s="2">
-        <v>0</v>
-      </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="14">
-        <v>0</v>
-      </c>
-      <c r="N18" s="2">
+      <c r="K18" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2"/>
+      <c r="N18" s="11">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2">
         <f t="shared" si="6"/>
         <v>3500</v>
       </c>
-      <c r="O18" s="2">
+      <c r="P18" s="2">
         <f t="shared" si="7"/>
         <v>3500</v>
       </c>
-      <c r="P18" s="2">
+      <c r="Q18" s="2">
         <f t="shared" si="2"/>
         <v>3900</v>
       </c>
-      <c r="Q18" s="2">
-        <v>0</v>
-      </c>
       <c r="R18" s="2">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
         <f t="shared" si="3"/>
         <v>44</v>
       </c>
-      <c r="S18" s="2">
+      <c r="T18" s="2">
         <f t="shared" si="8"/>
         <v>135</v>
       </c>
-      <c r="T18" s="2">
-        <v>0</v>
-      </c>
       <c r="U18" s="2">
         <v>0</v>
       </c>
       <c r="V18" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:22">
+      <c r="W18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:23">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -2934,62 +2953,65 @@
       <c r="E19" s="1">
         <v>14</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>84</v>
+      <c r="F19" s="1">
+        <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H19" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="I19" s="24" t="s">
+      <c r="H19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="J19" s="24" t="s">
+      <c r="J19" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="K19" s="2">
-        <v>0</v>
-      </c>
-      <c r="L19" s="2"/>
-      <c r="M19" s="14">
-        <v>0</v>
-      </c>
-      <c r="N19" s="2">
+      <c r="K19" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L19" s="2">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2"/>
+      <c r="N19" s="11">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2">
         <f t="shared" si="6"/>
         <v>3900</v>
       </c>
-      <c r="O19" s="2">
+      <c r="P19" s="2">
         <f t="shared" si="7"/>
         <v>3900</v>
       </c>
-      <c r="P19" s="2">
+      <c r="Q19" s="2">
         <f t="shared" si="2"/>
         <v>4100</v>
       </c>
-      <c r="Q19" s="2">
-        <v>0</v>
-      </c>
       <c r="R19" s="2">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2">
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
-      <c r="S19" s="2">
+      <c r="T19" s="2">
         <f t="shared" si="8"/>
         <v>150</v>
       </c>
-      <c r="T19" s="2">
-        <v>0</v>
-      </c>
       <c r="U19" s="2">
         <v>0</v>
       </c>
       <c r="V19" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:22">
+      <c r="W19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:23">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -2999,14 +3021,14 @@
       <c r="E20" s="1">
         <v>15</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>88</v>
+      <c r="F20" s="1">
+        <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="10" t="s">
         <v>89</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>90</v>
@@ -3014,47 +3036,50 @@
       <c r="J20" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="K20" s="2">
-        <v>0</v>
-      </c>
-      <c r="L20" s="2"/>
-      <c r="M20" s="14">
-        <v>0</v>
-      </c>
-      <c r="N20" s="2">
+      <c r="K20" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="L20" s="2">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2"/>
+      <c r="N20" s="11">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2">
         <f t="shared" si="6"/>
         <v>4300</v>
       </c>
-      <c r="O20" s="2">
+      <c r="P20" s="2">
         <f t="shared" si="7"/>
         <v>4300</v>
       </c>
-      <c r="P20" s="2">
+      <c r="Q20" s="2">
         <f t="shared" si="2"/>
         <v>4300</v>
       </c>
-      <c r="Q20" s="2">
-        <v>0</v>
-      </c>
       <c r="R20" s="2">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2">
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="S20" s="2">
+      <c r="T20" s="2">
         <f t="shared" si="8"/>
         <v>165</v>
       </c>
-      <c r="T20" s="2">
-        <v>0</v>
-      </c>
       <c r="U20" s="2">
         <v>0</v>
       </c>
       <c r="V20" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:22">
+      <c r="W20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:23">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -3064,14 +3089,14 @@
       <c r="E21" s="1">
         <v>16</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>92</v>
+      <c r="F21" s="1">
+        <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H21" s="10" t="s">
         <v>93</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>94</v>
@@ -3079,47 +3104,50 @@
       <c r="J21" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="K21" s="2">
-        <v>0</v>
-      </c>
-      <c r="L21" s="2"/>
-      <c r="M21" s="14">
-        <v>0</v>
-      </c>
-      <c r="N21" s="2">
-        <f t="shared" ref="N21:N25" si="9">N20+800</f>
+      <c r="K21" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="L21" s="2">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2"/>
+      <c r="N21" s="11">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2">
+        <f t="shared" ref="O21:O25" si="9">O20+800</f>
         <v>5100</v>
       </c>
-      <c r="O21" s="2">
-        <f t="shared" ref="O21:O25" si="10">O20+800</f>
+      <c r="P21" s="2">
+        <f t="shared" ref="P21:P25" si="10">P20+800</f>
         <v>5100</v>
       </c>
-      <c r="P21" s="2">
-        <f t="shared" ref="P21:P26" si="11">P20+400</f>
+      <c r="Q21" s="2">
+        <f t="shared" ref="Q21:Q26" si="11">Q20+400</f>
         <v>4700</v>
       </c>
-      <c r="Q21" s="2">
-        <v>0</v>
-      </c>
       <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="S21" s="2">
-        <f t="shared" ref="S21:S25" si="12">S20+25</f>
+      <c r="T21" s="2">
+        <f t="shared" ref="T21:T25" si="12">T20+25</f>
         <v>190</v>
       </c>
-      <c r="T21" s="2">
-        <v>0</v>
-      </c>
       <c r="U21" s="2">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2">
         <v>10</v>
       </c>
-      <c r="V21" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:22">
+      <c r="W21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:23">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -3129,14 +3157,14 @@
       <c r="E22" s="1">
         <v>17</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>96</v>
+      <c r="F22" s="1">
+        <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H22" s="10" t="s">
         <v>97</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>98</v>
@@ -3144,47 +3172,50 @@
       <c r="J22" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="K22" s="2">
-        <v>0</v>
-      </c>
-      <c r="L22" s="2"/>
-      <c r="M22" s="14">
-        <v>0</v>
-      </c>
-      <c r="N22" s="2">
+      <c r="K22" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2"/>
+      <c r="N22" s="11">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2">
         <f t="shared" si="9"/>
         <v>5900</v>
       </c>
-      <c r="O22" s="2">
+      <c r="P22" s="2">
         <f t="shared" si="10"/>
         <v>5900</v>
       </c>
-      <c r="P22" s="2">
+      <c r="Q22" s="2">
         <f t="shared" si="11"/>
         <v>5100</v>
       </c>
-      <c r="Q22" s="2">
-        <v>0</v>
-      </c>
       <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
         <f t="shared" si="3"/>
         <v>52</v>
       </c>
-      <c r="S22" s="2">
+      <c r="T22" s="2">
         <f t="shared" si="12"/>
         <v>215</v>
       </c>
-      <c r="T22" s="2">
-        <v>0</v>
-      </c>
       <c r="U22" s="2">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2">
         <v>20</v>
       </c>
-      <c r="V22" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:22">
+      <c r="W22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:23">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -3194,14 +3225,14 @@
       <c r="E23" s="1">
         <v>18</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>100</v>
+      <c r="F23" s="1">
+        <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H23" s="10" t="s">
         <v>101</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>102</v>
@@ -3209,47 +3240,50 @@
       <c r="J23" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="K23" s="2">
-        <v>0</v>
-      </c>
-      <c r="L23" s="2"/>
-      <c r="M23" s="14">
-        <v>0</v>
-      </c>
-      <c r="N23" s="2">
+      <c r="K23" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="L23" s="2">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2"/>
+      <c r="N23" s="11">
+        <v>0</v>
+      </c>
+      <c r="O23" s="2">
         <f t="shared" si="9"/>
         <v>6700</v>
       </c>
-      <c r="O23" s="2">
+      <c r="P23" s="2">
         <f t="shared" si="10"/>
         <v>6700</v>
       </c>
-      <c r="P23" s="2">
+      <c r="Q23" s="2">
         <f t="shared" si="11"/>
         <v>5500</v>
       </c>
-      <c r="Q23" s="2">
-        <v>0</v>
-      </c>
       <c r="R23" s="2">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="S23" s="2">
+      <c r="T23" s="2">
         <f t="shared" si="12"/>
         <v>240</v>
       </c>
-      <c r="T23" s="2">
-        <v>0</v>
-      </c>
       <c r="U23" s="2">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2">
         <v>30</v>
       </c>
-      <c r="V23" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:22">
+      <c r="W23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:23">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -3259,14 +3293,14 @@
       <c r="E24" s="1">
         <v>19</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>104</v>
+      <c r="F24" s="1">
+        <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H24" s="10" t="s">
         <v>105</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>106</v>
@@ -3274,47 +3308,50 @@
       <c r="J24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="K24" s="2">
-        <v>0</v>
-      </c>
-      <c r="L24" s="2"/>
-      <c r="M24" s="14">
-        <v>0</v>
-      </c>
-      <c r="N24" s="2">
+      <c r="K24" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="L24" s="2">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2"/>
+      <c r="N24" s="11">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2">
         <f t="shared" si="9"/>
         <v>7500</v>
       </c>
-      <c r="O24" s="2">
+      <c r="P24" s="2">
         <f t="shared" si="10"/>
         <v>7500</v>
       </c>
-      <c r="P24" s="2">
+      <c r="Q24" s="2">
         <f t="shared" si="11"/>
         <v>5900</v>
       </c>
-      <c r="Q24" s="2">
-        <v>0</v>
-      </c>
       <c r="R24" s="2">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2">
         <f t="shared" si="3"/>
         <v>56</v>
       </c>
-      <c r="S24" s="2">
+      <c r="T24" s="2">
         <f t="shared" si="12"/>
         <v>265</v>
       </c>
-      <c r="T24" s="2">
-        <v>0</v>
-      </c>
       <c r="U24" s="2">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2">
         <v>40</v>
       </c>
-      <c r="V24" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:22">
+      <c r="W24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:23">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -3324,2241 +3361,2490 @@
       <c r="E25" s="1">
         <v>20</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>108</v>
+      <c r="F25" s="1">
+        <v>20</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>94</v>
+        <v>109</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="J25" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="K25" s="2">
-        <v>0</v>
-      </c>
-      <c r="L25" s="2"/>
-      <c r="M25" s="14">
-        <v>0</v>
-      </c>
-      <c r="N25" s="2">
+      <c r="K25" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="L25" s="2">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2"/>
+      <c r="N25" s="11">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2">
         <f t="shared" si="9"/>
         <v>8300</v>
       </c>
-      <c r="O25" s="2">
+      <c r="P25" s="2">
         <f t="shared" si="10"/>
         <v>8300</v>
       </c>
-      <c r="P25" s="2">
+      <c r="Q25" s="2">
         <f t="shared" si="11"/>
         <v>6300</v>
       </c>
-      <c r="Q25" s="2">
-        <v>0</v>
-      </c>
       <c r="R25" s="2">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2">
         <f t="shared" si="3"/>
         <v>58</v>
       </c>
-      <c r="S25" s="2">
+      <c r="T25" s="2">
         <f t="shared" si="12"/>
         <v>290</v>
       </c>
-      <c r="T25" s="2">
-        <v>0</v>
-      </c>
       <c r="U25" s="2">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2">
         <v>50</v>
       </c>
-      <c r="V25" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="8:17">
-      <c r="H26" s="10"/>
-      <c r="M26" s="14"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="15"/>
-    </row>
-    <row r="27" customHeight="1" spans="8:17">
-      <c r="H27" s="10"/>
+      <c r="W25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="9:18">
+      <c r="I26" s="10"/>
+      <c r="N26" s="11"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="12"/>
+    </row>
+    <row r="27" customHeight="1" spans="9:18">
       <c r="I27" s="10"/>
-      <c r="M27" s="14"/>
-      <c r="Q27" s="2"/>
-    </row>
-    <row r="28" customHeight="1" spans="8:17">
-      <c r="H28" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="N27" s="11"/>
+      <c r="R27" s="2"/>
+    </row>
+    <row r="28" customHeight="1" spans="9:18">
       <c r="I28" s="10"/>
-      <c r="M28" s="14"/>
-      <c r="Q28" s="2"/>
-    </row>
-    <row r="29" customHeight="1" spans="8:17">
-      <c r="H29" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="N28" s="11"/>
+      <c r="R28" s="2"/>
+    </row>
+    <row r="29" customHeight="1" spans="9:18">
       <c r="I29" s="10"/>
-      <c r="M29" s="14"/>
-      <c r="Q29" s="2"/>
-    </row>
-    <row r="30" customHeight="1" spans="9:17">
-      <c r="I30" s="10"/>
-      <c r="M30" s="14"/>
-      <c r="Q30" s="2"/>
-    </row>
-    <row r="31" customHeight="1" spans="9:17">
-      <c r="I31" s="10"/>
-      <c r="M31" s="14"/>
-      <c r="Q31" s="2"/>
-    </row>
-    <row r="32" customHeight="1" spans="9:17">
-      <c r="I32" s="10"/>
-      <c r="M32" s="14"/>
-      <c r="Q32" s="2"/>
-    </row>
-    <row r="33" customHeight="1" spans="3:23">
-      <c r="C33" s="1">
+      <c r="J29" s="10"/>
+      <c r="N29" s="11"/>
+      <c r="R29" s="2"/>
+    </row>
+    <row r="30" customHeight="1" spans="10:18">
+      <c r="J30" s="10"/>
+      <c r="N30" s="11"/>
+      <c r="R30" s="2"/>
+    </row>
+    <row r="31" customHeight="1" spans="10:18">
+      <c r="J31" s="10"/>
+      <c r="N31" s="11"/>
+      <c r="R31" s="2"/>
+    </row>
+    <row r="32" customHeight="1" spans="10:18">
+      <c r="J32" s="10"/>
+      <c r="N32" s="11"/>
+      <c r="R32" s="2"/>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C33" s="7">
         <v>101</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33" s="7">
         <v>2</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="7">
+        <v>1</v>
+      </c>
+      <c r="F33" s="7">
         <v>10</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="H33" s="24" t="s">
+      <c r="H33" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="I33" s="24" t="s">
+      <c r="I33" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="J33" s="24" t="s">
+      <c r="J33" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="K33" s="25" t="s">
+      <c r="K33" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="L33" s="2"/>
-      <c r="M33" s="25" t="s">
+      <c r="L33" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="N33" s="15">
+      <c r="M33" s="2"/>
+      <c r="N33" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="O33" s="12">
         <v>10000</v>
       </c>
-      <c r="O33" s="15">
+      <c r="P33" s="12">
         <v>10000</v>
       </c>
-      <c r="P33" s="15">
+      <c r="Q33" s="12">
         <v>10000</v>
       </c>
-      <c r="Q33" s="15">
+      <c r="R33" s="12">
         <v>10000</v>
       </c>
-      <c r="R33" s="2">
-        <v>0</v>
-      </c>
-      <c r="S33" s="19">
+      <c r="S33" s="2">
+        <v>0</v>
+      </c>
+      <c r="T33" s="12">
         <v>150</v>
       </c>
-      <c r="T33" s="2">
+      <c r="U33" s="2">
         <v>150</v>
       </c>
-      <c r="U33" s="2">
+      <c r="V33" s="2">
         <v>99</v>
       </c>
-      <c r="V33" s="2">
+      <c r="W33" s="2">
         <v>100</v>
       </c>
-      <c r="W33" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:23">
-      <c r="C34" s="1">
+      <c r="X33" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y33" s="16"/>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C34" s="7">
         <v>102</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" s="7">
         <v>2</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="7">
+        <v>2</v>
+      </c>
+      <c r="F34" s="7">
         <v>11</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="G34" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I34" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="J34" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="K34" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="L34" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="M34" s="2"/>
+      <c r="N34" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="O34" s="12">
+        <f t="shared" ref="O33:O52" si="13">O33+1000</f>
+        <v>11000</v>
+      </c>
+      <c r="P34" s="12">
+        <f t="shared" ref="P33:P52" si="14">P33+1000</f>
+        <v>11000</v>
+      </c>
+      <c r="Q34" s="12">
+        <f t="shared" ref="Q34:Q52" si="15">Q33+2000</f>
+        <v>12000</v>
+      </c>
+      <c r="R34" s="2">
+        <f t="shared" ref="R34:R52" si="16">R33+2000</f>
+        <v>12000</v>
+      </c>
+      <c r="S34" s="2">
+        <v>0</v>
+      </c>
+      <c r="T34" s="2">
+        <f t="shared" ref="T34:T52" si="17">T33+20</f>
+        <v>170</v>
+      </c>
+      <c r="U34" s="2">
+        <f t="shared" ref="U34:U52" si="18">U33+30</f>
+        <v>180</v>
+      </c>
+      <c r="V34" s="2">
+        <v>99</v>
+      </c>
+      <c r="W34" s="2">
+        <v>100</v>
+      </c>
+      <c r="X34" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H34" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="I34" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="J34" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="K34" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="L34" s="2"/>
-      <c r="M34" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="N34" s="15">
-        <f t="shared" ref="N33:N52" si="13">N33+1000</f>
-        <v>11000</v>
-      </c>
-      <c r="O34" s="15">
-        <f t="shared" ref="O33:O52" si="14">O33+1000</f>
-        <v>11000</v>
-      </c>
-      <c r="P34" s="15">
-        <f t="shared" ref="P34:P52" si="15">P33+2000</f>
-        <v>12000</v>
-      </c>
-      <c r="Q34" s="2">
-        <f t="shared" ref="Q34:Q52" si="16">Q33+2000</f>
-        <v>12000</v>
-      </c>
-      <c r="R34" s="2">
-        <v>0</v>
-      </c>
-      <c r="S34" s="2">
-        <f t="shared" ref="S34:S52" si="17">S33+20</f>
-        <v>170</v>
-      </c>
-      <c r="T34" s="2">
-        <f t="shared" ref="T34:T52" si="18">T33+30</f>
-        <v>180</v>
-      </c>
-      <c r="U34" s="2">
-        <v>99</v>
-      </c>
-      <c r="V34" s="2">
-        <v>100</v>
-      </c>
-      <c r="W34" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:23">
-      <c r="C35" s="1">
+      <c r="Y34" s="16"/>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C35" s="7">
         <v>103</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" s="7">
         <v>2</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="7">
+        <v>3</v>
+      </c>
+      <c r="F35" s="7">
         <v>12</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H35" s="24" t="s">
+      <c r="G35" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="I35" s="24" t="s">
+      <c r="H35" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="J35" s="24" t="s">
+      <c r="I35" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="K35" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="L35" s="2"/>
-      <c r="M35" s="25" t="s">
+      <c r="J35" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="K35" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="N35" s="15">
+      <c r="L35" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="M35" s="2"/>
+      <c r="N35" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="O35" s="12">
         <f t="shared" si="13"/>
         <v>12000</v>
       </c>
-      <c r="O35" s="15">
+      <c r="P35" s="12">
         <f t="shared" si="14"/>
         <v>12000</v>
       </c>
-      <c r="P35" s="15">
+      <c r="Q35" s="12">
         <f t="shared" si="15"/>
         <v>14000</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="R35" s="2">
         <f t="shared" si="16"/>
         <v>14000</v>
       </c>
-      <c r="R35" s="2">
-        <v>0</v>
-      </c>
       <c r="S35" s="2">
+        <v>0</v>
+      </c>
+      <c r="T35" s="2">
         <f t="shared" si="17"/>
         <v>190</v>
       </c>
-      <c r="T35" s="2">
+      <c r="U35" s="2">
         <f t="shared" si="18"/>
         <v>210</v>
       </c>
-      <c r="U35" s="2">
+      <c r="V35" s="2">
         <v>99</v>
       </c>
-      <c r="V35" s="2">
+      <c r="W35" s="2">
         <v>100</v>
       </c>
-      <c r="W35" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:23">
-      <c r="C36" s="1">
+      <c r="X35" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y35" s="16"/>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C36" s="7">
         <v>104</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" s="7">
         <v>2</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="7">
+        <v>4</v>
+      </c>
+      <c r="F36" s="7">
         <v>13</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H36" s="24" t="s">
+      <c r="G36" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="I36" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="J36" s="24" t="s">
+      <c r="H36" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I36" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="K36" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="L36" s="2"/>
-      <c r="M36" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="N36" s="15">
+      <c r="J36" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="K36" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="L36" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="M36" s="2"/>
+      <c r="N36" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="O36" s="12">
         <f t="shared" si="13"/>
         <v>13000</v>
       </c>
-      <c r="O36" s="15">
+      <c r="P36" s="12">
         <f t="shared" si="14"/>
         <v>13000</v>
       </c>
-      <c r="P36" s="15">
+      <c r="Q36" s="12">
         <f t="shared" si="15"/>
         <v>16000</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="R36" s="2">
         <f t="shared" si="16"/>
         <v>16000</v>
       </c>
-      <c r="R36" s="2">
-        <v>0</v>
-      </c>
       <c r="S36" s="2">
+        <v>0</v>
+      </c>
+      <c r="T36" s="2">
         <f t="shared" si="17"/>
         <v>210</v>
       </c>
-      <c r="T36" s="2">
+      <c r="U36" s="2">
         <f t="shared" si="18"/>
         <v>240</v>
       </c>
-      <c r="U36" s="2">
+      <c r="V36" s="2">
         <v>99</v>
       </c>
-      <c r="V36" s="2">
+      <c r="W36" s="2">
         <v>100</v>
       </c>
-      <c r="W36" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:23">
-      <c r="C37" s="1">
+      <c r="X36" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y36" s="16"/>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C37" s="7">
         <v>105</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" s="7">
         <v>2</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="7">
+        <v>5</v>
+      </c>
+      <c r="F37" s="7">
         <v>14</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H37" s="24" t="s">
+      <c r="G37" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="I37" s="24" t="s">
+      <c r="H37" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I37" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="J37" s="24" t="s">
+      <c r="J37" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="K37" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="L37" s="2"/>
-      <c r="M37" s="25" t="s">
+      <c r="K37" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="N37" s="15">
+      <c r="L37" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="M37" s="2"/>
+      <c r="N37" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="O37" s="12">
         <f t="shared" si="13"/>
         <v>14000</v>
       </c>
-      <c r="O37" s="15">
+      <c r="P37" s="12">
         <f t="shared" si="14"/>
         <v>14000</v>
       </c>
-      <c r="P37" s="15">
+      <c r="Q37" s="12">
         <f t="shared" si="15"/>
         <v>18000</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="R37" s="2">
         <f t="shared" si="16"/>
         <v>18000</v>
       </c>
-      <c r="R37" s="2">
-        <v>0</v>
-      </c>
       <c r="S37" s="2">
+        <v>0</v>
+      </c>
+      <c r="T37" s="2">
         <f t="shared" si="17"/>
         <v>230</v>
       </c>
-      <c r="T37" s="2">
+      <c r="U37" s="2">
         <f t="shared" si="18"/>
         <v>270</v>
       </c>
-      <c r="U37" s="2">
+      <c r="V37" s="2">
         <v>99</v>
       </c>
-      <c r="V37" s="2">
+      <c r="W37" s="2">
         <v>100</v>
       </c>
-      <c r="W37" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:23">
-      <c r="C38" s="1">
+      <c r="X37" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y37" s="16"/>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C38" s="7">
         <v>106</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" s="7">
         <v>2</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38" s="7">
+        <v>6</v>
+      </c>
+      <c r="F38" s="7">
         <v>15</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H38" s="24" t="s">
+      <c r="G38" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="I38" s="24" t="s">
+      <c r="H38" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I38" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="J38" s="24" t="s">
+      <c r="J38" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="K38" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="L38" s="2"/>
-      <c r="M38" s="25" t="s">
+      <c r="K38" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="N38" s="15">
+      <c r="L38" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="M38" s="2"/>
+      <c r="N38" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="O38" s="12">
         <f t="shared" si="13"/>
         <v>15000</v>
       </c>
-      <c r="O38" s="15">
+      <c r="P38" s="12">
         <f t="shared" si="14"/>
         <v>15000</v>
       </c>
-      <c r="P38" s="15">
+      <c r="Q38" s="12">
         <f t="shared" si="15"/>
         <v>20000</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <f t="shared" si="16"/>
         <v>20000</v>
       </c>
-      <c r="R38" s="2">
-        <v>0</v>
-      </c>
       <c r="S38" s="2">
+        <v>0</v>
+      </c>
+      <c r="T38" s="2">
         <f t="shared" si="17"/>
         <v>250</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <f t="shared" si="18"/>
         <v>300</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>99</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>100</v>
       </c>
-      <c r="W38" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:24">
-      <c r="C39" s="11">
+      <c r="X38" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y38" s="16"/>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C39" s="7">
         <v>107</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="7">
         <v>2</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="7">
+        <v>7</v>
+      </c>
+      <c r="F39" s="7">
         <v>16</v>
       </c>
-      <c r="F39" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="G39" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="H39" s="24" t="s">
+      <c r="G39" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="I39" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="J39" s="24" t="s">
+      <c r="H39" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I39" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="K39" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="M39" s="25" t="s">
+      <c r="J39" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="K39" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="N39" s="15">
+      <c r="L39" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="N39" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="O39" s="12">
         <f t="shared" si="13"/>
         <v>16000</v>
       </c>
-      <c r="O39" s="15">
+      <c r="P39" s="12">
         <f t="shared" si="14"/>
         <v>16000</v>
       </c>
-      <c r="P39" s="15">
+      <c r="Q39" s="12">
         <f t="shared" si="15"/>
         <v>22000</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="R39" s="2">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="R39" s="2">
-        <v>0</v>
-      </c>
       <c r="S39" s="2">
+        <v>0</v>
+      </c>
+      <c r="T39" s="2">
         <f t="shared" si="17"/>
         <v>270</v>
       </c>
-      <c r="T39" s="2">
+      <c r="U39" s="2">
         <f t="shared" si="18"/>
         <v>330</v>
       </c>
-      <c r="U39" s="2">
+      <c r="V39" s="2">
         <v>99</v>
       </c>
-      <c r="V39" s="2">
+      <c r="W39" s="2">
         <v>100</v>
       </c>
-      <c r="W39" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="X39" s="21"/>
-    </row>
-    <row r="40" customHeight="1" spans="3:23">
-      <c r="C40" s="1">
+      <c r="X39" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y39" s="16"/>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C40" s="7">
         <v>108</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" s="7">
         <v>2</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40" s="7">
+        <v>8</v>
+      </c>
+      <c r="F40" s="7">
         <v>17</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H40" s="24" t="s">
+      <c r="G40" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="I40" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="J40" s="24" t="s">
+      <c r="H40" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I40" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="K40" s="25" t="s">
+      <c r="J40" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="K40" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="L40" s="2"/>
-      <c r="M40" s="25" t="s">
+      <c r="L40" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="N40" s="15">
+      <c r="M40" s="2"/>
+      <c r="N40" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="O40" s="12">
         <f t="shared" si="13"/>
         <v>17000</v>
       </c>
-      <c r="O40" s="15">
+      <c r="P40" s="12">
         <f t="shared" si="14"/>
         <v>17000</v>
       </c>
-      <c r="P40" s="15">
+      <c r="Q40" s="12">
         <f t="shared" si="15"/>
         <v>24000</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="R40" s="2">
         <f t="shared" si="16"/>
         <v>24000</v>
       </c>
-      <c r="R40" s="2">
-        <v>0</v>
-      </c>
       <c r="S40" s="2">
+        <v>0</v>
+      </c>
+      <c r="T40" s="2">
         <f t="shared" si="17"/>
         <v>290</v>
       </c>
-      <c r="T40" s="2">
+      <c r="U40" s="2">
         <f t="shared" si="18"/>
         <v>360</v>
       </c>
-      <c r="U40" s="2">
+      <c r="V40" s="2">
         <v>99</v>
       </c>
-      <c r="V40" s="2">
+      <c r="W40" s="2">
         <v>100</v>
       </c>
-      <c r="W40" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:23">
-      <c r="C41" s="1">
+      <c r="X40" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y40" s="16"/>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C41" s="7">
         <v>109</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41" s="7">
         <v>2</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="7">
+        <v>9</v>
+      </c>
+      <c r="F41" s="7">
         <v>18</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="G41" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I41" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="K41" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="L41" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H41" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="I41" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="J41" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="K41" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="L41" s="2"/>
-      <c r="M41" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="N41" s="15">
+      <c r="M41" s="2"/>
+      <c r="N41" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="O41" s="12">
         <f t="shared" si="13"/>
         <v>18000</v>
       </c>
-      <c r="O41" s="15">
+      <c r="P41" s="12">
         <f t="shared" si="14"/>
         <v>18000</v>
       </c>
-      <c r="P41" s="15">
+      <c r="Q41" s="12">
         <f t="shared" si="15"/>
         <v>26000</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="R41" s="2">
         <f t="shared" si="16"/>
         <v>26000</v>
       </c>
-      <c r="R41" s="2">
-        <v>0</v>
-      </c>
       <c r="S41" s="2">
+        <v>0</v>
+      </c>
+      <c r="T41" s="2">
         <f t="shared" si="17"/>
         <v>310</v>
       </c>
-      <c r="T41" s="2">
+      <c r="U41" s="2">
         <f t="shared" si="18"/>
         <v>390</v>
       </c>
-      <c r="U41" s="2">
+      <c r="V41" s="2">
         <v>99</v>
       </c>
-      <c r="V41" s="2">
+      <c r="W41" s="2">
         <v>100</v>
       </c>
-      <c r="W41" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:23">
-      <c r="C42" s="1">
+      <c r="X41" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y41" s="16"/>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C42" s="7">
         <v>110</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D42" s="7">
         <v>2</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="7">
+        <v>10</v>
+      </c>
+      <c r="F42" s="7">
         <v>19</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="G42" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I42" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="K42" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="L42" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H42" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="I42" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="J42" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="K42" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="L42" s="2"/>
-      <c r="M42" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="N42" s="15">
+      <c r="M42" s="2"/>
+      <c r="N42" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="O42" s="12">
         <f t="shared" si="13"/>
         <v>19000</v>
       </c>
-      <c r="O42" s="15">
+      <c r="P42" s="12">
         <f t="shared" si="14"/>
         <v>19000</v>
       </c>
-      <c r="P42" s="15">
+      <c r="Q42" s="12">
         <f t="shared" si="15"/>
         <v>28000</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="R42" s="2">
         <f t="shared" si="16"/>
         <v>28000</v>
       </c>
-      <c r="R42" s="2">
-        <v>0</v>
-      </c>
       <c r="S42" s="2">
+        <v>0</v>
+      </c>
+      <c r="T42" s="2">
         <f t="shared" si="17"/>
         <v>330</v>
       </c>
-      <c r="T42" s="2">
+      <c r="U42" s="2">
         <f t="shared" si="18"/>
         <v>420</v>
       </c>
-      <c r="U42" s="2">
+      <c r="V42" s="2">
         <v>99</v>
       </c>
-      <c r="V42" s="2">
+      <c r="W42" s="2">
         <v>100</v>
       </c>
-      <c r="W42" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="43" s="3" customFormat="1" customHeight="1" spans="3:24">
-      <c r="C43" s="12">
+      <c r="X42" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y42" s="16"/>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C43" s="7">
         <v>111</v>
       </c>
-      <c r="D43" s="12">
+      <c r="D43" s="7">
         <v>2</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43" s="7">
+        <v>11</v>
+      </c>
+      <c r="F43" s="7">
         <v>20</v>
       </c>
-      <c r="F43" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="H43" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="I43" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="J43" s="27" t="s">
+      <c r="G43" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="K43" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="L43" s="28" t="s">
+      <c r="H43" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I43" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="J43" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="K43" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="M43" s="28" t="s">
+      <c r="L43" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="N43" s="16">
+      <c r="M43" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="N43" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="O43" s="12">
         <f t="shared" si="13"/>
         <v>20000</v>
       </c>
-      <c r="O43" s="16">
+      <c r="P43" s="12">
         <f t="shared" si="14"/>
         <v>20000</v>
       </c>
-      <c r="P43" s="16">
+      <c r="Q43" s="12">
         <f t="shared" si="15"/>
         <v>30000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="2">
         <f t="shared" si="16"/>
         <v>30000</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
-      <c r="S43" s="3">
-        <f t="shared" ref="S43:S52" si="19">S42+30</f>
-        <v>360</v>
-      </c>
-      <c r="T43" s="3">
-        <f t="shared" ref="T43:T52" si="20">T42+40</f>
+      <c r="S43" s="2">
+        <v>0</v>
+      </c>
+      <c r="T43" s="2">
+        <f t="shared" si="17"/>
+        <v>350</v>
+      </c>
+      <c r="U43" s="2">
+        <f t="shared" ref="U43:U52" si="19">U42+40</f>
         <v>460</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="2">
         <v>99</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="2">
         <v>120</v>
       </c>
-      <c r="W43" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="X43" s="23"/>
-    </row>
-    <row r="44" customHeight="1" spans="3:23">
-      <c r="C44" s="1">
+      <c r="X43" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y43" s="16"/>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C44" s="7">
         <v>112</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" s="7">
         <v>2</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="7">
+        <v>12</v>
+      </c>
+      <c r="F44" s="7">
         <v>21</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H44" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="I44" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="J44" s="24" t="s">
+      <c r="G44" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="K44" s="25" t="s">
+      <c r="H44" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I44" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="L44" s="28" t="s">
+      <c r="J44" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="K44" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="M44" s="25" t="s">
+      <c r="L44" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="N44" s="15">
-        <f t="shared" ref="N44:N52" si="21">N43+5000</f>
+      <c r="M44" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="N44" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="O44" s="12">
+        <f t="shared" ref="O44:O52" si="20">O43+5000</f>
         <v>25000</v>
       </c>
-      <c r="O44" s="15">
-        <f t="shared" ref="O44:O52" si="22">O43+5000</f>
+      <c r="P44" s="12">
+        <f t="shared" ref="P44:P52" si="21">P43+5000</f>
         <v>25000</v>
       </c>
-      <c r="P44" s="15">
-        <f t="shared" ref="P44:P52" si="23">P43+4000</f>
+      <c r="Q44" s="12">
+        <f t="shared" ref="Q44:Q52" si="22">Q43+4000</f>
         <v>34000</v>
       </c>
-      <c r="Q44" s="15">
-        <f t="shared" ref="Q44:Q52" si="24">Q43+4000</f>
+      <c r="R44" s="12">
+        <f t="shared" ref="R44:R52" si="23">R43+4000</f>
         <v>34000</v>
       </c>
-      <c r="R44" s="2">
-        <v>0</v>
-      </c>
       <c r="S44" s="2">
+        <v>0</v>
+      </c>
+      <c r="T44" s="2">
+        <f t="shared" si="17"/>
+        <v>370</v>
+      </c>
+      <c r="U44" s="2">
         <f t="shared" si="19"/>
-        <v>390</v>
-      </c>
-      <c r="T44" s="2">
+        <v>500</v>
+      </c>
+      <c r="V44" s="2">
+        <v>99</v>
+      </c>
+      <c r="W44" s="2">
+        <v>140</v>
+      </c>
+      <c r="X44" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y44" s="16"/>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C45" s="7">
+        <v>113</v>
+      </c>
+      <c r="D45" s="7">
+        <v>2</v>
+      </c>
+      <c r="E45" s="7">
+        <v>13</v>
+      </c>
+      <c r="F45" s="7">
+        <v>22</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I45" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="J45" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="K45" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="L45" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="M45" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="N45" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="O45" s="12">
         <f t="shared" si="20"/>
-        <v>500</v>
-      </c>
-      <c r="U44" s="2">
-        <v>99</v>
-      </c>
-      <c r="V44" s="2">
-        <v>140</v>
-      </c>
-      <c r="W44" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:23">
-      <c r="C45" s="1">
-        <v>113</v>
-      </c>
-      <c r="D45" s="1">
-        <v>2</v>
-      </c>
-      <c r="E45" s="1">
-        <v>22</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H45" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="I45" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="J45" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="K45" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="L45" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="M45" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="N45" s="15">
+        <v>30000</v>
+      </c>
+      <c r="P45" s="12">
         <f t="shared" si="21"/>
         <v>30000</v>
       </c>
-      <c r="O45" s="15">
+      <c r="Q45" s="12">
         <f t="shared" si="22"/>
-        <v>30000</v>
-      </c>
-      <c r="P45" s="15">
+        <v>38000</v>
+      </c>
+      <c r="R45" s="12">
         <f t="shared" si="23"/>
         <v>38000</v>
       </c>
-      <c r="Q45" s="15">
-        <f t="shared" si="24"/>
-        <v>38000</v>
-      </c>
-      <c r="R45" s="2">
-        <v>0</v>
-      </c>
       <c r="S45" s="2">
+        <v>0</v>
+      </c>
+      <c r="T45" s="2">
+        <f t="shared" si="17"/>
+        <v>390</v>
+      </c>
+      <c r="U45" s="2">
         <f t="shared" si="19"/>
-        <v>420</v>
-      </c>
-      <c r="T45" s="2">
+        <v>540</v>
+      </c>
+      <c r="V45" s="2">
+        <v>99</v>
+      </c>
+      <c r="W45" s="2">
+        <f t="shared" ref="W45:W52" si="24">W44+20</f>
+        <v>160</v>
+      </c>
+      <c r="X45" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y45" s="16"/>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C46" s="7">
+        <v>114</v>
+      </c>
+      <c r="D46" s="7">
+        <v>2</v>
+      </c>
+      <c r="E46" s="7">
+        <v>14</v>
+      </c>
+      <c r="F46" s="7">
+        <v>23</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I46" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="J46" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="K46" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="L46" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="M46" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="N46" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="O46" s="12">
         <f t="shared" si="20"/>
-        <v>540</v>
-      </c>
-      <c r="U45" s="2">
-        <v>99</v>
-      </c>
-      <c r="V45" s="2">
-        <f t="shared" ref="V45:V52" si="25">V44+20</f>
-        <v>160</v>
-      </c>
-      <c r="W45" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:23">
-      <c r="C46" s="1">
-        <v>114</v>
-      </c>
-      <c r="D46" s="1">
-        <v>2</v>
-      </c>
-      <c r="E46" s="1">
-        <v>23</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H46" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="I46" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="J46" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="K46" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="L46" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="M46" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="N46" s="15">
+        <v>35000</v>
+      </c>
+      <c r="P46" s="12">
         <f t="shared" si="21"/>
         <v>35000</v>
       </c>
-      <c r="O46" s="15">
+      <c r="Q46" s="12">
         <f t="shared" si="22"/>
-        <v>35000</v>
-      </c>
-      <c r="P46" s="15">
+        <v>42000</v>
+      </c>
+      <c r="R46" s="12">
         <f t="shared" si="23"/>
         <v>42000</v>
       </c>
-      <c r="Q46" s="15">
+      <c r="S46" s="2">
+        <v>0</v>
+      </c>
+      <c r="T46" s="2">
+        <f t="shared" si="17"/>
+        <v>410</v>
+      </c>
+      <c r="U46" s="2">
+        <f t="shared" si="19"/>
+        <v>580</v>
+      </c>
+      <c r="V46" s="2">
+        <v>99</v>
+      </c>
+      <c r="W46" s="2">
         <f t="shared" si="24"/>
-        <v>42000</v>
-      </c>
-      <c r="R46" s="2">
-        <v>0</v>
-      </c>
-      <c r="S46" s="2">
-        <f t="shared" si="19"/>
-        <v>450</v>
-      </c>
-      <c r="T46" s="2">
+        <v>180</v>
+      </c>
+      <c r="X46" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y46" s="16"/>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C47" s="7">
+        <v>115</v>
+      </c>
+      <c r="D47" s="7">
+        <v>2</v>
+      </c>
+      <c r="E47" s="7">
+        <v>15</v>
+      </c>
+      <c r="F47" s="7">
+        <v>24</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I47" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="J47" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="K47" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="L47" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="M47" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="N47" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="O47" s="12">
         <f t="shared" si="20"/>
-        <v>580</v>
-      </c>
-      <c r="U46" s="2">
-        <v>99</v>
-      </c>
-      <c r="V46" s="2">
-        <f t="shared" si="25"/>
-        <v>180</v>
-      </c>
-      <c r="W46" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:23">
-      <c r="C47" s="1">
-        <v>115</v>
-      </c>
-      <c r="D47" s="1">
-        <v>2</v>
-      </c>
-      <c r="E47" s="1">
-        <v>24</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H47" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="I47" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="J47" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="K47" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="L47" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="M47" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="N47" s="15">
+        <v>40000</v>
+      </c>
+      <c r="P47" s="12">
         <f t="shared" si="21"/>
         <v>40000</v>
       </c>
-      <c r="O47" s="15">
+      <c r="Q47" s="12">
         <f t="shared" si="22"/>
-        <v>40000</v>
-      </c>
-      <c r="P47" s="15">
+        <v>46000</v>
+      </c>
+      <c r="R47" s="12">
         <f t="shared" si="23"/>
         <v>46000</v>
       </c>
-      <c r="Q47" s="15">
+      <c r="S47" s="2">
+        <v>0</v>
+      </c>
+      <c r="T47" s="2">
+        <f t="shared" si="17"/>
+        <v>430</v>
+      </c>
+      <c r="U47" s="2">
+        <f t="shared" si="19"/>
+        <v>620</v>
+      </c>
+      <c r="V47" s="2">
+        <v>99</v>
+      </c>
+      <c r="W47" s="2">
         <f t="shared" si="24"/>
-        <v>46000</v>
-      </c>
-      <c r="R47" s="2">
-        <v>0</v>
-      </c>
-      <c r="S47" s="2">
-        <f t="shared" si="19"/>
-        <v>480</v>
-      </c>
-      <c r="T47" s="2">
+        <v>200</v>
+      </c>
+      <c r="X47" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y47" s="16"/>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C48" s="7">
+        <v>116</v>
+      </c>
+      <c r="D48" s="7">
+        <v>2</v>
+      </c>
+      <c r="E48" s="7">
+        <v>16</v>
+      </c>
+      <c r="F48" s="7">
+        <v>25</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I48" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="J48" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="K48" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="L48" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="M48" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="N48" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="O48" s="12">
         <f t="shared" si="20"/>
-        <v>620</v>
-      </c>
-      <c r="U47" s="2">
-        <v>99</v>
-      </c>
-      <c r="V47" s="2">
-        <f t="shared" si="25"/>
-        <v>200</v>
-      </c>
-      <c r="W47" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:23">
-      <c r="C48" s="1">
-        <v>116</v>
-      </c>
-      <c r="D48" s="1">
-        <v>2</v>
-      </c>
-      <c r="E48" s="1">
-        <v>25</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H48" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="I48" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="J48" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="K48" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="L48" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="M48" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="N48" s="15">
+        <v>45000</v>
+      </c>
+      <c r="P48" s="12">
         <f t="shared" si="21"/>
         <v>45000</v>
       </c>
-      <c r="O48" s="15">
+      <c r="Q48" s="12">
         <f t="shared" si="22"/>
-        <v>45000</v>
-      </c>
-      <c r="P48" s="15">
+        <v>50000</v>
+      </c>
+      <c r="R48" s="12">
         <f t="shared" si="23"/>
         <v>50000</v>
       </c>
-      <c r="Q48" s="15">
+      <c r="S48" s="2">
+        <v>0</v>
+      </c>
+      <c r="T48" s="2">
+        <f t="shared" si="17"/>
+        <v>450</v>
+      </c>
+      <c r="U48" s="2">
+        <f t="shared" si="19"/>
+        <v>660</v>
+      </c>
+      <c r="V48" s="2">
+        <v>99</v>
+      </c>
+      <c r="W48" s="2">
         <f t="shared" si="24"/>
+        <v>220</v>
+      </c>
+      <c r="X48" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y48" s="16"/>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C49" s="7">
+        <v>117</v>
+      </c>
+      <c r="D49" s="7">
+        <v>2</v>
+      </c>
+      <c r="E49" s="7">
+        <v>17</v>
+      </c>
+      <c r="F49" s="7">
+        <v>26</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I49" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="J49" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="K49" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="L49" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="M49" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="N49" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="O49" s="12">
+        <f t="shared" si="20"/>
         <v>50000</v>
       </c>
-      <c r="R48" s="2">
-        <v>0</v>
-      </c>
-      <c r="S48" s="2">
-        <f t="shared" si="19"/>
-        <v>510</v>
-      </c>
-      <c r="T48" s="2">
-        <f t="shared" si="20"/>
-        <v>660</v>
-      </c>
-      <c r="U48" s="2">
-        <v>99</v>
-      </c>
-      <c r="V48" s="2">
-        <f t="shared" si="25"/>
-        <v>220</v>
-      </c>
-      <c r="W48" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:23">
-      <c r="C49" s="1">
-        <v>117</v>
-      </c>
-      <c r="D49" s="1">
-        <v>2</v>
-      </c>
-      <c r="E49" s="1">
-        <v>26</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H49" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="I49" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="J49" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="K49" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="L49" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="M49" s="25" t="s">
-        <v>201</v>
-      </c>
-      <c r="N49" s="15">
+      <c r="P49" s="12">
         <f t="shared" si="21"/>
         <v>50000</v>
       </c>
-      <c r="O49" s="15">
+      <c r="Q49" s="12">
         <f t="shared" si="22"/>
-        <v>50000</v>
-      </c>
-      <c r="P49" s="15">
+        <v>54000</v>
+      </c>
+      <c r="R49" s="12">
         <f t="shared" si="23"/>
         <v>54000</v>
       </c>
-      <c r="Q49" s="15">
+      <c r="S49" s="2">
+        <v>0</v>
+      </c>
+      <c r="T49" s="2">
+        <f t="shared" si="17"/>
+        <v>470</v>
+      </c>
+      <c r="U49" s="2">
+        <f t="shared" si="19"/>
+        <v>700</v>
+      </c>
+      <c r="V49" s="2">
+        <v>99</v>
+      </c>
+      <c r="W49" s="2">
         <f t="shared" si="24"/>
-        <v>54000</v>
-      </c>
-      <c r="R49" s="2">
-        <v>0</v>
-      </c>
-      <c r="S49" s="2">
-        <f t="shared" si="19"/>
-        <v>540</v>
-      </c>
-      <c r="T49" s="2">
+        <v>240</v>
+      </c>
+      <c r="X49" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y49" s="16"/>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C50" s="7">
+        <v>118</v>
+      </c>
+      <c r="D50" s="7">
+        <v>2</v>
+      </c>
+      <c r="E50" s="7">
+        <v>18</v>
+      </c>
+      <c r="F50" s="7">
+        <v>27</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I50" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="J50" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="K50" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="L50" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="M50" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="N50" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="O50" s="12">
         <f t="shared" si="20"/>
-        <v>700</v>
-      </c>
-      <c r="U49" s="2">
-        <v>99</v>
-      </c>
-      <c r="V49" s="2">
-        <f t="shared" si="25"/>
-        <v>240</v>
-      </c>
-      <c r="W49" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:23">
-      <c r="C50" s="1">
-        <v>118</v>
-      </c>
-      <c r="D50" s="1">
-        <v>2</v>
-      </c>
-      <c r="E50" s="1">
-        <v>27</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H50" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="I50" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="J50" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="K50" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="L50" s="28" t="s">
-        <v>206</v>
-      </c>
-      <c r="M50" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="N50" s="15">
+        <v>55000</v>
+      </c>
+      <c r="P50" s="12">
         <f t="shared" si="21"/>
         <v>55000</v>
       </c>
-      <c r="O50" s="15">
+      <c r="Q50" s="12">
         <f t="shared" si="22"/>
-        <v>55000</v>
-      </c>
-      <c r="P50" s="15">
+        <v>58000</v>
+      </c>
+      <c r="R50" s="12">
         <f t="shared" si="23"/>
         <v>58000</v>
       </c>
-      <c r="Q50" s="15">
+      <c r="S50" s="2">
+        <v>0</v>
+      </c>
+      <c r="T50" s="2">
+        <f t="shared" si="17"/>
+        <v>490</v>
+      </c>
+      <c r="U50" s="2">
+        <f t="shared" si="19"/>
+        <v>740</v>
+      </c>
+      <c r="V50" s="2">
+        <v>99</v>
+      </c>
+      <c r="W50" s="2">
         <f t="shared" si="24"/>
-        <v>58000</v>
-      </c>
-      <c r="R50" s="2">
-        <v>0</v>
-      </c>
-      <c r="S50" s="2">
-        <f t="shared" si="19"/>
-        <v>570</v>
-      </c>
-      <c r="T50" s="2">
+        <v>260</v>
+      </c>
+      <c r="X50" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y50" s="16"/>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C51" s="7">
+        <v>119</v>
+      </c>
+      <c r="D51" s="7">
+        <v>2</v>
+      </c>
+      <c r="E51" s="7">
+        <v>19</v>
+      </c>
+      <c r="F51" s="7">
+        <v>28</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I51" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="J51" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="K51" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="L51" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="M51" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="N51" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="O51" s="12">
         <f t="shared" si="20"/>
-        <v>740</v>
-      </c>
-      <c r="U50" s="2">
-        <v>99</v>
-      </c>
-      <c r="V50" s="2">
-        <f t="shared" si="25"/>
-        <v>260</v>
-      </c>
-      <c r="W50" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:23">
-      <c r="C51" s="1">
-        <v>119</v>
-      </c>
-      <c r="D51" s="1">
-        <v>2</v>
-      </c>
-      <c r="E51" s="1">
-        <v>28</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H51" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="I51" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="J51" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="K51" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="L51" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="M51" s="25" t="s">
-        <v>213</v>
-      </c>
-      <c r="N51" s="15">
+        <v>60000</v>
+      </c>
+      <c r="P51" s="12">
         <f t="shared" si="21"/>
         <v>60000</v>
       </c>
-      <c r="O51" s="15">
+      <c r="Q51" s="12">
         <f t="shared" si="22"/>
-        <v>60000</v>
-      </c>
-      <c r="P51" s="15">
+        <v>62000</v>
+      </c>
+      <c r="R51" s="12">
         <f t="shared" si="23"/>
         <v>62000</v>
       </c>
-      <c r="Q51" s="15">
+      <c r="S51" s="2">
+        <v>0</v>
+      </c>
+      <c r="T51" s="2">
+        <f t="shared" si="17"/>
+        <v>510</v>
+      </c>
+      <c r="U51" s="2">
+        <f t="shared" si="19"/>
+        <v>780</v>
+      </c>
+      <c r="V51" s="2">
+        <v>99</v>
+      </c>
+      <c r="W51" s="2">
         <f t="shared" si="24"/>
-        <v>62000</v>
-      </c>
-      <c r="R51" s="2">
-        <v>0</v>
-      </c>
-      <c r="S51" s="2">
-        <f t="shared" si="19"/>
-        <v>600</v>
-      </c>
-      <c r="T51" s="2">
+        <v>280</v>
+      </c>
+      <c r="X51" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y51" s="16"/>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C52" s="7">
+        <v>120</v>
+      </c>
+      <c r="D52" s="7">
+        <v>2</v>
+      </c>
+      <c r="E52" s="7">
+        <v>20</v>
+      </c>
+      <c r="F52" s="7">
+        <v>29</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I52" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="J52" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="K52" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="L52" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="M52" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="N52" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="O52" s="12">
         <f t="shared" si="20"/>
-        <v>780</v>
-      </c>
-      <c r="U51" s="2">
-        <v>99</v>
-      </c>
-      <c r="V51" s="2">
-        <f t="shared" si="25"/>
-        <v>280</v>
-      </c>
-      <c r="W51" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:23">
-      <c r="C52" s="1">
-        <v>120</v>
-      </c>
-      <c r="D52" s="1">
-        <v>2</v>
-      </c>
-      <c r="E52" s="1">
-        <v>29</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H52" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="I52" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="J52" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="K52" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="L52" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="M52" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="N52" s="15">
+        <v>65000</v>
+      </c>
+      <c r="P52" s="12">
         <f t="shared" si="21"/>
         <v>65000</v>
       </c>
-      <c r="O52" s="15">
+      <c r="Q52" s="12">
         <f t="shared" si="22"/>
-        <v>65000</v>
-      </c>
-      <c r="P52" s="15">
+        <v>66000</v>
+      </c>
+      <c r="R52" s="12">
         <f t="shared" si="23"/>
         <v>66000</v>
       </c>
-      <c r="Q52" s="15">
+      <c r="S52" s="2">
+        <v>0</v>
+      </c>
+      <c r="T52" s="2">
+        <f t="shared" si="17"/>
+        <v>530</v>
+      </c>
+      <c r="U52" s="2">
+        <f t="shared" si="19"/>
+        <v>820</v>
+      </c>
+      <c r="V52" s="2">
+        <v>99</v>
+      </c>
+      <c r="W52" s="2">
         <f t="shared" si="24"/>
-        <v>66000</v>
-      </c>
-      <c r="R52" s="2">
-        <v>0</v>
-      </c>
-      <c r="S52" s="2">
-        <f t="shared" si="19"/>
-        <v>630</v>
-      </c>
-      <c r="T52" s="2">
-        <f t="shared" si="20"/>
-        <v>820</v>
-      </c>
-      <c r="U52" s="2">
-        <v>99</v>
-      </c>
-      <c r="V52" s="2">
-        <f t="shared" si="25"/>
         <v>300</v>
       </c>
-      <c r="W52" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="13:17">
+      <c r="X52" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y52" s="16"/>
+    </row>
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="10"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="10"/>
+      <c r="L53" s="2"/>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" s="2"/>
       <c r="Q53" s="2"/>
-    </row>
-    <row r="54" customHeight="1" spans="13:17">
+      <c r="R53" s="2"/>
+      <c r="S53" s="2"/>
+      <c r="T53" s="2"/>
+      <c r="U53" s="2"/>
+      <c r="V53" s="2"/>
+      <c r="W53" s="2"/>
+      <c r="X53" s="2"/>
+      <c r="Y53" s="16"/>
+    </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" s="2"/>
       <c r="Q54" s="2"/>
-    </row>
-    <row r="55" customHeight="1" spans="13:17">
+      <c r="R54" s="2"/>
+      <c r="S54" s="2"/>
+      <c r="T54" s="2"/>
+      <c r="U54" s="2"/>
+      <c r="V54" s="2"/>
+      <c r="W54" s="2"/>
+      <c r="X54" s="2"/>
+      <c r="Y54" s="16"/>
+    </row>
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="10"/>
+      <c r="L55" s="2"/>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" s="2"/>
       <c r="Q55" s="2"/>
-    </row>
-    <row r="56" customHeight="1" spans="3:23">
-      <c r="C56" s="1">
+      <c r="R55" s="2"/>
+      <c r="S55" s="2"/>
+      <c r="T55" s="2"/>
+      <c r="U55" s="2"/>
+      <c r="V55" s="2"/>
+      <c r="W55" s="2"/>
+      <c r="X55" s="2"/>
+      <c r="Y55" s="16"/>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C56" s="7">
         <v>201</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D56" s="7">
         <v>3</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="7">
+        <v>1</v>
+      </c>
+      <c r="F56" s="7">
         <v>20</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="G56" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I56" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="J56" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="K56" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="L56" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="M56" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="O56" s="12">
+        <v>50000</v>
+      </c>
+      <c r="P56" s="12">
+        <v>50000</v>
+      </c>
+      <c r="Q56" s="12">
+        <v>50000</v>
+      </c>
+      <c r="R56" s="12">
+        <v>50000</v>
+      </c>
+      <c r="S56" s="2">
+        <v>0</v>
+      </c>
+      <c r="T56" s="12">
+        <v>300</v>
+      </c>
+      <c r="U56" s="2">
+        <v>400</v>
+      </c>
+      <c r="V56" s="2">
+        <v>99</v>
+      </c>
+      <c r="W56" s="2">
+        <v>200</v>
+      </c>
+      <c r="X56" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="H56" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="I56" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="J56" s="24" t="s">
+      <c r="Y56" s="16"/>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C57" s="7">
+        <v>202</v>
+      </c>
+      <c r="D57" s="7">
+        <v>3</v>
+      </c>
+      <c r="E57" s="7">
+        <v>2</v>
+      </c>
+      <c r="F57" s="7">
+        <v>21</v>
+      </c>
+      <c r="G57" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="K56" s="25" t="s">
+      <c r="H57" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I57" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="J57" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="K57" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="L57" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="M57" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="O57" s="12">
+        <f t="shared" ref="O57:R57" si="25">O56+10000</f>
+        <v>60000</v>
+      </c>
+      <c r="P57" s="12">
+        <f t="shared" si="25"/>
+        <v>60000</v>
+      </c>
+      <c r="Q57" s="12">
+        <f t="shared" si="25"/>
+        <v>60000</v>
+      </c>
+      <c r="R57" s="12">
+        <f t="shared" si="25"/>
+        <v>60000</v>
+      </c>
+      <c r="S57" s="2">
+        <v>0</v>
+      </c>
+      <c r="T57" s="2">
+        <f t="shared" ref="T57:T65" si="26">T56+30</f>
+        <v>330</v>
+      </c>
+      <c r="U57" s="2">
+        <f t="shared" ref="U57:U65" si="27">U56+30</f>
+        <v>430</v>
+      </c>
+      <c r="V57" s="2">
+        <v>99</v>
+      </c>
+      <c r="W57" s="2">
+        <f t="shared" ref="W57:W65" si="28">W56+20</f>
+        <v>220</v>
+      </c>
+      <c r="X57" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y57" s="16"/>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C58" s="7">
+        <v>203</v>
+      </c>
+      <c r="D58" s="7">
+        <v>3</v>
+      </c>
+      <c r="E58" s="7">
+        <v>3</v>
+      </c>
+      <c r="F58" s="7">
+        <v>22</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I58" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="L56" s="25" t="s">
+      <c r="J58" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="M56" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="N56" s="15">
-        <v>100000</v>
-      </c>
-      <c r="O56" s="15">
-        <v>100000</v>
-      </c>
-      <c r="P56" s="15">
-        <v>100000</v>
-      </c>
-      <c r="Q56" s="15">
-        <v>100000</v>
-      </c>
-      <c r="R56" s="2">
-        <v>0</v>
-      </c>
-      <c r="S56" s="19">
-        <v>400</v>
-      </c>
-      <c r="T56" s="2">
-        <v>600</v>
-      </c>
-      <c r="U56" s="2">
-        <v>99</v>
-      </c>
-      <c r="V56" s="2">
-        <v>200</v>
-      </c>
-      <c r="W56" s="26" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:23">
-      <c r="C57" s="1">
-        <v>202</v>
-      </c>
-      <c r="D57" s="1">
-        <v>3</v>
-      </c>
-      <c r="E57" s="1">
-        <v>21</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="H57" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="I57" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="J57" s="24" t="s">
+      <c r="K58" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="K57" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="L57" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="M57" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="N57" s="15">
-        <f t="shared" ref="N57:Q57" si="26">N56+20000</f>
-        <v>120000</v>
-      </c>
-      <c r="O57" s="15">
+      <c r="L58" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="M58" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="O58" s="12">
+        <f t="shared" ref="O58:R58" si="29">O57+10000</f>
+        <v>70000</v>
+      </c>
+      <c r="P58" s="12">
+        <f t="shared" si="29"/>
+        <v>70000</v>
+      </c>
+      <c r="Q58" s="12">
+        <f t="shared" si="29"/>
+        <v>70000</v>
+      </c>
+      <c r="R58" s="12">
+        <f t="shared" si="29"/>
+        <v>70000</v>
+      </c>
+      <c r="S58" s="2">
+        <v>0</v>
+      </c>
+      <c r="T58" s="2">
         <f t="shared" si="26"/>
-        <v>120000</v>
-      </c>
-      <c r="P57" s="15">
-        <f t="shared" si="26"/>
-        <v>120000</v>
-      </c>
-      <c r="Q57" s="15">
-        <f t="shared" si="26"/>
-        <v>120000</v>
-      </c>
-      <c r="R57" s="2">
-        <v>0</v>
-      </c>
-      <c r="S57" s="2">
-        <f t="shared" ref="S57:S65" si="27">S56+30</f>
-        <v>430</v>
-      </c>
-      <c r="T57" s="2">
-        <f t="shared" ref="T57:T65" si="28">T56+30</f>
-        <v>630</v>
-      </c>
-      <c r="U57" s="2">
-        <v>99</v>
-      </c>
-      <c r="V57" s="2">
-        <f t="shared" ref="V57:V65" si="29">V56+20</f>
-        <v>220</v>
-      </c>
-      <c r="W57" s="26" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:23">
-      <c r="C58" s="1">
-        <v>203</v>
-      </c>
-      <c r="D58" s="1">
-        <v>3</v>
-      </c>
-      <c r="E58" s="1">
-        <v>22</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="H58" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="I58" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="J58" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="K58" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="L58" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="M58" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="N58" s="15">
-        <f t="shared" ref="N58:Q58" si="30">N57+20000</f>
-        <v>140000</v>
-      </c>
-      <c r="O58" s="15">
-        <f t="shared" si="30"/>
-        <v>140000</v>
-      </c>
-      <c r="P58" s="15">
-        <f t="shared" si="30"/>
-        <v>140000</v>
-      </c>
-      <c r="Q58" s="15">
-        <f t="shared" si="30"/>
-        <v>140000</v>
-      </c>
-      <c r="R58" s="2">
-        <v>0</v>
-      </c>
-      <c r="S58" s="2">
+        <v>360</v>
+      </c>
+      <c r="U58" s="2">
         <f t="shared" si="27"/>
         <v>460</v>
       </c>
-      <c r="T58" s="2">
+      <c r="V58" s="2">
+        <v>99</v>
+      </c>
+      <c r="W58" s="2">
         <f t="shared" si="28"/>
-        <v>660</v>
-      </c>
-      <c r="U58" s="2">
-        <v>99</v>
-      </c>
-      <c r="V58" s="2">
-        <f t="shared" si="29"/>
         <v>240</v>
       </c>
-      <c r="W58" s="26" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:23">
-      <c r="C59" s="1">
+      <c r="X58" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y58" s="16"/>
+    </row>
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C59" s="7">
         <v>204</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D59" s="7">
         <v>3</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="7">
+        <v>4</v>
+      </c>
+      <c r="F59" s="7">
         <v>23</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="G59" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I59" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="J59" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="K59" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="H59" s="24" t="s">
-        <v>230</v>
-      </c>
-      <c r="I59" s="24" t="s">
-        <v>230</v>
-      </c>
-      <c r="J59" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="K59" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="L59" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="M59" s="24" t="s">
-        <v>230</v>
-      </c>
-      <c r="N59" s="15">
-        <f t="shared" ref="N59:Q59" si="31">N58+20000</f>
-        <v>160000</v>
-      </c>
-      <c r="O59" s="15">
-        <f t="shared" si="31"/>
-        <v>160000</v>
-      </c>
-      <c r="P59" s="15">
-        <f t="shared" si="31"/>
-        <v>160000</v>
-      </c>
-      <c r="Q59" s="15">
-        <f t="shared" si="31"/>
-        <v>160000</v>
-      </c>
-      <c r="R59" s="2">
-        <v>0</v>
+      <c r="L59" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="M59" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="O59" s="12">
+        <f t="shared" ref="O59:R59" si="30">O58+10000</f>
+        <v>80000</v>
+      </c>
+      <c r="P59" s="12">
+        <f t="shared" si="30"/>
+        <v>80000</v>
+      </c>
+      <c r="Q59" s="12">
+        <f t="shared" si="30"/>
+        <v>80000</v>
+      </c>
+      <c r="R59" s="12">
+        <f t="shared" si="30"/>
+        <v>80000</v>
       </c>
       <c r="S59" s="2">
+        <v>0</v>
+      </c>
+      <c r="T59" s="2">
+        <f t="shared" si="26"/>
+        <v>390</v>
+      </c>
+      <c r="U59" s="2">
         <f t="shared" si="27"/>
         <v>490</v>
       </c>
-      <c r="T59" s="2">
+      <c r="V59" s="2">
+        <v>99</v>
+      </c>
+      <c r="W59" s="2">
         <f t="shared" si="28"/>
-        <v>690</v>
-      </c>
-      <c r="U59" s="2">
-        <v>99</v>
-      </c>
-      <c r="V59" s="2">
-        <f t="shared" si="29"/>
         <v>260</v>
       </c>
-      <c r="W59" s="26" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:23">
-      <c r="C60" s="1">
+      <c r="X59" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y59" s="16"/>
+    </row>
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C60" s="7">
         <v>205</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D60" s="7">
         <v>3</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E60" s="7">
+        <v>5</v>
+      </c>
+      <c r="F60" s="7">
         <v>24</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="H60" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="I60" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="J60" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="K60" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="L60" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="M60" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="N60" s="15">
-        <f t="shared" ref="N60:Q60" si="32">N59+20000</f>
-        <v>180000</v>
-      </c>
-      <c r="O60" s="15">
-        <f t="shared" si="32"/>
-        <v>180000</v>
-      </c>
-      <c r="P60" s="15">
-        <f t="shared" si="32"/>
-        <v>180000</v>
-      </c>
-      <c r="Q60" s="15">
-        <f t="shared" si="32"/>
-        <v>180000</v>
-      </c>
-      <c r="R60" s="2">
-        <v>0</v>
+      <c r="G60" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I60" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="J60" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="K60" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="L60" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="M60" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="O60" s="12">
+        <f t="shared" ref="O60:R60" si="31">O59+10000</f>
+        <v>90000</v>
+      </c>
+      <c r="P60" s="12">
+        <f t="shared" si="31"/>
+        <v>90000</v>
+      </c>
+      <c r="Q60" s="12">
+        <f t="shared" si="31"/>
+        <v>90000</v>
+      </c>
+      <c r="R60" s="12">
+        <f t="shared" si="31"/>
+        <v>90000</v>
       </c>
       <c r="S60" s="2">
+        <v>0</v>
+      </c>
+      <c r="T60" s="2">
+        <f t="shared" si="26"/>
+        <v>420</v>
+      </c>
+      <c r="U60" s="2">
         <f t="shared" si="27"/>
         <v>520</v>
       </c>
-      <c r="T60" s="2">
+      <c r="V60" s="2">
+        <v>99</v>
+      </c>
+      <c r="W60" s="2">
         <f t="shared" si="28"/>
-        <v>720</v>
-      </c>
-      <c r="U60" s="2">
-        <v>99</v>
-      </c>
-      <c r="V60" s="2">
-        <f t="shared" si="29"/>
         <v>280</v>
       </c>
-      <c r="W60" s="26" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:23">
-      <c r="C61" s="1">
+      <c r="X60" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y60" s="16"/>
+    </row>
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C61" s="7">
         <v>206</v>
       </c>
-      <c r="D61" s="1">
+      <c r="D61" s="7">
         <v>3</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E61" s="7">
+        <v>6</v>
+      </c>
+      <c r="F61" s="7">
         <v>25</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="H61" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="I61" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="J61" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="K61" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="L61" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="M61" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="N61" s="15">
-        <f t="shared" ref="N61:Q61" si="33">N60+20000</f>
-        <v>200000</v>
-      </c>
-      <c r="O61" s="15">
-        <f t="shared" si="33"/>
-        <v>200000</v>
-      </c>
-      <c r="P61" s="15">
-        <f t="shared" si="33"/>
-        <v>200000</v>
-      </c>
-      <c r="Q61" s="15">
-        <f t="shared" si="33"/>
-        <v>200000</v>
-      </c>
-      <c r="R61" s="2">
-        <v>0</v>
+      <c r="G61" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I61" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="J61" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="K61" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="L61" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="M61" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="O61" s="12">
+        <f t="shared" ref="O61:R61" si="32">O60+10000</f>
+        <v>100000</v>
+      </c>
+      <c r="P61" s="12">
+        <f t="shared" si="32"/>
+        <v>100000</v>
+      </c>
+      <c r="Q61" s="12">
+        <f t="shared" si="32"/>
+        <v>100000</v>
+      </c>
+      <c r="R61" s="12">
+        <f t="shared" si="32"/>
+        <v>100000</v>
       </c>
       <c r="S61" s="2">
+        <v>0</v>
+      </c>
+      <c r="T61" s="2">
+        <f t="shared" si="26"/>
+        <v>450</v>
+      </c>
+      <c r="U61" s="2">
         <f t="shared" si="27"/>
         <v>550</v>
       </c>
-      <c r="T61" s="2">
+      <c r="V61" s="2">
+        <v>99</v>
+      </c>
+      <c r="W61" s="2">
         <f t="shared" si="28"/>
-        <v>750</v>
-      </c>
-      <c r="U61" s="2">
-        <v>99</v>
-      </c>
-      <c r="V61" s="2">
-        <f t="shared" si="29"/>
         <v>300</v>
       </c>
-      <c r="W61" s="26" t="s">
+      <c r="X61" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y61" s="16"/>
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C62" s="7">
+        <v>207</v>
+      </c>
+      <c r="D62" s="7">
+        <v>3</v>
+      </c>
+      <c r="E62" s="7">
+        <v>7</v>
+      </c>
+      <c r="F62" s="7">
+        <v>26</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I62" s="17" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="62" s="3" customFormat="1" customHeight="1" spans="3:24">
-      <c r="C62" s="1">
-        <v>207</v>
-      </c>
-      <c r="D62" s="1">
-        <v>3</v>
-      </c>
-      <c r="E62" s="1">
-        <v>26</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="H62" s="27" t="s">
-        <v>226</v>
-      </c>
-      <c r="I62" s="27" t="s">
-        <v>226</v>
-      </c>
-      <c r="J62" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="K62" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="L62" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="M62" s="27" t="s">
-        <v>226</v>
-      </c>
-      <c r="N62" s="15">
-        <f t="shared" ref="N62:Q62" si="34">N61+20000</f>
-        <v>220000</v>
-      </c>
-      <c r="O62" s="15">
-        <f t="shared" si="34"/>
-        <v>220000</v>
-      </c>
-      <c r="P62" s="15">
-        <f t="shared" si="34"/>
-        <v>220000</v>
-      </c>
-      <c r="Q62" s="15">
-        <f t="shared" si="34"/>
-        <v>220000</v>
-      </c>
-      <c r="R62" s="3">
-        <v>0</v>
+      <c r="J62" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="K62" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="L62" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="M62" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="O62" s="12">
+        <f t="shared" ref="O62:R62" si="33">O61+10000</f>
+        <v>110000</v>
+      </c>
+      <c r="P62" s="12">
+        <f t="shared" si="33"/>
+        <v>110000</v>
+      </c>
+      <c r="Q62" s="12">
+        <f t="shared" si="33"/>
+        <v>110000</v>
+      </c>
+      <c r="R62" s="12">
+        <f t="shared" si="33"/>
+        <v>110000</v>
       </c>
       <c r="S62" s="2">
+        <v>0</v>
+      </c>
+      <c r="T62" s="2">
+        <f t="shared" si="26"/>
+        <v>480</v>
+      </c>
+      <c r="U62" s="2">
         <f t="shared" si="27"/>
         <v>580</v>
       </c>
-      <c r="T62" s="2">
+      <c r="V62" s="2">
+        <v>99</v>
+      </c>
+      <c r="W62" s="2">
         <f t="shared" si="28"/>
-        <v>780</v>
-      </c>
-      <c r="U62" s="3">
-        <v>99</v>
-      </c>
-      <c r="V62" s="2">
-        <f t="shared" si="29"/>
         <v>320</v>
       </c>
-      <c r="W62" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="X62" s="23"/>
-    </row>
-    <row r="63" customHeight="1" spans="3:23">
-      <c r="C63" s="1">
+      <c r="X62" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y62" s="16"/>
+    </row>
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C63" s="7">
         <v>208</v>
       </c>
-      <c r="D63" s="1">
+      <c r="D63" s="7">
         <v>3</v>
       </c>
-      <c r="E63" s="1">
+      <c r="E63" s="7">
+        <v>8</v>
+      </c>
+      <c r="F63" s="7">
         <v>27</v>
       </c>
-      <c r="F63" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="H63" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="I63" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="J63" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="K63" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="L63" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="M63" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="N63" s="15">
-        <f t="shared" ref="N63:Q63" si="35">N62+20000</f>
-        <v>240000</v>
-      </c>
-      <c r="O63" s="15">
-        <f t="shared" si="35"/>
-        <v>240000</v>
-      </c>
-      <c r="P63" s="15">
-        <f t="shared" si="35"/>
-        <v>240000</v>
-      </c>
-      <c r="Q63" s="15">
-        <f t="shared" si="35"/>
-        <v>240000</v>
-      </c>
-      <c r="R63" s="2">
-        <v>0</v>
+      <c r="G63" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I63" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="J63" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="K63" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="L63" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="M63" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="O63" s="12">
+        <f t="shared" ref="O63:R63" si="34">O62+10000</f>
+        <v>120000</v>
+      </c>
+      <c r="P63" s="12">
+        <f t="shared" si="34"/>
+        <v>120000</v>
+      </c>
+      <c r="Q63" s="12">
+        <f t="shared" si="34"/>
+        <v>120000</v>
+      </c>
+      <c r="R63" s="12">
+        <f t="shared" si="34"/>
+        <v>120000</v>
       </c>
       <c r="S63" s="2">
+        <v>0</v>
+      </c>
+      <c r="T63" s="2">
+        <f t="shared" si="26"/>
+        <v>510</v>
+      </c>
+      <c r="U63" s="2">
         <f t="shared" si="27"/>
         <v>610</v>
       </c>
-      <c r="T63" s="2">
+      <c r="V63" s="2">
+        <v>99</v>
+      </c>
+      <c r="W63" s="2">
         <f t="shared" si="28"/>
-        <v>810</v>
-      </c>
-      <c r="U63" s="2">
-        <v>99</v>
-      </c>
-      <c r="V63" s="2">
-        <f t="shared" si="29"/>
         <v>340</v>
       </c>
-      <c r="W63" s="26" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:23">
-      <c r="C64" s="1">
+      <c r="X63" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y63" s="16"/>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C64" s="7">
         <v>209</v>
       </c>
-      <c r="D64" s="1">
+      <c r="D64" s="7">
         <v>3</v>
       </c>
-      <c r="E64" s="1">
+      <c r="E64" s="7">
+        <v>9</v>
+      </c>
+      <c r="F64" s="7">
         <v>28</v>
       </c>
-      <c r="F64" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="H64" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="I64" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="J64" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="K64" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="L64" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="M64" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="N64" s="15">
-        <f t="shared" ref="N64:Q64" si="36">N63+20000</f>
-        <v>260000</v>
-      </c>
-      <c r="O64" s="15">
-        <f t="shared" si="36"/>
-        <v>260000</v>
-      </c>
-      <c r="P64" s="15">
-        <f t="shared" si="36"/>
-        <v>260000</v>
-      </c>
-      <c r="Q64" s="15">
-        <f t="shared" si="36"/>
-        <v>260000</v>
-      </c>
-      <c r="R64" s="2">
-        <v>0</v>
+      <c r="G64" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I64" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="J64" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="K64" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="L64" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="M64" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="O64" s="12">
+        <f t="shared" ref="O64:R64" si="35">O63+10000</f>
+        <v>130000</v>
+      </c>
+      <c r="P64" s="12">
+        <f t="shared" si="35"/>
+        <v>130000</v>
+      </c>
+      <c r="Q64" s="12">
+        <f t="shared" si="35"/>
+        <v>130000</v>
+      </c>
+      <c r="R64" s="12">
+        <f t="shared" si="35"/>
+        <v>130000</v>
       </c>
       <c r="S64" s="2">
+        <v>0</v>
+      </c>
+      <c r="T64" s="2">
+        <f t="shared" si="26"/>
+        <v>540</v>
+      </c>
+      <c r="U64" s="2">
         <f t="shared" si="27"/>
         <v>640</v>
       </c>
-      <c r="T64" s="2">
+      <c r="V64" s="2">
+        <v>99</v>
+      </c>
+      <c r="W64" s="2">
         <f t="shared" si="28"/>
-        <v>840</v>
-      </c>
-      <c r="U64" s="2">
-        <v>99</v>
-      </c>
-      <c r="V64" s="2">
-        <f t="shared" si="29"/>
         <v>360</v>
       </c>
-      <c r="W64" s="26" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:23">
-      <c r="C65" s="1">
+      <c r="X64" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y64" s="16"/>
+    </row>
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C65" s="7">
         <v>210</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D65" s="7">
         <v>3</v>
       </c>
-      <c r="E65" s="1">
+      <c r="E65" s="7">
+        <v>10</v>
+      </c>
+      <c r="F65" s="7">
         <v>29</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="G65" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I65" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="J65" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="K65" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="L65" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="H65" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="I65" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="J65" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="K65" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="L65" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="M65" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="N65" s="15">
-        <f t="shared" ref="N65:Q65" si="37">N64+20000</f>
-        <v>280000</v>
-      </c>
-      <c r="O65" s="15">
-        <f t="shared" si="37"/>
-        <v>280000</v>
-      </c>
-      <c r="P65" s="15">
-        <f t="shared" si="37"/>
-        <v>280000</v>
-      </c>
-      <c r="Q65" s="15">
-        <f t="shared" si="37"/>
-        <v>280000</v>
-      </c>
-      <c r="R65" s="2">
-        <v>0</v>
+      <c r="M65" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="O65" s="12">
+        <f t="shared" ref="O65:R65" si="36">O64+10000</f>
+        <v>140000</v>
+      </c>
+      <c r="P65" s="12">
+        <f t="shared" si="36"/>
+        <v>140000</v>
+      </c>
+      <c r="Q65" s="12">
+        <f t="shared" si="36"/>
+        <v>140000</v>
+      </c>
+      <c r="R65" s="12">
+        <f t="shared" si="36"/>
+        <v>140000</v>
       </c>
       <c r="S65" s="2">
+        <v>0</v>
+      </c>
+      <c r="T65" s="2">
+        <f t="shared" si="26"/>
+        <v>570</v>
+      </c>
+      <c r="U65" s="2">
         <f t="shared" si="27"/>
         <v>670</v>
       </c>
-      <c r="T65" s="2">
+      <c r="V65" s="2">
+        <v>99</v>
+      </c>
+      <c r="W65" s="2">
         <f t="shared" si="28"/>
-        <v>870</v>
-      </c>
-      <c r="U65" s="2">
-        <v>99</v>
-      </c>
-      <c r="V65" s="2">
-        <f t="shared" si="29"/>
         <v>380</v>
       </c>
-      <c r="W65" s="26" t="s">
-        <v>224</v>
-      </c>
+      <c r="X65" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y65" s="16"/>
+    </row>
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="10"/>
+      <c r="J66" s="10"/>
+      <c r="K66" s="10"/>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="11"/>
+      <c r="O66" s="2"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="2"/>
+      <c r="S66" s="2"/>
+      <c r="T66" s="2"/>
+      <c r="U66" s="2"/>
+      <c r="V66" s="2"/>
+      <c r="W66" s="2"/>
+      <c r="X66" s="2"/>
+      <c r="Y66" s="16"/>
+    </row>
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="10"/>
+      <c r="J67" s="10"/>
+      <c r="K67" s="10"/>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="11"/>
+      <c r="O67" s="2"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="2"/>
+      <c r="S67" s="2"/>
+      <c r="T67" s="2"/>
+      <c r="U67" s="2"/>
+      <c r="V67" s="2"/>
+      <c r="W67" s="2"/>
+      <c r="X67" s="2"/>
+      <c r="Y67" s="16"/>
+    </row>
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:25">
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="10"/>
+      <c r="J68" s="10"/>
+      <c r="K68" s="10"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="11"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="2"/>
+      <c r="T68" s="2"/>
+      <c r="U68" s="2"/>
+      <c r="V68" s="2"/>
+      <c r="W68" s="2"/>
+      <c r="X68" s="2"/>
+      <c r="Y68" s="16"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:W5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:X5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterPillConfig.xlsx
+++ b/Excel/MonsterPillConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="248">
   <si>
     <t>ID</t>
   </si>
@@ -707,12 +707,21 @@
     <t>9E+160</t>
   </si>
   <si>
+    <t>1E+34</t>
+  </si>
+  <si>
     <t>炼神三层</t>
   </si>
   <si>
     <t>9E+170</t>
   </si>
   <si>
+    <t>1E+43</t>
+  </si>
+  <si>
+    <t>1E+38</t>
+  </si>
+  <si>
     <t>炼神四层</t>
   </si>
   <si>
@@ -731,6 +740,9 @@
     <t>9E+190</t>
   </si>
   <si>
+    <t>1E+49</t>
+  </si>
+  <si>
     <t>炼神六层</t>
   </si>
   <si>
@@ -743,34 +755,25 @@
     <t>9E+210</t>
   </si>
   <si>
-    <t>1E+70</t>
-  </si>
-  <si>
     <t>炼神八层</t>
   </si>
   <si>
     <t>9E+220</t>
   </si>
   <si>
-    <t>1E+75</t>
-  </si>
-  <si>
     <t>炼神九层</t>
   </si>
   <si>
     <t>9E+230</t>
   </si>
   <si>
-    <t>1E+80</t>
+    <t>1E+61</t>
   </si>
   <si>
     <t>炼神十层</t>
   </si>
   <si>
     <t>9E+240</t>
-  </si>
-  <si>
-    <t>1E+85</t>
   </si>
 </sst>
 </file>
@@ -5043,7 +5046,7 @@
         <v>221</v>
       </c>
       <c r="L56" s="18" t="s">
-        <v>188</v>
+        <v>78</v>
       </c>
       <c r="M56" s="18" t="s">
         <v>175</v>
@@ -5112,10 +5115,10 @@
         <v>224</v>
       </c>
       <c r="L57" s="18" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="M57" s="18" t="s">
-        <v>74</v>
+        <v>225</v>
       </c>
       <c r="N57" s="17" t="s">
         <v>145</v>
@@ -5173,7 +5176,7 @@
         <v>22</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H58" s="7" t="s">
         <v>220</v>
@@ -5185,13 +5188,13 @@
         <v>154</v>
       </c>
       <c r="K58" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L58" s="18" t="s">
-        <v>162</v>
+        <v>228</v>
       </c>
       <c r="M58" s="18" t="s">
-        <v>188</v>
+        <v>229</v>
       </c>
       <c r="N58" s="17" t="s">
         <v>154</v>
@@ -5249,28 +5252,28 @@
         <v>23</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>220</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K59" s="17" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="L59" s="18" t="s">
-        <v>205</v>
+        <v>150</v>
       </c>
       <c r="M59" s="18" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
       <c r="N59" s="17" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O59" s="12">
         <f t="shared" ref="O59:R59" si="30">O58+10000</f>
@@ -5325,28 +5328,28 @@
         <v>24</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>220</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J60" s="17" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K60" s="17" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="L60" s="18" t="s">
-        <v>155</v>
+        <v>236</v>
       </c>
       <c r="M60" s="18" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="N60" s="17" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="O60" s="12">
         <f t="shared" ref="O60:R60" si="31">O59+10000</f>
@@ -5401,7 +5404,7 @@
         <v>25</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>220</v>
@@ -5413,13 +5416,13 @@
         <v>221</v>
       </c>
       <c r="K61" s="17" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L61" s="18" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="M61" s="18" t="s">
-        <v>205</v>
+        <v>162</v>
       </c>
       <c r="N61" s="17" t="s">
         <v>221</v>
@@ -5477,7 +5480,7 @@
         <v>26</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>220</v>
@@ -5489,13 +5492,13 @@
         <v>224</v>
       </c>
       <c r="K62" s="17" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="L62" s="18" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="M62" s="18" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="N62" s="17" t="s">
         <v>224</v>
@@ -5553,28 +5556,28 @@
         <v>27</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H63" s="7" t="s">
         <v>220</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J63" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K63" s="17" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="L63" s="18" t="s">
-        <v>240</v>
+        <v>187</v>
       </c>
       <c r="M63" s="18" t="s">
-        <v>217</v>
+        <v>187</v>
       </c>
       <c r="N63" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O63" s="12">
         <f t="shared" ref="O63:R63" si="34">O62+10000</f>
@@ -5629,28 +5632,28 @@
         <v>28</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H64" s="7" t="s">
         <v>220</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="J64" s="17" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="K64" s="17" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L64" s="18" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M64" s="18" t="s">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="N64" s="17" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O64" s="12">
         <f t="shared" ref="O64:R64" si="35">O63+10000</f>
@@ -5705,28 +5708,28 @@
         <v>29</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>220</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="J65" s="17" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K65" s="17" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L65" s="18" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="M65" s="18" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="N65" s="17" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="O65" s="12">
         <f t="shared" ref="O65:R65" si="36">O64+10000</f>

--- a/Excel/MonsterPillConfig.xlsx
+++ b/Excel/MonsterPillConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="293">
   <si>
     <t>ID</t>
   </si>
@@ -774,6 +774,141 @@
   </si>
   <si>
     <t>9E+240</t>
+  </si>
+  <si>
+    <t>炼神十一层</t>
+  </si>
+  <si>
+    <t>9E+250</t>
+  </si>
+  <si>
+    <t>1E+67</t>
+  </si>
+  <si>
+    <t>1E+70</t>
+  </si>
+  <si>
+    <t>炼神十二层</t>
+  </si>
+  <si>
+    <t>9E+260</t>
+  </si>
+  <si>
+    <t>1E+74</t>
+  </si>
+  <si>
+    <t>炼神十三层</t>
+  </si>
+  <si>
+    <t>9E+270</t>
+  </si>
+  <si>
+    <t>1E+73</t>
+  </si>
+  <si>
+    <t>炼神十四层</t>
+  </si>
+  <si>
+    <t>9E+280</t>
+  </si>
+  <si>
+    <t>1E+76</t>
+  </si>
+  <si>
+    <t>1E+82</t>
+  </si>
+  <si>
+    <t>炼神十五层</t>
+  </si>
+  <si>
+    <t>9E+290</t>
+  </si>
+  <si>
+    <t>1E+79</t>
+  </si>
+  <si>
+    <t>1E+86</t>
+  </si>
+  <si>
+    <t>炼神十六层</t>
+  </si>
+  <si>
+    <t>9E+300</t>
+  </si>
+  <si>
+    <t>1E+90</t>
+  </si>
+  <si>
+    <t>炼神十七层</t>
+  </si>
+  <si>
+    <t>9E+310</t>
+  </si>
+  <si>
+    <t>1E+85</t>
+  </si>
+  <si>
+    <t>1E+94</t>
+  </si>
+  <si>
+    <t>炼神十八层</t>
+  </si>
+  <si>
+    <t>9E+320</t>
+  </si>
+  <si>
+    <t>炼神十九层</t>
+  </si>
+  <si>
+    <t>9E+330</t>
+  </si>
+  <si>
+    <t>1E+91</t>
+  </si>
+  <si>
+    <t>1E+102</t>
+  </si>
+  <si>
+    <t>炼神二十层</t>
+  </si>
+  <si>
+    <t>9E+340</t>
+  </si>
+  <si>
+    <t>1E+106</t>
+  </si>
+  <si>
+    <t>炼魂一层</t>
+  </si>
+  <si>
+    <t>炼魂魔物</t>
+  </si>
+  <si>
+    <t>炼魂二层</t>
+  </si>
+  <si>
+    <t>炼魂三层</t>
+  </si>
+  <si>
+    <t>炼魂四层</t>
+  </si>
+  <si>
+    <t>炼魂五层</t>
+  </si>
+  <si>
+    <t>炼魂六层</t>
+  </si>
+  <si>
+    <t>炼魂七层</t>
+  </si>
+  <si>
+    <t>炼魂八层</t>
+  </si>
+  <si>
+    <t>炼魂九层</t>
+  </si>
+  <si>
+    <t>炼魂十层</t>
   </si>
 </sst>
 </file>
@@ -1423,12 +1558,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1437,11 +1574,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
@@ -1768,7 +1903,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y68"/>
+  <dimension ref="A1:Y88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.125" style="3" customWidth="1"/>
@@ -1795,9 +1930,9 @@
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
@@ -1815,9 +1950,9 @@
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
@@ -1835,214 +1970,214 @@
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="V3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="X3" s="13" t="s">
+      <c r="X3" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="R4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="S4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="T4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="U4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="V4" s="6" t="s">
+      <c r="V4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="W4" s="6" t="s">
+      <c r="W4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="X4" s="13" t="s">
+      <c r="X4" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="M5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="Q5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="R5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="S5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="T5" s="6" t="s">
+      <c r="T5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="U5" s="6" t="s">
+      <c r="U5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="V5" s="6" t="s">
+      <c r="V5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="W5" s="6" t="s">
+      <c r="W5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="X5" s="13" t="s">
+      <c r="X5" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:24">
+    <row r="6" customHeight="1" spans="1:24">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -2108,7 +2243,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:24">
+    <row r="7" customHeight="1" spans="1:24">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -2179,7 +2314,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:24">
+    <row r="8" customHeight="1" spans="1:24">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -2250,7 +2385,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:24">
+    <row r="9" customHeight="1" spans="1:24">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -2321,7 +2456,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="3:24">
+    <row r="10" customHeight="1" spans="1:24">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -2392,7 +2527,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:24">
+    <row r="11" customHeight="1" spans="1:24">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -2459,9 +2594,9 @@
       <c r="W11" s="2">
         <v>0</v>
       </c>
-      <c r="X11" s="14"/>
-    </row>
-    <row r="12" customHeight="1" spans="3:24">
+      <c r="X11" s="12"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:24">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -2532,7 +2667,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:24">
+    <row r="13" customHeight="1" spans="1:24">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -2603,7 +2738,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:24">
+    <row r="14" customHeight="1" spans="1:24">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -2674,7 +2809,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:23">
+    <row r="15" customHeight="1" spans="1:24">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -2742,7 +2877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:23">
+    <row r="16" customHeight="1" spans="1:24">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -3422,62 +3557,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="9:18">
+    <row r="26" customHeight="1" spans="3:23">
       <c r="I26" s="10"/>
       <c r="N26" s="11"/>
       <c r="Q26" s="2"/>
-      <c r="R26" s="12"/>
-    </row>
-    <row r="27" customHeight="1" spans="9:18">
+      <c r="R26" s="13"/>
+    </row>
+    <row r="27" customHeight="1" spans="3:23">
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
       <c r="N27" s="11"/>
       <c r="R27" s="2"/>
     </row>
-    <row r="28" customHeight="1" spans="9:18">
+    <row r="28" customHeight="1" spans="3:23">
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
       <c r="N28" s="11"/>
       <c r="R28" s="2"/>
     </row>
-    <row r="29" customHeight="1" spans="9:18">
+    <row r="29" customHeight="1" spans="3:23">
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
       <c r="N29" s="11"/>
       <c r="R29" s="2"/>
     </row>
-    <row r="30" customHeight="1" spans="10:18">
+    <row r="30" customHeight="1" spans="3:23">
       <c r="J30" s="10"/>
       <c r="N30" s="11"/>
       <c r="R30" s="2"/>
     </row>
-    <row r="31" customHeight="1" spans="10:18">
+    <row r="31" customHeight="1" spans="3:23">
       <c r="J31" s="10"/>
       <c r="N31" s="11"/>
       <c r="R31" s="2"/>
     </row>
-    <row r="32" customHeight="1" spans="10:18">
+    <row r="32" customHeight="1" spans="3:23">
       <c r="J32" s="10"/>
       <c r="N32" s="11"/>
       <c r="R32" s="2"/>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C33" s="7">
+      <c r="C33" s="14">
         <v>101</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="14">
         <v>2</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="14">
         <v>1</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="14">
         <v>10</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="H33" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I33" s="17" t="s">
@@ -3496,22 +3631,22 @@
       <c r="N33" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="O33" s="12">
+      <c r="O33" s="13">
         <v>10000</v>
       </c>
-      <c r="P33" s="12">
+      <c r="P33" s="13">
         <v>10000</v>
       </c>
-      <c r="Q33" s="12">
+      <c r="Q33" s="13">
         <v>10000</v>
       </c>
-      <c r="R33" s="12">
+      <c r="R33" s="13">
         <v>10000</v>
       </c>
       <c r="S33" s="2">
         <v>0</v>
       </c>
-      <c r="T33" s="12">
+      <c r="T33" s="13">
         <v>150</v>
       </c>
       <c r="U33" s="2">
@@ -3529,22 +3664,22 @@
       <c r="Y33" s="16"/>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C34" s="7">
+      <c r="C34" s="14">
         <v>102</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="14">
         <v>2</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="14">
         <v>2</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="14">
         <v>11</v>
       </c>
-      <c r="G34" s="7" t="s">
+      <c r="G34" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="H34" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I34" s="17" t="s">
@@ -3563,15 +3698,15 @@
       <c r="N34" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="O34" s="12">
+      <c r="O34" s="13">
         <f t="shared" ref="O33:O52" si="13">O33+1000</f>
         <v>11000</v>
       </c>
-      <c r="P34" s="12">
+      <c r="P34" s="13">
         <f t="shared" ref="P33:P52" si="14">P33+1000</f>
         <v>11000</v>
       </c>
-      <c r="Q34" s="12">
+      <c r="Q34" s="13">
         <f t="shared" ref="Q34:Q52" si="15">Q33+2000</f>
         <v>12000</v>
       </c>
@@ -3602,22 +3737,22 @@
       <c r="Y34" s="16"/>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C35" s="7">
+      <c r="C35" s="14">
         <v>103</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="14">
         <v>2</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="14">
         <v>3</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="14">
         <v>12</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="G35" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="H35" s="7" t="s">
+      <c r="H35" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I35" s="17" t="s">
@@ -3636,15 +3771,15 @@
       <c r="N35" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="O35" s="12">
+      <c r="O35" s="13">
         <f t="shared" si="13"/>
         <v>12000</v>
       </c>
-      <c r="P35" s="12">
+      <c r="P35" s="13">
         <f t="shared" si="14"/>
         <v>12000</v>
       </c>
-      <c r="Q35" s="12">
+      <c r="Q35" s="13">
         <f t="shared" si="15"/>
         <v>14000</v>
       </c>
@@ -3675,22 +3810,22 @@
       <c r="Y35" s="16"/>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C36" s="7">
+      <c r="C36" s="14">
         <v>104</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="14">
         <v>2</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="14">
         <v>4</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36" s="14">
         <v>13</v>
       </c>
-      <c r="G36" s="7" t="s">
+      <c r="G36" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="H36" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I36" s="17" t="s">
@@ -3709,15 +3844,15 @@
       <c r="N36" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="O36" s="12">
+      <c r="O36" s="13">
         <f t="shared" si="13"/>
         <v>13000</v>
       </c>
-      <c r="P36" s="12">
+      <c r="P36" s="13">
         <f t="shared" si="14"/>
         <v>13000</v>
       </c>
-      <c r="Q36" s="12">
+      <c r="Q36" s="13">
         <f t="shared" si="15"/>
         <v>16000</v>
       </c>
@@ -3748,22 +3883,22 @@
       <c r="Y36" s="16"/>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C37" s="7">
+      <c r="C37" s="14">
         <v>105</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="14">
         <v>2</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="14">
         <v>5</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37" s="14">
         <v>14</v>
       </c>
-      <c r="G37" s="7" t="s">
+      <c r="G37" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="H37" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I37" s="17" t="s">
@@ -3782,15 +3917,15 @@
       <c r="N37" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="O37" s="12">
+      <c r="O37" s="13">
         <f t="shared" si="13"/>
         <v>14000</v>
       </c>
-      <c r="P37" s="12">
+      <c r="P37" s="13">
         <f t="shared" si="14"/>
         <v>14000</v>
       </c>
-      <c r="Q37" s="12">
+      <c r="Q37" s="13">
         <f t="shared" si="15"/>
         <v>18000</v>
       </c>
@@ -3821,22 +3956,22 @@
       <c r="Y37" s="16"/>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C38" s="7">
+      <c r="C38" s="14">
         <v>106</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="14">
         <v>2</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38" s="14">
         <v>6</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="14">
         <v>15</v>
       </c>
-      <c r="G38" s="7" t="s">
+      <c r="G38" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="H38" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I38" s="17" t="s">
@@ -3855,15 +3990,15 @@
       <c r="N38" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="O38" s="12">
+      <c r="O38" s="13">
         <f t="shared" si="13"/>
         <v>15000</v>
       </c>
-      <c r="P38" s="12">
+      <c r="P38" s="13">
         <f t="shared" si="14"/>
         <v>15000</v>
       </c>
-      <c r="Q38" s="12">
+      <c r="Q38" s="13">
         <f t="shared" si="15"/>
         <v>20000</v>
       </c>
@@ -3894,22 +4029,22 @@
       <c r="Y38" s="16"/>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C39" s="7">
+      <c r="C39" s="14">
         <v>107</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="14">
         <v>2</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="14">
         <v>7</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="14">
         <v>16</v>
       </c>
-      <c r="G39" s="7" t="s">
+      <c r="G39" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="H39" s="7" t="s">
+      <c r="H39" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I39" s="17" t="s">
@@ -3927,15 +4062,15 @@
       <c r="N39" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="O39" s="12">
+      <c r="O39" s="13">
         <f t="shared" si="13"/>
         <v>16000</v>
       </c>
-      <c r="P39" s="12">
+      <c r="P39" s="13">
         <f t="shared" si="14"/>
         <v>16000</v>
       </c>
-      <c r="Q39" s="12">
+      <c r="Q39" s="13">
         <f t="shared" si="15"/>
         <v>22000</v>
       </c>
@@ -3966,22 +4101,22 @@
       <c r="Y39" s="16"/>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C40" s="7">
+      <c r="C40" s="14">
         <v>108</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="14">
         <v>2</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E40" s="14">
         <v>8</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40" s="14">
         <v>17</v>
       </c>
-      <c r="G40" s="7" t="s">
+      <c r="G40" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="H40" s="7" t="s">
+      <c r="H40" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I40" s="17" t="s">
@@ -4000,15 +4135,15 @@
       <c r="N40" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="O40" s="12">
+      <c r="O40" s="13">
         <f t="shared" si="13"/>
         <v>17000</v>
       </c>
-      <c r="P40" s="12">
+      <c r="P40" s="13">
         <f t="shared" si="14"/>
         <v>17000</v>
       </c>
-      <c r="Q40" s="12">
+      <c r="Q40" s="13">
         <f t="shared" si="15"/>
         <v>24000</v>
       </c>
@@ -4039,22 +4174,22 @@
       <c r="Y40" s="16"/>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C41" s="7">
+      <c r="C41" s="14">
         <v>109</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="14">
         <v>2</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="14">
         <v>9</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41" s="14">
         <v>18</v>
       </c>
-      <c r="G41" s="7" t="s">
+      <c r="G41" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="H41" s="7" t="s">
+      <c r="H41" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I41" s="17" t="s">
@@ -4073,15 +4208,15 @@
       <c r="N41" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="O41" s="12">
+      <c r="O41" s="13">
         <f t="shared" si="13"/>
         <v>18000</v>
       </c>
-      <c r="P41" s="12">
+      <c r="P41" s="13">
         <f t="shared" si="14"/>
         <v>18000</v>
       </c>
-      <c r="Q41" s="12">
+      <c r="Q41" s="13">
         <f t="shared" si="15"/>
         <v>26000</v>
       </c>
@@ -4112,22 +4247,22 @@
       <c r="Y41" s="16"/>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C42" s="7">
+      <c r="C42" s="14">
         <v>110</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="14">
         <v>2</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E42" s="14">
         <v>10</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="14">
         <v>19</v>
       </c>
-      <c r="G42" s="7" t="s">
+      <c r="G42" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="H42" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I42" s="17" t="s">
@@ -4146,15 +4281,15 @@
       <c r="N42" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="O42" s="12">
+      <c r="O42" s="13">
         <f t="shared" si="13"/>
         <v>19000</v>
       </c>
-      <c r="P42" s="12">
+      <c r="P42" s="13">
         <f t="shared" si="14"/>
         <v>19000</v>
       </c>
-      <c r="Q42" s="12">
+      <c r="Q42" s="13">
         <f t="shared" si="15"/>
         <v>28000</v>
       </c>
@@ -4185,22 +4320,22 @@
       <c r="Y42" s="16"/>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C43" s="7">
+      <c r="C43" s="14">
         <v>111</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="14">
         <v>2</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E43" s="14">
         <v>11</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F43" s="14">
         <v>20</v>
       </c>
-      <c r="G43" s="7" t="s">
+      <c r="G43" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="H43" s="7" t="s">
+      <c r="H43" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I43" s="17" t="s">
@@ -4221,15 +4356,15 @@
       <c r="N43" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="O43" s="12">
+      <c r="O43" s="13">
         <f t="shared" si="13"/>
         <v>20000</v>
       </c>
-      <c r="P43" s="12">
+      <c r="P43" s="13">
         <f t="shared" si="14"/>
         <v>20000</v>
       </c>
-      <c r="Q43" s="12">
+      <c r="Q43" s="13">
         <f t="shared" si="15"/>
         <v>30000</v>
       </c>
@@ -4260,22 +4395,22 @@
       <c r="Y43" s="16"/>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C44" s="7">
+      <c r="C44" s="14">
         <v>112</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="14">
         <v>2</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E44" s="14">
         <v>12</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="14">
         <v>21</v>
       </c>
-      <c r="G44" s="7" t="s">
+      <c r="G44" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="H44" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I44" s="17" t="s">
@@ -4296,19 +4431,19 @@
       <c r="N44" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="O44" s="12">
+      <c r="O44" s="13">
         <f t="shared" ref="O44:O52" si="20">O43+5000</f>
         <v>25000</v>
       </c>
-      <c r="P44" s="12">
+      <c r="P44" s="13">
         <f t="shared" ref="P44:P52" si="21">P43+5000</f>
         <v>25000</v>
       </c>
-      <c r="Q44" s="12">
+      <c r="Q44" s="13">
         <f t="shared" ref="Q44:Q52" si="22">Q43+4000</f>
         <v>34000</v>
       </c>
-      <c r="R44" s="12">
+      <c r="R44" s="13">
         <f t="shared" ref="R44:R52" si="23">R43+4000</f>
         <v>34000</v>
       </c>
@@ -4335,22 +4470,22 @@
       <c r="Y44" s="16"/>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C45" s="7">
+      <c r="C45" s="14">
         <v>113</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="14">
         <v>2</v>
       </c>
-      <c r="E45" s="7">
+      <c r="E45" s="14">
         <v>13</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45" s="14">
         <v>22</v>
       </c>
-      <c r="G45" s="7" t="s">
+      <c r="G45" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="H45" s="7" t="s">
+      <c r="H45" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I45" s="17" t="s">
@@ -4371,19 +4506,19 @@
       <c r="N45" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="O45" s="12">
+      <c r="O45" s="13">
         <f t="shared" si="20"/>
         <v>30000</v>
       </c>
-      <c r="P45" s="12">
+      <c r="P45" s="13">
         <f t="shared" si="21"/>
         <v>30000</v>
       </c>
-      <c r="Q45" s="12">
+      <c r="Q45" s="13">
         <f t="shared" si="22"/>
         <v>38000</v>
       </c>
-      <c r="R45" s="12">
+      <c r="R45" s="13">
         <f t="shared" si="23"/>
         <v>38000</v>
       </c>
@@ -4411,22 +4546,22 @@
       <c r="Y45" s="16"/>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C46" s="7">
+      <c r="C46" s="14">
         <v>114</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D46" s="14">
         <v>2</v>
       </c>
-      <c r="E46" s="7">
+      <c r="E46" s="14">
         <v>14</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F46" s="14">
         <v>23</v>
       </c>
-      <c r="G46" s="7" t="s">
+      <c r="G46" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="H46" s="7" t="s">
+      <c r="H46" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I46" s="17" t="s">
@@ -4447,19 +4582,19 @@
       <c r="N46" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="O46" s="12">
+      <c r="O46" s="13">
         <f t="shared" si="20"/>
         <v>35000</v>
       </c>
-      <c r="P46" s="12">
+      <c r="P46" s="13">
         <f t="shared" si="21"/>
         <v>35000</v>
       </c>
-      <c r="Q46" s="12">
+      <c r="Q46" s="13">
         <f t="shared" si="22"/>
         <v>42000</v>
       </c>
-      <c r="R46" s="12">
+      <c r="R46" s="13">
         <f t="shared" si="23"/>
         <v>42000</v>
       </c>
@@ -4487,22 +4622,22 @@
       <c r="Y46" s="16"/>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C47" s="7">
+      <c r="C47" s="14">
         <v>115</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="14">
         <v>2</v>
       </c>
-      <c r="E47" s="7">
+      <c r="E47" s="14">
         <v>15</v>
       </c>
-      <c r="F47" s="7">
+      <c r="F47" s="14">
         <v>24</v>
       </c>
-      <c r="G47" s="7" t="s">
+      <c r="G47" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="H47" s="7" t="s">
+      <c r="H47" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I47" s="17" t="s">
@@ -4523,19 +4658,19 @@
       <c r="N47" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="O47" s="12">
+      <c r="O47" s="13">
         <f t="shared" si="20"/>
         <v>40000</v>
       </c>
-      <c r="P47" s="12">
+      <c r="P47" s="13">
         <f t="shared" si="21"/>
         <v>40000</v>
       </c>
-      <c r="Q47" s="12">
+      <c r="Q47" s="13">
         <f t="shared" si="22"/>
         <v>46000</v>
       </c>
-      <c r="R47" s="12">
+      <c r="R47" s="13">
         <f t="shared" si="23"/>
         <v>46000</v>
       </c>
@@ -4563,22 +4698,22 @@
       <c r="Y47" s="16"/>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C48" s="7">
+      <c r="C48" s="14">
         <v>116</v>
       </c>
-      <c r="D48" s="7">
+      <c r="D48" s="14">
         <v>2</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E48" s="14">
         <v>16</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F48" s="14">
         <v>25</v>
       </c>
-      <c r="G48" s="7" t="s">
+      <c r="G48" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="H48" s="7" t="s">
+      <c r="H48" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I48" s="17" t="s">
@@ -4599,19 +4734,19 @@
       <c r="N48" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="O48" s="12">
+      <c r="O48" s="13">
         <f t="shared" si="20"/>
         <v>45000</v>
       </c>
-      <c r="P48" s="12">
+      <c r="P48" s="13">
         <f t="shared" si="21"/>
         <v>45000</v>
       </c>
-      <c r="Q48" s="12">
+      <c r="Q48" s="13">
         <f t="shared" si="22"/>
         <v>50000</v>
       </c>
-      <c r="R48" s="12">
+      <c r="R48" s="13">
         <f t="shared" si="23"/>
         <v>50000</v>
       </c>
@@ -4639,22 +4774,22 @@
       <c r="Y48" s="16"/>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C49" s="7">
+      <c r="C49" s="14">
         <v>117</v>
       </c>
-      <c r="D49" s="7">
+      <c r="D49" s="14">
         <v>2</v>
       </c>
-      <c r="E49" s="7">
+      <c r="E49" s="14">
         <v>17</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F49" s="14">
         <v>26</v>
       </c>
-      <c r="G49" s="7" t="s">
+      <c r="G49" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="H49" s="7" t="s">
+      <c r="H49" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I49" s="17" t="s">
@@ -4675,19 +4810,19 @@
       <c r="N49" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="O49" s="12">
+      <c r="O49" s="13">
         <f t="shared" si="20"/>
         <v>50000</v>
       </c>
-      <c r="P49" s="12">
+      <c r="P49" s="13">
         <f t="shared" si="21"/>
         <v>50000</v>
       </c>
-      <c r="Q49" s="12">
+      <c r="Q49" s="13">
         <f t="shared" si="22"/>
         <v>54000</v>
       </c>
-      <c r="R49" s="12">
+      <c r="R49" s="13">
         <f t="shared" si="23"/>
         <v>54000</v>
       </c>
@@ -4715,22 +4850,22 @@
       <c r="Y49" s="16"/>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C50" s="7">
+      <c r="C50" s="14">
         <v>118</v>
       </c>
-      <c r="D50" s="7">
+      <c r="D50" s="14">
         <v>2</v>
       </c>
-      <c r="E50" s="7">
+      <c r="E50" s="14">
         <v>18</v>
       </c>
-      <c r="F50" s="7">
+      <c r="F50" s="14">
         <v>27</v>
       </c>
-      <c r="G50" s="7" t="s">
+      <c r="G50" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="H50" s="7" t="s">
+      <c r="H50" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I50" s="17" t="s">
@@ -4751,19 +4886,19 @@
       <c r="N50" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="O50" s="12">
+      <c r="O50" s="13">
         <f t="shared" si="20"/>
         <v>55000</v>
       </c>
-      <c r="P50" s="12">
+      <c r="P50" s="13">
         <f t="shared" si="21"/>
         <v>55000</v>
       </c>
-      <c r="Q50" s="12">
+      <c r="Q50" s="13">
         <f t="shared" si="22"/>
         <v>58000</v>
       </c>
-      <c r="R50" s="12">
+      <c r="R50" s="13">
         <f t="shared" si="23"/>
         <v>58000</v>
       </c>
@@ -4791,22 +4926,22 @@
       <c r="Y50" s="16"/>
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C51" s="7">
+      <c r="C51" s="14">
         <v>119</v>
       </c>
-      <c r="D51" s="7">
+      <c r="D51" s="14">
         <v>2</v>
       </c>
-      <c r="E51" s="7">
+      <c r="E51" s="14">
         <v>19</v>
       </c>
-      <c r="F51" s="7">
+      <c r="F51" s="14">
         <v>28</v>
       </c>
-      <c r="G51" s="7" t="s">
+      <c r="G51" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="H51" s="7" t="s">
+      <c r="H51" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I51" s="17" t="s">
@@ -4827,19 +4962,19 @@
       <c r="N51" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="O51" s="12">
+      <c r="O51" s="13">
         <f t="shared" si="20"/>
         <v>60000</v>
       </c>
-      <c r="P51" s="12">
+      <c r="P51" s="13">
         <f t="shared" si="21"/>
         <v>60000</v>
       </c>
-      <c r="Q51" s="12">
+      <c r="Q51" s="13">
         <f t="shared" si="22"/>
         <v>62000</v>
       </c>
-      <c r="R51" s="12">
+      <c r="R51" s="13">
         <f t="shared" si="23"/>
         <v>62000</v>
       </c>
@@ -4867,22 +5002,22 @@
       <c r="Y51" s="16"/>
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C52" s="7">
+      <c r="C52" s="14">
         <v>120</v>
       </c>
-      <c r="D52" s="7">
+      <c r="D52" s="14">
         <v>2</v>
       </c>
-      <c r="E52" s="7">
+      <c r="E52" s="14">
         <v>20</v>
       </c>
-      <c r="F52" s="7">
+      <c r="F52" s="14">
         <v>29</v>
       </c>
-      <c r="G52" s="7" t="s">
+      <c r="G52" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="H52" s="7" t="s">
+      <c r="H52" s="14" t="s">
         <v>113</v>
       </c>
       <c r="I52" s="17" t="s">
@@ -4903,19 +5038,19 @@
       <c r="N52" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="O52" s="12">
+      <c r="O52" s="13">
         <f t="shared" si="20"/>
         <v>65000</v>
       </c>
-      <c r="P52" s="12">
+      <c r="P52" s="13">
         <f t="shared" si="21"/>
         <v>65000</v>
       </c>
-      <c r="Q52" s="12">
+      <c r="Q52" s="13">
         <f t="shared" si="22"/>
         <v>66000</v>
       </c>
-      <c r="R52" s="12">
+      <c r="R52" s="13">
         <f t="shared" si="23"/>
         <v>66000</v>
       </c>
@@ -4943,12 +5078,12 @@
       <c r="Y52" s="16"/>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
       <c r="I53" s="10"/>
       <c r="J53" s="10"/>
       <c r="K53" s="10"/>
@@ -4968,12 +5103,12 @@
       <c r="Y53" s="16"/>
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
       <c r="I54" s="10"/>
       <c r="J54" s="10"/>
       <c r="K54" s="10"/>
@@ -4993,12 +5128,12 @@
       <c r="Y54" s="16"/>
     </row>
     <row r="55" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
       <c r="I55" s="10"/>
       <c r="J55" s="10"/>
       <c r="K55" s="10"/>
@@ -5018,22 +5153,22 @@
       <c r="Y55" s="16"/>
     </row>
     <row r="56" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C56" s="7">
+      <c r="C56" s="14">
         <v>201</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D56" s="14">
         <v>3</v>
       </c>
-      <c r="E56" s="7">
+      <c r="E56" s="14">
         <v>1</v>
       </c>
-      <c r="F56" s="7">
+      <c r="F56" s="14">
         <v>20</v>
       </c>
-      <c r="G56" s="7" t="s">
+      <c r="G56" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="H56" s="7" t="s">
+      <c r="H56" s="14" t="s">
         <v>220</v>
       </c>
       <c r="I56" s="17" t="s">
@@ -5054,22 +5189,22 @@
       <c r="N56" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="O56" s="12">
+      <c r="O56" s="13">
         <v>50000</v>
       </c>
-      <c r="P56" s="12">
+      <c r="P56" s="13">
         <v>50000</v>
       </c>
-      <c r="Q56" s="12">
+      <c r="Q56" s="13">
         <v>50000</v>
       </c>
-      <c r="R56" s="12">
+      <c r="R56" s="13">
         <v>50000</v>
       </c>
       <c r="S56" s="2">
         <v>0</v>
       </c>
-      <c r="T56" s="12">
+      <c r="T56" s="13">
         <v>300</v>
       </c>
       <c r="U56" s="2">
@@ -5087,22 +5222,22 @@
       <c r="Y56" s="16"/>
     </row>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C57" s="7">
+      <c r="C57" s="14">
         <v>202</v>
       </c>
-      <c r="D57" s="7">
+      <c r="D57" s="14">
         <v>3</v>
       </c>
-      <c r="E57" s="7">
+      <c r="E57" s="14">
         <v>2</v>
       </c>
-      <c r="F57" s="7">
+      <c r="F57" s="14">
         <v>21</v>
       </c>
-      <c r="G57" s="7" t="s">
+      <c r="G57" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="H57" s="7" t="s">
+      <c r="H57" s="14" t="s">
         <v>220</v>
       </c>
       <c r="I57" s="17" t="s">
@@ -5123,19 +5258,19 @@
       <c r="N57" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="O57" s="12">
+      <c r="O57" s="13">
         <f t="shared" ref="O57:R57" si="25">O56+10000</f>
         <v>60000</v>
       </c>
-      <c r="P57" s="12">
+      <c r="P57" s="13">
         <f t="shared" si="25"/>
         <v>60000</v>
       </c>
-      <c r="Q57" s="12">
+      <c r="Q57" s="13">
         <f t="shared" si="25"/>
         <v>60000</v>
       </c>
-      <c r="R57" s="12">
+      <c r="R57" s="13">
         <f t="shared" si="25"/>
         <v>60000</v>
       </c>
@@ -5143,18 +5278,18 @@
         <v>0</v>
       </c>
       <c r="T57" s="2">
-        <f t="shared" ref="T57:T65" si="26">T56+30</f>
+        <f t="shared" ref="T57:T75" si="26">T56+30</f>
         <v>330</v>
       </c>
       <c r="U57" s="2">
-        <f t="shared" ref="U57:U65" si="27">U56+30</f>
+        <f t="shared" ref="U57:U75" si="27">U56+30</f>
         <v>430</v>
       </c>
       <c r="V57" s="2">
         <v>99</v>
       </c>
       <c r="W57" s="2">
-        <f t="shared" ref="W57:W65" si="28">W56+20</f>
+        <f t="shared" ref="W57:W75" si="28">W56+20</f>
         <v>220</v>
       </c>
       <c r="X57" s="19" t="s">
@@ -5163,22 +5298,22 @@
       <c r="Y57" s="16"/>
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C58" s="7">
+      <c r="C58" s="14">
         <v>203</v>
       </c>
-      <c r="D58" s="7">
+      <c r="D58" s="14">
         <v>3</v>
       </c>
-      <c r="E58" s="7">
+      <c r="E58" s="14">
         <v>3</v>
       </c>
-      <c r="F58" s="7">
+      <c r="F58" s="14">
         <v>22</v>
       </c>
-      <c r="G58" s="7" t="s">
+      <c r="G58" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="H58" s="7" t="s">
+      <c r="H58" s="14" t="s">
         <v>220</v>
       </c>
       <c r="I58" s="17" t="s">
@@ -5199,19 +5334,19 @@
       <c r="N58" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="O58" s="12">
+      <c r="O58" s="13">
         <f t="shared" ref="O58:R58" si="29">O57+10000</f>
         <v>70000</v>
       </c>
-      <c r="P58" s="12">
+      <c r="P58" s="13">
         <f t="shared" si="29"/>
         <v>70000</v>
       </c>
-      <c r="Q58" s="12">
+      <c r="Q58" s="13">
         <f t="shared" si="29"/>
         <v>70000</v>
       </c>
-      <c r="R58" s="12">
+      <c r="R58" s="13">
         <f t="shared" si="29"/>
         <v>70000</v>
       </c>
@@ -5239,22 +5374,22 @@
       <c r="Y58" s="16"/>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C59" s="7">
+      <c r="C59" s="14">
         <v>204</v>
       </c>
-      <c r="D59" s="7">
+      <c r="D59" s="14">
         <v>3</v>
       </c>
-      <c r="E59" s="7">
+      <c r="E59" s="14">
         <v>4</v>
       </c>
-      <c r="F59" s="7">
+      <c r="F59" s="14">
         <v>23</v>
       </c>
-      <c r="G59" s="7" t="s">
+      <c r="G59" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="H59" s="7" t="s">
+      <c r="H59" s="14" t="s">
         <v>220</v>
       </c>
       <c r="I59" s="17" t="s">
@@ -5275,19 +5410,19 @@
       <c r="N59" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="O59" s="12">
+      <c r="O59" s="13">
         <f t="shared" ref="O59:R59" si="30">O58+10000</f>
         <v>80000</v>
       </c>
-      <c r="P59" s="12">
+      <c r="P59" s="13">
         <f t="shared" si="30"/>
         <v>80000</v>
       </c>
-      <c r="Q59" s="12">
+      <c r="Q59" s="13">
         <f t="shared" si="30"/>
         <v>80000</v>
       </c>
-      <c r="R59" s="12">
+      <c r="R59" s="13">
         <f t="shared" si="30"/>
         <v>80000</v>
       </c>
@@ -5315,22 +5450,22 @@
       <c r="Y59" s="16"/>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C60" s="7">
+      <c r="C60" s="14">
         <v>205</v>
       </c>
-      <c r="D60" s="7">
+      <c r="D60" s="14">
         <v>3</v>
       </c>
-      <c r="E60" s="7">
+      <c r="E60" s="14">
         <v>5</v>
       </c>
-      <c r="F60" s="7">
+      <c r="F60" s="14">
         <v>24</v>
       </c>
-      <c r="G60" s="7" t="s">
+      <c r="G60" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="H60" s="7" t="s">
+      <c r="H60" s="14" t="s">
         <v>220</v>
       </c>
       <c r="I60" s="17" t="s">
@@ -5351,19 +5486,19 @@
       <c r="N60" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="O60" s="12">
+      <c r="O60" s="13">
         <f t="shared" ref="O60:R60" si="31">O59+10000</f>
         <v>90000</v>
       </c>
-      <c r="P60" s="12">
+      <c r="P60" s="13">
         <f t="shared" si="31"/>
         <v>90000</v>
       </c>
-      <c r="Q60" s="12">
+      <c r="Q60" s="13">
         <f t="shared" si="31"/>
         <v>90000</v>
       </c>
-      <c r="R60" s="12">
+      <c r="R60" s="13">
         <f t="shared" si="31"/>
         <v>90000</v>
       </c>
@@ -5391,22 +5526,22 @@
       <c r="Y60" s="16"/>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C61" s="7">
+      <c r="C61" s="14">
         <v>206</v>
       </c>
-      <c r="D61" s="7">
+      <c r="D61" s="14">
         <v>3</v>
       </c>
-      <c r="E61" s="7">
+      <c r="E61" s="14">
         <v>6</v>
       </c>
-      <c r="F61" s="7">
+      <c r="F61" s="14">
         <v>25</v>
       </c>
-      <c r="G61" s="7" t="s">
+      <c r="G61" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="H61" s="7" t="s">
+      <c r="H61" s="14" t="s">
         <v>220</v>
       </c>
       <c r="I61" s="17" t="s">
@@ -5427,19 +5562,19 @@
       <c r="N61" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="O61" s="12">
+      <c r="O61" s="13">
         <f t="shared" ref="O61:R61" si="32">O60+10000</f>
         <v>100000</v>
       </c>
-      <c r="P61" s="12">
+      <c r="P61" s="13">
         <f t="shared" si="32"/>
         <v>100000</v>
       </c>
-      <c r="Q61" s="12">
+      <c r="Q61" s="13">
         <f t="shared" si="32"/>
         <v>100000</v>
       </c>
-      <c r="R61" s="12">
+      <c r="R61" s="13">
         <f t="shared" si="32"/>
         <v>100000</v>
       </c>
@@ -5467,22 +5602,22 @@
       <c r="Y61" s="16"/>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C62" s="7">
+      <c r="C62" s="14">
         <v>207</v>
       </c>
-      <c r="D62" s="7">
+      <c r="D62" s="14">
         <v>3</v>
       </c>
-      <c r="E62" s="7">
+      <c r="E62" s="14">
         <v>7</v>
       </c>
-      <c r="F62" s="7">
+      <c r="F62" s="14">
         <v>26</v>
       </c>
-      <c r="G62" s="7" t="s">
+      <c r="G62" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="H62" s="7" t="s">
+      <c r="H62" s="14" t="s">
         <v>220</v>
       </c>
       <c r="I62" s="17" t="s">
@@ -5503,19 +5638,19 @@
       <c r="N62" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="O62" s="12">
+      <c r="O62" s="13">
         <f t="shared" ref="O62:R62" si="33">O61+10000</f>
         <v>110000</v>
       </c>
-      <c r="P62" s="12">
+      <c r="P62" s="13">
         <f t="shared" si="33"/>
         <v>110000</v>
       </c>
-      <c r="Q62" s="12">
+      <c r="Q62" s="13">
         <f t="shared" si="33"/>
         <v>110000</v>
       </c>
-      <c r="R62" s="12">
+      <c r="R62" s="13">
         <f t="shared" si="33"/>
         <v>110000</v>
       </c>
@@ -5543,22 +5678,22 @@
       <c r="Y62" s="16"/>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C63" s="7">
+      <c r="C63" s="14">
         <v>208</v>
       </c>
-      <c r="D63" s="7">
+      <c r="D63" s="14">
         <v>3</v>
       </c>
-      <c r="E63" s="7">
+      <c r="E63" s="14">
         <v>8</v>
       </c>
-      <c r="F63" s="7">
+      <c r="F63" s="14">
         <v>27</v>
       </c>
-      <c r="G63" s="7" t="s">
+      <c r="G63" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="H63" s="7" t="s">
+      <c r="H63" s="14" t="s">
         <v>220</v>
       </c>
       <c r="I63" s="17" t="s">
@@ -5579,19 +5714,19 @@
       <c r="N63" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="O63" s="12">
+      <c r="O63" s="13">
         <f t="shared" ref="O63:R63" si="34">O62+10000</f>
         <v>120000</v>
       </c>
-      <c r="P63" s="12">
+      <c r="P63" s="13">
         <f t="shared" si="34"/>
         <v>120000</v>
       </c>
-      <c r="Q63" s="12">
+      <c r="Q63" s="13">
         <f t="shared" si="34"/>
         <v>120000</v>
       </c>
-      <c r="R63" s="12">
+      <c r="R63" s="13">
         <f t="shared" si="34"/>
         <v>120000</v>
       </c>
@@ -5619,22 +5754,22 @@
       <c r="Y63" s="16"/>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C64" s="7">
+      <c r="C64" s="14">
         <v>209</v>
       </c>
-      <c r="D64" s="7">
+      <c r="D64" s="14">
         <v>3</v>
       </c>
-      <c r="E64" s="7">
+      <c r="E64" s="14">
         <v>9</v>
       </c>
-      <c r="F64" s="7">
+      <c r="F64" s="14">
         <v>28</v>
       </c>
-      <c r="G64" s="7" t="s">
+      <c r="G64" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="H64" s="7" t="s">
+      <c r="H64" s="14" t="s">
         <v>220</v>
       </c>
       <c r="I64" s="17" t="s">
@@ -5655,19 +5790,19 @@
       <c r="N64" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="O64" s="12">
+      <c r="O64" s="13">
         <f t="shared" ref="O64:R64" si="35">O63+10000</f>
         <v>130000</v>
       </c>
-      <c r="P64" s="12">
+      <c r="P64" s="13">
         <f t="shared" si="35"/>
         <v>130000</v>
       </c>
-      <c r="Q64" s="12">
+      <c r="Q64" s="13">
         <f t="shared" si="35"/>
         <v>130000</v>
       </c>
-      <c r="R64" s="12">
+      <c r="R64" s="13">
         <f t="shared" si="35"/>
         <v>130000</v>
       </c>
@@ -5695,22 +5830,22 @@
       <c r="Y64" s="16"/>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C65" s="7">
+      <c r="C65" s="14">
         <v>210</v>
       </c>
-      <c r="D65" s="7">
+      <c r="D65" s="14">
         <v>3</v>
       </c>
-      <c r="E65" s="7">
+      <c r="E65" s="14">
         <v>10</v>
       </c>
-      <c r="F65" s="7">
+      <c r="F65" s="14">
         <v>29</v>
       </c>
-      <c r="G65" s="7" t="s">
+      <c r="G65" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="H65" s="7" t="s">
+      <c r="H65" s="14" t="s">
         <v>220</v>
       </c>
       <c r="I65" s="17" t="s">
@@ -5731,20 +5866,20 @@
       <c r="N65" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="O65" s="12">
-        <f t="shared" ref="O65:R65" si="36">O64+10000</f>
+      <c r="O65" s="13">
+        <f t="shared" ref="O65:O75" si="36">O64+10000</f>
         <v>140000</v>
       </c>
-      <c r="P65" s="12">
-        <f t="shared" si="36"/>
+      <c r="P65" s="13">
+        <f t="shared" ref="P65:P75" si="37">P64+10000</f>
         <v>140000</v>
       </c>
-      <c r="Q65" s="12">
-        <f t="shared" si="36"/>
+      <c r="Q65" s="13">
+        <f t="shared" ref="Q65:Q75" si="38">Q64+10000</f>
         <v>140000</v>
       </c>
-      <c r="R65" s="12">
-        <f t="shared" si="36"/>
+      <c r="R65" s="13">
+        <f t="shared" ref="R65:R75" si="39">R64+10000</f>
         <v>140000</v>
       </c>
       <c r="S65" s="2">
@@ -5771,79 +5906,1481 @@
       <c r="Y65" s="16"/>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="7"/>
-      <c r="H66" s="7"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10"/>
-      <c r="K66" s="10"/>
-      <c r="L66" s="2"/>
-      <c r="M66" s="2"/>
-      <c r="N66" s="11"/>
-      <c r="O66" s="2"/>
-      <c r="P66" s="2"/>
-      <c r="Q66" s="2"/>
-      <c r="R66" s="2"/>
-      <c r="S66" s="2"/>
-      <c r="T66" s="2"/>
-      <c r="U66" s="2"/>
-      <c r="V66" s="2"/>
-      <c r="W66" s="2"/>
-      <c r="X66" s="2"/>
+      <c r="C66" s="14">
+        <v>211</v>
+      </c>
+      <c r="D66" s="14">
+        <v>3</v>
+      </c>
+      <c r="E66" s="14">
+        <v>11</v>
+      </c>
+      <c r="F66" s="14">
+        <v>30</v>
+      </c>
+      <c r="G66" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="H66" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="I66" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="J66" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K66" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="L66" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="M66" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="O66" s="13">
+        <f t="shared" si="36"/>
+        <v>150000</v>
+      </c>
+      <c r="P66" s="13">
+        <f t="shared" si="37"/>
+        <v>150000</v>
+      </c>
+      <c r="Q66" s="13">
+        <f t="shared" si="38"/>
+        <v>150000</v>
+      </c>
+      <c r="R66" s="13">
+        <f t="shared" si="39"/>
+        <v>150000</v>
+      </c>
+      <c r="S66" s="2">
+        <v>0</v>
+      </c>
+      <c r="T66" s="2">
+        <f t="shared" si="26"/>
+        <v>600</v>
+      </c>
+      <c r="U66" s="2">
+        <f t="shared" si="27"/>
+        <v>700</v>
+      </c>
+      <c r="V66" s="2">
+        <v>99</v>
+      </c>
+      <c r="W66" s="2">
+        <v>400</v>
+      </c>
+      <c r="X66" s="19" t="s">
+        <v>222</v>
+      </c>
       <c r="Y66" s="16"/>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
-      <c r="K67" s="10"/>
-      <c r="L67" s="2"/>
-      <c r="M67" s="2"/>
-      <c r="N67" s="11"/>
-      <c r="O67" s="2"/>
-      <c r="P67" s="2"/>
-      <c r="Q67" s="2"/>
-      <c r="R67" s="2"/>
-      <c r="S67" s="2"/>
-      <c r="T67" s="2"/>
-      <c r="U67" s="2"/>
-      <c r="V67" s="2"/>
-      <c r="W67" s="2"/>
-      <c r="X67" s="2"/>
+      <c r="C67" s="14">
+        <v>212</v>
+      </c>
+      <c r="D67" s="14">
+        <v>3</v>
+      </c>
+      <c r="E67" s="14">
+        <v>12</v>
+      </c>
+      <c r="F67" s="14">
+        <v>31</v>
+      </c>
+      <c r="G67" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="H67" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="I67" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="J67" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K67" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="L67" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="M67" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="O67" s="13">
+        <f t="shared" si="36"/>
+        <v>160000</v>
+      </c>
+      <c r="P67" s="13">
+        <f t="shared" si="37"/>
+        <v>160000</v>
+      </c>
+      <c r="Q67" s="13">
+        <f t="shared" si="38"/>
+        <v>160000</v>
+      </c>
+      <c r="R67" s="13">
+        <f t="shared" si="39"/>
+        <v>160000</v>
+      </c>
+      <c r="S67" s="2">
+        <v>0</v>
+      </c>
+      <c r="T67" s="2">
+        <f t="shared" si="26"/>
+        <v>630</v>
+      </c>
+      <c r="U67" s="2">
+        <f t="shared" si="27"/>
+        <v>730</v>
+      </c>
+      <c r="V67" s="2">
+        <v>99</v>
+      </c>
+      <c r="W67" s="2">
+        <v>400</v>
+      </c>
+      <c r="X67" s="19" t="s">
+        <v>222</v>
+      </c>
       <c r="Y67" s="16"/>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:25">
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="10"/>
-      <c r="K68" s="10"/>
-      <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
-      <c r="N68" s="11"/>
-      <c r="O68" s="2"/>
-      <c r="P68" s="2"/>
-      <c r="Q68" s="2"/>
-      <c r="R68" s="2"/>
-      <c r="S68" s="2"/>
-      <c r="T68" s="2"/>
-      <c r="U68" s="2"/>
-      <c r="V68" s="2"/>
-      <c r="W68" s="2"/>
-      <c r="X68" s="2"/>
+      <c r="C68" s="14">
+        <v>213</v>
+      </c>
+      <c r="D68" s="14">
+        <v>3</v>
+      </c>
+      <c r="E68" s="14">
+        <v>13</v>
+      </c>
+      <c r="F68" s="14">
+        <v>32</v>
+      </c>
+      <c r="G68" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="H68" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="I68" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="J68" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K68" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="L68" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="M68" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="N68" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="O68" s="13">
+        <f t="shared" si="36"/>
+        <v>170000</v>
+      </c>
+      <c r="P68" s="13">
+        <f t="shared" si="37"/>
+        <v>170000</v>
+      </c>
+      <c r="Q68" s="13">
+        <f t="shared" si="38"/>
+        <v>170000</v>
+      </c>
+      <c r="R68" s="13">
+        <f t="shared" si="39"/>
+        <v>170000</v>
+      </c>
+      <c r="S68" s="2">
+        <v>0</v>
+      </c>
+      <c r="T68" s="2">
+        <f t="shared" si="26"/>
+        <v>660</v>
+      </c>
+      <c r="U68" s="2">
+        <f t="shared" si="27"/>
+        <v>760</v>
+      </c>
+      <c r="V68" s="2">
+        <v>99</v>
+      </c>
+      <c r="W68" s="2">
+        <v>400</v>
+      </c>
+      <c r="X68" s="19" t="s">
+        <v>222</v>
+      </c>
       <c r="Y68" s="16"/>
+    </row>
+    <row r="69" customHeight="1" spans="3:25">
+      <c r="C69" s="14">
+        <v>214</v>
+      </c>
+      <c r="D69" s="14">
+        <v>3</v>
+      </c>
+      <c r="E69" s="14">
+        <v>14</v>
+      </c>
+      <c r="F69" s="14">
+        <v>33</v>
+      </c>
+      <c r="G69" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="H69" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="I69" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="J69" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K69" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="L69" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="M69" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="N69" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="O69" s="13">
+        <f t="shared" si="36"/>
+        <v>180000</v>
+      </c>
+      <c r="P69" s="13">
+        <f t="shared" si="37"/>
+        <v>180000</v>
+      </c>
+      <c r="Q69" s="13">
+        <f t="shared" si="38"/>
+        <v>180000</v>
+      </c>
+      <c r="R69" s="13">
+        <f t="shared" si="39"/>
+        <v>180000</v>
+      </c>
+      <c r="S69" s="2">
+        <v>0</v>
+      </c>
+      <c r="T69" s="2">
+        <f t="shared" si="26"/>
+        <v>690</v>
+      </c>
+      <c r="U69" s="2">
+        <f t="shared" si="27"/>
+        <v>790</v>
+      </c>
+      <c r="V69" s="2">
+        <v>99</v>
+      </c>
+      <c r="W69" s="2">
+        <v>400</v>
+      </c>
+      <c r="X69" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:25">
+      <c r="C70" s="14">
+        <v>215</v>
+      </c>
+      <c r="D70" s="14">
+        <v>3</v>
+      </c>
+      <c r="E70" s="14">
+        <v>15</v>
+      </c>
+      <c r="F70" s="14">
+        <v>34</v>
+      </c>
+      <c r="G70" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="H70" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="I70" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="J70" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K70" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="L70" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="M70" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="N70" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="O70" s="13">
+        <f t="shared" si="36"/>
+        <v>190000</v>
+      </c>
+      <c r="P70" s="13">
+        <f t="shared" si="37"/>
+        <v>190000</v>
+      </c>
+      <c r="Q70" s="13">
+        <f t="shared" si="38"/>
+        <v>190000</v>
+      </c>
+      <c r="R70" s="13">
+        <f t="shared" si="39"/>
+        <v>190000</v>
+      </c>
+      <c r="S70" s="2">
+        <v>0</v>
+      </c>
+      <c r="T70" s="2">
+        <f t="shared" si="26"/>
+        <v>720</v>
+      </c>
+      <c r="U70" s="2">
+        <f t="shared" si="27"/>
+        <v>820</v>
+      </c>
+      <c r="V70" s="2">
+        <v>99</v>
+      </c>
+      <c r="W70" s="2">
+        <v>400</v>
+      </c>
+      <c r="X70" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:25">
+      <c r="C71" s="14">
+        <v>216</v>
+      </c>
+      <c r="D71" s="14">
+        <v>3</v>
+      </c>
+      <c r="E71" s="14">
+        <v>16</v>
+      </c>
+      <c r="F71" s="14">
+        <v>35</v>
+      </c>
+      <c r="G71" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="H71" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="I71" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="J71" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K71" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="L71" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="M71" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="N71" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="O71" s="13">
+        <f t="shared" si="36"/>
+        <v>200000</v>
+      </c>
+      <c r="P71" s="13">
+        <f t="shared" si="37"/>
+        <v>200000</v>
+      </c>
+      <c r="Q71" s="13">
+        <f t="shared" si="38"/>
+        <v>200000</v>
+      </c>
+      <c r="R71" s="13">
+        <f t="shared" si="39"/>
+        <v>200000</v>
+      </c>
+      <c r="S71" s="2">
+        <v>0</v>
+      </c>
+      <c r="T71" s="2">
+        <f t="shared" si="26"/>
+        <v>750</v>
+      </c>
+      <c r="U71" s="2">
+        <f t="shared" si="27"/>
+        <v>850</v>
+      </c>
+      <c r="V71" s="2">
+        <v>99</v>
+      </c>
+      <c r="W71" s="2">
+        <v>400</v>
+      </c>
+      <c r="X71" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:25">
+      <c r="C72" s="14">
+        <v>217</v>
+      </c>
+      <c r="D72" s="14">
+        <v>3</v>
+      </c>
+      <c r="E72" s="14">
+        <v>17</v>
+      </c>
+      <c r="F72" s="14">
+        <v>36</v>
+      </c>
+      <c r="G72" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="H72" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="I72" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="J72" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K72" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="L72" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="M72" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="N72" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="O72" s="13">
+        <f t="shared" si="36"/>
+        <v>210000</v>
+      </c>
+      <c r="P72" s="13">
+        <f t="shared" si="37"/>
+        <v>210000</v>
+      </c>
+      <c r="Q72" s="13">
+        <f t="shared" si="38"/>
+        <v>210000</v>
+      </c>
+      <c r="R72" s="13">
+        <f t="shared" si="39"/>
+        <v>210000</v>
+      </c>
+      <c r="S72" s="2">
+        <v>0</v>
+      </c>
+      <c r="T72" s="2">
+        <f t="shared" si="26"/>
+        <v>780</v>
+      </c>
+      <c r="U72" s="2">
+        <f t="shared" si="27"/>
+        <v>880</v>
+      </c>
+      <c r="V72" s="2">
+        <v>99</v>
+      </c>
+      <c r="W72" s="2">
+        <v>400</v>
+      </c>
+      <c r="X72" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:25">
+      <c r="C73" s="14">
+        <v>218</v>
+      </c>
+      <c r="D73" s="14">
+        <v>3</v>
+      </c>
+      <c r="E73" s="14">
+        <v>18</v>
+      </c>
+      <c r="F73" s="14">
+        <v>37</v>
+      </c>
+      <c r="G73" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="H73" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="I73" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="J73" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K73" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="L73" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="M73" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="N73" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="O73" s="13">
+        <f t="shared" si="36"/>
+        <v>220000</v>
+      </c>
+      <c r="P73" s="13">
+        <f t="shared" si="37"/>
+        <v>220000</v>
+      </c>
+      <c r="Q73" s="13">
+        <f t="shared" si="38"/>
+        <v>220000</v>
+      </c>
+      <c r="R73" s="13">
+        <f t="shared" si="39"/>
+        <v>220000</v>
+      </c>
+      <c r="S73" s="2">
+        <v>0</v>
+      </c>
+      <c r="T73" s="2">
+        <f t="shared" si="26"/>
+        <v>810</v>
+      </c>
+      <c r="U73" s="2">
+        <f t="shared" si="27"/>
+        <v>910</v>
+      </c>
+      <c r="V73" s="2">
+        <v>99</v>
+      </c>
+      <c r="W73" s="2">
+        <v>400</v>
+      </c>
+      <c r="X73" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:25">
+      <c r="C74" s="14">
+        <v>219</v>
+      </c>
+      <c r="D74" s="14">
+        <v>3</v>
+      </c>
+      <c r="E74" s="14">
+        <v>19</v>
+      </c>
+      <c r="F74" s="14">
+        <v>38</v>
+      </c>
+      <c r="G74" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="H74" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="I74" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="J74" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K74" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="L74" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="M74" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="N74" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="O74" s="13">
+        <f t="shared" si="36"/>
+        <v>230000</v>
+      </c>
+      <c r="P74" s="13">
+        <f t="shared" si="37"/>
+        <v>230000</v>
+      </c>
+      <c r="Q74" s="13">
+        <f t="shared" si="38"/>
+        <v>230000</v>
+      </c>
+      <c r="R74" s="13">
+        <f t="shared" si="39"/>
+        <v>230000</v>
+      </c>
+      <c r="S74" s="2">
+        <v>0</v>
+      </c>
+      <c r="T74" s="2">
+        <f t="shared" si="26"/>
+        <v>840</v>
+      </c>
+      <c r="U74" s="2">
+        <f t="shared" si="27"/>
+        <v>940</v>
+      </c>
+      <c r="V74" s="2">
+        <v>99</v>
+      </c>
+      <c r="W74" s="2">
+        <v>400</v>
+      </c>
+      <c r="X74" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:25">
+      <c r="C75" s="14">
+        <v>220</v>
+      </c>
+      <c r="D75" s="14">
+        <v>3</v>
+      </c>
+      <c r="E75" s="14">
+        <v>20</v>
+      </c>
+      <c r="F75" s="14">
+        <v>39</v>
+      </c>
+      <c r="G75" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="H75" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="I75" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="J75" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K75" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="L75" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="M75" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="N75" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="O75" s="13">
+        <f t="shared" si="36"/>
+        <v>240000</v>
+      </c>
+      <c r="P75" s="13">
+        <f t="shared" si="37"/>
+        <v>240000</v>
+      </c>
+      <c r="Q75" s="13">
+        <f t="shared" si="38"/>
+        <v>240000</v>
+      </c>
+      <c r="R75" s="13">
+        <f t="shared" si="39"/>
+        <v>240000</v>
+      </c>
+      <c r="S75" s="2">
+        <v>0</v>
+      </c>
+      <c r="T75" s="2">
+        <f t="shared" si="26"/>
+        <v>870</v>
+      </c>
+      <c r="U75" s="2">
+        <f t="shared" si="27"/>
+        <v>970</v>
+      </c>
+      <c r="V75" s="2">
+        <v>99</v>
+      </c>
+      <c r="W75" s="2">
+        <v>400</v>
+      </c>
+      <c r="X75" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:25">
+      <c r="C79" s="14">
+        <v>301</v>
+      </c>
+      <c r="D79" s="14">
+        <v>4</v>
+      </c>
+      <c r="E79" s="14">
+        <v>1</v>
+      </c>
+      <c r="F79" s="14">
+        <v>30</v>
+      </c>
+      <c r="G79" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="H79" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="I79" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="J79" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K79" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="L79" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="M79" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="N79" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="O79" s="13">
+        <v>200000</v>
+      </c>
+      <c r="P79" s="13">
+        <v>200000</v>
+      </c>
+      <c r="Q79" s="13">
+        <v>200000</v>
+      </c>
+      <c r="R79" s="13">
+        <v>200000</v>
+      </c>
+      <c r="S79" s="2">
+        <v>0</v>
+      </c>
+      <c r="T79" s="2">
+        <v>750</v>
+      </c>
+      <c r="U79" s="2">
+        <v>850</v>
+      </c>
+      <c r="V79" s="2">
+        <v>99</v>
+      </c>
+      <c r="W79" s="2">
+        <v>400</v>
+      </c>
+      <c r="X79" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:25">
+      <c r="C80" s="14">
+        <v>302</v>
+      </c>
+      <c r="D80" s="14">
+        <v>4</v>
+      </c>
+      <c r="E80" s="14">
+        <v>2</v>
+      </c>
+      <c r="F80" s="14">
+        <v>31</v>
+      </c>
+      <c r="G80" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="H80" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="I80" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="J80" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K80" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="L80" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="M80" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="N80" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="O80" s="13">
+        <f t="shared" ref="O80:R80" si="40">O79+20000</f>
+        <v>220000</v>
+      </c>
+      <c r="P80" s="13">
+        <f t="shared" si="40"/>
+        <v>220000</v>
+      </c>
+      <c r="Q80" s="13">
+        <f t="shared" si="40"/>
+        <v>220000</v>
+      </c>
+      <c r="R80" s="13">
+        <f t="shared" si="40"/>
+        <v>220000</v>
+      </c>
+      <c r="S80" s="2">
+        <v>0</v>
+      </c>
+      <c r="T80" s="2">
+        <f t="shared" ref="T79:T88" si="41">T79+30</f>
+        <v>780</v>
+      </c>
+      <c r="U80" s="2">
+        <f t="shared" ref="U79:U88" si="42">U79+30</f>
+        <v>880</v>
+      </c>
+      <c r="V80" s="2">
+        <v>99</v>
+      </c>
+      <c r="W80" s="2">
+        <v>400</v>
+      </c>
+      <c r="X80" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:24">
+      <c r="C81" s="14">
+        <v>303</v>
+      </c>
+      <c r="D81" s="14">
+        <v>4</v>
+      </c>
+      <c r="E81" s="14">
+        <v>3</v>
+      </c>
+      <c r="F81" s="14">
+        <v>32</v>
+      </c>
+      <c r="G81" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="H81" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="I81" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="J81" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K81" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="L81" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="M81" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="N81" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="O81" s="13">
+        <f t="shared" ref="O81:R81" si="43">O80+20000</f>
+        <v>240000</v>
+      </c>
+      <c r="P81" s="13">
+        <f t="shared" si="43"/>
+        <v>240000</v>
+      </c>
+      <c r="Q81" s="13">
+        <f t="shared" si="43"/>
+        <v>240000</v>
+      </c>
+      <c r="R81" s="13">
+        <f t="shared" si="43"/>
+        <v>240000</v>
+      </c>
+      <c r="S81" s="2">
+        <v>0</v>
+      </c>
+      <c r="T81" s="2">
+        <f t="shared" si="41"/>
+        <v>810</v>
+      </c>
+      <c r="U81" s="2">
+        <f t="shared" si="42"/>
+        <v>910</v>
+      </c>
+      <c r="V81" s="2">
+        <v>99</v>
+      </c>
+      <c r="W81" s="2">
+        <v>400</v>
+      </c>
+      <c r="X81" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:24">
+      <c r="C82" s="14">
+        <v>304</v>
+      </c>
+      <c r="D82" s="14">
+        <v>4</v>
+      </c>
+      <c r="E82" s="14">
+        <v>4</v>
+      </c>
+      <c r="F82" s="14">
+        <v>33</v>
+      </c>
+      <c r="G82" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="H82" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="I82" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="J82" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K82" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="L82" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="M82" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="N82" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="O82" s="13">
+        <f t="shared" ref="O82:R82" si="44">O81+20000</f>
+        <v>260000</v>
+      </c>
+      <c r="P82" s="13">
+        <f t="shared" si="44"/>
+        <v>260000</v>
+      </c>
+      <c r="Q82" s="13">
+        <f t="shared" si="44"/>
+        <v>260000</v>
+      </c>
+      <c r="R82" s="13">
+        <f t="shared" si="44"/>
+        <v>260000</v>
+      </c>
+      <c r="S82" s="2">
+        <v>0</v>
+      </c>
+      <c r="T82" s="2">
+        <f t="shared" si="41"/>
+        <v>840</v>
+      </c>
+      <c r="U82" s="2">
+        <f t="shared" si="42"/>
+        <v>940</v>
+      </c>
+      <c r="V82" s="2">
+        <v>99</v>
+      </c>
+      <c r="W82" s="2">
+        <v>400</v>
+      </c>
+      <c r="X82" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:24">
+      <c r="C83" s="14">
+        <v>305</v>
+      </c>
+      <c r="D83" s="14">
+        <v>4</v>
+      </c>
+      <c r="E83" s="14">
+        <v>5</v>
+      </c>
+      <c r="F83" s="14">
+        <v>34</v>
+      </c>
+      <c r="G83" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="H83" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="I83" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="J83" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K83" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="L83" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="M83" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="N83" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="O83" s="13">
+        <f t="shared" ref="O83:R83" si="45">O82+20000</f>
+        <v>280000</v>
+      </c>
+      <c r="P83" s="13">
+        <f t="shared" si="45"/>
+        <v>280000</v>
+      </c>
+      <c r="Q83" s="13">
+        <f t="shared" si="45"/>
+        <v>280000</v>
+      </c>
+      <c r="R83" s="13">
+        <f t="shared" si="45"/>
+        <v>280000</v>
+      </c>
+      <c r="S83" s="2">
+        <v>0</v>
+      </c>
+      <c r="T83" s="2">
+        <f t="shared" si="41"/>
+        <v>870</v>
+      </c>
+      <c r="U83" s="2">
+        <f t="shared" si="42"/>
+        <v>970</v>
+      </c>
+      <c r="V83" s="2">
+        <v>99</v>
+      </c>
+      <c r="W83" s="2">
+        <v>400</v>
+      </c>
+      <c r="X83" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:24">
+      <c r="C84" s="14">
+        <v>306</v>
+      </c>
+      <c r="D84" s="14">
+        <v>4</v>
+      </c>
+      <c r="E84" s="14">
+        <v>6</v>
+      </c>
+      <c r="F84" s="14">
+        <v>35</v>
+      </c>
+      <c r="G84" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="H84" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="I84" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="J84" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K84" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="L84" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="M84" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="N84" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="O84" s="13">
+        <f t="shared" ref="O84:R84" si="46">O83+20000</f>
+        <v>300000</v>
+      </c>
+      <c r="P84" s="13">
+        <f t="shared" si="46"/>
+        <v>300000</v>
+      </c>
+      <c r="Q84" s="13">
+        <f t="shared" si="46"/>
+        <v>300000</v>
+      </c>
+      <c r="R84" s="13">
+        <f t="shared" si="46"/>
+        <v>300000</v>
+      </c>
+      <c r="S84" s="2">
+        <v>0</v>
+      </c>
+      <c r="T84" s="2">
+        <f t="shared" si="41"/>
+        <v>900</v>
+      </c>
+      <c r="U84" s="2">
+        <f t="shared" si="42"/>
+        <v>1000</v>
+      </c>
+      <c r="V84" s="2">
+        <v>99</v>
+      </c>
+      <c r="W84" s="2">
+        <v>400</v>
+      </c>
+      <c r="X84" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:24">
+      <c r="C85" s="14">
+        <v>307</v>
+      </c>
+      <c r="D85" s="14">
+        <v>4</v>
+      </c>
+      <c r="E85" s="14">
+        <v>7</v>
+      </c>
+      <c r="F85" s="14">
+        <v>36</v>
+      </c>
+      <c r="G85" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="H85" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="I85" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="J85" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K85" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="L85" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="M85" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="N85" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="O85" s="13">
+        <f t="shared" ref="O85:R85" si="47">O84+20000</f>
+        <v>320000</v>
+      </c>
+      <c r="P85" s="13">
+        <f t="shared" si="47"/>
+        <v>320000</v>
+      </c>
+      <c r="Q85" s="13">
+        <f t="shared" si="47"/>
+        <v>320000</v>
+      </c>
+      <c r="R85" s="13">
+        <f t="shared" si="47"/>
+        <v>320000</v>
+      </c>
+      <c r="S85" s="2">
+        <v>0</v>
+      </c>
+      <c r="T85" s="2">
+        <f t="shared" si="41"/>
+        <v>930</v>
+      </c>
+      <c r="U85" s="2">
+        <f t="shared" si="42"/>
+        <v>1030</v>
+      </c>
+      <c r="V85" s="2">
+        <v>99</v>
+      </c>
+      <c r="W85" s="2">
+        <v>400</v>
+      </c>
+      <c r="X85" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:24">
+      <c r="C86" s="14">
+        <v>308</v>
+      </c>
+      <c r="D86" s="14">
+        <v>4</v>
+      </c>
+      <c r="E86" s="14">
+        <v>8</v>
+      </c>
+      <c r="F86" s="14">
+        <v>37</v>
+      </c>
+      <c r="G86" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="H86" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="I86" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="J86" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K86" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="L86" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="M86" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="N86" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="O86" s="13">
+        <f t="shared" ref="O86:R86" si="48">O85+20000</f>
+        <v>340000</v>
+      </c>
+      <c r="P86" s="13">
+        <f t="shared" si="48"/>
+        <v>340000</v>
+      </c>
+      <c r="Q86" s="13">
+        <f t="shared" si="48"/>
+        <v>340000</v>
+      </c>
+      <c r="R86" s="13">
+        <f t="shared" si="48"/>
+        <v>340000</v>
+      </c>
+      <c r="S86" s="2">
+        <v>0</v>
+      </c>
+      <c r="T86" s="2">
+        <f t="shared" si="41"/>
+        <v>960</v>
+      </c>
+      <c r="U86" s="2">
+        <f t="shared" si="42"/>
+        <v>1060</v>
+      </c>
+      <c r="V86" s="2">
+        <v>99</v>
+      </c>
+      <c r="W86" s="2">
+        <v>400</v>
+      </c>
+      <c r="X86" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:24">
+      <c r="C87" s="14">
+        <v>309</v>
+      </c>
+      <c r="D87" s="14">
+        <v>4</v>
+      </c>
+      <c r="E87" s="14">
+        <v>9</v>
+      </c>
+      <c r="F87" s="14">
+        <v>38</v>
+      </c>
+      <c r="G87" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="H87" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="I87" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="J87" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K87" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="L87" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="M87" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="N87" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="O87" s="13">
+        <f t="shared" ref="O87:R87" si="49">O86+20000</f>
+        <v>360000</v>
+      </c>
+      <c r="P87" s="13">
+        <f t="shared" si="49"/>
+        <v>360000</v>
+      </c>
+      <c r="Q87" s="13">
+        <f t="shared" si="49"/>
+        <v>360000</v>
+      </c>
+      <c r="R87" s="13">
+        <f t="shared" si="49"/>
+        <v>360000</v>
+      </c>
+      <c r="S87" s="2">
+        <v>0</v>
+      </c>
+      <c r="T87" s="2">
+        <f t="shared" si="41"/>
+        <v>990</v>
+      </c>
+      <c r="U87" s="2">
+        <f t="shared" si="42"/>
+        <v>1090</v>
+      </c>
+      <c r="V87" s="2">
+        <v>99</v>
+      </c>
+      <c r="W87" s="2">
+        <v>400</v>
+      </c>
+      <c r="X87" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:24">
+      <c r="C88" s="14">
+        <v>310</v>
+      </c>
+      <c r="D88" s="14">
+        <v>4</v>
+      </c>
+      <c r="E88" s="14">
+        <v>10</v>
+      </c>
+      <c r="F88" s="14">
+        <v>39</v>
+      </c>
+      <c r="G88" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="H88" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="I88" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="J88" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K88" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="L88" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="M88" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="N88" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="O88" s="13">
+        <f t="shared" ref="O88:R88" si="50">O87+20000</f>
+        <v>380000</v>
+      </c>
+      <c r="P88" s="13">
+        <f t="shared" si="50"/>
+        <v>380000</v>
+      </c>
+      <c r="Q88" s="13">
+        <f t="shared" si="50"/>
+        <v>380000</v>
+      </c>
+      <c r="R88" s="13">
+        <f t="shared" si="50"/>
+        <v>380000</v>
+      </c>
+      <c r="S88" s="2">
+        <v>0</v>
+      </c>
+      <c r="T88" s="2">
+        <f t="shared" si="41"/>
+        <v>1020</v>
+      </c>
+      <c r="U88" s="2">
+        <f t="shared" si="42"/>
+        <v>1120</v>
+      </c>
+      <c r="V88" s="2">
+        <v>99</v>
+      </c>
+      <c r="W88" s="2">
+        <v>400</v>
+      </c>
+      <c r="X88" s="19" t="s">
+        <v>222</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/MonsterPillConfig.xlsx
+++ b/Excel/MonsterPillConfig.xlsx
@@ -6676,11 +6676,11 @@
       <c r="K79" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="L79" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="M79" s="18" t="s">
-        <v>251</v>
+      <c r="L79" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="M79" s="17" t="s">
+        <v>145</v>
       </c>
       <c r="N79" s="17" t="s">
         <v>238</v>
@@ -6744,11 +6744,11 @@
       <c r="K80" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="L80" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="M80" s="18" t="s">
-        <v>254</v>
+      <c r="L80" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="M80" s="17" t="s">
+        <v>154</v>
       </c>
       <c r="N80" s="17" t="s">
         <v>240</v>
@@ -6818,11 +6818,11 @@
       <c r="K81" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="L81" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="M81" s="18" t="s">
-        <v>164</v>
+      <c r="L81" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="M81" s="17" t="s">
+        <v>231</v>
       </c>
       <c r="N81" s="17" t="s">
         <v>242</v>
@@ -6892,11 +6892,11 @@
       <c r="K82" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="L82" s="18" t="s">
-        <v>260</v>
-      </c>
-      <c r="M82" s="18" t="s">
-        <v>261</v>
+      <c r="L82" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="M82" s="17" t="s">
+        <v>234</v>
       </c>
       <c r="N82" s="17" t="s">
         <v>244</v>
@@ -6966,11 +6966,11 @@
       <c r="K83" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="L83" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="M83" s="18" t="s">
-        <v>265</v>
+      <c r="L83" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="M83" s="17" t="s">
+        <v>221</v>
       </c>
       <c r="N83" s="17" t="s">
         <v>247</v>
@@ -7040,11 +7040,11 @@
       <c r="K84" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="L84" s="18" t="s">
-        <v>261</v>
-      </c>
-      <c r="M84" s="18" t="s">
-        <v>268</v>
+      <c r="L84" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="M84" s="17" t="s">
+        <v>224</v>
       </c>
       <c r="N84" s="17" t="s">
         <v>249</v>
@@ -7114,11 +7114,11 @@
       <c r="K85" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="L85" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="M85" s="18" t="s">
-        <v>272</v>
+      <c r="L85" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="M85" s="17" t="s">
+        <v>227</v>
       </c>
       <c r="N85" s="17" t="s">
         <v>253</v>
@@ -7188,11 +7188,11 @@
       <c r="K86" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="L86" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="M86" s="18" t="s">
-        <v>176</v>
+      <c r="L86" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="M86" s="17" t="s">
+        <v>232</v>
       </c>
       <c r="N86" s="17" t="s">
         <v>256</v>
@@ -7262,11 +7262,11 @@
       <c r="K87" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="L87" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="M87" s="18" t="s">
-        <v>278</v>
+      <c r="L87" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="M87" s="17" t="s">
+        <v>235</v>
       </c>
       <c r="N87" s="17" t="s">
         <v>259</v>
@@ -7336,11 +7336,11 @@
       <c r="K88" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="L88" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="M88" s="18" t="s">
-        <v>281</v>
+      <c r="L88" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="M88" s="17" t="s">
+        <v>238</v>
       </c>
       <c r="N88" s="17" t="s">
         <v>263</v>
